--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH76" headerRowCount="1">
-  <autoFilter ref="A1:EH76"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH77" headerRowCount="1">
+  <autoFilter ref="A1:EH77"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH76"/>
+  <dimension ref="A1:EH77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -3030,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DE5" t="n">
         <v>0.5</v>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -5226,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DE10" t="n">
         <v>1.57</v>
@@ -9593,7 +9593,7 @@
         <v>1.63</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -11786,7 +11786,7 @@
         <v>25</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DE25" t="n">
         <v>0.57</v>
@@ -14421,7 +14421,7 @@
         <v>0.5</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF31" t="n">
         <v>0.33</v>
@@ -17930,7 +17930,7 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DE39" t="n">
         <v>1.86</v>
@@ -17963,7 +17963,7 @@
         <v>3.9</v>
       </c>
       <c r="DO39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20109,7 +20109,7 @@
         <v>1.25</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF44" t="n">
         <v>1.5</v>
@@ -25370,7 +25370,7 @@
         <v>70</v>
       </c>
       <c r="DD56" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DE56" t="n">
         <v>1.25</v>
@@ -25403,7 +25403,7 @@
         <v>4.13</v>
       </c>
       <c r="DO56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -25809,7 +25809,7 @@
         <v>1.86</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF57" t="n">
         <v>1.75</v>
@@ -28029,7 +28029,7 @@
         <v>1.38</v>
       </c>
       <c r="DE62" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DF62" t="n">
         <v>1.17</v>
@@ -28059,7 +28059,7 @@
         <v>3.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29337,7 +29337,7 @@
         <v>1.43</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF65" t="n">
         <v>1.4</v>
@@ -31962,7 +31962,7 @@
         <v>54</v>
       </c>
       <c r="DD71" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DE71" t="n">
         <v>0.43</v>
@@ -31995,7 +31995,7 @@
         <v>3.31</v>
       </c>
       <c r="DO71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -32842,7 +32842,7 @@
         <v>72</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DE73" t="n">
         <v>1.71</v>
@@ -34250,6 +34250,442 @@
       </c>
       <c r="EG76" t="inlineStr"/>
       <c r="EH76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>5</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2</v>
+      </c>
+      <c r="I77" t="n">
+        <v>3</v>
+      </c>
+      <c r="J77" t="n">
+        <v>3</v>
+      </c>
+      <c r="K77" t="n">
+        <v>5</v>
+      </c>
+      <c r="L77" t="n">
+        <v>8</v>
+      </c>
+      <c r="M77" t="n">
+        <v>3</v>
+      </c>
+      <c r="N77" t="n">
+        <v>2</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>4</v>
+      </c>
+      <c r="R77" t="n">
+        <v>4</v>
+      </c>
+      <c r="S77" t="n">
+        <v>8</v>
+      </c>
+      <c r="T77" t="n">
+        <v>8</v>
+      </c>
+      <c r="U77" t="n">
+        <v>12</v>
+      </c>
+      <c r="V77" t="n">
+        <v>12</v>
+      </c>
+      <c r="W77" t="n">
+        <v>15</v>
+      </c>
+      <c r="X77" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Estadio Nemesio Camacho El Campín</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AC77" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>2142</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>58</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ77" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM77" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS77" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV77" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW77" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX77" t="n">
+        <v>40</v>
+      </c>
+      <c r="BY77" t="n">
+        <v>71</v>
+      </c>
+      <c r="BZ77" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA77" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CB77" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN77" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR77" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS77" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU77" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV77" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX77" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY77" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ77" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA77" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB77" t="n">
+        <v>27</v>
+      </c>
+      <c r="DC77" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD77" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DE77" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DF77" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG77" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DH77" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DI77" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DJ77" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK77" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL77" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DM77" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="DN77" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DO77" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP77" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ77" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR77" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV77" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW77" t="inlineStr"/>
+      <c r="DX77" t="inlineStr"/>
+      <c r="DY77" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="DZ77" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EA77" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="EB77" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EC77" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="ED77" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EE77" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EF77" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EG77" t="inlineStr"/>
+      <c r="EH77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH77" headerRowCount="1">
-  <autoFilter ref="A1:EH77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH81" headerRowCount="1">
+  <autoFilter ref="A1:EH81"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH77"/>
+  <dimension ref="A1:EH81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1746,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DE2" t="n">
         <v>1.25</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2185,7 +2185,7 @@
         <v>1.25</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2626,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE4" t="n">
         <v>2.13</v>
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3033,7 +3033,7 @@
         <v>2.5</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3477,7 +3477,7 @@
         <v>1.57</v>
       </c>
       <c r="DE6" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE8" t="n">
         <v>1.38</v>
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4790,7 +4790,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE9" t="n">
         <v>1.5</v>
@@ -4823,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5665,7 +5665,7 @@
         <v>0.75</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6525,7 +6525,7 @@
         <v>1.5</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6555,7 +6555,7 @@
         <v>1.86</v>
       </c>
       <c r="DO13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -6966,7 +6966,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DE14" t="n">
         <v>1.25</v>
@@ -6999,7 +6999,7 @@
         <v>1.99</v>
       </c>
       <c r="DO14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP14" t="b">
         <v>0</v>
@@ -8282,10 +8282,10 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>2.13</v>
       </c>
       <c r="DO17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9154,10 +9154,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9187,7 +9187,7 @@
         <v>2.56</v>
       </c>
       <c r="DO19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9590,7 +9590,7 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE20" t="n">
         <v>1.11</v>
@@ -9623,7 +9623,7 @@
         <v>4.47</v>
       </c>
       <c r="DO20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -11350,10 +11350,10 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -11383,7 +11383,7 @@
         <v>1.88</v>
       </c>
       <c r="DO24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -11789,7 +11789,7 @@
         <v>1.11</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -11819,7 +11819,7 @@
         <v>2.57</v>
       </c>
       <c r="DO25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12233,7 +12233,7 @@
         <v>1.88</v>
       </c>
       <c r="DE26" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -13102,7 +13102,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE28" t="n">
         <v>2.13</v>
@@ -13135,7 +13135,7 @@
         <v>2.03</v>
       </c>
       <c r="DO28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -13546,10 +13546,10 @@
         <v>75</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -13579,7 +13579,7 @@
         <v>3.03</v>
       </c>
       <c r="DO29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14418,7 +14418,7 @@
         <v>67</v>
       </c>
       <c r="DD31" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE31" t="n">
         <v>1.11</v>
@@ -14451,7 +14451,7 @@
         <v>2.8</v>
       </c>
       <c r="DO31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -14865,7 +14865,7 @@
         <v>1.57</v>
       </c>
       <c r="DE32" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF32" t="n">
         <v>1.67</v>
@@ -15742,10 +15742,10 @@
         <v>59</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DF34" t="n">
         <v>1.67</v>
@@ -15775,7 +15775,7 @@
         <v>2.49</v>
       </c>
       <c r="DO34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -16614,7 +16614,7 @@
         <v>84</v>
       </c>
       <c r="DD36" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DE36" t="n">
         <v>0.88</v>
@@ -17494,10 +17494,10 @@
         <v>67</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DF38" t="n">
         <v>0.67</v>
@@ -17527,7 +17527,7 @@
         <v>2.42</v>
       </c>
       <c r="DO38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -17933,7 +17933,7 @@
         <v>2.5</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF39" t="n">
         <v>3</v>
@@ -20522,10 +20522,10 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF45" t="n">
         <v>2</v>
@@ -20555,7 +20555,7 @@
         <v>2.5</v>
       </c>
       <c r="DO45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -20958,10 +20958,10 @@
         <v>50</v>
       </c>
       <c r="DD46" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF46" t="n">
         <v>0.25</v>
@@ -20991,7 +20991,7 @@
         <v>2.87</v>
       </c>
       <c r="DO46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -21405,7 +21405,7 @@
         <v>1.38</v>
       </c>
       <c r="DE47" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF47" t="n">
         <v>1.5</v>
@@ -21826,10 +21826,10 @@
         <v>59</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF48" t="n">
         <v>1.33</v>
@@ -21859,7 +21859,7 @@
         <v>1.75</v>
       </c>
       <c r="DO48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23602,7 +23602,7 @@
         <v>70</v>
       </c>
       <c r="DD52" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DE52" t="n">
         <v>1.57</v>
@@ -24474,10 +24474,10 @@
         <v>68</v>
       </c>
       <c r="DD54" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE54" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DF54" t="n">
         <v>0.2</v>
@@ -24507,7 +24507,7 @@
         <v>1.66</v>
       </c>
       <c r="DO54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -24926,10 +24926,10 @@
         <v>80</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DF55" t="n">
         <v>1.4</v>
@@ -24959,7 +24959,7 @@
         <v>3.39</v>
       </c>
       <c r="DO55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -25806,7 +25806,7 @@
         <v>70</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE57" t="n">
         <v>1.11</v>
@@ -25839,7 +25839,7 @@
         <v>2.74</v>
       </c>
       <c r="DO57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -26250,7 +26250,7 @@
         <v>59</v>
       </c>
       <c r="DD58" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DE58" t="n">
         <v>1.25</v>
@@ -26697,7 +26697,7 @@
         <v>0.88</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF59" t="n">
         <v>0.83</v>
@@ -26727,7 +26727,7 @@
         <v>2.53</v>
       </c>
       <c r="DO59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -27593,7 +27593,7 @@
         <v>1.5</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF61" t="n">
         <v>1.5</v>
@@ -28465,7 +28465,7 @@
         <v>1.25</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF63" t="n">
         <v>1.17</v>
@@ -28898,7 +28898,7 @@
         <v>60</v>
       </c>
       <c r="DD64" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DE64" t="n">
         <v>0.75</v>
@@ -28931,7 +28931,7 @@
         <v>1.97</v>
       </c>
       <c r="DO64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -29334,7 +29334,7 @@
         <v>57</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE65" t="n">
         <v>1.11</v>
@@ -29367,7 +29367,7 @@
         <v>2.22</v>
       </c>
       <c r="DO65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -29766,10 +29766,10 @@
         <v>90</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF66" t="n">
         <v>1.8</v>
@@ -29799,7 +29799,7 @@
         <v>3.08</v>
       </c>
       <c r="DO66" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -30646,7 +30646,7 @@
         <v>62</v>
       </c>
       <c r="DD68" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DE68" t="n">
         <v>1.88</v>
@@ -30679,7 +30679,7 @@
         <v>1.99</v>
       </c>
       <c r="DO68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -31090,7 +31090,7 @@
         <v>57</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE69" t="n">
         <v>1.25</v>
@@ -31965,7 +31965,7 @@
         <v>2.5</v>
       </c>
       <c r="DE71" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF71" t="n">
         <v>2.25</v>
@@ -32401,7 +32401,7 @@
         <v>2.13</v>
       </c>
       <c r="DE72" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF72" t="n">
         <v>2</v>
@@ -32845,7 +32845,7 @@
         <v>1.11</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -32875,7 +32875,7 @@
         <v>3.26</v>
       </c>
       <c r="DO73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -33270,7 +33270,7 @@
         <v>69</v>
       </c>
       <c r="DD74" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE74" t="n">
         <v>1.57</v>
@@ -33706,10 +33706,10 @@
         <v>83</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DF75" t="n">
         <v>1.67</v>
@@ -33739,7 +33739,7 @@
         <v>2.17</v>
       </c>
       <c r="DO75" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -34686,6 +34686,1766 @@
       </c>
       <c r="EG77" t="inlineStr"/>
       <c r="EH77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>9</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>46080.02083333334</v>
+      </c>
+      <c r="G78" t="n">
+        <v>5</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>6</v>
+      </c>
+      <c r="J78" t="n">
+        <v>7</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="n">
+        <v>8</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>12</v>
+      </c>
+      <c r="R78" t="n">
+        <v>3</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>22</v>
+      </c>
+      <c r="V78" t="n">
+        <v>5</v>
+      </c>
+      <c r="W78" t="n">
+        <v>6</v>
+      </c>
+      <c r="X78" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>Estadio Nemesio Camacho El Campín</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AC78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>2136</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV78" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW78" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX78" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY78" t="n">
+        <v>54</v>
+      </c>
+      <c r="BZ78" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CA78" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="CB78" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR78" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS78" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU78" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV78" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX78" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY78" t="n">
+        <v>16</v>
+      </c>
+      <c r="CZ78" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA78" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB78" t="n">
+        <v>13</v>
+      </c>
+      <c r="DC78" t="n">
+        <v>61</v>
+      </c>
+      <c r="DD78" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DE78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF78" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG78" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DH78" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI78" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DJ78" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK78" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL78" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DM78" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="DN78" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DO78" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW78" t="inlineStr"/>
+      <c r="DX78" t="inlineStr"/>
+      <c r="DY78" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="DZ78" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EA78" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="EB78" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EC78" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="ED78" t="inlineStr">
+        <is>
+          <t>10.57</t>
+        </is>
+      </c>
+      <c r="EE78" t="inlineStr">
+        <is>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="EF78" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EG78" t="inlineStr"/>
+      <c r="EH78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>9</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Boyacá Chicó</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>46081.0625</v>
+      </c>
+      <c r="G79" t="n">
+        <v>3</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>3</v>
+      </c>
+      <c r="J79" t="n">
+        <v>7</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="n">
+        <v>8</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>9</v>
+      </c>
+      <c r="R79" t="n">
+        <v>3</v>
+      </c>
+      <c r="S79" t="n">
+        <v>11</v>
+      </c>
+      <c r="T79" t="n">
+        <v>10</v>
+      </c>
+      <c r="U79" t="n">
+        <v>20</v>
+      </c>
+      <c r="V79" t="n">
+        <v>13</v>
+      </c>
+      <c r="W79" t="n">
+        <v>16</v>
+      </c>
+      <c r="X79" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Estadio Palogrande</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>Carrera 24 # 64 - 00, Manizales</t>
+        </is>
+      </c>
+      <c r="AC79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>2135</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>79</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>106</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>46</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>9</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX79" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY79" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ79" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA79" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC79" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD79" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DE79" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DF79" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DI79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DJ79" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK79" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL79" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DM79" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DN79" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="DO79" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS79" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT79" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU79" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV79" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW79" t="inlineStr"/>
+      <c r="DX79" t="inlineStr"/>
+      <c r="DY79" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="DZ79" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EA79" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="EB79" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EC79" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="ED79" t="inlineStr">
+        <is>
+          <t>9.61</t>
+        </is>
+      </c>
+      <c r="EE79" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EG79" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>9</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Alianza Petrolera</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>46081.88194444445</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>3</v>
+      </c>
+      <c r="I80" t="n">
+        <v>3</v>
+      </c>
+      <c r="J80" t="n">
+        <v>6</v>
+      </c>
+      <c r="K80" t="n">
+        <v>5</v>
+      </c>
+      <c r="L80" t="n">
+        <v>11</v>
+      </c>
+      <c r="M80" t="n">
+        <v>4</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>2</v>
+      </c>
+      <c r="R80" t="n">
+        <v>9</v>
+      </c>
+      <c r="S80" t="n">
+        <v>8</v>
+      </c>
+      <c r="T80" t="n">
+        <v>6</v>
+      </c>
+      <c r="U80" t="n">
+        <v>10</v>
+      </c>
+      <c r="V80" t="n">
+        <v>15</v>
+      </c>
+      <c r="W80" t="n">
+        <v>9</v>
+      </c>
+      <c r="X80" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Estadio Armando Maestre Pavajeau</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>, Valledupar</t>
+        </is>
+      </c>
+      <c r="AC80" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>2141</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI80" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>68</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>9</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV80" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX80" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY80" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ80" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA80" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC80" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD80" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DE80" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF80" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DI80" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DJ80" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK80" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL80" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DM80" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DN80" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="DO80" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW80" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="DX80" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="DY80" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="DZ80" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EA80" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="EB80" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EC80" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="ED80" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EE80" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EF80" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EG80" t="inlineStr"/>
+      <c r="EH80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>9</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Jaguares de Córdoba</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>46081.97222222222</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2</v>
+      </c>
+      <c r="J81" t="n">
+        <v>14</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>14</v>
+      </c>
+      <c r="M81" t="n">
+        <v>4</v>
+      </c>
+      <c r="N81" t="n">
+        <v>4</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>3</v>
+      </c>
+      <c r="R81" t="n">
+        <v>3</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="n">
+        <v>6</v>
+      </c>
+      <c r="U81" t="n">
+        <v>18</v>
+      </c>
+      <c r="V81" t="n">
+        <v>9</v>
+      </c>
+      <c r="W81" t="n">
+        <v>4</v>
+      </c>
+      <c r="X81" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Estadio de Fútbol Jaraguay de Montería</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>, Montería</t>
+        </is>
+      </c>
+      <c r="AC81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>2131</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS81" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT81" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV81" t="n">
+        <v>15</v>
+      </c>
+      <c r="BW81" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX81" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY81" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ81" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CA81" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="CB81" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR81" t="n">
+        <v>7</v>
+      </c>
+      <c r="CS81" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU81" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV81" t="n">
+        <v>4</v>
+      </c>
+      <c r="CW81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ81" t="n">
+        <v>72</v>
+      </c>
+      <c r="DA81" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB81" t="n">
+        <v>57</v>
+      </c>
+      <c r="DC81" t="n">
+        <v>93</v>
+      </c>
+      <c r="DD81" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE81" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DF81" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG81" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DH81" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DI81" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DJ81" t="n">
+        <v>29</v>
+      </c>
+      <c r="DK81" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL81" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DM81" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DN81" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="DO81" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP81" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ81" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW81" t="inlineStr"/>
+      <c r="DX81" t="inlineStr"/>
+      <c r="DY81" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="DZ81" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EA81" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="EB81" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EC81" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="ED81" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EE81" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EF81" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="EG81" t="inlineStr"/>
+      <c r="EH81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH81" headerRowCount="1">
-  <autoFilter ref="A1:EH81"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH86" headerRowCount="1">
+  <autoFilter ref="A1:EH86"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH81"/>
+  <dimension ref="A1:EH86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -2182,7 +2182,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE3" t="n">
         <v>0.38</v>
@@ -2629,7 +2629,7 @@
         <v>2</v>
       </c>
       <c r="DE4" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -3030,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="DE5" t="n">
         <v>0.44</v>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DE6" t="n">
         <v>1.22</v>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -3910,10 +3910,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4349,7 +4349,7 @@
         <v>1.25</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4793,7 +4793,7 @@
         <v>1.88</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>1.11</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE11" t="n">
         <v>1.78</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6106,10 +6106,10 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
         <v>1.82</v>
       </c>
       <c r="DO12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6522,7 +6522,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE13" t="n">
         <v>0.38</v>
@@ -6969,7 +6969,7 @@
         <v>0.5</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>1.25</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7435,7 +7435,7 @@
         <v>3.19</v>
       </c>
       <c r="DO15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -7854,10 +7854,10 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -7887,7 +7887,7 @@
         <v>2.53</v>
       </c>
       <c r="DO16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8718,10 +8718,10 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DF18" t="n">
         <v>1</v>
@@ -8751,7 +8751,7 @@
         <v>1.44</v>
       </c>
       <c r="DO18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -10026,10 +10026,10 @@
         <v>100</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10059,7 +10059,7 @@
         <v>2.47</v>
       </c>
       <c r="DO21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10470,7 +10470,7 @@
         <v>25</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE22" t="n">
         <v>1.25</v>
@@ -10914,10 +10914,10 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DF23" t="n">
         <v>0</v>
@@ -10947,7 +10947,7 @@
         <v>2.38</v>
       </c>
       <c r="DO23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12230,7 +12230,7 @@
         <v>75</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DE26" t="n">
         <v>1.22</v>
@@ -12263,7 +12263,7 @@
         <v>2.13</v>
       </c>
       <c r="DO26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -12666,10 +12666,10 @@
         <v>75</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DF27" t="n">
         <v>0.5</v>
@@ -12699,7 +12699,7 @@
         <v>2.21</v>
       </c>
       <c r="DO27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13105,7 +13105,7 @@
         <v>1.25</v>
       </c>
       <c r="DE28" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -13990,10 +13990,10 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF30" t="n">
         <v>0.33</v>
@@ -14023,7 +14023,7 @@
         <v>2.24</v>
       </c>
       <c r="DO30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14862,7 +14862,7 @@
         <v>50</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DE32" t="n">
         <v>0.38</v>
@@ -14895,7 +14895,7 @@
         <v>2.62</v>
       </c>
       <c r="DO32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15298,10 +15298,10 @@
         <v>50</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE33" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DF33" t="n">
         <v>1</v>
@@ -15331,7 +15331,7 @@
         <v>2.29</v>
       </c>
       <c r="DO33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16181,7 +16181,7 @@
         <v>1.25</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF35" t="n">
         <v>1.67</v>
@@ -16211,7 +16211,7 @@
         <v>2.16</v>
       </c>
       <c r="DO35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -16617,7 +16617,7 @@
         <v>1.22</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF36" t="n">
         <v>0</v>
@@ -16647,7 +16647,7 @@
         <v>2.84</v>
       </c>
       <c r="DO36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP36" t="b">
         <v>0</v>
@@ -17050,10 +17050,10 @@
         <v>84</v>
       </c>
       <c r="DD37" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DF37" t="n">
         <v>2</v>
@@ -17083,7 +17083,7 @@
         <v>2.43</v>
       </c>
       <c r="DO37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -17930,7 +17930,7 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="DE39" t="n">
         <v>2</v>
@@ -17963,7 +17963,7 @@
         <v>3.9</v>
       </c>
       <c r="DO39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -18366,10 +18366,10 @@
         <v>88</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF40" t="n">
         <v>2.25</v>
@@ -18399,7 +18399,7 @@
         <v>2.56</v>
       </c>
       <c r="DO40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP40" t="b">
         <v>0</v>
@@ -18798,10 +18798,10 @@
         <v>63</v>
       </c>
       <c r="DD41" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DE41" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DF41" t="n">
         <v>0.5</v>
@@ -18831,7 +18831,7 @@
         <v>2.9</v>
       </c>
       <c r="DO41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -19234,10 +19234,10 @@
         <v>88</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF42" t="n">
         <v>1.25</v>
@@ -19267,7 +19267,7 @@
         <v>2.02</v>
       </c>
       <c r="DO42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -19670,7 +19670,7 @@
         <v>63</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE43" t="n">
         <v>1.25</v>
@@ -20106,7 +20106,7 @@
         <v>50</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE44" t="n">
         <v>1.11</v>
@@ -20139,7 +20139,7 @@
         <v>3.37</v>
       </c>
       <c r="DO44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21402,7 +21402,7 @@
         <v>63</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE47" t="n">
         <v>1.22</v>
@@ -21435,7 +21435,7 @@
         <v>2.48</v>
       </c>
       <c r="DO47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP47" t="b">
         <v>0</v>
@@ -22270,10 +22270,10 @@
         <v>80</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE49" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF49" t="n">
         <v>0.4</v>
@@ -22303,7 +22303,7 @@
         <v>2.37</v>
       </c>
       <c r="DO49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -22717,7 +22717,7 @@
         <v>1.25</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DF50" t="n">
         <v>1.8</v>
@@ -23158,10 +23158,10 @@
         <v>60</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DF51" t="n">
         <v>1.8</v>
@@ -23191,7 +23191,7 @@
         <v>2.38</v>
       </c>
       <c r="DO51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP51" t="b">
         <v>0</v>
@@ -23605,7 +23605,7 @@
         <v>1.22</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF52" t="n">
         <v>0.4</v>
@@ -23635,7 +23635,7 @@
         <v>2.56</v>
       </c>
       <c r="DO52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -24046,10 +24046,10 @@
         <v>60</v>
       </c>
       <c r="DD53" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -24079,7 +24079,7 @@
         <v>2.58</v>
       </c>
       <c r="DO53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25370,10 +25370,10 @@
         <v>70</v>
       </c>
       <c r="DD56" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF56" t="n">
         <v>3</v>
@@ -25403,7 +25403,7 @@
         <v>4.13</v>
       </c>
       <c r="DO56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -26694,7 +26694,7 @@
         <v>64</v>
       </c>
       <c r="DD59" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DE59" t="n">
         <v>0.5</v>
@@ -27146,10 +27146,10 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DE60" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DF60" t="n">
         <v>2.17</v>
@@ -27179,7 +27179,7 @@
         <v>2.31</v>
       </c>
       <c r="DO60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -27590,7 +27590,7 @@
         <v>50</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE61" t="n">
         <v>1.78</v>
@@ -27623,7 +27623,7 @@
         <v>2.63</v>
       </c>
       <c r="DO61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -28026,10 +28026,10 @@
         <v>75</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE62" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="DF62" t="n">
         <v>1.17</v>
@@ -28059,7 +28059,7 @@
         <v>3.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -28462,7 +28462,7 @@
         <v>59</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE63" t="n">
         <v>0.44</v>
@@ -28495,7 +28495,7 @@
         <v>2.4</v>
       </c>
       <c r="DO63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -28901,7 +28901,7 @@
         <v>0.38</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF64" t="n">
         <v>0.4</v>
@@ -30205,7 +30205,7 @@
         <v>1.25</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF67" t="n">
         <v>1.29</v>
@@ -30649,7 +30649,7 @@
         <v>0.5</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DF68" t="n">
         <v>0.5</v>
@@ -31093,7 +31093,7 @@
         <v>1.78</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF69" t="n">
         <v>1.43</v>
@@ -31123,7 +31123,7 @@
         <v>3.02</v>
       </c>
       <c r="DO69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -31526,10 +31526,10 @@
         <v>55</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DF70" t="n">
         <v>1.67</v>
@@ -31559,7 +31559,7 @@
         <v>2.63</v>
       </c>
       <c r="DO70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP70" t="b">
         <v>0</v>
@@ -31962,7 +31962,7 @@
         <v>54</v>
       </c>
       <c r="DD71" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="DE71" t="n">
         <v>0.38</v>
@@ -31995,7 +31995,7 @@
         <v>3.31</v>
       </c>
       <c r="DO71" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -32398,7 +32398,7 @@
         <v>64</v>
       </c>
       <c r="DD72" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DE72" t="n">
         <v>1.22</v>
@@ -32431,7 +32431,7 @@
         <v>2.49</v>
       </c>
       <c r="DO72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -33273,7 +33273,7 @@
         <v>0.44</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF74" t="n">
         <v>0.57</v>
@@ -33303,7 +33303,7 @@
         <v>2.19</v>
       </c>
       <c r="DO74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -34142,10 +34142,10 @@
         <v>65</v>
       </c>
       <c r="DD76" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DF76" t="n">
         <v>0.43</v>
@@ -34175,7 +34175,7 @@
         <v>2.09</v>
       </c>
       <c r="DO76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -34589,7 +34589,7 @@
         <v>1.11</v>
       </c>
       <c r="DE77" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="DF77" t="n">
         <v>1.25</v>
@@ -34619,7 +34619,7 @@
         <v>3.5</v>
       </c>
       <c r="DO77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -35628,7 +35628,7 @@
         <v>2</v>
       </c>
       <c r="R80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S80" t="n">
         <v>8</v>
@@ -35640,7 +35640,7 @@
         <v>10</v>
       </c>
       <c r="V80" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W80" t="n">
         <v>9</v>
@@ -35815,10 +35815,10 @@
         <v>0.99</v>
       </c>
       <c r="CA80" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="CB80" t="n">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="CC80" t="n">
         <v>0</v>
@@ -35970,42 +35970,42 @@
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="EB80" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EC80" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="ED80" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EE80" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="EF80" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EG80" t="inlineStr"/>
@@ -36402,11 +36402,19 @@
       <c r="DV81" t="b">
         <v>0</v>
       </c>
-      <c r="DW81" t="inlineStr"/>
-      <c r="DX81" t="inlineStr"/>
+      <c r="DW81" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DX81" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
       <c r="DY81" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="DZ81" t="inlineStr">
@@ -36416,36 +36424,2224 @@
       </c>
       <c r="EA81" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="EB81" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EC81" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="ED81" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EE81" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EF81" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="EG81" t="inlineStr"/>
       <c r="EH81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>9</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>46082.0625</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2</v>
+      </c>
+      <c r="I82" t="n">
+        <v>3</v>
+      </c>
+      <c r="J82" t="n">
+        <v>12</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" t="n">
+        <v>14</v>
+      </c>
+      <c r="M82" t="n">
+        <v>4</v>
+      </c>
+      <c r="N82" t="n">
+        <v>2</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>10</v>
+      </c>
+      <c r="R82" t="n">
+        <v>3</v>
+      </c>
+      <c r="S82" t="n">
+        <v>9</v>
+      </c>
+      <c r="T82" t="n">
+        <v>3</v>
+      </c>
+      <c r="U82" t="n">
+        <v>19</v>
+      </c>
+      <c r="V82" t="n">
+        <v>6</v>
+      </c>
+      <c r="W82" t="n">
+        <v>10</v>
+      </c>
+      <c r="X82" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Estadio Atanasio Girardot</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
+        </is>
+      </c>
+      <c r="AC82" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>2139</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI82" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK82" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM82" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN82" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS82" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV82" t="n">
+        <v>47</v>
+      </c>
+      <c r="BW82" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX82" t="n">
+        <v>93</v>
+      </c>
+      <c r="BY82" t="n">
+        <v>65</v>
+      </c>
+      <c r="BZ82" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CA82" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="CB82" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="CC82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR82" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS82" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU82" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV82" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX82" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY82" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ82" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA82" t="n">
+        <v>66</v>
+      </c>
+      <c r="DB82" t="n">
+        <v>41</v>
+      </c>
+      <c r="DC82" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD82" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DE82" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DF82" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DG82" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DH82" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DI82" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DJ82" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK82" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL82" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DM82" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DN82" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DO82" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP82" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ82" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR82" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV82" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW82" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="DX82" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="DY82" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="DZ82" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EA82" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="EB82" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EC82" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="ED82" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EE82" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EF82" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EG82" t="inlineStr"/>
+      <c r="EH82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>9</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>46082.79166666666</v>
+      </c>
+      <c r="G83" t="n">
+        <v>3</v>
+      </c>
+      <c r="H83" t="n">
+        <v>2</v>
+      </c>
+      <c r="I83" t="n">
+        <v>5</v>
+      </c>
+      <c r="J83" t="n">
+        <v>6</v>
+      </c>
+      <c r="K83" t="n">
+        <v>5</v>
+      </c>
+      <c r="L83" t="n">
+        <v>11</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>10</v>
+      </c>
+      <c r="R83" t="n">
+        <v>5</v>
+      </c>
+      <c r="S83" t="n">
+        <v>12</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>22</v>
+      </c>
+      <c r="V83" t="n">
+        <v>7</v>
+      </c>
+      <c r="W83" t="n">
+        <v>7</v>
+      </c>
+      <c r="X83" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>Estadio Departamental Libertad</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>Carrera 8, San Juan de Pasto</t>
+        </is>
+      </c>
+      <c r="AC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>2143</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI83" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL83" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM83" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN83" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV83" t="n">
+        <v>115</v>
+      </c>
+      <c r="BW83" t="n">
+        <v>69</v>
+      </c>
+      <c r="BX83" t="n">
+        <v>159</v>
+      </c>
+      <c r="BY83" t="n">
+        <v>121</v>
+      </c>
+      <c r="BZ83" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CA83" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CB83" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="CC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM83" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR83" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS83" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU83" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV83" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX83" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY83" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ83" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA83" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB83" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC83" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD83" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE83" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF83" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DG83" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH83" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DI83" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DJ83" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK83" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL83" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DM83" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DN83" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="DO83" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP83" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ83" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR83" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS83" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT83" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV83" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW83" t="inlineStr"/>
+      <c r="DX83" t="inlineStr"/>
+      <c r="DY83" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="DZ83" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EA83" t="inlineStr">
+        <is>
+          <t>3.78</t>
+        </is>
+      </c>
+      <c r="EB83" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EC83" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="ED83" t="inlineStr">
+        <is>
+          <t>7.11</t>
+        </is>
+      </c>
+      <c r="EE83" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
+      </c>
+      <c r="EF83" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EG83" t="inlineStr"/>
+      <c r="EH83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>9</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Rionegro Águilas</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>La Equidad</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>46082.875</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>4</v>
+      </c>
+      <c r="K84" t="n">
+        <v>6</v>
+      </c>
+      <c r="L84" t="n">
+        <v>10</v>
+      </c>
+      <c r="M84" t="n">
+        <v>4</v>
+      </c>
+      <c r="N84" t="n">
+        <v>2</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>5</v>
+      </c>
+      <c r="R84" t="n">
+        <v>4</v>
+      </c>
+      <c r="S84" t="n">
+        <v>7</v>
+      </c>
+      <c r="T84" t="n">
+        <v>6</v>
+      </c>
+      <c r="U84" t="n">
+        <v>12</v>
+      </c>
+      <c r="V84" t="n">
+        <v>10</v>
+      </c>
+      <c r="W84" t="n">
+        <v>13</v>
+      </c>
+      <c r="X84" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>Estadio Alberto Grisales</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>Route 45A, Rionegro, Antioquia</t>
+        </is>
+      </c>
+      <c r="AC84" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>73</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ84" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM84" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN84" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT84" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV84" t="n">
+        <v>85</v>
+      </c>
+      <c r="BW84" t="n">
+        <v>77</v>
+      </c>
+      <c r="BX84" t="n">
+        <v>153</v>
+      </c>
+      <c r="BY84" t="n">
+        <v>154</v>
+      </c>
+      <c r="BZ84" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CA84" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CB84" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="CC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR84" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS84" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU84" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV84" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX84" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY84" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ84" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA84" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB84" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC84" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE84" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF84" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DG84" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DH84" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DI84" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DJ84" t="n">
+        <v>41</v>
+      </c>
+      <c r="DK84" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL84" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DM84" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DN84" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="DO84" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW84" t="inlineStr"/>
+      <c r="DX84" t="inlineStr"/>
+      <c r="DY84" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="DZ84" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EA84" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="EB84" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EC84" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="ED84" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="EE84" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EF84" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EG84" t="inlineStr"/>
+      <c r="EH84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>16</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>46082.96527777778</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" t="n">
+        <v>2</v>
+      </c>
+      <c r="J85" t="n">
+        <v>6</v>
+      </c>
+      <c r="K85" t="n">
+        <v>5</v>
+      </c>
+      <c r="L85" t="n">
+        <v>11</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" t="n">
+        <v>3</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>2</v>
+      </c>
+      <c r="R85" t="n">
+        <v>3</v>
+      </c>
+      <c r="S85" t="n">
+        <v>11</v>
+      </c>
+      <c r="T85" t="n">
+        <v>10</v>
+      </c>
+      <c r="U85" t="n">
+        <v>13</v>
+      </c>
+      <c r="V85" t="n">
+        <v>13</v>
+      </c>
+      <c r="W85" t="n">
+        <v>14</v>
+      </c>
+      <c r="X85" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>Estadio Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>BN 25, Palmira</t>
+        </is>
+      </c>
+      <c r="AC85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ85" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK85" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM85" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV85" t="n">
+        <v>11</v>
+      </c>
+      <c r="BW85" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX85" t="n">
+        <v>86</v>
+      </c>
+      <c r="BY85" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ85" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CA85" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CB85" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR85" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS85" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU85" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV85" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX85" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY85" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ85" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA85" t="n">
+        <v>63</v>
+      </c>
+      <c r="DB85" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC85" t="n">
+        <v>51</v>
+      </c>
+      <c r="DD85" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE85" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DF85" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH85" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DI85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DJ85" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK85" t="n">
+        <v>38</v>
+      </c>
+      <c r="DL85" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DM85" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DN85" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="DO85" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR85" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS85" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT85" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU85" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW85" t="inlineStr"/>
+      <c r="DX85" t="inlineStr"/>
+      <c r="DY85" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="DZ85" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EA85" t="inlineStr">
+        <is>
+          <t>4.63</t>
+        </is>
+      </c>
+      <c r="EB85" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EC85" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="ED85" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="EE85" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EF85" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EG85" t="inlineStr"/>
+      <c r="EH85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>9</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>46083.0625</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="n">
+        <v>6</v>
+      </c>
+      <c r="K86" t="n">
+        <v>4</v>
+      </c>
+      <c r="L86" t="n">
+        <v>10</v>
+      </c>
+      <c r="M86" t="n">
+        <v>2</v>
+      </c>
+      <c r="N86" t="n">
+        <v>4</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
+      </c>
+      <c r="P86" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>2</v>
+      </c>
+      <c r="R86" t="n">
+        <v>4</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="n">
+        <v>8</v>
+      </c>
+      <c r="U86" t="n">
+        <v>12</v>
+      </c>
+      <c r="V86" t="n">
+        <v>12</v>
+      </c>
+      <c r="W86" t="n">
+        <v>13</v>
+      </c>
+      <c r="X86" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Murillo Toro</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
+        </is>
+      </c>
+      <c r="AC86" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>2140</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI86" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL86" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM86" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN86" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP86" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS86" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT86" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV86" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW86" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX86" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY86" t="n">
+        <v>63</v>
+      </c>
+      <c r="BZ86" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CA86" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CB86" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="CC86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM86" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR86" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS86" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU86" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV86" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX86" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY86" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ86" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA86" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB86" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC86" t="n">
+        <v>61</v>
+      </c>
+      <c r="DD86" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE86" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DF86" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG86" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DH86" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI86" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DJ86" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK86" t="n">
+        <v>28</v>
+      </c>
+      <c r="DL86" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DM86" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DN86" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="DO86" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP86" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ86" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR86" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS86" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT86" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU86" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV86" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW86" t="inlineStr"/>
+      <c r="DX86" t="inlineStr"/>
+      <c r="DY86" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="DZ86" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EA86" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="EB86" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EC86" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="ED86" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EE86" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EF86" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EG86" t="inlineStr"/>
+      <c r="EH86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH86" headerRowCount="1">
-  <autoFilter ref="A1:EH86"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH87" headerRowCount="1">
+  <autoFilter ref="A1:EH87"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH86"/>
+  <dimension ref="A1:EH87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -2182,7 +2182,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE3" t="n">
         <v>0.38</v>
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DE8" t="n">
         <v>1.33</v>
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -6969,7 +6969,7 @@
         <v>0.5</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -10470,7 +10470,7 @@
         <v>25</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE22" t="n">
         <v>1.25</v>
@@ -13102,7 +13102,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DE28" t="n">
         <v>2</v>
@@ -13135,7 +13135,7 @@
         <v>2.03</v>
       </c>
       <c r="DO28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -13993,7 +13993,7 @@
         <v>0.67</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF30" t="n">
         <v>0.33</v>
@@ -15745,7 +15745,7 @@
         <v>1.78</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF34" t="n">
         <v>1.67</v>
@@ -15775,7 +15775,7 @@
         <v>2.49</v>
       </c>
       <c r="DO34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -20106,7 +20106,7 @@
         <v>50</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE44" t="n">
         <v>1.11</v>
@@ -21826,7 +21826,7 @@
         <v>59</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DE48" t="n">
         <v>0.5</v>
@@ -24477,7 +24477,7 @@
         <v>0.44</v>
       </c>
       <c r="DE54" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF54" t="n">
         <v>0.2</v>
@@ -24507,7 +24507,7 @@
         <v>1.66</v>
       </c>
       <c r="DO54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -25373,7 +25373,7 @@
         <v>2.14</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF56" t="n">
         <v>3</v>
@@ -28462,7 +28462,7 @@
         <v>59</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE63" t="n">
         <v>0.44</v>
@@ -29334,7 +29334,7 @@
         <v>57</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DE65" t="n">
         <v>1.11</v>
@@ -29367,7 +29367,7 @@
         <v>2.22</v>
       </c>
       <c r="DO65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31093,7 +31093,7 @@
         <v>1.78</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF69" t="n">
         <v>1.43</v>
@@ -33709,7 +33709,7 @@
         <v>2</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF75" t="n">
         <v>1.67</v>
@@ -36346,7 +36346,7 @@
         <v>93</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DE81" t="n">
         <v>1.88</v>
@@ -38109,7 +38109,7 @@
         <v>1.33</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF85" t="n">
         <v>1.38</v>
@@ -38642,6 +38642,442 @@
       </c>
       <c r="EG86" t="inlineStr"/>
       <c r="EH86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>10</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Jaguares de Córdoba</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>46086.04166666666</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" t="n">
+        <v>3</v>
+      </c>
+      <c r="J87" t="n">
+        <v>7</v>
+      </c>
+      <c r="K87" t="n">
+        <v>3</v>
+      </c>
+      <c r="L87" t="n">
+        <v>10</v>
+      </c>
+      <c r="M87" t="n">
+        <v>3</v>
+      </c>
+      <c r="N87" t="n">
+        <v>2</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>6</v>
+      </c>
+      <c r="R87" t="n">
+        <v>5</v>
+      </c>
+      <c r="S87" t="n">
+        <v>4</v>
+      </c>
+      <c r="T87" t="n">
+        <v>7</v>
+      </c>
+      <c r="U87" t="n">
+        <v>10</v>
+      </c>
+      <c r="V87" t="n">
+        <v>12</v>
+      </c>
+      <c r="W87" t="n">
+        <v>14</v>
+      </c>
+      <c r="X87" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>Estadio Metropolitano de Techo</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AC87" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>2152</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>58</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI87" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK87" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL87" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM87" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN87" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR87" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT87" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV87" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW87" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX87" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY87" t="n">
+        <v>65</v>
+      </c>
+      <c r="BZ87" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CA87" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CB87" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="CC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR87" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS87" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU87" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV87" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX87" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY87" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ87" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA87" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB87" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC87" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD87" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DE87" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DF87" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DG87" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH87" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DI87" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DJ87" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK87" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL87" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DM87" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DN87" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DO87" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP87" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ87" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR87" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV87" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW87" t="inlineStr"/>
+      <c r="DX87" t="inlineStr"/>
+      <c r="DY87" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="DZ87" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EA87" t="inlineStr">
+        <is>
+          <t>3.78</t>
+        </is>
+      </c>
+      <c r="EB87" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EC87" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="ED87" t="inlineStr">
+        <is>
+          <t>6.43</t>
+        </is>
+      </c>
+      <c r="EE87" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="EF87" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EG87" t="inlineStr"/>
+      <c r="EH87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH87" headerRowCount="1">
-  <autoFilter ref="A1:EH87"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH90" headerRowCount="1">
+  <autoFilter ref="A1:EH90"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH87"/>
+  <dimension ref="A1:EH90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1749,7 +1749,7 @@
         <v>0.5</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>1.4</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2629,7 +2629,7 @@
         <v>2</v>
       </c>
       <c r="DE4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -4349,7 +4349,7 @@
         <v>1.11</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4790,7 +4790,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DE9" t="n">
         <v>1.67</v>
@@ -4823,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5665,7 +5665,7 @@
         <v>0.67</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DE12" t="n">
         <v>0.67</v>
@@ -6525,7 +6525,7 @@
         <v>1.67</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6555,7 +6555,7 @@
         <v>1.86</v>
       </c>
       <c r="DO13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7402,7 +7402,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE15" t="n">
         <v>1.75</v>
@@ -7854,7 +7854,7 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE16" t="n">
         <v>0.78</v>
@@ -9157,7 +9157,7 @@
         <v>1.22</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9187,7 +9187,7 @@
         <v>2.56</v>
       </c>
       <c r="DO19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9590,7 +9590,7 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DE20" t="n">
         <v>1.11</v>
@@ -10473,7 +10473,7 @@
         <v>1.4</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF22" t="n">
         <v>2</v>
@@ -10503,7 +10503,7 @@
         <v>2.27</v>
       </c>
       <c r="DO22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11350,7 +11350,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="DE24" t="n">
         <v>0.44</v>
@@ -11383,7 +11383,7 @@
         <v>1.88</v>
       </c>
       <c r="DO24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12669,7 +12669,7 @@
         <v>1.5</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DF27" t="n">
         <v>0.5</v>
@@ -13105,7 +13105,7 @@
         <v>1.11</v>
       </c>
       <c r="DE28" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -13549,7 +13549,7 @@
         <v>2</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -14865,7 +14865,7 @@
         <v>1.75</v>
       </c>
       <c r="DE32" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="DF32" t="n">
         <v>1.67</v>
@@ -15298,7 +15298,7 @@
         <v>50</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE33" t="n">
         <v>2</v>
@@ -15742,7 +15742,7 @@
         <v>59</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DE34" t="n">
         <v>1.11</v>
@@ -16178,7 +16178,7 @@
         <v>67</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE35" t="n">
         <v>1.5</v>
@@ -17050,7 +17050,7 @@
         <v>84</v>
       </c>
       <c r="DD37" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DE37" t="n">
         <v>1.67</v>
@@ -17497,7 +17497,7 @@
         <v>0.5</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DF38" t="n">
         <v>0.67</v>
@@ -18801,7 +18801,7 @@
         <v>0.78</v>
       </c>
       <c r="DE41" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DF41" t="n">
         <v>0.5</v>
@@ -19673,7 +19673,7 @@
         <v>1.67</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF43" t="n">
         <v>2</v>
@@ -19703,7 +19703,7 @@
         <v>1.9</v>
       </c>
       <c r="DO43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20522,7 +20522,7 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DE45" t="n">
         <v>0.44</v>
@@ -20555,7 +20555,7 @@
         <v>2.5</v>
       </c>
       <c r="DO45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -20958,10 +20958,10 @@
         <v>50</v>
       </c>
       <c r="DD46" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF46" t="n">
         <v>0.25</v>
@@ -20991,7 +20991,7 @@
         <v>2.87</v>
       </c>
       <c r="DO46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -21402,7 +21402,7 @@
         <v>63</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE47" t="n">
         <v>1.22</v>
@@ -22714,7 +22714,7 @@
         <v>60</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE50" t="n">
         <v>2</v>
@@ -22747,7 +22747,7 @@
         <v>1.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24046,10 +24046,10 @@
         <v>60</v>
       </c>
       <c r="DD53" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -24079,7 +24079,7 @@
         <v>2.58</v>
       </c>
       <c r="DO53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -24926,10 +24926,10 @@
         <v>80</v>
       </c>
       <c r="DD55" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DE55" t="n">
         <v>1.78</v>
-      </c>
-      <c r="DE55" t="n">
-        <v>1.88</v>
       </c>
       <c r="DF55" t="n">
         <v>1.4</v>
@@ -24959,7 +24959,7 @@
         <v>3.39</v>
       </c>
       <c r="DO55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26253,7 +26253,7 @@
         <v>1.22</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF58" t="n">
         <v>0.83</v>
@@ -26283,7 +26283,7 @@
         <v>2</v>
       </c>
       <c r="DO58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -27149,7 +27149,7 @@
         <v>2</v>
       </c>
       <c r="DE60" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DF60" t="n">
         <v>2.17</v>
@@ -27593,7 +27593,7 @@
         <v>1.67</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF61" t="n">
         <v>1.5</v>
@@ -28026,7 +28026,7 @@
         <v>75</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE62" t="n">
         <v>2.14</v>
@@ -28898,7 +28898,7 @@
         <v>60</v>
       </c>
       <c r="DD64" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="DE64" t="n">
         <v>0.67</v>
@@ -28931,7 +28931,7 @@
         <v>1.97</v>
       </c>
       <c r="DO64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -29766,7 +29766,7 @@
         <v>90</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DE66" t="n">
         <v>2</v>
@@ -30202,7 +30202,7 @@
         <v>71</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE67" t="n">
         <v>0.78</v>
@@ -30235,7 +30235,7 @@
         <v>2.55</v>
       </c>
       <c r="DO67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -31090,7 +31090,7 @@
         <v>57</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DE69" t="n">
         <v>1.4</v>
@@ -31123,7 +31123,7 @@
         <v>3.02</v>
       </c>
       <c r="DO69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -31529,7 +31529,7 @@
         <v>1.75</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DF70" t="n">
         <v>1.67</v>
@@ -31965,7 +31965,7 @@
         <v>2.14</v>
       </c>
       <c r="DE71" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="DF71" t="n">
         <v>2.25</v>
@@ -32398,7 +32398,7 @@
         <v>64</v>
       </c>
       <c r="DD72" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DE72" t="n">
         <v>1.22</v>
@@ -32845,7 +32845,7 @@
         <v>1.11</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -32875,7 +32875,7 @@
         <v>3.26</v>
       </c>
       <c r="DO73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35458,7 +35458,7 @@
         <v>63</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DE79" t="n">
         <v>0.44</v>
@@ -35902,7 +35902,7 @@
         <v>65</v>
       </c>
       <c r="DD80" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="DE80" t="n">
         <v>2</v>
@@ -36349,7 +36349,7 @@
         <v>1.11</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DF81" t="n">
         <v>1.43</v>
@@ -36379,7 +36379,7 @@
         <v>2.39</v>
       </c>
       <c r="DO81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -37673,7 +37673,7 @@
         <v>1.5</v>
       </c>
       <c r="DE84" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DF84" t="n">
         <v>1.57</v>
@@ -38106,7 +38106,7 @@
         <v>51</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DE85" t="n">
         <v>1.4</v>
@@ -38139,7 +38139,7 @@
         <v>2.74</v>
       </c>
       <c r="DO85" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -38692,7 +38692,7 @@
         <v>3</v>
       </c>
       <c r="N87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -38744,7 +38744,7 @@
         <v>3</v>
       </c>
       <c r="AD87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE87" t="n">
         <v>1.35</v>
@@ -38864,13 +38864,13 @@
         <v>2</v>
       </c>
       <c r="BR87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BS87" t="n">
         <v>1</v>
       </c>
       <c r="BT87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BU87" t="n">
         <v>1</v>
@@ -39078,6 +39078,1338 @@
       </c>
       <c r="EG87" t="inlineStr"/>
       <c r="EH87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>10</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Llaneros</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>La Equidad</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>46086.96527777778</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" t="n">
+        <v>2</v>
+      </c>
+      <c r="J88" t="n">
+        <v>7</v>
+      </c>
+      <c r="K88" t="n">
+        <v>3</v>
+      </c>
+      <c r="L88" t="n">
+        <v>10</v>
+      </c>
+      <c r="M88" t="n">
+        <v>2</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>1</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>2</v>
+      </c>
+      <c r="R88" t="n">
+        <v>1</v>
+      </c>
+      <c r="S88" t="n">
+        <v>6</v>
+      </c>
+      <c r="T88" t="n">
+        <v>5</v>
+      </c>
+      <c r="U88" t="n">
+        <v>8</v>
+      </c>
+      <c r="V88" t="n">
+        <v>6</v>
+      </c>
+      <c r="W88" t="n">
+        <v>12</v>
+      </c>
+      <c r="X88" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Calle Lombana</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>, Villavicencio</t>
+        </is>
+      </c>
+      <c r="AC88" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT88" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV88" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW88" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX88" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY88" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ88" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CA88" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CB88" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CC88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR88" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS88" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU88" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV88" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX88" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY88" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ88" t="n">
+        <v>46</v>
+      </c>
+      <c r="DA88" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB88" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC88" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD88" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DE88" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DF88" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG88" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH88" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DI88" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ88" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK88" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL88" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="DM88" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DN88" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DO88" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP88" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ88" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR88" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS88" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT88" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU88" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV88" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW88" t="inlineStr"/>
+      <c r="DX88" t="inlineStr"/>
+      <c r="DY88" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="DZ88" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EA88" t="inlineStr">
+        <is>
+          <t>5.10</t>
+        </is>
+      </c>
+      <c r="EB88" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EC88" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="ED88" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="EE88" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EF88" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EG88" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH88" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>10</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Alianza Petrolera</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>46087.05555555555</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2</v>
+      </c>
+      <c r="J89" t="n">
+        <v>12</v>
+      </c>
+      <c r="K89" t="n">
+        <v>4</v>
+      </c>
+      <c r="L89" t="n">
+        <v>16</v>
+      </c>
+      <c r="M89" t="n">
+        <v>3</v>
+      </c>
+      <c r="N89" t="n">
+        <v>4</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>7</v>
+      </c>
+      <c r="R89" t="n">
+        <v>3</v>
+      </c>
+      <c r="S89" t="n">
+        <v>11</v>
+      </c>
+      <c r="T89" t="n">
+        <v>8</v>
+      </c>
+      <c r="U89" t="n">
+        <v>18</v>
+      </c>
+      <c r="V89" t="n">
+        <v>11</v>
+      </c>
+      <c r="W89" t="n">
+        <v>10</v>
+      </c>
+      <c r="X89" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>Estadio Metropolitano Roberto Meléndez</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>Intersección de la Avenida Circunvalar con la Calle 45, Barranquilla</t>
+        </is>
+      </c>
+      <c r="AC89" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>51</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF89" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI89" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK89" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM89" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN89" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR89" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT89" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV89" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW89" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX89" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY89" t="n">
+        <v>66</v>
+      </c>
+      <c r="BZ89" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CA89" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CB89" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="CC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR89" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS89" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU89" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV89" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX89" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY89" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ89" t="n">
+        <v>57</v>
+      </c>
+      <c r="DA89" t="n">
+        <v>94</v>
+      </c>
+      <c r="DB89" t="n">
+        <v>57</v>
+      </c>
+      <c r="DC89" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD89" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DE89" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DF89" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DG89" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DH89" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DI89" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DJ89" t="n">
+        <v>44</v>
+      </c>
+      <c r="DK89" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL89" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DM89" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DN89" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="DO89" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP89" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ89" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR89" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS89" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT89" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU89" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV89" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW89" t="inlineStr"/>
+      <c r="DX89" t="inlineStr"/>
+      <c r="DY89" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="DZ89" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EA89" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="EB89" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EC89" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="ED89" t="inlineStr">
+        <is>
+          <t>6.54</t>
+        </is>
+      </c>
+      <c r="EE89" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
+      </c>
+      <c r="EF89" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EG89" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH89" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>10</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>46088.0625</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I90" t="n">
+        <v>2</v>
+      </c>
+      <c r="J90" t="n">
+        <v>12</v>
+      </c>
+      <c r="K90" t="n">
+        <v>2</v>
+      </c>
+      <c r="L90" t="n">
+        <v>14</v>
+      </c>
+      <c r="M90" t="n">
+        <v>4</v>
+      </c>
+      <c r="N90" t="n">
+        <v>5</v>
+      </c>
+      <c r="O90" t="n">
+        <v>2</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>3</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7</v>
+      </c>
+      <c r="S90" t="n">
+        <v>13</v>
+      </c>
+      <c r="T90" t="n">
+        <v>6</v>
+      </c>
+      <c r="U90" t="n">
+        <v>16</v>
+      </c>
+      <c r="V90" t="n">
+        <v>13</v>
+      </c>
+      <c r="W90" t="n">
+        <v>15</v>
+      </c>
+      <c r="X90" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>Estadio Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>BN 25, Palmira</t>
+        </is>
+      </c>
+      <c r="AC90" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ90" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB90" t="n">
+        <v>2135</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF90" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI90" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK90" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM90" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN90" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ90" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR90" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS90" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT90" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV90" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW90" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX90" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY90" t="n">
+        <v>58</v>
+      </c>
+      <c r="BZ90" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CA90" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CB90" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="CC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR90" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS90" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU90" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV90" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX90" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY90" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ90" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA90" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB90" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC90" t="n">
+        <v>56</v>
+      </c>
+      <c r="DD90" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DE90" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DF90" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG90" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DH90" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI90" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DJ90" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK90" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL90" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DM90" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="DN90" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="DO90" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP90" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ90" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW90" t="inlineStr"/>
+      <c r="DX90" t="inlineStr"/>
+      <c r="DY90" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="DZ90" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EA90" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="EB90" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EC90" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="ED90" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="EE90" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EF90" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EG90" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EH90" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH90" headerRowCount="1">
-  <autoFilter ref="A1:EH90"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH91" headerRowCount="1">
+  <autoFilter ref="A1:EH91"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH90"/>
+  <dimension ref="A1:EH91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -3030,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DE5" t="n">
         <v>0.44</v>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -5229,7 +5229,7 @@
         <v>1.11</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -8718,7 +8718,7 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE18" t="n">
         <v>2</v>
@@ -8751,7 +8751,7 @@
         <v>1.44</v>
       </c>
       <c r="DO18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -12666,7 +12666,7 @@
         <v>75</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE27" t="n">
         <v>1.2</v>
@@ -12699,7 +12699,7 @@
         <v>2.21</v>
       </c>
       <c r="DO27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -16181,7 +16181,7 @@
         <v>1.22</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF35" t="n">
         <v>1.67</v>
@@ -16211,7 +16211,7 @@
         <v>2.16</v>
       </c>
       <c r="DO35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17930,7 +17930,7 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DE39" t="n">
         <v>2</v>
@@ -17963,7 +17963,7 @@
         <v>3.9</v>
       </c>
       <c r="DO39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19234,7 +19234,7 @@
         <v>88</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE42" t="n">
         <v>0.67</v>
@@ -19267,7 +19267,7 @@
         <v>2.02</v>
       </c>
       <c r="DO42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -23605,7 +23605,7 @@
         <v>1.22</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF52" t="n">
         <v>0.4</v>
@@ -23635,7 +23635,7 @@
         <v>2.56</v>
       </c>
       <c r="DO52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25370,7 +25370,7 @@
         <v>70</v>
       </c>
       <c r="DD56" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DE56" t="n">
         <v>1.4</v>
@@ -25403,7 +25403,7 @@
         <v>4.13</v>
       </c>
       <c r="DO56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28029,7 +28029,7 @@
         <v>1.2</v>
       </c>
       <c r="DE62" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF62" t="n">
         <v>1.17</v>
@@ -28059,7 +28059,7 @@
         <v>3.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31962,7 +31962,7 @@
         <v>54</v>
       </c>
       <c r="DD71" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DE71" t="n">
         <v>0.44</v>
@@ -31995,7 +31995,7 @@
         <v>3.31</v>
       </c>
       <c r="DO71" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -33273,7 +33273,7 @@
         <v>0.44</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF74" t="n">
         <v>0.57</v>
@@ -33303,7 +33303,7 @@
         <v>2.19</v>
       </c>
       <c r="DO74" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -34589,7 +34589,7 @@
         <v>1.11</v>
       </c>
       <c r="DE77" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF77" t="n">
         <v>1.25</v>
@@ -34619,7 +34619,7 @@
         <v>3.5</v>
       </c>
       <c r="DO77" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -37670,7 +37670,7 @@
         <v>60</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE84" t="n">
         <v>1.9</v>
@@ -37703,7 +37703,7 @@
         <v>2.54</v>
       </c>
       <c r="DO84" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP84" t="b">
         <v>0</v>
@@ -38545,7 +38545,7 @@
         <v>1.67</v>
       </c>
       <c r="DE86" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF86" t="n">
         <v>1.5</v>
@@ -38575,7 +38575,7 @@
         <v>3.17</v>
       </c>
       <c r="DO86" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -40410,6 +40410,442 @@
           <t>1.86</t>
         </is>
       </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>10</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Rionegro Águilas</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>46088.875</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" t="n">
+        <v>3</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="n">
+        <v>6</v>
+      </c>
+      <c r="L91" t="n">
+        <v>7</v>
+      </c>
+      <c r="M91" t="n">
+        <v>3</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7</v>
+      </c>
+      <c r="S91" t="n">
+        <v>8</v>
+      </c>
+      <c r="T91" t="n">
+        <v>11</v>
+      </c>
+      <c r="U91" t="n">
+        <v>9</v>
+      </c>
+      <c r="V91" t="n">
+        <v>18</v>
+      </c>
+      <c r="W91" t="n">
+        <v>12</v>
+      </c>
+      <c r="X91" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>Estadio Alberto Grisales</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>Route 45A, Rionegro, Antioquia</t>
+        </is>
+      </c>
+      <c r="AC91" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ91" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR91" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AS91" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT91" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU91" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>2142</v>
+      </c>
+      <c r="BC91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD91" t="n">
+        <v>53</v>
+      </c>
+      <c r="BE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF91" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ91" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM91" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ91" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT91" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV91" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW91" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX91" t="n">
+        <v>64</v>
+      </c>
+      <c r="BY91" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ91" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="CA91" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CB91" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="CC91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR91" t="n">
+        <v>9</v>
+      </c>
+      <c r="CS91" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU91" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV91" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX91" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY91" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ91" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA91" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB91" t="n">
+        <v>21</v>
+      </c>
+      <c r="DC91" t="n">
+        <v>61</v>
+      </c>
+      <c r="DD91" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE91" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DF91" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG91" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DH91" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI91" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DJ91" t="n">
+        <v>46</v>
+      </c>
+      <c r="DK91" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL91" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DM91" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DN91" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DO91" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP91" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ91" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR91" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV91" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW91" t="inlineStr"/>
+      <c r="DX91" t="inlineStr"/>
+      <c r="DY91" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="DZ91" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EA91" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EB91" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EC91" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="ED91" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EE91" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="EF91" t="inlineStr">
+        <is>
+          <t>4.27</t>
+        </is>
+      </c>
+      <c r="EG91" t="inlineStr"/>
+      <c r="EH91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH91" headerRowCount="1">
-  <autoFilter ref="A1:EH91"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH96" headerRowCount="1">
+  <autoFilter ref="A1:EH96"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH91"/>
+  <dimension ref="A1:EH96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2626,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DE4" t="n">
         <v>1.9</v>
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3030,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE5" t="n">
         <v>0.44</v>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3474,10 +3474,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -3910,7 +3910,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DE7" t="n">
         <v>0.78</v>
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DE8" t="n">
         <v>1.2</v>
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4790,7 +4790,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DE9" t="n">
         <v>1.67</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE11" t="n">
         <v>1.9</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6109,7 +6109,7 @@
         <v>1.9</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
         <v>1.82</v>
       </c>
       <c r="DO12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6966,7 +6966,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE14" t="n">
         <v>1.4</v>
@@ -6999,7 +6999,7 @@
         <v>1.99</v>
       </c>
       <c r="DO14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP14" t="b">
         <v>0</v>
@@ -7402,10 +7402,10 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7435,7 +7435,7 @@
         <v>3.19</v>
       </c>
       <c r="DO15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8285,7 +8285,7 @@
         <v>0.44</v>
       </c>
       <c r="DE17" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>2.13</v>
       </c>
       <c r="DO17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -8721,7 +8721,7 @@
         <v>1.33</v>
       </c>
       <c r="DE18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF18" t="n">
         <v>1</v>
@@ -9154,10 +9154,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9187,7 +9187,7 @@
         <v>2.56</v>
       </c>
       <c r="DO19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10026,10 +10026,10 @@
         <v>100</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10059,7 +10059,7 @@
         <v>2.47</v>
       </c>
       <c r="DO21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10473,7 +10473,7 @@
         <v>1.4</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF22" t="n">
         <v>2</v>
@@ -10503,7 +10503,7 @@
         <v>2.27</v>
       </c>
       <c r="DO22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11789,7 +11789,7 @@
         <v>1.11</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -11819,7 +11819,7 @@
         <v>2.57</v>
       </c>
       <c r="DO25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12230,10 +12230,10 @@
         <v>75</v>
       </c>
       <c r="DD26" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -12263,7 +12263,7 @@
         <v>2.13</v>
       </c>
       <c r="DO26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13102,7 +13102,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DE28" t="n">
         <v>1.9</v>
@@ -13135,7 +13135,7 @@
         <v>2.03</v>
       </c>
       <c r="DO28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -13546,7 +13546,7 @@
         <v>75</v>
       </c>
       <c r="DD29" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DE29" t="n">
         <v>1.9</v>
@@ -13579,7 +13579,7 @@
         <v>3.03</v>
       </c>
       <c r="DO29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -13990,7 +13990,7 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE30" t="n">
         <v>1.4</v>
@@ -14023,7 +14023,7 @@
         <v>2.24</v>
       </c>
       <c r="DO30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14862,7 +14862,7 @@
         <v>50</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE32" t="n">
         <v>0.44</v>
@@ -14895,7 +14895,7 @@
         <v>2.62</v>
       </c>
       <c r="DO32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15301,7 +15301,7 @@
         <v>1.2</v>
       </c>
       <c r="DE33" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF33" t="n">
         <v>1</v>
@@ -15331,7 +15331,7 @@
         <v>2.29</v>
       </c>
       <c r="DO33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -15745,7 +15745,7 @@
         <v>1.9</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF34" t="n">
         <v>1.67</v>
@@ -15775,7 +15775,7 @@
         <v>2.49</v>
       </c>
       <c r="DO34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -16178,7 +16178,7 @@
         <v>67</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE35" t="n">
         <v>1.33</v>
@@ -16614,7 +16614,7 @@
         <v>84</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE36" t="n">
         <v>0.78</v>
@@ -17494,10 +17494,10 @@
         <v>67</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF38" t="n">
         <v>0.67</v>
@@ -17527,7 +17527,7 @@
         <v>2.42</v>
       </c>
       <c r="DO38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -17930,10 +17930,10 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE39" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DF39" t="n">
         <v>3</v>
@@ -17963,7 +17963,7 @@
         <v>3.9</v>
       </c>
       <c r="DO39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -18366,10 +18366,10 @@
         <v>88</v>
       </c>
       <c r="DD40" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF40" t="n">
         <v>2.25</v>
@@ -18399,7 +18399,7 @@
         <v>2.56</v>
       </c>
       <c r="DO40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP40" t="b">
         <v>0</v>
@@ -19237,7 +19237,7 @@
         <v>1.33</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF42" t="n">
         <v>1.25</v>
@@ -19673,7 +19673,7 @@
         <v>1.67</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF43" t="n">
         <v>2</v>
@@ -20522,7 +20522,7 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DE45" t="n">
         <v>0.44</v>
@@ -21405,7 +21405,7 @@
         <v>1.2</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF47" t="n">
         <v>1.5</v>
@@ -21435,7 +21435,7 @@
         <v>2.48</v>
       </c>
       <c r="DO47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP47" t="b">
         <v>0</v>
@@ -21826,10 +21826,10 @@
         <v>59</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF48" t="n">
         <v>1.33</v>
@@ -21859,7 +21859,7 @@
         <v>1.75</v>
       </c>
       <c r="DO48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -22270,7 +22270,7 @@
         <v>80</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE49" t="n">
         <v>0.78</v>
@@ -22714,10 +22714,10 @@
         <v>60</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE50" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF50" t="n">
         <v>1.8</v>
@@ -22747,7 +22747,7 @@
         <v>1.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -23158,7 +23158,7 @@
         <v>60</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE51" t="n">
         <v>1.67</v>
@@ -23191,7 +23191,7 @@
         <v>2.38</v>
       </c>
       <c r="DO51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP51" t="b">
         <v>0</v>
@@ -23602,7 +23602,7 @@
         <v>70</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE52" t="n">
         <v>1.33</v>
@@ -24477,7 +24477,7 @@
         <v>0.44</v>
       </c>
       <c r="DE54" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF54" t="n">
         <v>0.2</v>
@@ -24929,7 +24929,7 @@
         <v>1.9</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF55" t="n">
         <v>1.4</v>
@@ -24959,7 +24959,7 @@
         <v>3.39</v>
       </c>
       <c r="DO55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -25370,7 +25370,7 @@
         <v>70</v>
       </c>
       <c r="DD56" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE56" t="n">
         <v>1.4</v>
@@ -25403,7 +25403,7 @@
         <v>4.13</v>
       </c>
       <c r="DO56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -25806,7 +25806,7 @@
         <v>70</v>
       </c>
       <c r="DD57" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DE57" t="n">
         <v>1.11</v>
@@ -25839,7 +25839,7 @@
         <v>2.74</v>
       </c>
       <c r="DO57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -26250,10 +26250,10 @@
         <v>59</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF58" t="n">
         <v>0.83</v>
@@ -26283,7 +26283,7 @@
         <v>2</v>
       </c>
       <c r="DO58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -26697,7 +26697,7 @@
         <v>0.78</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF59" t="n">
         <v>0.83</v>
@@ -26727,7 +26727,7 @@
         <v>2.53</v>
       </c>
       <c r="DO59" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -27146,7 +27146,7 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DE60" t="n">
         <v>1.9</v>
@@ -27179,7 +27179,7 @@
         <v>2.31</v>
       </c>
       <c r="DO60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -28029,7 +28029,7 @@
         <v>1.2</v>
       </c>
       <c r="DE62" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DF62" t="n">
         <v>1.17</v>
@@ -28059,7 +28059,7 @@
         <v>3.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -28901,7 +28901,7 @@
         <v>0.44</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF64" t="n">
         <v>0.4</v>
@@ -29334,7 +29334,7 @@
         <v>57</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DE65" t="n">
         <v>1.11</v>
@@ -29766,10 +29766,10 @@
         <v>90</v>
       </c>
       <c r="DD66" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE66" t="n">
         <v>1.78</v>
-      </c>
-      <c r="DE66" t="n">
-        <v>2</v>
       </c>
       <c r="DF66" t="n">
         <v>1.8</v>
@@ -29799,7 +29799,7 @@
         <v>3.08</v>
       </c>
       <c r="DO66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -30202,7 +30202,7 @@
         <v>71</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE67" t="n">
         <v>0.78</v>
@@ -30646,10 +30646,10 @@
         <v>62</v>
       </c>
       <c r="DD68" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE68" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF68" t="n">
         <v>0.5</v>
@@ -30679,7 +30679,7 @@
         <v>1.99</v>
       </c>
       <c r="DO68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -31526,7 +31526,7 @@
         <v>55</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE70" t="n">
         <v>1.2</v>
@@ -31559,7 +31559,7 @@
         <v>2.63</v>
       </c>
       <c r="DO70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP70" t="b">
         <v>0</v>
@@ -31962,7 +31962,7 @@
         <v>54</v>
       </c>
       <c r="DD71" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE71" t="n">
         <v>0.44</v>
@@ -31995,7 +31995,7 @@
         <v>3.31</v>
       </c>
       <c r="DO71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -32401,7 +32401,7 @@
         <v>1.9</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF72" t="n">
         <v>2</v>
@@ -32431,7 +32431,7 @@
         <v>2.49</v>
       </c>
       <c r="DO72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -32845,7 +32845,7 @@
         <v>1.11</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -33706,10 +33706,10 @@
         <v>83</v>
       </c>
       <c r="DD75" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF75" t="n">
         <v>1.67</v>
@@ -33739,7 +33739,7 @@
         <v>2.17</v>
       </c>
       <c r="DO75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -34142,7 +34142,7 @@
         <v>65</v>
       </c>
       <c r="DD76" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE76" t="n">
         <v>1.67</v>
@@ -34589,7 +34589,7 @@
         <v>1.11</v>
       </c>
       <c r="DE77" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DF77" t="n">
         <v>1.25</v>
@@ -34619,7 +34619,7 @@
         <v>3.5</v>
       </c>
       <c r="DO77" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -35022,10 +35022,10 @@
         <v>61</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF78" t="n">
         <v>1</v>
@@ -35055,7 +35055,7 @@
         <v>2.25</v>
       </c>
       <c r="DO78" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -35905,7 +35905,7 @@
         <v>0.44</v>
       </c>
       <c r="DE80" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DF80" t="n">
         <v>0.43</v>
@@ -35935,7 +35935,7 @@
         <v>2.69</v>
       </c>
       <c r="DO80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -36346,10 +36346,10 @@
         <v>93</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF81" t="n">
         <v>1.43</v>
@@ -36379,7 +36379,7 @@
         <v>2.39</v>
       </c>
       <c r="DO81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -36793,7 +36793,7 @@
         <v>0.78</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF82" t="n">
         <v>0.88</v>
@@ -36823,7 +36823,7 @@
         <v>2.82</v>
       </c>
       <c r="DO82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -37234,10 +37234,10 @@
         <v>82</v>
       </c>
       <c r="DD83" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF83" t="n">
         <v>1.88</v>
@@ -37267,7 +37267,7 @@
         <v>2.12</v>
       </c>
       <c r="DO83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -38545,7 +38545,7 @@
         <v>1.67</v>
       </c>
       <c r="DE86" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DF86" t="n">
         <v>1.5</v>
@@ -38575,7 +38575,7 @@
         <v>3.17</v>
       </c>
       <c r="DO86" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -38981,7 +38981,7 @@
         <v>1.4</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF87" t="n">
         <v>1.22</v>
@@ -39011,7 +39011,7 @@
         <v>2.24</v>
       </c>
       <c r="DO87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -39414,7 +39414,7 @@
         <v>60</v>
       </c>
       <c r="DD88" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE88" t="n">
         <v>1.9</v>
@@ -39447,7 +39447,7 @@
         <v>2.31</v>
       </c>
       <c r="DO88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -39858,7 +39858,7 @@
         <v>75</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DE89" t="n">
         <v>0.44</v>
@@ -40749,7 +40749,7 @@
         <v>1.33</v>
       </c>
       <c r="DE91" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DF91" t="n">
         <v>1.5</v>
@@ -40779,7 +40779,7 @@
         <v>3.05</v>
       </c>
       <c r="DO91" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -40846,6 +40846,2218 @@
       </c>
       <c r="EG91" t="inlineStr"/>
       <c r="EH91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>16</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Llaneros</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Jaguares de Córdoba</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>46090.875</v>
+      </c>
+      <c r="G92" t="n">
+        <v>2</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>2</v>
+      </c>
+      <c r="J92" t="n">
+        <v>2</v>
+      </c>
+      <c r="K92" t="n">
+        <v>7</v>
+      </c>
+      <c r="L92" t="n">
+        <v>9</v>
+      </c>
+      <c r="M92" t="n">
+        <v>2</v>
+      </c>
+      <c r="N92" t="n">
+        <v>4</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>2</v>
+      </c>
+      <c r="R92" t="n">
+        <v>4</v>
+      </c>
+      <c r="S92" t="n">
+        <v>9</v>
+      </c>
+      <c r="T92" t="n">
+        <v>11</v>
+      </c>
+      <c r="U92" t="n">
+        <v>11</v>
+      </c>
+      <c r="V92" t="n">
+        <v>15</v>
+      </c>
+      <c r="W92" t="n">
+        <v>21</v>
+      </c>
+      <c r="X92" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Calle Lombana</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>, Villavicencio</t>
+        </is>
+      </c>
+      <c r="AC92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ92" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR92" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS92" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AT92" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB92" t="n">
+        <v>2159</v>
+      </c>
+      <c r="BC92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD92" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ92" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL92" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM92" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN92" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR92" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT92" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV92" t="n">
+        <v>31</v>
+      </c>
+      <c r="BW92" t="n">
+        <v>32</v>
+      </c>
+      <c r="BX92" t="n">
+        <v>66</v>
+      </c>
+      <c r="BY92" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ92" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CA92" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CB92" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="CC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR92" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS92" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU92" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV92" t="n">
+        <v>21</v>
+      </c>
+      <c r="CW92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX92" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY92" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ92" t="n">
+        <v>39</v>
+      </c>
+      <c r="DA92" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB92" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC92" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD92" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DE92" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF92" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DG92" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DH92" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DI92" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DJ92" t="n">
+        <v>61</v>
+      </c>
+      <c r="DK92" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL92" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="DM92" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DN92" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DO92" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP92" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ92" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW92" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="DX92" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="DY92" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="DZ92" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EA92" t="inlineStr">
+        <is>
+          <t>4.37</t>
+        </is>
+      </c>
+      <c r="EB92" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EC92" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="ED92" t="inlineStr">
+        <is>
+          <t>4.26</t>
+        </is>
+      </c>
+      <c r="EE92" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EF92" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EG92" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EH92" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>10</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>46090.97222222222</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>2</v>
+      </c>
+      <c r="J93" t="n">
+        <v>5</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="n">
+        <v>6</v>
+      </c>
+      <c r="M93" t="n">
+        <v>2</v>
+      </c>
+      <c r="N93" t="n">
+        <v>5</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>5</v>
+      </c>
+      <c r="R93" t="n">
+        <v>2</v>
+      </c>
+      <c r="S93" t="n">
+        <v>16</v>
+      </c>
+      <c r="T93" t="n">
+        <v>2</v>
+      </c>
+      <c r="U93" t="n">
+        <v>21</v>
+      </c>
+      <c r="V93" t="n">
+        <v>4</v>
+      </c>
+      <c r="W93" t="n">
+        <v>12</v>
+      </c>
+      <c r="X93" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>Estadio Nemesio Camacho El Campín</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AC93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>2136</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>84</v>
+      </c>
+      <c r="BE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF93" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK93" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN93" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS93" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV93" t="n">
+        <v>10</v>
+      </c>
+      <c r="BW93" t="n">
+        <v>14</v>
+      </c>
+      <c r="BX93" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY93" t="n">
+        <v>72</v>
+      </c>
+      <c r="BZ93" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CA93" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="CB93" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR93" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS93" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU93" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV93" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CY93" t="n">
+        <v>18</v>
+      </c>
+      <c r="CZ93" t="n">
+        <v>73</v>
+      </c>
+      <c r="DA93" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB93" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC93" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD93" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DE93" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DF93" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DG93" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH93" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DI93" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DJ93" t="n">
+        <v>28</v>
+      </c>
+      <c r="DK93" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL93" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM93" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="DN93" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="DO93" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP93" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ93" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW93" t="inlineStr"/>
+      <c r="DX93" t="inlineStr"/>
+      <c r="DY93" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="DZ93" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EA93" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EB93" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EC93" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="ED93" t="inlineStr">
+        <is>
+          <t>11.29</t>
+        </is>
+      </c>
+      <c r="EE93" t="inlineStr">
+        <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="EF93" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EG93" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EH93" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>10</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>46091.0625</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>2</v>
+      </c>
+      <c r="J94" t="n">
+        <v>2</v>
+      </c>
+      <c r="K94" t="n">
+        <v>5</v>
+      </c>
+      <c r="L94" t="n">
+        <v>7</v>
+      </c>
+      <c r="M94" t="n">
+        <v>5</v>
+      </c>
+      <c r="N94" t="n">
+        <v>4</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>3</v>
+      </c>
+      <c r="R94" t="n">
+        <v>2</v>
+      </c>
+      <c r="S94" t="n">
+        <v>7</v>
+      </c>
+      <c r="T94" t="n">
+        <v>12</v>
+      </c>
+      <c r="U94" t="n">
+        <v>10</v>
+      </c>
+      <c r="V94" t="n">
+        <v>14</v>
+      </c>
+      <c r="W94" t="n">
+        <v>8</v>
+      </c>
+      <c r="X94" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>68</v>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>Estadio Departamental Libertad</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>Carrera 8, San Juan de Pasto</t>
+        </is>
+      </c>
+      <c r="AC94" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>2143</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF94" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL94" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN94" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP94" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS94" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT94" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV94" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW94" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX94" t="n">
+        <v>54</v>
+      </c>
+      <c r="BY94" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ94" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CA94" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CB94" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR94" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS94" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU94" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV94" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX94" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY94" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ94" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA94" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB94" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC94" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD94" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DE94" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DF94" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG94" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH94" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI94" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ94" t="n">
+        <v>41</v>
+      </c>
+      <c r="DK94" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL94" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM94" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DN94" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="DO94" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP94" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ94" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW94" t="inlineStr"/>
+      <c r="DX94" t="inlineStr"/>
+      <c r="DY94" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="DZ94" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EA94" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="EB94" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EC94" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="ED94" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="EE94" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="EF94" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EG94" t="inlineStr"/>
+      <c r="EH94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>10</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>46091.97222222222</v>
+      </c>
+      <c r="G95" t="n">
+        <v>3</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>3</v>
+      </c>
+      <c r="J95" t="n">
+        <v>8</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="n">
+        <v>9</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1</v>
+      </c>
+      <c r="N95" t="n">
+        <v>4</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>5</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
+      <c r="S95" t="n">
+        <v>15</v>
+      </c>
+      <c r="T95" t="n">
+        <v>4</v>
+      </c>
+      <c r="U95" t="n">
+        <v>20</v>
+      </c>
+      <c r="V95" t="n">
+        <v>5</v>
+      </c>
+      <c r="W95" t="n">
+        <v>11</v>
+      </c>
+      <c r="X95" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>Estadio Alfonso López</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>Carrera 36 Nº 53-12, Cabecera del Llano, Bucaramanga</t>
+        </is>
+      </c>
+      <c r="AC95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ95" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT95" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AU95" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>2139</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI95" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM95" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN95" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR95" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT95" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV95" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW95" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX95" t="n">
+        <v>112</v>
+      </c>
+      <c r="BY95" t="n">
+        <v>43</v>
+      </c>
+      <c r="BZ95" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CA95" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="CB95" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR95" t="n">
+        <v>10</v>
+      </c>
+      <c r="CS95" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU95" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV95" t="n">
+        <v>3</v>
+      </c>
+      <c r="CW95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX95" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY95" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ95" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA95" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB95" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC95" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD95" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DE95" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DF95" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG95" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH95" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DI95" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DJ95" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK95" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL95" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DM95" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DN95" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="DO95" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW95" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="DX95" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="DY95" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="DZ95" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EA95" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EB95" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EC95" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="ED95" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="EE95" t="inlineStr">
+        <is>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="EF95" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EG95" t="inlineStr"/>
+      <c r="EH95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>3</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>46092.0625</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>4</v>
+      </c>
+      <c r="I96" t="n">
+        <v>4</v>
+      </c>
+      <c r="J96" t="n">
+        <v>3</v>
+      </c>
+      <c r="K96" t="n">
+        <v>4</v>
+      </c>
+      <c r="L96" t="n">
+        <v>7</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>2</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6</v>
+      </c>
+      <c r="S96" t="n">
+        <v>2</v>
+      </c>
+      <c r="T96" t="n">
+        <v>10</v>
+      </c>
+      <c r="U96" t="n">
+        <v>4</v>
+      </c>
+      <c r="V96" t="n">
+        <v>16</v>
+      </c>
+      <c r="W96" t="n">
+        <v>12</v>
+      </c>
+      <c r="X96" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>Estadio Metropolitano Roberto Meléndez</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>Intersección de la Avenida Circunvalar con la Calle 45, Barranquilla</t>
+        </is>
+      </c>
+      <c r="AC96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>2142</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF96" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ96" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM96" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV96" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW96" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX96" t="n">
+        <v>57</v>
+      </c>
+      <c r="BY96" t="n">
+        <v>105</v>
+      </c>
+      <c r="BZ96" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="CA96" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CB96" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR96" t="n">
+        <v>8</v>
+      </c>
+      <c r="CS96" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU96" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV96" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX96" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY96" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ96" t="n">
+        <v>71</v>
+      </c>
+      <c r="DA96" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB96" t="n">
+        <v>41</v>
+      </c>
+      <c r="DC96" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD96" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE96" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DF96" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DG96" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DH96" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DI96" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DJ96" t="n">
+        <v>29</v>
+      </c>
+      <c r="DK96" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL96" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DM96" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DN96" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="DO96" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP96" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ96" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR96" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS96" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW96" t="inlineStr"/>
+      <c r="DX96" t="inlineStr"/>
+      <c r="DY96" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="DZ96" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EA96" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EB96" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EC96" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="ED96" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EE96" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EF96" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EG96" t="inlineStr"/>
+      <c r="EH96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH96" headerRowCount="1">
-  <autoFilter ref="A1:EH96"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH98" headerRowCount="1">
+  <autoFilter ref="A1:EH98"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH96"/>
+  <dimension ref="A1:EH98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1749,7 +1749,7 @@
         <v>0.44</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -3030,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DE5" t="n">
         <v>0.44</v>
@@ -3910,7 +3910,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="DE7" t="n">
         <v>0.78</v>
@@ -5665,7 +5665,7 @@
         <v>0.6</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -7402,7 +7402,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE15" t="n">
         <v>1.89</v>
@@ -8721,7 +8721,7 @@
         <v>1.33</v>
       </c>
       <c r="DE18" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="DF18" t="n">
         <v>1</v>
@@ -9590,7 +9590,7 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DE20" t="n">
         <v>1.11</v>
@@ -10473,7 +10473,7 @@
         <v>1.4</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF22" t="n">
         <v>2</v>
@@ -12230,7 +12230,7 @@
         <v>75</v>
       </c>
       <c r="DD26" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="DE26" t="n">
         <v>1.4</v>
@@ -13549,7 +13549,7 @@
         <v>1.78</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -15301,7 +15301,7 @@
         <v>1.2</v>
       </c>
       <c r="DE33" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="DF33" t="n">
         <v>1</v>
@@ -15742,7 +15742,7 @@
         <v>59</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DE34" t="n">
         <v>1</v>
@@ -16178,7 +16178,7 @@
         <v>67</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE35" t="n">
         <v>1.33</v>
@@ -17930,7 +17930,7 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DE39" t="n">
         <v>1.78</v>
@@ -18366,7 +18366,7 @@
         <v>88</v>
       </c>
       <c r="DD40" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="DE40" t="n">
         <v>1.89</v>
@@ -19673,7 +19673,7 @@
         <v>1.67</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF43" t="n">
         <v>2</v>
@@ -20961,7 +20961,7 @@
         <v>0.44</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF46" t="n">
         <v>0.25</v>
@@ -22714,10 +22714,10 @@
         <v>60</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE50" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="DF50" t="n">
         <v>1.8</v>
@@ -22747,7 +22747,7 @@
         <v>1.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24926,7 +24926,7 @@
         <v>80</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DE55" t="n">
         <v>1.6</v>
@@ -25370,7 +25370,7 @@
         <v>70</v>
       </c>
       <c r="DD56" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DE56" t="n">
         <v>1.4</v>
@@ -25403,7 +25403,7 @@
         <v>4.13</v>
       </c>
       <c r="DO56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -26253,7 +26253,7 @@
         <v>1.4</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF58" t="n">
         <v>0.83</v>
@@ -27146,7 +27146,7 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="DE60" t="n">
         <v>1.9</v>
@@ -27593,7 +27593,7 @@
         <v>1.67</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF61" t="n">
         <v>1.5</v>
@@ -28029,7 +28029,7 @@
         <v>1.2</v>
       </c>
       <c r="DE62" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DF62" t="n">
         <v>1.17</v>
@@ -28059,7 +28059,7 @@
         <v>3.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30202,7 +30202,7 @@
         <v>71</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE67" t="n">
         <v>0.78</v>
@@ -30649,7 +30649,7 @@
         <v>0.44</v>
       </c>
       <c r="DE68" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="DF68" t="n">
         <v>0.5</v>
@@ -31090,7 +31090,7 @@
         <v>57</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DE69" t="n">
         <v>1.4</v>
@@ -31962,7 +31962,7 @@
         <v>54</v>
       </c>
       <c r="DD71" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DE71" t="n">
         <v>0.44</v>
@@ -34589,7 +34589,7 @@
         <v>1.11</v>
       </c>
       <c r="DE77" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DF77" t="n">
         <v>1.25</v>
@@ -35458,7 +35458,7 @@
         <v>63</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DE79" t="n">
         <v>0.44</v>
@@ -37234,7 +37234,7 @@
         <v>82</v>
       </c>
       <c r="DD83" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="DE83" t="n">
         <v>0.6</v>
@@ -38545,7 +38545,7 @@
         <v>1.67</v>
       </c>
       <c r="DE86" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DF86" t="n">
         <v>1.5</v>
@@ -39414,7 +39414,7 @@
         <v>60</v>
       </c>
       <c r="DD88" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE88" t="n">
         <v>1.9</v>
@@ -40305,7 +40305,7 @@
         <v>1.2</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF90" t="n">
         <v>1.33</v>
@@ -40749,7 +40749,7 @@
         <v>1.33</v>
       </c>
       <c r="DE91" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DF91" t="n">
         <v>1.5</v>
@@ -41182,7 +41182,7 @@
         <v>73</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE92" t="n">
         <v>1</v>
@@ -42078,7 +42078,7 @@
         <v>78</v>
       </c>
       <c r="DD94" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="DE94" t="n">
         <v>1.78</v>
@@ -42961,7 +42961,7 @@
         <v>1.6</v>
       </c>
       <c r="DE96" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DF96" t="n">
         <v>1.78</v>
@@ -42991,7 +42991,7 @@
         <v>3.39</v>
       </c>
       <c r="DO96" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -43058,6 +43058,886 @@
       </c>
       <c r="EG96" t="inlineStr"/>
       <c r="EH96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>11</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>46094.97222222222</v>
+      </c>
+      <c r="G97" t="n">
+        <v>4</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2</v>
+      </c>
+      <c r="I97" t="n">
+        <v>6</v>
+      </c>
+      <c r="J97" t="n">
+        <v>2</v>
+      </c>
+      <c r="K97" t="n">
+        <v>7</v>
+      </c>
+      <c r="L97" t="n">
+        <v>9</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1</v>
+      </c>
+      <c r="N97" t="n">
+        <v>4</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>7</v>
+      </c>
+      <c r="R97" t="n">
+        <v>5</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="n">
+        <v>16</v>
+      </c>
+      <c r="U97" t="n">
+        <v>12</v>
+      </c>
+      <c r="V97" t="n">
+        <v>21</v>
+      </c>
+      <c r="W97" t="n">
+        <v>4</v>
+      </c>
+      <c r="X97" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>Estadio Palogrande</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>Carrera 24 # 64 - 00, Manizales</t>
+        </is>
+      </c>
+      <c r="AC97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ97" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR97" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS97" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT97" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU97" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ97" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB97" t="n">
+        <v>2135</v>
+      </c>
+      <c r="BC97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF97" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ97" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL97" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM97" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN97" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR97" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT97" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV97" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW97" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX97" t="n">
+        <v>101</v>
+      </c>
+      <c r="BY97" t="n">
+        <v>97</v>
+      </c>
+      <c r="BZ97" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CA97" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CB97" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CC97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR97" t="n">
+        <v>4</v>
+      </c>
+      <c r="CS97" t="n">
+        <v>7</v>
+      </c>
+      <c r="CT97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU97" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV97" t="n">
+        <v>4</v>
+      </c>
+      <c r="CW97" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX97" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY97" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ97" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA97" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB97" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC97" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD97" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE97" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DF97" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DG97" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DH97" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DI97" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DJ97" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK97" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL97" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DM97" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DN97" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="DO97" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP97" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ97" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR97" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS97" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT97" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU97" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV97" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW97" t="inlineStr"/>
+      <c r="DX97" t="inlineStr"/>
+      <c r="DY97" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="DZ97" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EA97" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="EB97" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EC97" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="ED97" t="inlineStr">
+        <is>
+          <t>5.12</t>
+        </is>
+      </c>
+      <c r="EE97" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="EF97" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EG97" t="inlineStr"/>
+      <c r="EH97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>11</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Llaneros</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>46095.0625</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>2</v>
+      </c>
+      <c r="J98" t="n">
+        <v>5</v>
+      </c>
+      <c r="K98" t="n">
+        <v>4</v>
+      </c>
+      <c r="L98" t="n">
+        <v>9</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1</v>
+      </c>
+      <c r="N98" t="n">
+        <v>2</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>3</v>
+      </c>
+      <c r="R98" t="n">
+        <v>2</v>
+      </c>
+      <c r="S98" t="n">
+        <v>7</v>
+      </c>
+      <c r="T98" t="n">
+        <v>16</v>
+      </c>
+      <c r="U98" t="n">
+        <v>10</v>
+      </c>
+      <c r="V98" t="n">
+        <v>18</v>
+      </c>
+      <c r="W98" t="n">
+        <v>8</v>
+      </c>
+      <c r="X98" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>Estadio Atanasio Girardot</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
+        </is>
+      </c>
+      <c r="AC98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ98" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR98" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT98" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AU98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB98" t="n">
+        <v>2142</v>
+      </c>
+      <c r="BC98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD98" t="n">
+        <v>52</v>
+      </c>
+      <c r="BE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT98" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV98" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW98" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX98" t="n">
+        <v>77</v>
+      </c>
+      <c r="BY98" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ98" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CA98" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CB98" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="CC98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR98" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS98" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU98" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV98" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX98" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY98" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ98" t="n">
+        <v>49</v>
+      </c>
+      <c r="DA98" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB98" t="n">
+        <v>21</v>
+      </c>
+      <c r="DC98" t="n">
+        <v>74</v>
+      </c>
+      <c r="DD98" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DE98" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DF98" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DG98" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DH98" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DI98" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ98" t="n">
+        <v>51</v>
+      </c>
+      <c r="DK98" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL98" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DM98" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="DN98" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="DO98" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW98" t="inlineStr"/>
+      <c r="DX98" t="inlineStr"/>
+      <c r="DY98" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="DZ98" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EA98" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EB98" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EC98" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="ED98" t="inlineStr">
+        <is>
+          <t>9.76</t>
+        </is>
+      </c>
+      <c r="EE98" t="inlineStr">
+        <is>
+          <t>4.97</t>
+        </is>
+      </c>
+      <c r="EF98" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EG98" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EH98" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH98" headerRowCount="1">
-  <autoFilter ref="A1:EH98"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH106" headerRowCount="1">
+  <autoFilter ref="A1:EH106"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH98"/>
+  <dimension ref="A1:EH106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1746,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE2" t="n">
         <v>1.27</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2182,10 +2182,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2626,10 +2626,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3033,7 +3033,7 @@
         <v>2.4</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3474,10 +3474,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -3913,7 +3913,7 @@
         <v>1.91</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4346,10 +4346,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4790,11 +4790,11 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DE9" t="n">
         <v>1.6</v>
       </c>
-      <c r="DE9" t="n">
-        <v>1.67</v>
-      </c>
       <c r="DF9" t="n">
         <v>0</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DE11" t="n">
         <v>2</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6106,10 +6106,10 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
         <v>1.82</v>
       </c>
       <c r="DO12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6522,10 +6522,10 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6555,7 +6555,7 @@
         <v>1.86</v>
       </c>
       <c r="DO13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -6966,10 +6966,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -6999,7 +6999,7 @@
         <v>1.99</v>
       </c>
       <c r="DO14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP14" t="b">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>1.27</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7435,7 +7435,7 @@
         <v>3.19</v>
       </c>
       <c r="DO15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -7854,10 +7854,10 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -7887,7 +7887,7 @@
         <v>2.53</v>
       </c>
       <c r="DO16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8282,10 +8282,10 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>2.13</v>
       </c>
       <c r="DO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -8718,7 +8718,7 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE18" t="n">
         <v>1.91</v>
@@ -8751,7 +8751,7 @@
         <v>1.44</v>
       </c>
       <c r="DO18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9154,10 +9154,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9187,7 +9187,7 @@
         <v>2.56</v>
       </c>
       <c r="DO19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9593,7 +9593,7 @@
         <v>2</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -9623,7 +9623,7 @@
         <v>4.47</v>
       </c>
       <c r="DO20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10026,10 +10026,10 @@
         <v>100</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10059,7 +10059,7 @@
         <v>2.47</v>
       </c>
       <c r="DO21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10470,7 +10470,7 @@
         <v>25</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE22" t="n">
         <v>1.27</v>
@@ -10503,7 +10503,7 @@
         <v>2.27</v>
       </c>
       <c r="DO22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -10914,10 +10914,10 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DF23" t="n">
         <v>0</v>
@@ -10947,7 +10947,7 @@
         <v>2.38</v>
       </c>
       <c r="DO23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11350,10 +11350,10 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -11383,7 +11383,7 @@
         <v>1.88</v>
       </c>
       <c r="DO24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -11786,10 +11786,10 @@
         <v>25</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -11819,7 +11819,7 @@
         <v>2.57</v>
       </c>
       <c r="DO25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12233,7 +12233,7 @@
         <v>1.91</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -12263,7 +12263,7 @@
         <v>2.13</v>
       </c>
       <c r="DO26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -12666,10 +12666,10 @@
         <v>75</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DF27" t="n">
         <v>0.5</v>
@@ -12699,7 +12699,7 @@
         <v>2.21</v>
       </c>
       <c r="DO27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13102,10 +13102,10 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -13135,7 +13135,7 @@
         <v>2.03</v>
       </c>
       <c r="DO28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -13546,7 +13546,7 @@
         <v>75</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="DE29" t="n">
         <v>2</v>
@@ -13579,7 +13579,7 @@
         <v>3.03</v>
       </c>
       <c r="DO29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -13990,10 +13990,10 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF30" t="n">
         <v>0.33</v>
@@ -14023,7 +14023,7 @@
         <v>2.24</v>
       </c>
       <c r="DO30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14418,10 +14418,10 @@
         <v>67</v>
       </c>
       <c r="DD31" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF31" t="n">
         <v>0.33</v>
@@ -14451,7 +14451,7 @@
         <v>2.8</v>
       </c>
       <c r="DO31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -14862,10 +14862,10 @@
         <v>50</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DE32" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DF32" t="n">
         <v>1.67</v>
@@ -14895,7 +14895,7 @@
         <v>2.62</v>
       </c>
       <c r="DO32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15298,7 +15298,7 @@
         <v>50</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DE33" t="n">
         <v>1.91</v>
@@ -15331,7 +15331,7 @@
         <v>2.29</v>
       </c>
       <c r="DO33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -15745,7 +15745,7 @@
         <v>2</v>
       </c>
       <c r="DE34" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF34" t="n">
         <v>1.67</v>
@@ -15775,7 +15775,7 @@
         <v>2.49</v>
       </c>
       <c r="DO34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -16181,7 +16181,7 @@
         <v>1.27</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DF35" t="n">
         <v>1.67</v>
@@ -16211,7 +16211,7 @@
         <v>2.16</v>
       </c>
       <c r="DO35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -16614,10 +16614,10 @@
         <v>84</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF36" t="n">
         <v>0</v>
@@ -16647,7 +16647,7 @@
         <v>2.84</v>
       </c>
       <c r="DO36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP36" t="b">
         <v>0</v>
@@ -17050,10 +17050,10 @@
         <v>84</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DF37" t="n">
         <v>2</v>
@@ -17083,7 +17083,7 @@
         <v>2.43</v>
       </c>
       <c r="DO37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -17494,10 +17494,10 @@
         <v>67</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF38" t="n">
         <v>0.67</v>
@@ -17527,7 +17527,7 @@
         <v>2.42</v>
       </c>
       <c r="DO38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -17933,7 +17933,7 @@
         <v>2.4</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="DF39" t="n">
         <v>3</v>
@@ -17963,7 +17963,7 @@
         <v>3.9</v>
       </c>
       <c r="DO39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -18369,7 +18369,7 @@
         <v>1.91</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DF40" t="n">
         <v>2.25</v>
@@ -18399,7 +18399,7 @@
         <v>2.56</v>
       </c>
       <c r="DO40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP40" t="b">
         <v>0</v>
@@ -18798,10 +18798,10 @@
         <v>63</v>
       </c>
       <c r="DD41" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DE41" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DF41" t="n">
         <v>0.5</v>
@@ -18831,7 +18831,7 @@
         <v>2.9</v>
       </c>
       <c r="DO41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -19234,10 +19234,10 @@
         <v>88</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DF42" t="n">
         <v>1.25</v>
@@ -19267,7 +19267,7 @@
         <v>2.02</v>
       </c>
       <c r="DO42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -19670,7 +19670,7 @@
         <v>63</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DE43" t="n">
         <v>1.27</v>
@@ -19703,7 +19703,7 @@
         <v>1.9</v>
       </c>
       <c r="DO43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20106,10 +20106,10 @@
         <v>50</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF44" t="n">
         <v>1.5</v>
@@ -20139,7 +20139,7 @@
         <v>3.37</v>
       </c>
       <c r="DO44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -20522,10 +20522,10 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="DF45" t="n">
         <v>2</v>
@@ -20555,7 +20555,7 @@
         <v>2.5</v>
       </c>
       <c r="DO45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -20958,7 +20958,7 @@
         <v>50</v>
       </c>
       <c r="DD46" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DE46" t="n">
         <v>2</v>
@@ -20991,7 +20991,7 @@
         <v>2.87</v>
       </c>
       <c r="DO46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -21402,10 +21402,10 @@
         <v>63</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF47" t="n">
         <v>1.5</v>
@@ -21435,7 +21435,7 @@
         <v>2.48</v>
       </c>
       <c r="DO47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP47" t="b">
         <v>0</v>
@@ -21826,10 +21826,10 @@
         <v>59</v>
       </c>
       <c r="DD48" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF48" t="n">
         <v>1.33</v>
@@ -21859,7 +21859,7 @@
         <v>1.75</v>
       </c>
       <c r="DO48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -22270,10 +22270,10 @@
         <v>80</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DE49" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF49" t="n">
         <v>0.4</v>
@@ -22303,7 +22303,7 @@
         <v>2.37</v>
       </c>
       <c r="DO49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -23158,10 +23158,10 @@
         <v>60</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DF51" t="n">
         <v>1.8</v>
@@ -23191,7 +23191,7 @@
         <v>2.38</v>
       </c>
       <c r="DO51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP51" t="b">
         <v>0</v>
@@ -23602,10 +23602,10 @@
         <v>70</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DF52" t="n">
         <v>0.4</v>
@@ -23635,7 +23635,7 @@
         <v>2.56</v>
       </c>
       <c r="DO52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -24046,10 +24046,10 @@
         <v>60</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -24079,7 +24079,7 @@
         <v>2.58</v>
       </c>
       <c r="DO53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -24474,10 +24474,10 @@
         <v>68</v>
       </c>
       <c r="DD54" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="DE54" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF54" t="n">
         <v>0.2</v>
@@ -24507,7 +24507,7 @@
         <v>1.66</v>
       </c>
       <c r="DO54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -24929,7 +24929,7 @@
         <v>2</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF55" t="n">
         <v>1.4</v>
@@ -24959,7 +24959,7 @@
         <v>3.39</v>
       </c>
       <c r="DO55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -25373,7 +25373,7 @@
         <v>2.4</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF56" t="n">
         <v>3</v>
@@ -25806,10 +25806,10 @@
         <v>70</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF57" t="n">
         <v>1.75</v>
@@ -25839,7 +25839,7 @@
         <v>2.74</v>
       </c>
       <c r="DO57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -26250,7 +26250,7 @@
         <v>59</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE58" t="n">
         <v>1.27</v>
@@ -26283,7 +26283,7 @@
         <v>2</v>
       </c>
       <c r="DO58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -26694,10 +26694,10 @@
         <v>64</v>
       </c>
       <c r="DD59" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF59" t="n">
         <v>0.83</v>
@@ -26727,7 +26727,7 @@
         <v>2.53</v>
       </c>
       <c r="DO59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -27149,7 +27149,7 @@
         <v>1.91</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DF60" t="n">
         <v>2.17</v>
@@ -27179,7 +27179,7 @@
         <v>2.31</v>
       </c>
       <c r="DO60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -27590,7 +27590,7 @@
         <v>50</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DE61" t="n">
         <v>2</v>
@@ -27623,7 +27623,7 @@
         <v>2.63</v>
       </c>
       <c r="DO61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -28026,7 +28026,7 @@
         <v>75</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DE62" t="n">
         <v>2.4</v>
@@ -28462,10 +28462,10 @@
         <v>59</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="DF63" t="n">
         <v>1.17</v>
@@ -28495,7 +28495,7 @@
         <v>2.4</v>
       </c>
       <c r="DO63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -28898,10 +28898,10 @@
         <v>60</v>
       </c>
       <c r="DD64" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DF64" t="n">
         <v>0.4</v>
@@ -28931,7 +28931,7 @@
         <v>1.97</v>
       </c>
       <c r="DO64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -29334,10 +29334,10 @@
         <v>57</v>
       </c>
       <c r="DD65" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF65" t="n">
         <v>1.4</v>
@@ -29367,7 +29367,7 @@
         <v>2.22</v>
       </c>
       <c r="DO65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -29766,10 +29766,10 @@
         <v>90</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="DF66" t="n">
         <v>1.8</v>
@@ -29799,7 +29799,7 @@
         <v>3.08</v>
       </c>
       <c r="DO66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -30205,7 +30205,7 @@
         <v>1.27</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF67" t="n">
         <v>1.29</v>
@@ -30235,7 +30235,7 @@
         <v>2.55</v>
       </c>
       <c r="DO67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -30646,7 +30646,7 @@
         <v>62</v>
       </c>
       <c r="DD68" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE68" t="n">
         <v>1.91</v>
@@ -30679,7 +30679,7 @@
         <v>1.99</v>
       </c>
       <c r="DO68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -31093,7 +31093,7 @@
         <v>2</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF69" t="n">
         <v>1.43</v>
@@ -31123,7 +31123,7 @@
         <v>3.02</v>
       </c>
       <c r="DO69" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -31526,10 +31526,10 @@
         <v>55</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DF70" t="n">
         <v>1.67</v>
@@ -31559,7 +31559,7 @@
         <v>2.63</v>
       </c>
       <c r="DO70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP70" t="b">
         <v>0</v>
@@ -31965,7 +31965,7 @@
         <v>2.4</v>
       </c>
       <c r="DE71" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DF71" t="n">
         <v>2.25</v>
@@ -31995,7 +31995,7 @@
         <v>3.31</v>
       </c>
       <c r="DO71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -32398,10 +32398,10 @@
         <v>64</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF72" t="n">
         <v>2</v>
@@ -32431,7 +32431,7 @@
         <v>2.49</v>
       </c>
       <c r="DO72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -32842,10 +32842,10 @@
         <v>72</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -32875,7 +32875,7 @@
         <v>3.26</v>
       </c>
       <c r="DO73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -33270,10 +33270,10 @@
         <v>69</v>
       </c>
       <c r="DD74" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DF74" t="n">
         <v>0.57</v>
@@ -33303,7 +33303,7 @@
         <v>2.19</v>
       </c>
       <c r="DO74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -33706,10 +33706,10 @@
         <v>83</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="DE75" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF75" t="n">
         <v>1.67</v>
@@ -33739,7 +33739,7 @@
         <v>2.17</v>
       </c>
       <c r="DO75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -34142,10 +34142,10 @@
         <v>65</v>
       </c>
       <c r="DD76" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DF76" t="n">
         <v>0.43</v>
@@ -34175,7 +34175,7 @@
         <v>2.09</v>
       </c>
       <c r="DO76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -34586,7 +34586,7 @@
         <v>65</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DE77" t="n">
         <v>2.4</v>
@@ -34619,7 +34619,7 @@
         <v>3.5</v>
       </c>
       <c r="DO77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -35022,10 +35022,10 @@
         <v>61</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF78" t="n">
         <v>1</v>
@@ -35055,7 +35055,7 @@
         <v>2.25</v>
       </c>
       <c r="DO78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -35461,7 +35461,7 @@
         <v>2</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="DF79" t="n">
         <v>1.63</v>
@@ -35491,7 +35491,7 @@
         <v>2.48</v>
       </c>
       <c r="DO79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -35902,10 +35902,10 @@
         <v>65</v>
       </c>
       <c r="DD80" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="DF80" t="n">
         <v>0.43</v>
@@ -35935,7 +35935,7 @@
         <v>2.69</v>
       </c>
       <c r="DO80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -36346,10 +36346,10 @@
         <v>93</v>
       </c>
       <c r="DD81" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF81" t="n">
         <v>1.43</v>
@@ -36379,7 +36379,7 @@
         <v>2.39</v>
       </c>
       <c r="DO81" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -36790,10 +36790,10 @@
         <v>60</v>
       </c>
       <c r="DD82" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DF82" t="n">
         <v>0.88</v>
@@ -36823,7 +36823,7 @@
         <v>2.82</v>
       </c>
       <c r="DO82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -37237,7 +37237,7 @@
         <v>1.91</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DF83" t="n">
         <v>1.88</v>
@@ -37267,7 +37267,7 @@
         <v>2.12</v>
       </c>
       <c r="DO83" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -37670,10 +37670,10 @@
         <v>60</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DF84" t="n">
         <v>1.57</v>
@@ -37703,7 +37703,7 @@
         <v>2.54</v>
       </c>
       <c r="DO84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP84" t="b">
         <v>0</v>
@@ -38106,10 +38106,10 @@
         <v>51</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF85" t="n">
         <v>1.38</v>
@@ -38139,7 +38139,7 @@
         <v>2.74</v>
       </c>
       <c r="DO85" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -38542,7 +38542,7 @@
         <v>61</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DE86" t="n">
         <v>2.4</v>
@@ -38575,7 +38575,7 @@
         <v>3.17</v>
       </c>
       <c r="DO86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -38978,10 +38978,10 @@
         <v>78</v>
       </c>
       <c r="DD87" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE87" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF87" t="n">
         <v>1.22</v>
@@ -39011,7 +39011,7 @@
         <v>2.24</v>
       </c>
       <c r="DO87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -39417,7 +39417,7 @@
         <v>1.27</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DF88" t="n">
         <v>1.25</v>
@@ -39447,7 +39447,7 @@
         <v>2.31</v>
       </c>
       <c r="DO88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -39858,10 +39858,10 @@
         <v>75</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DF89" t="n">
         <v>1.88</v>
@@ -39891,7 +39891,7 @@
         <v>2.77</v>
       </c>
       <c r="DO89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -40302,7 +40302,7 @@
         <v>56</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DE90" t="n">
         <v>2</v>
@@ -40335,7 +40335,7 @@
         <v>2.91</v>
       </c>
       <c r="DO90" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -40746,7 +40746,7 @@
         <v>61</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE91" t="n">
         <v>2.4</v>
@@ -40779,7 +40779,7 @@
         <v>3.05</v>
       </c>
       <c r="DO91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -41185,7 +41185,7 @@
         <v>1.27</v>
       </c>
       <c r="DE92" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF92" t="n">
         <v>1.22</v>
@@ -41215,7 +41215,7 @@
         <v>1.85</v>
       </c>
       <c r="DO92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -41634,10 +41634,10 @@
         <v>78</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DF93" t="n">
         <v>1.22</v>
@@ -41667,7 +41667,7 @@
         <v>2.35</v>
       </c>
       <c r="DO93" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -42081,7 +42081,7 @@
         <v>1.91</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="DF94" t="n">
         <v>2</v>
@@ -42111,7 +42111,7 @@
         <v>2.91</v>
       </c>
       <c r="DO94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -42514,10 +42514,10 @@
         <v>69</v>
       </c>
       <c r="DD95" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DE95" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF95" t="n">
         <v>1.75</v>
@@ -42547,7 +42547,7 @@
         <v>2.19</v>
       </c>
       <c r="DO95" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -42958,7 +42958,7 @@
         <v>88</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DE96" t="n">
         <v>2.4</v>
@@ -43938,6 +43938,3518 @@
           <t>1.85</t>
         </is>
       </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>11</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>La Equidad</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>46095.79166666666</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>4</v>
+      </c>
+      <c r="K99" t="n">
+        <v>4</v>
+      </c>
+      <c r="L99" t="n">
+        <v>8</v>
+      </c>
+      <c r="M99" t="n">
+        <v>2</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>1</v>
+      </c>
+      <c r="R99" t="n">
+        <v>2</v>
+      </c>
+      <c r="S99" t="n">
+        <v>6</v>
+      </c>
+      <c r="T99" t="n">
+        <v>13</v>
+      </c>
+      <c r="U99" t="n">
+        <v>7</v>
+      </c>
+      <c r="V99" t="n">
+        <v>15</v>
+      </c>
+      <c r="W99" t="n">
+        <v>9</v>
+      </c>
+      <c r="X99" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>Estadio Metropolitano de Techo</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AC99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT99" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AU99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV99" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW99" t="n">
+        <v>32</v>
+      </c>
+      <c r="BX99" t="n">
+        <v>86</v>
+      </c>
+      <c r="BY99" t="n">
+        <v>116</v>
+      </c>
+      <c r="BZ99" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="CA99" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CB99" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR99" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS99" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU99" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV99" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX99" t="n">
+        <v>17</v>
+      </c>
+      <c r="CY99" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ99" t="n">
+        <v>58</v>
+      </c>
+      <c r="DA99" t="n">
+        <v>74</v>
+      </c>
+      <c r="DB99" t="n">
+        <v>52</v>
+      </c>
+      <c r="DC99" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD99" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DE99" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DF99" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DG99" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DH99" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DI99" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DJ99" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK99" t="n">
+        <v>27</v>
+      </c>
+      <c r="DL99" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DM99" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DN99" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DO99" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW99" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="DX99" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="DY99" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="DZ99" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EA99" t="inlineStr">
+        <is>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="EB99" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EC99" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="ED99" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EE99" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="EF99" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EG99" t="inlineStr"/>
+      <c r="EH99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>11</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>46095.88194444445</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2</v>
+      </c>
+      <c r="I100" t="n">
+        <v>2</v>
+      </c>
+      <c r="J100" t="n">
+        <v>8</v>
+      </c>
+      <c r="K100" t="n">
+        <v>4</v>
+      </c>
+      <c r="L100" t="n">
+        <v>12</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1</v>
+      </c>
+      <c r="N100" t="n">
+        <v>3</v>
+      </c>
+      <c r="O100" t="n">
+        <v>1</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>3</v>
+      </c>
+      <c r="R100" t="n">
+        <v>5</v>
+      </c>
+      <c r="S100" t="n">
+        <v>7</v>
+      </c>
+      <c r="T100" t="n">
+        <v>4</v>
+      </c>
+      <c r="U100" t="n">
+        <v>10</v>
+      </c>
+      <c r="V100" t="n">
+        <v>9</v>
+      </c>
+      <c r="W100" t="n">
+        <v>4</v>
+      </c>
+      <c r="X100" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>Estadio General Santander</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>Avenida 0A 3-56, Barrio Lleras Restrepo, Cúcuta</t>
+        </is>
+      </c>
+      <c r="AC100" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB100" t="n">
+        <v>2132</v>
+      </c>
+      <c r="BC100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD100" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF100" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK100" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT100" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV100" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW100" t="n">
+        <v>19</v>
+      </c>
+      <c r="BX100" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY100" t="n">
+        <v>57</v>
+      </c>
+      <c r="BZ100" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR100" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS100" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU100" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV100" t="n">
+        <v>4</v>
+      </c>
+      <c r="CW100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX100" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY100" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ100" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA100" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB100" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC100" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD100" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="DE100" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DF100" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DG100" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DH100" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DI100" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DJ100" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK100" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL100" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DM100" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DN100" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DO100" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP100" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ100" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW100" t="inlineStr"/>
+      <c r="DX100" t="inlineStr"/>
+      <c r="DY100" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="DZ100" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EA100" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="EB100" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EC100" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="ED100" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EE100" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EF100" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="EG100" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EH100" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>11</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Boyacá Chicó</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>46095.97222222222</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" t="n">
+        <v>3</v>
+      </c>
+      <c r="J101" t="n">
+        <v>4</v>
+      </c>
+      <c r="K101" t="n">
+        <v>7</v>
+      </c>
+      <c r="L101" t="n">
+        <v>11</v>
+      </c>
+      <c r="M101" t="n">
+        <v>7</v>
+      </c>
+      <c r="N101" t="n">
+        <v>4</v>
+      </c>
+      <c r="O101" t="n">
+        <v>1</v>
+      </c>
+      <c r="P101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>3</v>
+      </c>
+      <c r="R101" t="n">
+        <v>8</v>
+      </c>
+      <c r="S101" t="n">
+        <v>6</v>
+      </c>
+      <c r="T101" t="n">
+        <v>16</v>
+      </c>
+      <c r="U101" t="n">
+        <v>9</v>
+      </c>
+      <c r="V101" t="n">
+        <v>24</v>
+      </c>
+      <c r="W101" t="n">
+        <v>6</v>
+      </c>
+      <c r="X101" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr"/>
+      <c r="AC101" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>2151</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI101" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL101" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM101" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN101" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO101" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ101" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR101" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS101" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT101" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV101" t="n">
+        <v>11</v>
+      </c>
+      <c r="BW101" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX101" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY101" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ101" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="CA101" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CB101" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR101" t="n">
+        <v>4</v>
+      </c>
+      <c r="CS101" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU101" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV101" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ101" t="n">
+        <v>58</v>
+      </c>
+      <c r="DA101" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB101" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC101" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD101" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DE101" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DF101" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DG101" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DH101" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DI101" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ101" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK101" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL101" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DM101" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DN101" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DO101" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW101" t="inlineStr"/>
+      <c r="DX101" t="inlineStr"/>
+      <c r="DY101" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="DZ101" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EA101" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="EB101" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EC101" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="ED101" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EE101" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="EF101" t="inlineStr">
+        <is>
+          <t>5.56</t>
+        </is>
+      </c>
+      <c r="EG101" t="inlineStr"/>
+      <c r="EH101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>11</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Alianza Petrolera</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>46096.0625</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>2</v>
+      </c>
+      <c r="J102" t="n">
+        <v>6</v>
+      </c>
+      <c r="K102" t="n">
+        <v>4</v>
+      </c>
+      <c r="L102" t="n">
+        <v>10</v>
+      </c>
+      <c r="M102" t="n">
+        <v>2</v>
+      </c>
+      <c r="N102" t="n">
+        <v>2</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>4</v>
+      </c>
+      <c r="R102" t="n">
+        <v>1</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="n">
+        <v>6</v>
+      </c>
+      <c r="U102" t="n">
+        <v>9</v>
+      </c>
+      <c r="V102" t="n">
+        <v>7</v>
+      </c>
+      <c r="W102" t="n">
+        <v>7</v>
+      </c>
+      <c r="X102" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>Estadio Nemesio Camacho El Campín</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AC102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD102" t="n">
+        <v>61</v>
+      </c>
+      <c r="BE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT102" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV102" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW102" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX102" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY102" t="n">
+        <v>71</v>
+      </c>
+      <c r="BZ102" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CA102" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="CB102" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR102" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS102" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU102" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV102" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX102" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY102" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ102" t="n">
+        <v>39</v>
+      </c>
+      <c r="DA102" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB102" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC102" t="n">
+        <v>56</v>
+      </c>
+      <c r="DD102" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DE102" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF102" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DG102" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DH102" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DI102" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DJ102" t="n">
+        <v>62</v>
+      </c>
+      <c r="DK102" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL102" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DM102" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DN102" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DO102" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP102" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ102" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV102" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW102" t="inlineStr"/>
+      <c r="DX102" t="inlineStr"/>
+      <c r="DY102" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="DZ102" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EA102" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="EB102" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EC102" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="ED102" t="inlineStr">
+        <is>
+          <t>7.41</t>
+        </is>
+      </c>
+      <c r="EE102" t="inlineStr">
+        <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="EF102" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EG102" t="inlineStr"/>
+      <c r="EH102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>11</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Rionegro Águilas</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>46096.85416666666</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" t="n">
+        <v>2</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" t="n">
+        <v>3</v>
+      </c>
+      <c r="M103" t="n">
+        <v>2</v>
+      </c>
+      <c r="N103" t="n">
+        <v>1</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>3</v>
+      </c>
+      <c r="R103" t="n">
+        <v>2</v>
+      </c>
+      <c r="S103" t="n">
+        <v>4</v>
+      </c>
+      <c r="T103" t="n">
+        <v>12</v>
+      </c>
+      <c r="U103" t="n">
+        <v>7</v>
+      </c>
+      <c r="V103" t="n">
+        <v>14</v>
+      </c>
+      <c r="W103" t="n">
+        <v>11</v>
+      </c>
+      <c r="X103" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>Estadio Hernán Ramírez Villegas</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>Villa Olímpica Pereira, Pereira</t>
+        </is>
+      </c>
+      <c r="AC103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR103" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AT103" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>2147</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD103" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT103" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV103" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW103" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX103" t="n">
+        <v>88</v>
+      </c>
+      <c r="BY103" t="n">
+        <v>96</v>
+      </c>
+      <c r="BZ103" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CA103" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CB103" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR103" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS103" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU103" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV103" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX103" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY103" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ103" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA103" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB103" t="n">
+        <v>11</v>
+      </c>
+      <c r="DC103" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD103" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DE103" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF103" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DG103" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH103" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DI103" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DJ103" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK103" t="n">
+        <v>28</v>
+      </c>
+      <c r="DL103" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DM103" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DN103" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="DO103" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW103" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="DX103" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="DY103" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="DZ103" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EA103" t="inlineStr">
+        <is>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="EB103" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EC103" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="ED103" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EE103" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EF103" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EG103" t="inlineStr"/>
+      <c r="EH103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>11</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>46096.88194444445</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" t="n">
+        <v>2</v>
+      </c>
+      <c r="J104" t="n">
+        <v>3</v>
+      </c>
+      <c r="K104" t="n">
+        <v>4</v>
+      </c>
+      <c r="L104" t="n">
+        <v>7</v>
+      </c>
+      <c r="M104" t="n">
+        <v>3</v>
+      </c>
+      <c r="N104" t="n">
+        <v>6</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>6</v>
+      </c>
+      <c r="R104" t="n">
+        <v>3</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="n">
+        <v>7</v>
+      </c>
+      <c r="U104" t="n">
+        <v>16</v>
+      </c>
+      <c r="V104" t="n">
+        <v>10</v>
+      </c>
+      <c r="W104" t="n">
+        <v>15</v>
+      </c>
+      <c r="X104" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>Estadio Olímpico Pascual Guerrero</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>Carrera 36 entre Calles 5 y 5B3, Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="AC104" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD104" t="n">
+        <v>33</v>
+      </c>
+      <c r="BE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ104" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM104" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP104" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS104" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT104" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV104" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW104" t="n">
+        <v>32</v>
+      </c>
+      <c r="BX104" t="n">
+        <v>96</v>
+      </c>
+      <c r="BY104" t="n">
+        <v>66</v>
+      </c>
+      <c r="BZ104" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CA104" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CB104" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM104" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR104" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS104" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU104" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV104" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX104" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY104" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ104" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA104" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB104" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC104" t="n">
+        <v>61</v>
+      </c>
+      <c r="DD104" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DE104" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DF104" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DG104" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DH104" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DI104" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DJ104" t="n">
+        <v>56</v>
+      </c>
+      <c r="DK104" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL104" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DM104" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DN104" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="DO104" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW104" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="DX104" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="DY104" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="DZ104" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EA104" t="inlineStr">
+        <is>
+          <t>4.59</t>
+        </is>
+      </c>
+      <c r="EB104" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EC104" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="ED104" t="inlineStr">
+        <is>
+          <t>4.47</t>
+        </is>
+      </c>
+      <c r="EE104" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EF104" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EG104" t="inlineStr"/>
+      <c r="EH104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>11</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Jaguares de Córdoba</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>46096.97222222222</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" t="n">
+        <v>2</v>
+      </c>
+      <c r="I105" t="n">
+        <v>3</v>
+      </c>
+      <c r="J105" t="n">
+        <v>5</v>
+      </c>
+      <c r="K105" t="n">
+        <v>6</v>
+      </c>
+      <c r="L105" t="n">
+        <v>11</v>
+      </c>
+      <c r="M105" t="n">
+        <v>4</v>
+      </c>
+      <c r="N105" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>4</v>
+      </c>
+      <c r="R105" t="n">
+        <v>4</v>
+      </c>
+      <c r="S105" t="n">
+        <v>8</v>
+      </c>
+      <c r="T105" t="n">
+        <v>5</v>
+      </c>
+      <c r="U105" t="n">
+        <v>12</v>
+      </c>
+      <c r="V105" t="n">
+        <v>9</v>
+      </c>
+      <c r="W105" t="n">
+        <v>5</v>
+      </c>
+      <c r="X105" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>Estadio de Fútbol Jaraguay de Montería</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>, Montería</t>
+        </is>
+      </c>
+      <c r="AC105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU105" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB105" t="n">
+        <v>2137</v>
+      </c>
+      <c r="BC105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD105" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ105" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT105" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV105" t="n">
+        <v>4</v>
+      </c>
+      <c r="BW105" t="n">
+        <v>16</v>
+      </c>
+      <c r="BX105" t="n">
+        <v>49</v>
+      </c>
+      <c r="BY105" t="n">
+        <v>116</v>
+      </c>
+      <c r="BZ105" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CA105" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="CB105" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS105" t="n">
+        <v>9</v>
+      </c>
+      <c r="CT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU105" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV105" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ105" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA105" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB105" t="n">
+        <v>37</v>
+      </c>
+      <c r="DC105" t="n">
+        <v>74</v>
+      </c>
+      <c r="DD105" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DE105" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF105" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG105" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DH105" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI105" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DJ105" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK105" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL105" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DM105" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DN105" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="DO105" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS105" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT105" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU105" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW105" t="inlineStr"/>
+      <c r="DX105" t="inlineStr"/>
+      <c r="DY105" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="DZ105" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EA105" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EB105" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EC105" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="ED105" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EE105" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EF105" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="EG105" t="inlineStr"/>
+      <c r="EH105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>11</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>46097.0625</v>
+      </c>
+      <c r="G106" t="n">
+        <v>2</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" t="n">
+        <v>3</v>
+      </c>
+      <c r="J106" t="n">
+        <v>5</v>
+      </c>
+      <c r="K106" t="n">
+        <v>3</v>
+      </c>
+      <c r="L106" t="n">
+        <v>8</v>
+      </c>
+      <c r="M106" t="n">
+        <v>3</v>
+      </c>
+      <c r="N106" t="n">
+        <v>4</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>7</v>
+      </c>
+      <c r="R106" t="n">
+        <v>3</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="n">
+        <v>6</v>
+      </c>
+      <c r="U106" t="n">
+        <v>12</v>
+      </c>
+      <c r="V106" t="n">
+        <v>9</v>
+      </c>
+      <c r="W106" t="n">
+        <v>14</v>
+      </c>
+      <c r="X106" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>Estadio Metropolitano Roberto Meléndez</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>Intersección de la Avenida Circunvalar con la Calle 45, Barranquilla</t>
+        </is>
+      </c>
+      <c r="AC106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR106" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB106" t="n">
+        <v>2131</v>
+      </c>
+      <c r="BC106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD106" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR106" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT106" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV106" t="n">
+        <v>31</v>
+      </c>
+      <c r="BW106" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX106" t="n">
+        <v>69</v>
+      </c>
+      <c r="BY106" t="n">
+        <v>82</v>
+      </c>
+      <c r="BZ106" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CA106" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="CB106" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR106" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS106" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU106" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV106" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX106" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY106" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ106" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA106" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB106" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC106" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD106" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DE106" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DF106" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DG106" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DH106" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DI106" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ106" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK106" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL106" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DM106" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DN106" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="DO106" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP106" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ106" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR106" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV106" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW106" t="inlineStr"/>
+      <c r="DX106" t="inlineStr"/>
+      <c r="DY106" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="DZ106" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EA106" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="EB106" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EC106" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="ED106" t="inlineStr">
+        <is>
+          <t>4.74</t>
+        </is>
+      </c>
+      <c r="EE106" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="EF106" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EG106" t="inlineStr"/>
+      <c r="EH106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH106" headerRowCount="1">
-  <autoFilter ref="A1:EH106"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH108" headerRowCount="1">
+  <autoFilter ref="A1:EH108"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH106"/>
+  <dimension ref="A1:EH108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1749,7 +1749,7 @@
         <v>0.4</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -3030,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="DE5" t="n">
         <v>0.7</v>
@@ -3477,7 +3477,7 @@
         <v>1.8</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DE11" t="n">
         <v>2</v>
@@ -6109,7 +6109,7 @@
         <v>1.82</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -7402,7 +7402,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DE15" t="n">
         <v>1.8</v>
@@ -9154,7 +9154,7 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="DE19" t="n">
         <v>1.73</v>
@@ -10026,7 +10026,7 @@
         <v>100</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DE21" t="n">
         <v>1.8</v>
@@ -10473,7 +10473,7 @@
         <v>1.27</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DF22" t="n">
         <v>2</v>
@@ -12233,7 +12233,7 @@
         <v>1.91</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -13990,7 +13990,7 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DE30" t="n">
         <v>1.27</v>
@@ -16178,7 +16178,7 @@
         <v>67</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DE35" t="n">
         <v>1.5</v>
@@ -16614,7 +16614,7 @@
         <v>84</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="DE36" t="n">
         <v>1</v>
@@ -17930,7 +17930,7 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="DE39" t="n">
         <v>1.7</v>
@@ -19237,7 +19237,7 @@
         <v>1.5</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DF42" t="n">
         <v>1.25</v>
@@ -19673,7 +19673,7 @@
         <v>1.6</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DF43" t="n">
         <v>2</v>
@@ -21405,7 +21405,7 @@
         <v>1.36</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="DF47" t="n">
         <v>1.5</v>
@@ -22270,7 +22270,7 @@
         <v>80</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DE49" t="n">
         <v>1</v>
@@ -22714,7 +22714,7 @@
         <v>60</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DE50" t="n">
         <v>1.91</v>
@@ -23602,7 +23602,7 @@
         <v>70</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="DE52" t="n">
         <v>1.5</v>
@@ -25370,7 +25370,7 @@
         <v>70</v>
       </c>
       <c r="DD56" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="DE56" t="n">
         <v>1.27</v>
@@ -25403,7 +25403,7 @@
         <v>4.13</v>
       </c>
       <c r="DO56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -26250,10 +26250,10 @@
         <v>59</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DF58" t="n">
         <v>0.83</v>
@@ -26283,7 +26283,7 @@
         <v>2</v>
       </c>
       <c r="DO58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28029,7 +28029,7 @@
         <v>1.36</v>
       </c>
       <c r="DE62" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="DF62" t="n">
         <v>1.17</v>
@@ -28059,7 +28059,7 @@
         <v>3.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -28901,7 +28901,7 @@
         <v>0.5</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DF64" t="n">
         <v>0.4</v>
@@ -30202,7 +30202,7 @@
         <v>71</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DE67" t="n">
         <v>1</v>
@@ -31962,7 +31962,7 @@
         <v>54</v>
       </c>
       <c r="DD71" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="DE71" t="n">
         <v>0.5</v>
@@ -32401,7 +32401,7 @@
         <v>1.82</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="DF72" t="n">
         <v>2</v>
@@ -34142,7 +34142,7 @@
         <v>65</v>
       </c>
       <c r="DD76" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DE76" t="n">
         <v>1.6</v>
@@ -34589,7 +34589,7 @@
         <v>1.1</v>
       </c>
       <c r="DE77" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="DF77" t="n">
         <v>1.25</v>
@@ -35022,7 +35022,7 @@
         <v>61</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="DE78" t="n">
         <v>0.4</v>
@@ -37237,7 +37237,7 @@
         <v>1.91</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DF83" t="n">
         <v>1.88</v>
@@ -38545,7 +38545,7 @@
         <v>1.6</v>
       </c>
       <c r="DE86" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="DF86" t="n">
         <v>1.5</v>
@@ -39414,7 +39414,7 @@
         <v>60</v>
       </c>
       <c r="DD88" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DE88" t="n">
         <v>1.82</v>
@@ -40749,7 +40749,7 @@
         <v>1.5</v>
       </c>
       <c r="DE91" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="DF91" t="n">
         <v>1.5</v>
@@ -41182,7 +41182,7 @@
         <v>73</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DE92" t="n">
         <v>0.91</v>
@@ -41634,10 +41634,10 @@
         <v>78</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DF93" t="n">
         <v>1.22</v>
@@ -41667,7 +41667,7 @@
         <v>2.35</v>
       </c>
       <c r="DO93" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -42961,7 +42961,7 @@
         <v>1.73</v>
       </c>
       <c r="DE96" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="DF96" t="n">
         <v>1.78</v>
@@ -42991,7 +42991,7 @@
         <v>3.39</v>
       </c>
       <c r="DO96" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -43830,10 +43830,10 @@
         <v>74</v>
       </c>
       <c r="DD98" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DF98" t="n">
         <v>2.33</v>
@@ -43863,7 +43863,7 @@
         <v>2.76</v>
       </c>
       <c r="DO98" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -44718,7 +44718,7 @@
         <v>70</v>
       </c>
       <c r="DD100" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DE100" t="n">
         <v>1.36</v>
@@ -45157,7 +45157,7 @@
         <v>0.7</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="DF101" t="n">
         <v>0.44</v>
@@ -47079,28 +47079,28 @@
         <v>3</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T106" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U106" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V106" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W106" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X106" t="n">
         <v>8</v>
       </c>
       <c r="Y106" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Z106" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
@@ -47260,13 +47260,13 @@
         <v>82</v>
       </c>
       <c r="BZ106" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="CA106" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="CB106" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="CC106" t="n">
         <v>0</v>
@@ -47450,6 +47450,886 @@
       </c>
       <c r="EG106" t="inlineStr"/>
       <c r="EH106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>12</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Llaneros</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>46098.88194444445</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" t="n">
+        <v>4</v>
+      </c>
+      <c r="J107" t="n">
+        <v>3</v>
+      </c>
+      <c r="K107" t="n">
+        <v>5</v>
+      </c>
+      <c r="L107" t="n">
+        <v>8</v>
+      </c>
+      <c r="M107" t="n">
+        <v>3</v>
+      </c>
+      <c r="N107" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>4</v>
+      </c>
+      <c r="R107" t="n">
+        <v>4</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="n">
+        <v>8</v>
+      </c>
+      <c r="U107" t="n">
+        <v>14</v>
+      </c>
+      <c r="V107" t="n">
+        <v>12</v>
+      </c>
+      <c r="W107" t="n">
+        <v>17</v>
+      </c>
+      <c r="X107" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Calle Lombana</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>, Villavicencio</t>
+        </is>
+      </c>
+      <c r="AC107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU107" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD107" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO107" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS107" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV107" t="n">
+        <v>33</v>
+      </c>
+      <c r="BW107" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX107" t="n">
+        <v>84</v>
+      </c>
+      <c r="BY107" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ107" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CA107" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CB107" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="CC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR107" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS107" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU107" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV107" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX107" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY107" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ107" t="n">
+        <v>41</v>
+      </c>
+      <c r="DA107" t="n">
+        <v>91</v>
+      </c>
+      <c r="DB107" t="n">
+        <v>37</v>
+      </c>
+      <c r="DC107" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD107" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE107" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DF107" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DG107" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="DH107" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DI107" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="DJ107" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK107" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL107" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DM107" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DN107" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="DO107" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW107" t="inlineStr"/>
+      <c r="DX107" t="inlineStr"/>
+      <c r="DY107" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="DZ107" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EA107" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="EB107" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EC107" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="ED107" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="EE107" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EF107" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EG107" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH107" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>12</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>46099.0625</v>
+      </c>
+      <c r="G108" t="n">
+        <v>3</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>3</v>
+      </c>
+      <c r="J108" t="n">
+        <v>6</v>
+      </c>
+      <c r="K108" t="n">
+        <v>3</v>
+      </c>
+      <c r="L108" t="n">
+        <v>9</v>
+      </c>
+      <c r="M108" t="n">
+        <v>2</v>
+      </c>
+      <c r="N108" t="n">
+        <v>5</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>7</v>
+      </c>
+      <c r="R108" t="n">
+        <v>1</v>
+      </c>
+      <c r="S108" t="n">
+        <v>13</v>
+      </c>
+      <c r="T108" t="n">
+        <v>7</v>
+      </c>
+      <c r="U108" t="n">
+        <v>20</v>
+      </c>
+      <c r="V108" t="n">
+        <v>8</v>
+      </c>
+      <c r="W108" t="n">
+        <v>16</v>
+      </c>
+      <c r="X108" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>Estadio Nemesio Camacho El Campín</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AC108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU108" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB108" t="n">
+        <v>2136</v>
+      </c>
+      <c r="BC108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD108" t="n">
+        <v>52</v>
+      </c>
+      <c r="BE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ108" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK108" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM108" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN108" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP108" t="n">
+        <v>5</v>
+      </c>
+      <c r="BQ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS108" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV108" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW108" t="n">
+        <v>20</v>
+      </c>
+      <c r="BX108" t="n">
+        <v>66</v>
+      </c>
+      <c r="BY108" t="n">
+        <v>66</v>
+      </c>
+      <c r="BZ108" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CA108" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="CB108" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR108" t="n">
+        <v>9</v>
+      </c>
+      <c r="CS108" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU108" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV108" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX108" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY108" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ108" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA108" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB108" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC108" t="n">
+        <v>68</v>
+      </c>
+      <c r="DD108" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DE108" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DF108" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DG108" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DH108" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DI108" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DJ108" t="n">
+        <v>33</v>
+      </c>
+      <c r="DK108" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL108" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DM108" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DN108" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="DO108" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP108" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ108" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR108" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW108" t="inlineStr"/>
+      <c r="DX108" t="inlineStr"/>
+      <c r="DY108" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="DZ108" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EA108" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="EB108" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EC108" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="ED108" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EE108" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EF108" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EG108" t="inlineStr"/>
+      <c r="EH108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH108" headerRowCount="1">
-  <autoFilter ref="A1:EH108"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH115" headerRowCount="1">
+  <autoFilter ref="A1:EH115"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH108"/>
+  <dimension ref="A1:EH115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1746,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DE2" t="n">
         <v>1.25</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2182,10 +2182,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2629,7 +2629,7 @@
         <v>1.7</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
         <v>2.18</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE6" t="n">
         <v>1.42</v>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -3910,10 +3910,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DE7" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4346,10 +4346,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4790,11 +4790,11 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DE9" t="n">
         <v>1.73</v>
       </c>
-      <c r="DE9" t="n">
-        <v>1.6</v>
-      </c>
       <c r="DF9" t="n">
         <v>0</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5226,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DE10" t="n">
         <v>1.5</v>
@@ -5665,7 +5665,7 @@
         <v>0.58</v>
       </c>
       <c r="DE11" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6106,7 +6106,7 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DE12" t="n">
         <v>0.58</v>
@@ -6139,7 +6139,7 @@
         <v>1.82</v>
       </c>
       <c r="DO12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6522,10 +6522,10 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6555,7 +6555,7 @@
         <v>1.86</v>
       </c>
       <c r="DO13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -6966,10 +6966,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -6999,7 +6999,7 @@
         <v>1.99</v>
       </c>
       <c r="DO14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP14" t="b">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>1.25</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7435,7 +7435,7 @@
         <v>3.19</v>
       </c>
       <c r="DO15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -7854,10 +7854,10 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE16" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -7887,7 +7887,7 @@
         <v>2.53</v>
       </c>
       <c r="DO16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8282,7 +8282,7 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DE17" t="n">
         <v>1.7</v>
@@ -8721,7 +8721,7 @@
         <v>1.5</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DF18" t="n">
         <v>1</v>
@@ -9157,7 +9157,7 @@
         <v>1.42</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9187,7 +9187,7 @@
         <v>2.56</v>
       </c>
       <c r="DO19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9590,10 +9590,10 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -9623,7 +9623,7 @@
         <v>4.47</v>
       </c>
       <c r="DO20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10029,7 +10029,7 @@
         <v>0.58</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10059,7 +10059,7 @@
         <v>2.47</v>
       </c>
       <c r="DO21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10470,7 +10470,7 @@
         <v>25</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DE22" t="n">
         <v>1.25</v>
@@ -10503,7 +10503,7 @@
         <v>2.27</v>
       </c>
       <c r="DO22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -10914,10 +10914,10 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF23" t="n">
         <v>0</v>
@@ -10947,7 +10947,7 @@
         <v>2.38</v>
       </c>
       <c r="DO23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11350,10 +11350,10 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -11383,7 +11383,7 @@
         <v>1.88</v>
       </c>
       <c r="DO24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -11786,10 +11786,10 @@
         <v>25</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -11819,7 +11819,7 @@
         <v>2.57</v>
       </c>
       <c r="DO25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12230,7 +12230,7 @@
         <v>75</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DE26" t="n">
         <v>1.42</v>
@@ -12263,7 +12263,7 @@
         <v>2.13</v>
       </c>
       <c r="DO26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -12669,7 +12669,7 @@
         <v>1.5</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DF27" t="n">
         <v>0.5</v>
@@ -13102,10 +13102,10 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -13135,7 +13135,7 @@
         <v>2.03</v>
       </c>
       <c r="DO28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -13549,7 +13549,7 @@
         <v>1.7</v>
       </c>
       <c r="DE29" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -13993,7 +13993,7 @@
         <v>0.58</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF30" t="n">
         <v>0.33</v>
@@ -14023,7 +14023,7 @@
         <v>2.24</v>
       </c>
       <c r="DO30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14418,10 +14418,10 @@
         <v>67</v>
       </c>
       <c r="DD31" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DF31" t="n">
         <v>0.33</v>
@@ -14451,7 +14451,7 @@
         <v>2.8</v>
       </c>
       <c r="DO31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -14862,10 +14862,10 @@
         <v>50</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE32" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="DF32" t="n">
         <v>1.67</v>
@@ -14895,7 +14895,7 @@
         <v>2.62</v>
       </c>
       <c r="DO32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15298,10 +15298,10 @@
         <v>50</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE33" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DF33" t="n">
         <v>1</v>
@@ -15331,7 +15331,7 @@
         <v>2.29</v>
       </c>
       <c r="DO33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -15742,10 +15742,10 @@
         <v>59</v>
       </c>
       <c r="DD34" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DF34" t="n">
         <v>1.67</v>
@@ -15775,7 +15775,7 @@
         <v>2.49</v>
       </c>
       <c r="DO34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -16617,7 +16617,7 @@
         <v>1.42</v>
       </c>
       <c r="DE36" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF36" t="n">
         <v>0</v>
@@ -16647,7 +16647,7 @@
         <v>2.84</v>
       </c>
       <c r="DO36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP36" t="b">
         <v>0</v>
@@ -17050,10 +17050,10 @@
         <v>84</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF37" t="n">
         <v>2</v>
@@ -17083,7 +17083,7 @@
         <v>2.43</v>
       </c>
       <c r="DO37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -17494,10 +17494,10 @@
         <v>67</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF38" t="n">
         <v>0.67</v>
@@ -17527,7 +17527,7 @@
         <v>2.42</v>
       </c>
       <c r="DO38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18366,10 +18366,10 @@
         <v>88</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DF40" t="n">
         <v>2.25</v>
@@ -18399,7 +18399,7 @@
         <v>2.56</v>
       </c>
       <c r="DO40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP40" t="b">
         <v>0</v>
@@ -18798,10 +18798,10 @@
         <v>63</v>
       </c>
       <c r="DD41" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DE41" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF41" t="n">
         <v>0.5</v>
@@ -18831,7 +18831,7 @@
         <v>2.9</v>
       </c>
       <c r="DO41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -19670,7 +19670,7 @@
         <v>63</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DE43" t="n">
         <v>1.25</v>
@@ -19703,7 +19703,7 @@
         <v>1.9</v>
       </c>
       <c r="DO43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20106,10 +20106,10 @@
         <v>50</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DF44" t="n">
         <v>1.5</v>
@@ -20139,7 +20139,7 @@
         <v>3.37</v>
       </c>
       <c r="DO44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -20522,10 +20522,10 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DF45" t="n">
         <v>2</v>
@@ -20555,7 +20555,7 @@
         <v>2.5</v>
       </c>
       <c r="DO45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -20958,10 +20958,10 @@
         <v>50</v>
       </c>
       <c r="DD46" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="DE46" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DF46" t="n">
         <v>0.25</v>
@@ -20991,7 +20991,7 @@
         <v>2.87</v>
       </c>
       <c r="DO46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -21402,7 +21402,7 @@
         <v>63</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE47" t="n">
         <v>1.42</v>
@@ -21435,7 +21435,7 @@
         <v>2.48</v>
       </c>
       <c r="DO47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP47" t="b">
         <v>0</v>
@@ -21826,10 +21826,10 @@
         <v>59</v>
       </c>
       <c r="DD48" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DF48" t="n">
         <v>1.33</v>
@@ -21859,7 +21859,7 @@
         <v>1.75</v>
       </c>
       <c r="DO48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -22273,7 +22273,7 @@
         <v>0.58</v>
       </c>
       <c r="DE49" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF49" t="n">
         <v>0.4</v>
@@ -22303,7 +22303,7 @@
         <v>2.37</v>
       </c>
       <c r="DO49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -22717,7 +22717,7 @@
         <v>1.25</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DF50" t="n">
         <v>1.8</v>
@@ -22747,7 +22747,7 @@
         <v>1.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -23158,10 +23158,10 @@
         <v>60</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF51" t="n">
         <v>1.8</v>
@@ -23191,7 +23191,7 @@
         <v>2.38</v>
       </c>
       <c r="DO51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP51" t="b">
         <v>0</v>
@@ -24046,10 +24046,10 @@
         <v>60</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -24079,7 +24079,7 @@
         <v>2.58</v>
       </c>
       <c r="DO53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -24474,10 +24474,10 @@
         <v>68</v>
       </c>
       <c r="DD54" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DF54" t="n">
         <v>0.2</v>
@@ -24507,7 +24507,7 @@
         <v>1.66</v>
       </c>
       <c r="DO54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -24926,10 +24926,10 @@
         <v>80</v>
       </c>
       <c r="DD55" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF55" t="n">
         <v>1.4</v>
@@ -24959,7 +24959,7 @@
         <v>3.39</v>
       </c>
       <c r="DO55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -25373,7 +25373,7 @@
         <v>2.18</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF56" t="n">
         <v>3</v>
@@ -25809,7 +25809,7 @@
         <v>1.7</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DF57" t="n">
         <v>1.75</v>
@@ -26694,10 +26694,10 @@
         <v>64</v>
       </c>
       <c r="DD59" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DF59" t="n">
         <v>0.83</v>
@@ -26727,7 +26727,7 @@
         <v>2.53</v>
       </c>
       <c r="DO59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -27146,10 +27146,10 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF60" t="n">
         <v>2.17</v>
@@ -27179,7 +27179,7 @@
         <v>2.31</v>
       </c>
       <c r="DO60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -27590,10 +27590,10 @@
         <v>50</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DE61" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DF61" t="n">
         <v>1.5</v>
@@ -27623,7 +27623,7 @@
         <v>2.63</v>
       </c>
       <c r="DO61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -28026,7 +28026,7 @@
         <v>75</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE62" t="n">
         <v>2.18</v>
@@ -28462,10 +28462,10 @@
         <v>59</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DF63" t="n">
         <v>1.17</v>
@@ -28495,7 +28495,7 @@
         <v>2.4</v>
       </c>
       <c r="DO63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -28898,7 +28898,7 @@
         <v>60</v>
       </c>
       <c r="DD64" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="DE64" t="n">
         <v>0.58</v>
@@ -28931,7 +28931,7 @@
         <v>1.97</v>
       </c>
       <c r="DO64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -29334,10 +29334,10 @@
         <v>57</v>
       </c>
       <c r="DD65" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DF65" t="n">
         <v>1.4</v>
@@ -29367,7 +29367,7 @@
         <v>2.22</v>
       </c>
       <c r="DO65" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -29766,7 +29766,7 @@
         <v>90</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DE66" t="n">
         <v>1.7</v>
@@ -30205,7 +30205,7 @@
         <v>1.25</v>
       </c>
       <c r="DE67" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF67" t="n">
         <v>1.29</v>
@@ -30235,7 +30235,7 @@
         <v>2.55</v>
       </c>
       <c r="DO67" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -30646,10 +30646,10 @@
         <v>62</v>
       </c>
       <c r="DD68" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DF68" t="n">
         <v>0.5</v>
@@ -30679,7 +30679,7 @@
         <v>1.99</v>
       </c>
       <c r="DO68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -31090,10 +31090,10 @@
         <v>57</v>
       </c>
       <c r="DD69" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF69" t="n">
         <v>1.43</v>
@@ -31123,7 +31123,7 @@
         <v>3.02</v>
       </c>
       <c r="DO69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -31526,10 +31526,10 @@
         <v>55</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DF70" t="n">
         <v>1.67</v>
@@ -31559,7 +31559,7 @@
         <v>2.63</v>
       </c>
       <c r="DO70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP70" t="b">
         <v>0</v>
@@ -31965,7 +31965,7 @@
         <v>2.18</v>
       </c>
       <c r="DE71" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="DF71" t="n">
         <v>2.25</v>
@@ -31995,7 +31995,7 @@
         <v>3.31</v>
       </c>
       <c r="DO71" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -32398,7 +32398,7 @@
         <v>64</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DE72" t="n">
         <v>1.42</v>
@@ -32431,7 +32431,7 @@
         <v>2.49</v>
       </c>
       <c r="DO72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -32842,10 +32842,10 @@
         <v>72</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -32875,7 +32875,7 @@
         <v>3.26</v>
       </c>
       <c r="DO73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -33270,7 +33270,7 @@
         <v>69</v>
       </c>
       <c r="DD74" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DE74" t="n">
         <v>1.5</v>
@@ -33709,7 +33709,7 @@
         <v>1.7</v>
       </c>
       <c r="DE75" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DF75" t="n">
         <v>1.67</v>
@@ -34145,7 +34145,7 @@
         <v>0.58</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF76" t="n">
         <v>0.43</v>
@@ -34175,7 +34175,7 @@
         <v>2.09</v>
       </c>
       <c r="DO76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -34586,7 +34586,7 @@
         <v>65</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DE77" t="n">
         <v>2.18</v>
@@ -34619,7 +34619,7 @@
         <v>3.5</v>
       </c>
       <c r="DO77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -35025,7 +35025,7 @@
         <v>1.42</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DF78" t="n">
         <v>1</v>
@@ -35055,7 +35055,7 @@
         <v>2.25</v>
       </c>
       <c r="DO78" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -35458,10 +35458,10 @@
         <v>63</v>
       </c>
       <c r="DD79" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DF79" t="n">
         <v>1.63</v>
@@ -35491,7 +35491,7 @@
         <v>2.48</v>
       </c>
       <c r="DO79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -35902,7 +35902,7 @@
         <v>65</v>
       </c>
       <c r="DD80" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="DE80" t="n">
         <v>1.7</v>
@@ -36346,10 +36346,10 @@
         <v>93</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF81" t="n">
         <v>1.43</v>
@@ -36379,7 +36379,7 @@
         <v>2.39</v>
       </c>
       <c r="DO81" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -36790,10 +36790,10 @@
         <v>60</v>
       </c>
       <c r="DD82" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DF82" t="n">
         <v>0.88</v>
@@ -36823,7 +36823,7 @@
         <v>2.82</v>
       </c>
       <c r="DO82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -37234,7 +37234,7 @@
         <v>82</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DE83" t="n">
         <v>0.58</v>
@@ -37267,7 +37267,7 @@
         <v>2.12</v>
       </c>
       <c r="DO83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -37673,7 +37673,7 @@
         <v>1.5</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF84" t="n">
         <v>1.57</v>
@@ -38106,10 +38106,10 @@
         <v>51</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF85" t="n">
         <v>1.38</v>
@@ -38139,7 +38139,7 @@
         <v>2.74</v>
       </c>
       <c r="DO85" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -38542,7 +38542,7 @@
         <v>61</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DE86" t="n">
         <v>2.18</v>
@@ -38575,7 +38575,7 @@
         <v>3.17</v>
       </c>
       <c r="DO86" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -38978,10 +38978,10 @@
         <v>78</v>
       </c>
       <c r="DD87" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DF87" t="n">
         <v>1.22</v>
@@ -39011,7 +39011,7 @@
         <v>2.24</v>
       </c>
       <c r="DO87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -39417,7 +39417,7 @@
         <v>1.25</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF88" t="n">
         <v>1.25</v>
@@ -39447,7 +39447,7 @@
         <v>2.31</v>
       </c>
       <c r="DO88" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -39858,10 +39858,10 @@
         <v>75</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="DF89" t="n">
         <v>1.88</v>
@@ -39891,7 +39891,7 @@
         <v>2.77</v>
       </c>
       <c r="DO89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -40302,10 +40302,10 @@
         <v>56</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE90" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DF90" t="n">
         <v>1.33</v>
@@ -40335,7 +40335,7 @@
         <v>2.91</v>
       </c>
       <c r="DO90" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -41185,7 +41185,7 @@
         <v>1.25</v>
       </c>
       <c r="DE92" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DF92" t="n">
         <v>1.22</v>
@@ -41215,7 +41215,7 @@
         <v>1.85</v>
       </c>
       <c r="DO92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -42078,7 +42078,7 @@
         <v>78</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DE94" t="n">
         <v>1.7</v>
@@ -42514,10 +42514,10 @@
         <v>69</v>
       </c>
       <c r="DD95" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE95" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DF95" t="n">
         <v>1.75</v>
@@ -42547,7 +42547,7 @@
         <v>2.19</v>
       </c>
       <c r="DO95" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -42958,7 +42958,7 @@
         <v>88</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DE96" t="n">
         <v>2.18</v>
@@ -43394,10 +43394,10 @@
         <v>70</v>
       </c>
       <c r="DD97" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DF97" t="n">
         <v>1.9</v>
@@ -43427,7 +43427,7 @@
         <v>2.98</v>
       </c>
       <c r="DO97" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -44274,10 +44274,10 @@
         <v>64</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DF99" t="n">
         <v>1.9</v>
@@ -44307,7 +44307,7 @@
         <v>2.56</v>
       </c>
       <c r="DO99" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP99" t="b">
         <v>0</v>
@@ -44721,7 +44721,7 @@
         <v>0.58</v>
       </c>
       <c r="DE100" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DF100" t="n">
         <v>0.6</v>
@@ -44751,7 +44751,7 @@
         <v>2.22</v>
       </c>
       <c r="DO100" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -45154,7 +45154,7 @@
         <v>59</v>
       </c>
       <c r="DD101" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DE101" t="n">
         <v>1.42</v>
@@ -45187,7 +45187,7 @@
         <v>2.38</v>
       </c>
       <c r="DO101" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -45590,10 +45590,10 @@
         <v>56</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DE102" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="DF102" t="n">
         <v>1.11</v>
@@ -45623,7 +45623,7 @@
         <v>2.71</v>
       </c>
       <c r="DO102" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -46026,7 +46026,7 @@
         <v>67</v>
       </c>
       <c r="DD103" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DE103" t="n">
         <v>1.5</v>
@@ -46473,7 +46473,7 @@
         <v>1.7</v>
       </c>
       <c r="DE104" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DF104" t="n">
         <v>1.78</v>
@@ -46914,10 +46914,10 @@
         <v>74</v>
       </c>
       <c r="DD105" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DE105" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF105" t="n">
         <v>1</v>
@@ -46947,7 +46947,7 @@
         <v>2.51</v>
       </c>
       <c r="DO105" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -47350,10 +47350,10 @@
         <v>80</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DE106" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF106" t="n">
         <v>1.6</v>
@@ -47383,7 +47383,7 @@
         <v>2.91</v>
       </c>
       <c r="DO106" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -48330,6 +48330,3090 @@
       </c>
       <c r="EG108" t="inlineStr"/>
       <c r="EH108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>12</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Boyacá Chicó</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>46099.88194444445</v>
+      </c>
+      <c r="G109" t="n">
+        <v>2</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>2</v>
+      </c>
+      <c r="J109" t="n">
+        <v>4</v>
+      </c>
+      <c r="K109" t="n">
+        <v>2</v>
+      </c>
+      <c r="L109" t="n">
+        <v>6</v>
+      </c>
+      <c r="M109" t="n">
+        <v>2</v>
+      </c>
+      <c r="N109" t="n">
+        <v>2</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>4</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>13</v>
+      </c>
+      <c r="T109" t="n">
+        <v>2</v>
+      </c>
+      <c r="U109" t="n">
+        <v>17</v>
+      </c>
+      <c r="V109" t="n">
+        <v>2</v>
+      </c>
+      <c r="W109" t="n">
+        <v>14</v>
+      </c>
+      <c r="X109" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>Estadio Departamental Libertad</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>Carrera 8, San Juan de Pasto</t>
+        </is>
+      </c>
+      <c r="AC109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB109" t="n">
+        <v>2143</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK109" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT109" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV109" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW109" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX109" t="n">
+        <v>66</v>
+      </c>
+      <c r="BY109" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ109" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CA109" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CB109" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CC109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN109" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR109" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS109" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU109" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV109" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX109" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY109" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ109" t="n">
+        <v>58</v>
+      </c>
+      <c r="DA109" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB109" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC109" t="n">
+        <v>72</v>
+      </c>
+      <c r="DD109" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE109" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DF109" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DG109" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DH109" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DI109" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DJ109" t="n">
+        <v>43</v>
+      </c>
+      <c r="DK109" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL109" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM109" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DN109" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DO109" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW109" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="DX109" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="DY109" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="DZ109" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EA109" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="EB109" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EC109" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="ED109" t="inlineStr">
+        <is>
+          <t>9.13</t>
+        </is>
+      </c>
+      <c r="EE109" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="EF109" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EG109" t="inlineStr"/>
+      <c r="EH109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>12</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>La Equidad</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>46099.97222222222</v>
+      </c>
+      <c r="G110" t="n">
+        <v>2</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2</v>
+      </c>
+      <c r="I110" t="n">
+        <v>4</v>
+      </c>
+      <c r="J110" t="n">
+        <v>11</v>
+      </c>
+      <c r="K110" t="n">
+        <v>4</v>
+      </c>
+      <c r="L110" t="n">
+        <v>15</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1</v>
+      </c>
+      <c r="N110" t="n">
+        <v>1</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>8</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6</v>
+      </c>
+      <c r="S110" t="n">
+        <v>18</v>
+      </c>
+      <c r="T110" t="n">
+        <v>3</v>
+      </c>
+      <c r="U110" t="n">
+        <v>26</v>
+      </c>
+      <c r="V110" t="n">
+        <v>9</v>
+      </c>
+      <c r="W110" t="n">
+        <v>5</v>
+      </c>
+      <c r="X110" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>72</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>Estadio Metropolitano de Techo</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AC110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV110" t="n">
+        <v>33</v>
+      </c>
+      <c r="BW110" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX110" t="n">
+        <v>130</v>
+      </c>
+      <c r="BY110" t="n">
+        <v>54</v>
+      </c>
+      <c r="BZ110" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CA110" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CB110" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="CC110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR110" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS110" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU110" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV110" t="n">
+        <v>2</v>
+      </c>
+      <c r="CW110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX110" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY110" t="n">
+        <v>16</v>
+      </c>
+      <c r="CZ110" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA110" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB110" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC110" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD110" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DE110" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DF110" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DG110" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DH110" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DI110" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DJ110" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK110" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL110" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DM110" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DN110" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DO110" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP110" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ110" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR110" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS110" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV110" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW110" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="DX110" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="DY110" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="DZ110" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EA110" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="EB110" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EC110" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="ED110" t="inlineStr">
+        <is>
+          <t>9.14</t>
+        </is>
+      </c>
+      <c r="EE110" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+      <c r="EF110" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EG110" t="inlineStr"/>
+      <c r="EH110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>12</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>46100.02083333334</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" t="n">
+        <v>2</v>
+      </c>
+      <c r="J111" t="n">
+        <v>9</v>
+      </c>
+      <c r="K111" t="n">
+        <v>3</v>
+      </c>
+      <c r="L111" t="n">
+        <v>12</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1</v>
+      </c>
+      <c r="N111" t="n">
+        <v>2</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>3</v>
+      </c>
+      <c r="R111" t="n">
+        <v>2</v>
+      </c>
+      <c r="S111" t="n">
+        <v>9</v>
+      </c>
+      <c r="T111" t="n">
+        <v>9</v>
+      </c>
+      <c r="U111" t="n">
+        <v>12</v>
+      </c>
+      <c r="V111" t="n">
+        <v>11</v>
+      </c>
+      <c r="W111" t="n">
+        <v>9</v>
+      </c>
+      <c r="X111" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>Estadio Alfonso López</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>Carrera 36 Nº 53-12, Cabecera del Llano, Bucaramanga</t>
+        </is>
+      </c>
+      <c r="AC111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD111" t="n">
+        <v>61</v>
+      </c>
+      <c r="BE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT111" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV111" t="n">
+        <v>64</v>
+      </c>
+      <c r="BW111" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX111" t="n">
+        <v>119</v>
+      </c>
+      <c r="BY111" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ111" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CA111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB111" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR111" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS111" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU111" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV111" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX111" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY111" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ111" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA111" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB111" t="n">
+        <v>48</v>
+      </c>
+      <c r="DC111" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD111" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DE111" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DF111" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DG111" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH111" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DI111" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ111" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK111" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL111" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DM111" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DN111" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="DO111" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP111" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ111" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR111" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS111" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT111" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU111" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV111" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW111" t="inlineStr"/>
+      <c r="DX111" t="inlineStr"/>
+      <c r="DY111" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="DZ111" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EA111" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EB111" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EC111" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="ED111" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="EE111" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EF111" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EG111" t="inlineStr"/>
+      <c r="EH111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>12</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>46100.0625</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" t="n">
+        <v>2</v>
+      </c>
+      <c r="J112" t="n">
+        <v>6</v>
+      </c>
+      <c r="K112" t="n">
+        <v>9</v>
+      </c>
+      <c r="L112" t="n">
+        <v>15</v>
+      </c>
+      <c r="M112" t="n">
+        <v>4</v>
+      </c>
+      <c r="N112" t="n">
+        <v>4</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>7</v>
+      </c>
+      <c r="R112" t="n">
+        <v>3</v>
+      </c>
+      <c r="S112" t="n">
+        <v>7</v>
+      </c>
+      <c r="T112" t="n">
+        <v>6</v>
+      </c>
+      <c r="U112" t="n">
+        <v>14</v>
+      </c>
+      <c r="V112" t="n">
+        <v>9</v>
+      </c>
+      <c r="W112" t="n">
+        <v>14</v>
+      </c>
+      <c r="X112" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>Estadio Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>BN 25, Palmira</t>
+        </is>
+      </c>
+      <c r="AC112" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>58</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ112" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT112" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV112" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW112" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX112" t="n">
+        <v>68</v>
+      </c>
+      <c r="BY112" t="n">
+        <v>62</v>
+      </c>
+      <c r="BZ112" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CA112" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CB112" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="CC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR112" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS112" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU112" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV112" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX112" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY112" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ112" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA112" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB112" t="n">
+        <v>14</v>
+      </c>
+      <c r="DC112" t="n">
+        <v>53</v>
+      </c>
+      <c r="DD112" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE112" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DF112" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DG112" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DH112" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DI112" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DJ112" t="n">
+        <v>62</v>
+      </c>
+      <c r="DK112" t="n">
+        <v>28</v>
+      </c>
+      <c r="DL112" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DM112" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DN112" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="DO112" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP112" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ112" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR112" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS112" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT112" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU112" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV112" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW112" t="inlineStr"/>
+      <c r="DX112" t="inlineStr"/>
+      <c r="DY112" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="DZ112" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EA112" t="inlineStr">
+        <is>
+          <t>5.17</t>
+        </is>
+      </c>
+      <c r="EB112" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EC112" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="ED112" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="EE112" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EF112" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EG112" t="inlineStr"/>
+      <c r="EH112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>12</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Alianza Petrolera</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Jaguares de Córdoba</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>46100.88194444445</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" t="n">
+        <v>2</v>
+      </c>
+      <c r="K113" t="n">
+        <v>6</v>
+      </c>
+      <c r="L113" t="n">
+        <v>8</v>
+      </c>
+      <c r="M113" t="n">
+        <v>3</v>
+      </c>
+      <c r="N113" t="n">
+        <v>2</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>4</v>
+      </c>
+      <c r="R113" t="n">
+        <v>2</v>
+      </c>
+      <c r="S113" t="n">
+        <v>4</v>
+      </c>
+      <c r="T113" t="n">
+        <v>12</v>
+      </c>
+      <c r="U113" t="n">
+        <v>8</v>
+      </c>
+      <c r="V113" t="n">
+        <v>14</v>
+      </c>
+      <c r="W113" t="n">
+        <v>17</v>
+      </c>
+      <c r="X113" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>64</v>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>Estadio Armando Maestre Pavajeau</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>, Valledupar</t>
+        </is>
+      </c>
+      <c r="AC113" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AU113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB113" t="n">
+        <v>2146</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL113" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN113" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS113" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV113" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW113" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX113" t="n">
+        <v>58</v>
+      </c>
+      <c r="BY113" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ113" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CA113" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CB113" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR113" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS113" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU113" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV113" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX113" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY113" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ113" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA113" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB113" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC113" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD113" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DE113" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DF113" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG113" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DH113" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI113" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DJ113" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK113" t="n">
+        <v>14</v>
+      </c>
+      <c r="DL113" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DM113" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DN113" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DO113" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP113" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW113" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="DX113" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="DY113" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="DZ113" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EA113" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="EB113" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EC113" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="ED113" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="EE113" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EF113" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EG113" t="inlineStr"/>
+      <c r="EH113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>12</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>46100.97222222222</v>
+      </c>
+      <c r="G114" t="n">
+        <v>2</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>2</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" t="n">
+        <v>3</v>
+      </c>
+      <c r="L114" t="n">
+        <v>4</v>
+      </c>
+      <c r="M114" t="n">
+        <v>2</v>
+      </c>
+      <c r="N114" t="n">
+        <v>1</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>5</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
+        <v>7</v>
+      </c>
+      <c r="T114" t="n">
+        <v>9</v>
+      </c>
+      <c r="U114" t="n">
+        <v>12</v>
+      </c>
+      <c r="V114" t="n">
+        <v>9</v>
+      </c>
+      <c r="W114" t="n">
+        <v>13</v>
+      </c>
+      <c r="X114" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Murillo Toro</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
+        </is>
+      </c>
+      <c r="AC114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>2140</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>61</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF114" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV114" t="n">
+        <v>13</v>
+      </c>
+      <c r="BW114" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX114" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY114" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ114" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CA114" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CB114" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CC114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR114" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS114" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU114" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV114" t="n">
+        <v>4</v>
+      </c>
+      <c r="CW114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX114" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY114" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ114" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA114" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB114" t="n">
+        <v>24</v>
+      </c>
+      <c r="DC114" t="n">
+        <v>52</v>
+      </c>
+      <c r="DD114" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DE114" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DF114" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DG114" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DH114" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DI114" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DJ114" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK114" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL114" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DM114" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DN114" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DO114" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP114" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ114" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW114" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="DX114" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="DY114" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="DZ114" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EA114" t="inlineStr">
+        <is>
+          <t>3.98</t>
+        </is>
+      </c>
+      <c r="EB114" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EC114" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="ED114" t="inlineStr">
+        <is>
+          <t>5.81</t>
+        </is>
+      </c>
+      <c r="EE114" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EF114" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EG114" t="inlineStr"/>
+      <c r="EH114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>12</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>46101.0625</v>
+      </c>
+      <c r="G115" t="n">
+        <v>2</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>2</v>
+      </c>
+      <c r="J115" t="n">
+        <v>6</v>
+      </c>
+      <c r="K115" t="n">
+        <v>6</v>
+      </c>
+      <c r="L115" t="n">
+        <v>12</v>
+      </c>
+      <c r="M115" t="n">
+        <v>3</v>
+      </c>
+      <c r="N115" t="n">
+        <v>1</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>7</v>
+      </c>
+      <c r="R115" t="n">
+        <v>2</v>
+      </c>
+      <c r="S115" t="n">
+        <v>11</v>
+      </c>
+      <c r="T115" t="n">
+        <v>9</v>
+      </c>
+      <c r="U115" t="n">
+        <v>18</v>
+      </c>
+      <c r="V115" t="n">
+        <v>11</v>
+      </c>
+      <c r="W115" t="n">
+        <v>16</v>
+      </c>
+      <c r="X115" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>Estadio Atanasio Girardot</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
+        </is>
+      </c>
+      <c r="AC115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>2137</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>72</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ115" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK115" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM115" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN115" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ115" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT115" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV115" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW115" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX115" t="n">
+        <v>77</v>
+      </c>
+      <c r="BY115" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ115" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CA115" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CB115" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="CC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR115" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS115" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU115" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV115" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX115" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY115" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ115" t="n">
+        <v>72</v>
+      </c>
+      <c r="DA115" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB115" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC115" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD115" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DE115" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DF115" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG115" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DH115" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI115" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DJ115" t="n">
+        <v>29</v>
+      </c>
+      <c r="DK115" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL115" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM115" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DN115" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="DO115" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP115" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ115" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW115" t="inlineStr"/>
+      <c r="DX115" t="inlineStr"/>
+      <c r="DY115" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="DZ115" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EA115" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EB115" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EC115" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="ED115" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="EE115" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="EF115" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EG115" t="inlineStr"/>
+      <c r="EH115" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH115" headerRowCount="1">
-  <autoFilter ref="A1:EH115"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH119" headerRowCount="1">
+  <autoFilter ref="A1:EH119"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -280,8 +280,8 @@
     <tableColumn id="134" name="pinnacle_ft_2"/>
     <tableColumn id="135" name="pinnacle_ft_x"/>
     <tableColumn id="136" name="pinnacle_ft_1"/>
-    <tableColumn id="137" name="pinnacle_corners_over_95"/>
-    <tableColumn id="138" name="pinnacle_corners_under_95"/>
+    <tableColumn id="137" name="pinnacle_corners_under_95"/>
+    <tableColumn id="138" name="pinnacle_corners_over_95"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH115"/>
+  <dimension ref="A1:EH119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -715,8 +715,8 @@
     <col width="18" customWidth="1" min="134" max="134"/>
     <col width="18" customWidth="1" min="135" max="135"/>
     <col width="18" customWidth="1" min="136" max="136"/>
-    <col width="31.2" customWidth="1" min="137" max="137"/>
-    <col width="32.4" customWidth="1" min="138" max="138"/>
+    <col width="32.4" customWidth="1" min="137" max="137"/>
+    <col width="31.2" customWidth="1" min="138" max="138"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="EG1" s="1" t="inlineStr">
         <is>
+          <t>pinnacle_corners_under_95</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
           <t>pinnacle_corners_over_95</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_corners_under_95</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
         <v>1.17</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="EG3" t="inlineStr">
         <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
           <t>1.94</t>
-        </is>
-      </c>
-      <c r="EH3" t="inlineStr">
-        <is>
-          <t>1.79</t>
         </is>
       </c>
     </row>
@@ -2626,10 +2626,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3030,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE5" t="n">
         <v>0.64</v>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="EG5" t="inlineStr">
         <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
           <t>1.90</t>
-        </is>
-      </c>
-      <c r="EH5" t="inlineStr">
-        <is>
-          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
         <v>1.73</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -4349,7 +4349,7 @@
         <v>0.83</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>1.09</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5665,7 +5665,7 @@
         <v>0.58</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DE12" t="n">
         <v>0.58</v>
@@ -6525,7 +6525,7 @@
         <v>1.73</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6622,12 +6622,12 @@
       </c>
       <c r="EG13" t="inlineStr">
         <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EH13" t="inlineStr">
+        <is>
           <t>1.80</t>
-        </is>
-      </c>
-      <c r="EH13" t="inlineStr">
-        <is>
-          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -7510,12 +7510,12 @@
       </c>
       <c r="EG15" t="inlineStr">
         <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH15" t="inlineStr">
+        <is>
           <t>1.84</t>
-        </is>
-      </c>
-      <c r="EH15" t="inlineStr">
-        <is>
-          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DE16" t="n">
         <v>1.18</v>
@@ -8285,7 +8285,7 @@
         <v>0.64</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>2.13</v>
       </c>
       <c r="DO17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -8718,7 +8718,7 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE18" t="n">
         <v>2</v>
@@ -8751,7 +8751,7 @@
         <v>1.44</v>
       </c>
       <c r="DO18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9154,7 +9154,7 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DE19" t="n">
         <v>1.58</v>
@@ -9590,7 +9590,7 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DE20" t="n">
         <v>1.09</v>
@@ -11350,7 +11350,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DE24" t="n">
         <v>0.64</v>
@@ -11886,12 +11886,12 @@
       </c>
       <c r="EG25" t="inlineStr">
         <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EH25" t="inlineStr">
+        <is>
           <t>1.91</t>
-        </is>
-      </c>
-      <c r="EH25" t="inlineStr">
-        <is>
-          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -12233,7 +12233,7 @@
         <v>2</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -12666,10 +12666,10 @@
         <v>75</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DF27" t="n">
         <v>0.5</v>
@@ -12699,7 +12699,7 @@
         <v>2.21</v>
       </c>
       <c r="DO27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13105,7 +13105,7 @@
         <v>0.83</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -13546,10 +13546,10 @@
         <v>75</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -13579,7 +13579,7 @@
         <v>3.03</v>
       </c>
       <c r="DO29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -13646,12 +13646,12 @@
       </c>
       <c r="EG29" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EH29" t="inlineStr">
+        <is>
           <t>1.95</t>
-        </is>
-      </c>
-      <c r="EH29" t="inlineStr">
-        <is>
-          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -14865,7 +14865,7 @@
         <v>1.73</v>
       </c>
       <c r="DE32" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF32" t="n">
         <v>1.67</v>
@@ -15298,7 +15298,7 @@
         <v>50</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DE33" t="n">
         <v>2</v>
@@ -15742,7 +15742,7 @@
         <v>59</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DE34" t="n">
         <v>0.83</v>
@@ -16181,7 +16181,7 @@
         <v>1.25</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF35" t="n">
         <v>1.67</v>
@@ -16211,7 +16211,7 @@
         <v>2.16</v>
       </c>
       <c r="DO35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -16614,7 +16614,7 @@
         <v>84</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DE36" t="n">
         <v>1.18</v>
@@ -17050,7 +17050,7 @@
         <v>84</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DE37" t="n">
         <v>1.73</v>
@@ -17930,10 +17930,10 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF39" t="n">
         <v>3</v>
@@ -17963,7 +17963,7 @@
         <v>3.9</v>
       </c>
       <c r="DO39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -18801,7 +18801,7 @@
         <v>1.18</v>
       </c>
       <c r="DE41" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DF41" t="n">
         <v>0.5</v>
@@ -19234,7 +19234,7 @@
         <v>88</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE42" t="n">
         <v>0.58</v>
@@ -19267,7 +19267,7 @@
         <v>2.02</v>
       </c>
       <c r="DO42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20958,10 +20958,10 @@
         <v>50</v>
       </c>
       <c r="DD46" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DF46" t="n">
         <v>0.25</v>
@@ -20991,7 +20991,7 @@
         <v>2.87</v>
       </c>
       <c r="DO46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -21402,10 +21402,10 @@
         <v>63</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF47" t="n">
         <v>1.5</v>
@@ -21435,7 +21435,7 @@
         <v>2.48</v>
       </c>
       <c r="DO47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP47" t="b">
         <v>0</v>
@@ -23602,10 +23602,10 @@
         <v>70</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF52" t="n">
         <v>0.4</v>
@@ -23635,7 +23635,7 @@
         <v>2.56</v>
       </c>
       <c r="DO52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -23702,12 +23702,12 @@
       </c>
       <c r="EG52" t="inlineStr">
         <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH52" t="inlineStr">
+        <is>
           <t>1.85</t>
-        </is>
-      </c>
-      <c r="EH52" t="inlineStr">
-        <is>
-          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -24046,10 +24046,10 @@
         <v>60</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -24079,7 +24079,7 @@
         <v>2.58</v>
       </c>
       <c r="DO53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -24582,12 +24582,12 @@
       </c>
       <c r="EG54" t="inlineStr">
         <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EH54" t="inlineStr">
+        <is>
           <t>1.94</t>
-        </is>
-      </c>
-      <c r="EH54" t="inlineStr">
-        <is>
-          <t>1.79</t>
         </is>
       </c>
     </row>
@@ -24926,7 +24926,7 @@
         <v>80</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DE55" t="n">
         <v>1.58</v>
@@ -25026,12 +25026,12 @@
       </c>
       <c r="EG55" t="inlineStr">
         <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EH55" t="inlineStr">
+        <is>
           <t>1.78</t>
-        </is>
-      </c>
-      <c r="EH55" t="inlineStr">
-        <is>
-          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -25370,7 +25370,7 @@
         <v>70</v>
       </c>
       <c r="DD56" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE56" t="n">
         <v>1.17</v>
@@ -25403,7 +25403,7 @@
         <v>4.13</v>
       </c>
       <c r="DO56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -25806,7 +25806,7 @@
         <v>70</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE57" t="n">
         <v>1.09</v>
@@ -25839,7 +25839,7 @@
         <v>2.74</v>
       </c>
       <c r="DO57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -26250,7 +26250,7 @@
         <v>59</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DE58" t="n">
         <v>1.25</v>
@@ -26350,12 +26350,12 @@
       </c>
       <c r="EG58" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EH58" t="inlineStr">
+        <is>
           <t>1.95</t>
-        </is>
-      </c>
-      <c r="EH58" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -26802,12 +26802,12 @@
       </c>
       <c r="EG59" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EH59" t="inlineStr">
+        <is>
           <t>1.95</t>
-        </is>
-      </c>
-      <c r="EH59" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -27149,7 +27149,7 @@
         <v>2</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DF60" t="n">
         <v>2.17</v>
@@ -27593,7 +27593,7 @@
         <v>1.73</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DF61" t="n">
         <v>1.5</v>
@@ -28026,10 +28026,10 @@
         <v>75</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DE62" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DF62" t="n">
         <v>1.17</v>
@@ -28059,7 +28059,7 @@
         <v>3.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -28898,7 +28898,7 @@
         <v>60</v>
       </c>
       <c r="DD64" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DE64" t="n">
         <v>0.58</v>
@@ -28931,7 +28931,7 @@
         <v>1.97</v>
       </c>
       <c r="DO64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -29769,7 +29769,7 @@
         <v>1.58</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF66" t="n">
         <v>1.8</v>
@@ -29799,7 +29799,7 @@
         <v>3.08</v>
       </c>
       <c r="DO66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31090,7 +31090,7 @@
         <v>57</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DE69" t="n">
         <v>1.17</v>
@@ -31529,7 +31529,7 @@
         <v>1.73</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DF70" t="n">
         <v>1.67</v>
@@ -31962,10 +31962,10 @@
         <v>54</v>
       </c>
       <c r="DD71" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE71" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF71" t="n">
         <v>2.25</v>
@@ -31995,7 +31995,7 @@
         <v>3.31</v>
       </c>
       <c r="DO71" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -32398,10 +32398,10 @@
         <v>64</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF72" t="n">
         <v>2</v>
@@ -32431,7 +32431,7 @@
         <v>2.49</v>
       </c>
       <c r="DO72" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -33273,7 +33273,7 @@
         <v>0.64</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF74" t="n">
         <v>0.57</v>
@@ -33303,7 +33303,7 @@
         <v>2.19</v>
       </c>
       <c r="DO74" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -33706,7 +33706,7 @@
         <v>83</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE75" t="n">
         <v>0.83</v>
@@ -33739,7 +33739,7 @@
         <v>2.17</v>
       </c>
       <c r="DO75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -34589,7 +34589,7 @@
         <v>1.09</v>
       </c>
       <c r="DE77" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DF77" t="n">
         <v>1.25</v>
@@ -35022,7 +35022,7 @@
         <v>61</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DE78" t="n">
         <v>0.45</v>
@@ -35458,7 +35458,7 @@
         <v>63</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DE79" t="n">
         <v>0.64</v>
@@ -35558,12 +35558,12 @@
       </c>
       <c r="EG79" t="inlineStr">
         <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
           <t>1.88</t>
-        </is>
-      </c>
-      <c r="EH79" t="inlineStr">
-        <is>
-          <t>1.84</t>
         </is>
       </c>
     </row>
@@ -35902,10 +35902,10 @@
         <v>65</v>
       </c>
       <c r="DD80" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF80" t="n">
         <v>0.43</v>
@@ -35935,7 +35935,7 @@
         <v>2.69</v>
       </c>
       <c r="DO80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -37670,10 +37670,10 @@
         <v>60</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DF84" t="n">
         <v>1.57</v>
@@ -37703,7 +37703,7 @@
         <v>2.54</v>
       </c>
       <c r="DO84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP84" t="b">
         <v>0</v>
@@ -38106,7 +38106,7 @@
         <v>51</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DE85" t="n">
         <v>1.17</v>
@@ -38545,7 +38545,7 @@
         <v>1.73</v>
       </c>
       <c r="DE86" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DF86" t="n">
         <v>1.5</v>
@@ -39417,7 +39417,7 @@
         <v>1.25</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DF88" t="n">
         <v>1.25</v>
@@ -39514,12 +39514,12 @@
       </c>
       <c r="EG88" t="inlineStr">
         <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EH88" t="inlineStr">
+        <is>
           <t>1.88</t>
-        </is>
-      </c>
-      <c r="EH88" t="inlineStr">
-        <is>
-          <t>1.84</t>
         </is>
       </c>
     </row>
@@ -39861,7 +39861,7 @@
         <v>1.58</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF89" t="n">
         <v>1.88</v>
@@ -39891,7 +39891,7 @@
         <v>2.77</v>
       </c>
       <c r="DO89" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -39958,12 +39958,12 @@
       </c>
       <c r="EG89" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EH89" t="inlineStr">
+        <is>
           <t>1.96</t>
-        </is>
-      </c>
-      <c r="EH89" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -40302,10 +40302,10 @@
         <v>56</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DF90" t="n">
         <v>1.33</v>
@@ -40335,7 +40335,7 @@
         <v>2.91</v>
       </c>
       <c r="DO90" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -40402,12 +40402,12 @@
       </c>
       <c r="EG90" t="inlineStr">
         <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EH90" t="inlineStr">
+        <is>
           <t>1.87</t>
-        </is>
-      </c>
-      <c r="EH90" t="inlineStr">
-        <is>
-          <t>1.86</t>
         </is>
       </c>
     </row>
@@ -40746,10 +40746,10 @@
         <v>61</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE91" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DF91" t="n">
         <v>1.5</v>
@@ -40779,7 +40779,7 @@
         <v>3.05</v>
       </c>
       <c r="DO91" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -41290,12 +41290,12 @@
       </c>
       <c r="EG92" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH92" t="inlineStr">
+        <is>
           <t>1.76</t>
-        </is>
-      </c>
-      <c r="EH92" t="inlineStr">
-        <is>
-          <t>1.96</t>
         </is>
       </c>
     </row>
@@ -41634,7 +41634,7 @@
         <v>78</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DE93" t="n">
         <v>0.58</v>
@@ -41734,12 +41734,12 @@
       </c>
       <c r="EG93" t="inlineStr">
         <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EH93" t="inlineStr">
+        <is>
           <t>1.92</t>
-        </is>
-      </c>
-      <c r="EH93" t="inlineStr">
-        <is>
-          <t>1.81</t>
         </is>
       </c>
     </row>
@@ -42081,7 +42081,7 @@
         <v>2</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF94" t="n">
         <v>2</v>
@@ -42111,7 +42111,7 @@
         <v>2.91</v>
       </c>
       <c r="DO94" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -42961,7 +42961,7 @@
         <v>1.58</v>
       </c>
       <c r="DE96" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DF96" t="n">
         <v>1.78</v>
@@ -42991,7 +42991,7 @@
         <v>3.39</v>
       </c>
       <c r="DO96" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -43394,7 +43394,7 @@
         <v>70</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DE97" t="n">
         <v>2</v>
@@ -43830,7 +43830,7 @@
         <v>74</v>
       </c>
       <c r="DD98" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE98" t="n">
         <v>1.25</v>
@@ -43863,7 +43863,7 @@
         <v>2.76</v>
       </c>
       <c r="DO98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -43930,12 +43930,12 @@
       </c>
       <c r="EG98" t="inlineStr">
         <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EH98" t="inlineStr">
+        <is>
           <t>1.87</t>
-        </is>
-      </c>
-      <c r="EH98" t="inlineStr">
-        <is>
-          <t>1.85</t>
         </is>
       </c>
     </row>
@@ -44274,7 +44274,7 @@
         <v>64</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DE99" t="n">
         <v>1.73</v>
@@ -44721,7 +44721,7 @@
         <v>0.58</v>
       </c>
       <c r="DE100" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DF100" t="n">
         <v>0.6</v>
@@ -44818,12 +44818,12 @@
       </c>
       <c r="EG100" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EH100" t="inlineStr">
+        <is>
           <t>1.92</t>
-        </is>
-      </c>
-      <c r="EH100" t="inlineStr">
-        <is>
-          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -45157,7 +45157,7 @@
         <v>0.64</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DF101" t="n">
         <v>0.44</v>
@@ -45593,7 +45593,7 @@
         <v>1.09</v>
       </c>
       <c r="DE102" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DF102" t="n">
         <v>1.11</v>
@@ -46029,7 +46029,7 @@
         <v>0.45</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF103" t="n">
         <v>0.44</v>
@@ -46059,7 +46059,7 @@
         <v>2.12</v>
       </c>
       <c r="DO103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -46470,7 +46470,7 @@
         <v>61</v>
       </c>
       <c r="DD104" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE104" t="n">
         <v>1.73</v>
@@ -46503,7 +46503,7 @@
         <v>2.83</v>
       </c>
       <c r="DO104" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -47886,12 +47886,12 @@
       </c>
       <c r="EG107" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EH107" t="inlineStr">
+        <is>
           <t>1.96</t>
-        </is>
-      </c>
-      <c r="EH107" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -48230,10 +48230,10 @@
         <v>68</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DE108" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DF108" t="n">
         <v>1.27</v>
@@ -48263,7 +48263,7 @@
         <v>3.19</v>
       </c>
       <c r="DO108" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -49110,7 +49110,7 @@
         <v>63</v>
       </c>
       <c r="DD110" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DE110" t="n">
         <v>0.45</v>
@@ -49557,7 +49557,7 @@
         <v>1.73</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DF111" t="n">
         <v>1.8</v>
@@ -49990,7 +49990,7 @@
         <v>53</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DE112" t="n">
         <v>1.09</v>
@@ -50276,7 +50276,7 @@
         <v>0</v>
       </c>
       <c r="BF113" t="n">
-        <v>-1</v>
+        <v>1000</v>
       </c>
       <c r="BG113" t="n">
         <v>2</v>
@@ -50426,7 +50426,7 @@
         <v>71</v>
       </c>
       <c r="DD113" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="DE113" t="n">
         <v>0.83</v>
@@ -50459,7 +50459,7 @@
         <v>2.1</v>
       </c>
       <c r="DO113" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -50720,7 +50720,7 @@
         <v>0</v>
       </c>
       <c r="BF114" t="n">
-        <v>-1</v>
+        <v>5000</v>
       </c>
       <c r="BG114" t="n">
         <v>2</v>
@@ -51414,6 +51414,1790 @@
       </c>
       <c r="EG115" t="inlineStr"/>
       <c r="EH115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>12</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Rionegro Águilas</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>46101.875</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" t="n">
+        <v>7</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" t="n">
+        <v>8</v>
+      </c>
+      <c r="M116" t="n">
+        <v>3</v>
+      </c>
+      <c r="N116" t="n">
+        <v>2</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>3</v>
+      </c>
+      <c r="R116" t="n">
+        <v>1</v>
+      </c>
+      <c r="S116" t="n">
+        <v>9</v>
+      </c>
+      <c r="T116" t="n">
+        <v>5</v>
+      </c>
+      <c r="U116" t="n">
+        <v>12</v>
+      </c>
+      <c r="V116" t="n">
+        <v>6</v>
+      </c>
+      <c r="W116" t="n">
+        <v>13</v>
+      </c>
+      <c r="X116" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>Estadio Alberto Grisales</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>Route 45A, Rionegro, Antioquia</t>
+        </is>
+      </c>
+      <c r="AC116" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>2141</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK116" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM116" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN116" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ116" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR116" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT116" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV116" t="n">
+        <v>78</v>
+      </c>
+      <c r="BW116" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX116" t="n">
+        <v>113</v>
+      </c>
+      <c r="BY116" t="n">
+        <v>68</v>
+      </c>
+      <c r="BZ116" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CA116" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="CB116" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR116" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS116" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU116" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV116" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX116" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY116" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ116" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA116" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB116" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC116" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD116" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DE116" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DF116" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG116" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DH116" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI116" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DJ116" t="n">
+        <v>55</v>
+      </c>
+      <c r="DK116" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL116" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DM116" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DN116" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="DO116" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP116" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW116" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="DX116" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="DY116" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="DZ116" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EA116" t="inlineStr">
+        <is>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="EB116" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EC116" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="ED116" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EE116" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="EF116" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EG116" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EH116" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>13</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>46102.97222222222</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>4</v>
+      </c>
+      <c r="I117" t="n">
+        <v>5</v>
+      </c>
+      <c r="J117" t="n">
+        <v>4</v>
+      </c>
+      <c r="K117" t="n">
+        <v>4</v>
+      </c>
+      <c r="L117" t="n">
+        <v>8</v>
+      </c>
+      <c r="M117" t="n">
+        <v>2</v>
+      </c>
+      <c r="N117" t="n">
+        <v>3</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>3</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7</v>
+      </c>
+      <c r="S117" t="n">
+        <v>15</v>
+      </c>
+      <c r="T117" t="n">
+        <v>11</v>
+      </c>
+      <c r="U117" t="n">
+        <v>18</v>
+      </c>
+      <c r="V117" t="n">
+        <v>18</v>
+      </c>
+      <c r="W117" t="n">
+        <v>2</v>
+      </c>
+      <c r="X117" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>Estadio Palogrande</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>Carrera 24 # 64 - 00, Manizales</t>
+        </is>
+      </c>
+      <c r="AC117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>2136</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>71</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>123</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>60</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>9</v>
+      </c>
+      <c r="CT117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX117" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY117" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ117" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA117" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB117" t="n">
+        <v>46</v>
+      </c>
+      <c r="DC117" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD117" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DE117" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DF117" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DG117" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DH117" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DI117" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DJ117" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK117" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL117" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DM117" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DN117" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="DO117" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW117" t="inlineStr"/>
+      <c r="DX117" t="inlineStr"/>
+      <c r="DY117" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="DZ117" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EA117" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EB117" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EC117" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="ED117" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="EE117" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EF117" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EG117" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EH117" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>13</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>La Equidad</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>46103.0625</v>
+      </c>
+      <c r="G118" t="n">
+        <v>3</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>3</v>
+      </c>
+      <c r="J118" t="n">
+        <v>6</v>
+      </c>
+      <c r="K118" t="n">
+        <v>4</v>
+      </c>
+      <c r="L118" t="n">
+        <v>10</v>
+      </c>
+      <c r="M118" t="n">
+        <v>3</v>
+      </c>
+      <c r="N118" t="n">
+        <v>2</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>8</v>
+      </c>
+      <c r="R118" t="n">
+        <v>1</v>
+      </c>
+      <c r="S118" t="n">
+        <v>14</v>
+      </c>
+      <c r="T118" t="n">
+        <v>10</v>
+      </c>
+      <c r="U118" t="n">
+        <v>22</v>
+      </c>
+      <c r="V118" t="n">
+        <v>11</v>
+      </c>
+      <c r="W118" t="n">
+        <v>7</v>
+      </c>
+      <c r="X118" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>Estadio Atanasio Girardot</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
+        </is>
+      </c>
+      <c r="AC118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>2142</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>52</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>111</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>57</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU118" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV118" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX118" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY118" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ118" t="n">
+        <v>66</v>
+      </c>
+      <c r="DA118" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB118" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC118" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD118" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DE118" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DF118" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DG118" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH118" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DI118" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ118" t="n">
+        <v>35</v>
+      </c>
+      <c r="DK118" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL118" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DM118" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DN118" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DO118" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP118" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ118" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR118" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW118" t="inlineStr"/>
+      <c r="DX118" t="inlineStr"/>
+      <c r="DY118" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="DZ118" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="EA118" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EB118" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EC118" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="ED118" t="inlineStr">
+        <is>
+          <t>7.57</t>
+        </is>
+      </c>
+      <c r="EE118" t="inlineStr">
+        <is>
+          <t>4.53</t>
+        </is>
+      </c>
+      <c r="EF118" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EG118" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EH118" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>13</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Alianza Petrolera</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>46103.875</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" t="n">
+        <v>2</v>
+      </c>
+      <c r="K119" t="n">
+        <v>6</v>
+      </c>
+      <c r="L119" t="n">
+        <v>8</v>
+      </c>
+      <c r="M119" t="n">
+        <v>2</v>
+      </c>
+      <c r="N119" t="n">
+        <v>1</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>4</v>
+      </c>
+      <c r="R119" t="n">
+        <v>1</v>
+      </c>
+      <c r="S119" t="n">
+        <v>3</v>
+      </c>
+      <c r="T119" t="n">
+        <v>6</v>
+      </c>
+      <c r="U119" t="n">
+        <v>7</v>
+      </c>
+      <c r="V119" t="n">
+        <v>7</v>
+      </c>
+      <c r="W119" t="n">
+        <v>13</v>
+      </c>
+      <c r="X119" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>Estadio Armando Maestre Pavajeau</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>, Valledupar</t>
+        </is>
+      </c>
+      <c r="AC119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>2146</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>105</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU119" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV119" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX119" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY119" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ119" t="n">
+        <v>30</v>
+      </c>
+      <c r="DA119" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB119" t="n">
+        <v>27</v>
+      </c>
+      <c r="DC119" t="n">
+        <v>57</v>
+      </c>
+      <c r="DD119" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DE119" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DF119" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DG119" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH119" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DI119" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DJ119" t="n">
+        <v>70</v>
+      </c>
+      <c r="DK119" t="n">
+        <v>26</v>
+      </c>
+      <c r="DL119" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DM119" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DN119" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="DO119" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW119" t="inlineStr"/>
+      <c r="DX119" t="inlineStr"/>
+      <c r="DY119" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="DZ119" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EA119" t="inlineStr">
+        <is>
+          <t>4.83</t>
+        </is>
+      </c>
+      <c r="EB119" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="ED119" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="EE119" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EF119" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EG119" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EH119" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH119" headerRowCount="1">
-  <autoFilter ref="A1:EH119"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH125" headerRowCount="1">
+  <autoFilter ref="A1:EH125"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH119"/>
+  <dimension ref="A1:EH125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1746,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DE2" t="n">
         <v>1.25</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2182,7 +2182,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DE3" t="n">
         <v>0.92</v>
@@ -3033,7 +3033,7 @@
         <v>2.25</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DE6" t="n">
         <v>1.54</v>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -3910,10 +3910,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DE8" t="n">
         <v>1.23</v>
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4790,10 +4790,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4823,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DE11" t="n">
         <v>1.77</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6109,7 +6109,7 @@
         <v>1.62</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
         <v>1.82</v>
       </c>
       <c r="DO12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6522,7 +6522,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DE13" t="n">
         <v>0.92</v>
@@ -6555,7 +6555,7 @@
         <v>1.86</v>
       </c>
       <c r="DO13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -6966,10 +6966,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -6999,7 +6999,7 @@
         <v>1.99</v>
       </c>
       <c r="DO14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP14" t="b">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>1.25</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7435,7 +7435,7 @@
         <v>3.19</v>
       </c>
       <c r="DO15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -7857,7 +7857,7 @@
         <v>1.23</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -7887,7 +7887,7 @@
         <v>2.53</v>
       </c>
       <c r="DO16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8282,7 +8282,7 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DE17" t="n">
         <v>1.82</v>
@@ -8718,10 +8718,10 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE18" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DF18" t="n">
         <v>1</v>
@@ -8751,7 +8751,7 @@
         <v>1.44</v>
       </c>
       <c r="DO18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9157,7 +9157,7 @@
         <v>1.54</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9187,7 +9187,7 @@
         <v>2.56</v>
       </c>
       <c r="DO19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9593,7 +9593,7 @@
         <v>1.77</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -9623,7 +9623,7 @@
         <v>4.47</v>
       </c>
       <c r="DO20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10026,10 +10026,10 @@
         <v>100</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10059,7 +10059,7 @@
         <v>2.47</v>
       </c>
       <c r="DO21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10470,7 +10470,7 @@
         <v>25</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DE22" t="n">
         <v>1.25</v>
@@ -10914,10 +10914,10 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DF23" t="n">
         <v>0</v>
@@ -10947,7 +10947,7 @@
         <v>2.38</v>
       </c>
       <c r="DO23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11353,7 +11353,7 @@
         <v>0.92</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -11383,7 +11383,7 @@
         <v>1.88</v>
       </c>
       <c r="DO24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -11786,10 +11786,10 @@
         <v>25</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -11819,7 +11819,7 @@
         <v>2.57</v>
       </c>
       <c r="DO25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12230,7 +12230,7 @@
         <v>75</v>
       </c>
       <c r="DD26" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DE26" t="n">
         <v>1.54</v>
@@ -12263,7 +12263,7 @@
         <v>2.13</v>
       </c>
       <c r="DO26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -12666,7 +12666,7 @@
         <v>75</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE27" t="n">
         <v>1.23</v>
@@ -12699,7 +12699,7 @@
         <v>2.21</v>
       </c>
       <c r="DO27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13102,7 +13102,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DE28" t="n">
         <v>1.62</v>
@@ -13135,7 +13135,7 @@
         <v>2.03</v>
       </c>
       <c r="DO28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -13990,10 +13990,10 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF30" t="n">
         <v>0.33</v>
@@ -14023,7 +14023,7 @@
         <v>2.24</v>
       </c>
       <c r="DO30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14418,10 +14418,10 @@
         <v>67</v>
       </c>
       <c r="DD31" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DF31" t="n">
         <v>0.33</v>
@@ -14451,7 +14451,7 @@
         <v>2.8</v>
       </c>
       <c r="DO31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -14862,7 +14862,7 @@
         <v>50</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DE32" t="n">
         <v>0.92</v>
@@ -14895,7 +14895,7 @@
         <v>2.62</v>
       </c>
       <c r="DO32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15301,7 +15301,7 @@
         <v>1.23</v>
       </c>
       <c r="DE33" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DF33" t="n">
         <v>1</v>
@@ -15331,7 +15331,7 @@
         <v>2.29</v>
       </c>
       <c r="DO33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -15745,7 +15745,7 @@
         <v>1.77</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF34" t="n">
         <v>1.67</v>
@@ -15775,7 +15775,7 @@
         <v>2.49</v>
       </c>
       <c r="DO34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -16181,7 +16181,7 @@
         <v>1.25</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DF35" t="n">
         <v>1.67</v>
@@ -16211,7 +16211,7 @@
         <v>2.16</v>
       </c>
       <c r="DO35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -16617,7 +16617,7 @@
         <v>1.54</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="DF36" t="n">
         <v>0</v>
@@ -16647,7 +16647,7 @@
         <v>2.84</v>
       </c>
       <c r="DO36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP36" t="b">
         <v>0</v>
@@ -17053,7 +17053,7 @@
         <v>1.62</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DF37" t="n">
         <v>2</v>
@@ -17083,7 +17083,7 @@
         <v>2.43</v>
       </c>
       <c r="DO37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -17494,10 +17494,10 @@
         <v>67</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF38" t="n">
         <v>0.67</v>
@@ -17527,7 +17527,7 @@
         <v>2.42</v>
       </c>
       <c r="DO38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18366,10 +18366,10 @@
         <v>88</v>
       </c>
       <c r="DD40" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF40" t="n">
         <v>2.25</v>
@@ -18399,7 +18399,7 @@
         <v>2.56</v>
       </c>
       <c r="DO40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP40" t="b">
         <v>0</v>
@@ -18798,7 +18798,7 @@
         <v>63</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="DE41" t="n">
         <v>1.62</v>
@@ -18831,7 +18831,7 @@
         <v>2.9</v>
       </c>
       <c r="DO41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -19234,10 +19234,10 @@
         <v>88</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DF42" t="n">
         <v>1.25</v>
@@ -19267,7 +19267,7 @@
         <v>2.02</v>
       </c>
       <c r="DO42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -19670,7 +19670,7 @@
         <v>63</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DE43" t="n">
         <v>1.25</v>
@@ -19703,7 +19703,7 @@
         <v>1.9</v>
       </c>
       <c r="DO43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20106,10 +20106,10 @@
         <v>50</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DF44" t="n">
         <v>1.5</v>
@@ -20139,7 +20139,7 @@
         <v>3.37</v>
       </c>
       <c r="DO44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -20522,10 +20522,10 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DF45" t="n">
         <v>2</v>
@@ -20555,7 +20555,7 @@
         <v>2.5</v>
       </c>
       <c r="DO45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -21826,10 +21826,10 @@
         <v>59</v>
       </c>
       <c r="DD48" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF48" t="n">
         <v>1.33</v>
@@ -21859,7 +21859,7 @@
         <v>1.75</v>
       </c>
       <c r="DO48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -22270,10 +22270,10 @@
         <v>80</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="DF49" t="n">
         <v>0.4</v>
@@ -22303,7 +22303,7 @@
         <v>2.37</v>
       </c>
       <c r="DO49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -22717,7 +22717,7 @@
         <v>1.25</v>
       </c>
       <c r="DE50" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DF50" t="n">
         <v>1.8</v>
@@ -23158,10 +23158,10 @@
         <v>60</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DF51" t="n">
         <v>1.8</v>
@@ -23191,7 +23191,7 @@
         <v>2.38</v>
       </c>
       <c r="DO51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP51" t="b">
         <v>0</v>
@@ -23605,7 +23605,7 @@
         <v>1.54</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DF52" t="n">
         <v>0.4</v>
@@ -23635,7 +23635,7 @@
         <v>2.56</v>
       </c>
       <c r="DO52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -24474,10 +24474,10 @@
         <v>68</v>
       </c>
       <c r="DD54" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF54" t="n">
         <v>0.2</v>
@@ -24507,7 +24507,7 @@
         <v>1.66</v>
       </c>
       <c r="DO54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -24929,7 +24929,7 @@
         <v>1.77</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF55" t="n">
         <v>1.4</v>
@@ -24959,7 +24959,7 @@
         <v>3.39</v>
       </c>
       <c r="DO55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -25373,7 +25373,7 @@
         <v>2.25</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF56" t="n">
         <v>3</v>
@@ -25809,7 +25809,7 @@
         <v>1.82</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DF57" t="n">
         <v>1.75</v>
@@ -26694,10 +26694,10 @@
         <v>64</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF59" t="n">
         <v>0.83</v>
@@ -26727,7 +26727,7 @@
         <v>2.53</v>
       </c>
       <c r="DO59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -27146,7 +27146,7 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DE60" t="n">
         <v>1.62</v>
@@ -27179,7 +27179,7 @@
         <v>2.31</v>
       </c>
       <c r="DO60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -27590,7 +27590,7 @@
         <v>50</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DE61" t="n">
         <v>1.77</v>
@@ -27623,7 +27623,7 @@
         <v>2.63</v>
       </c>
       <c r="DO61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -28462,10 +28462,10 @@
         <v>59</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DF63" t="n">
         <v>1.17</v>
@@ -28495,7 +28495,7 @@
         <v>2.4</v>
       </c>
       <c r="DO63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -28901,7 +28901,7 @@
         <v>0.92</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DF64" t="n">
         <v>0.4</v>
@@ -29334,10 +29334,10 @@
         <v>57</v>
       </c>
       <c r="DD65" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DF65" t="n">
         <v>1.4</v>
@@ -29367,7 +29367,7 @@
         <v>2.22</v>
       </c>
       <c r="DO65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -29766,7 +29766,7 @@
         <v>90</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE66" t="n">
         <v>1.82</v>
@@ -30205,7 +30205,7 @@
         <v>1.25</v>
       </c>
       <c r="DE67" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="DF67" t="n">
         <v>1.29</v>
@@ -30235,7 +30235,7 @@
         <v>2.55</v>
       </c>
       <c r="DO67" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -30646,10 +30646,10 @@
         <v>62</v>
       </c>
       <c r="DD68" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DE68" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DF68" t="n">
         <v>0.5</v>
@@ -30679,7 +30679,7 @@
         <v>1.99</v>
       </c>
       <c r="DO68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -31093,7 +31093,7 @@
         <v>1.77</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF69" t="n">
         <v>1.43</v>
@@ -31123,7 +31123,7 @@
         <v>3.02</v>
       </c>
       <c r="DO69" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -31526,7 +31526,7 @@
         <v>55</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DE70" t="n">
         <v>1.23</v>
@@ -31559,7 +31559,7 @@
         <v>2.63</v>
       </c>
       <c r="DO70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP70" t="b">
         <v>0</v>
@@ -32842,10 +32842,10 @@
         <v>72</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -32875,7 +32875,7 @@
         <v>3.26</v>
       </c>
       <c r="DO73" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -33270,10 +33270,10 @@
         <v>69</v>
       </c>
       <c r="DD74" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DF74" t="n">
         <v>0.57</v>
@@ -33303,7 +33303,7 @@
         <v>2.19</v>
       </c>
       <c r="DO74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -33709,7 +33709,7 @@
         <v>1.82</v>
       </c>
       <c r="DE75" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF75" t="n">
         <v>1.67</v>
@@ -34142,10 +34142,10 @@
         <v>65</v>
       </c>
       <c r="DD76" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DF76" t="n">
         <v>0.43</v>
@@ -34175,7 +34175,7 @@
         <v>2.09</v>
       </c>
       <c r="DO76" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -34586,7 +34586,7 @@
         <v>65</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DE77" t="n">
         <v>2.25</v>
@@ -34619,7 +34619,7 @@
         <v>3.5</v>
       </c>
       <c r="DO77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -35025,7 +35025,7 @@
         <v>1.54</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF78" t="n">
         <v>1</v>
@@ -35055,7 +35055,7 @@
         <v>2.25</v>
       </c>
       <c r="DO78" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -35461,7 +35461,7 @@
         <v>1.77</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DF79" t="n">
         <v>1.63</v>
@@ -35491,7 +35491,7 @@
         <v>2.48</v>
       </c>
       <c r="DO79" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -36346,10 +36346,10 @@
         <v>93</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF81" t="n">
         <v>1.43</v>
@@ -36379,7 +36379,7 @@
         <v>2.39</v>
       </c>
       <c r="DO81" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -36790,10 +36790,10 @@
         <v>60</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF82" t="n">
         <v>0.88</v>
@@ -36823,7 +36823,7 @@
         <v>2.82</v>
       </c>
       <c r="DO82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -37234,10 +37234,10 @@
         <v>82</v>
       </c>
       <c r="DD83" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DF83" t="n">
         <v>1.88</v>
@@ -37267,7 +37267,7 @@
         <v>2.12</v>
       </c>
       <c r="DO83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -37670,7 +37670,7 @@
         <v>60</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE84" t="n">
         <v>1.62</v>
@@ -37703,7 +37703,7 @@
         <v>2.54</v>
       </c>
       <c r="DO84" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP84" t="b">
         <v>0</v>
@@ -38109,7 +38109,7 @@
         <v>1.23</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF85" t="n">
         <v>1.38</v>
@@ -38139,7 +38139,7 @@
         <v>2.74</v>
       </c>
       <c r="DO85" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -38542,7 +38542,7 @@
         <v>61</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DE86" t="n">
         <v>2.25</v>
@@ -38575,7 +38575,7 @@
         <v>3.17</v>
       </c>
       <c r="DO86" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -38978,10 +38978,10 @@
         <v>78</v>
       </c>
       <c r="DD87" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF87" t="n">
         <v>1.22</v>
@@ -39011,7 +39011,7 @@
         <v>2.24</v>
       </c>
       <c r="DO87" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -39858,7 +39858,7 @@
         <v>75</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE89" t="n">
         <v>0.92</v>
@@ -40746,7 +40746,7 @@
         <v>61</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE91" t="n">
         <v>2.25</v>
@@ -40779,7 +40779,7 @@
         <v>3.05</v>
       </c>
       <c r="DO91" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -41185,7 +41185,7 @@
         <v>1.25</v>
       </c>
       <c r="DE92" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF92" t="n">
         <v>1.22</v>
@@ -41637,7 +41637,7 @@
         <v>1.54</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DF93" t="n">
         <v>1.22</v>
@@ -41667,7 +41667,7 @@
         <v>2.35</v>
       </c>
       <c r="DO93" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -42078,7 +42078,7 @@
         <v>78</v>
       </c>
       <c r="DD94" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DE94" t="n">
         <v>1.82</v>
@@ -42514,10 +42514,10 @@
         <v>69</v>
       </c>
       <c r="DD95" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DE95" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF95" t="n">
         <v>1.75</v>
@@ -42547,7 +42547,7 @@
         <v>2.19</v>
       </c>
       <c r="DO95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -42958,7 +42958,7 @@
         <v>88</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE96" t="n">
         <v>2.25</v>
@@ -43397,7 +43397,7 @@
         <v>1.77</v>
       </c>
       <c r="DE97" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DF97" t="n">
         <v>1.9</v>
@@ -43427,7 +43427,7 @@
         <v>2.98</v>
       </c>
       <c r="DO97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -44277,7 +44277,7 @@
         <v>1.62</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF99" t="n">
         <v>1.9</v>
@@ -44307,7 +44307,7 @@
         <v>2.56</v>
       </c>
       <c r="DO99" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP99" t="b">
         <v>0</v>
@@ -44718,7 +44718,7 @@
         <v>70</v>
       </c>
       <c r="DD100" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DE100" t="n">
         <v>1.23</v>
@@ -44751,7 +44751,7 @@
         <v>2.22</v>
       </c>
       <c r="DO100" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -45154,7 +45154,7 @@
         <v>59</v>
       </c>
       <c r="DD101" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DE101" t="n">
         <v>1.54</v>
@@ -45187,7 +45187,7 @@
         <v>2.38</v>
       </c>
       <c r="DO101" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -45590,7 +45590,7 @@
         <v>56</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DE102" t="n">
         <v>0.92</v>
@@ -45623,7 +45623,7 @@
         <v>2.71</v>
       </c>
       <c r="DO102" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -46026,10 +46026,10 @@
         <v>67</v>
       </c>
       <c r="DD103" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DF103" t="n">
         <v>0.44</v>
@@ -46059,7 +46059,7 @@
         <v>2.12</v>
       </c>
       <c r="DO103" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -46473,7 +46473,7 @@
         <v>1.82</v>
       </c>
       <c r="DE104" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DF104" t="n">
         <v>1.78</v>
@@ -46914,10 +46914,10 @@
         <v>74</v>
       </c>
       <c r="DD105" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DE105" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="DF105" t="n">
         <v>1</v>
@@ -46947,7 +46947,7 @@
         <v>2.51</v>
       </c>
       <c r="DO105" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -47350,10 +47350,10 @@
         <v>80</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE106" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF106" t="n">
         <v>1.6</v>
@@ -47383,7 +47383,7 @@
         <v>2.91</v>
       </c>
       <c r="DO106" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -47789,7 +47789,7 @@
         <v>1.25</v>
       </c>
       <c r="DE107" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DF107" t="n">
         <v>1.27</v>
@@ -48666,10 +48666,10 @@
         <v>72</v>
       </c>
       <c r="DD109" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DE109" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DF109" t="n">
         <v>1.91</v>
@@ -48699,7 +48699,7 @@
         <v>2.33</v>
       </c>
       <c r="DO109" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -49113,7 +49113,7 @@
         <v>1.62</v>
       </c>
       <c r="DE110" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF110" t="n">
         <v>1.82</v>
@@ -49143,7 +49143,7 @@
         <v>2.1</v>
       </c>
       <c r="DO110" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -49554,7 +49554,7 @@
         <v>67</v>
       </c>
       <c r="DD111" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DE111" t="n">
         <v>1.77</v>
@@ -49587,7 +49587,7 @@
         <v>2.93</v>
       </c>
       <c r="DO111" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -49993,7 +49993,7 @@
         <v>1.23</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DF112" t="n">
         <v>1.36</v>
@@ -50023,7 +50023,7 @@
         <v>2.73</v>
       </c>
       <c r="DO112" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -50429,7 +50429,7 @@
         <v>0.92</v>
       </c>
       <c r="DE113" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DF113" t="n">
         <v>0.5</v>
@@ -50870,10 +50870,10 @@
         <v>52</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DE114" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF114" t="n">
         <v>1.6</v>
@@ -50903,7 +50903,7 @@
         <v>2.67</v>
       </c>
       <c r="DO114" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -51314,10 +51314,10 @@
         <v>85</v>
       </c>
       <c r="DD115" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DF115" t="n">
         <v>1</v>
@@ -51347,7 +51347,7 @@
         <v>3.04</v>
       </c>
       <c r="DO115" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -51750,7 +51750,7 @@
         <v>70</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE116" t="n">
         <v>1.82</v>
@@ -53150,54 +53150,2670 @@
       <c r="DX119" t="inlineStr"/>
       <c r="DY119" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="DZ119" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EA119" t="inlineStr">
+        <is>
+          <t>5.55</t>
+        </is>
+      </c>
+      <c r="EB119" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="ED119" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="EE119" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="EF119" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EG119" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EH119" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>13</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Boyacá Chicó</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>46104.79166666666</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" t="n">
+        <v>3</v>
+      </c>
+      <c r="K120" t="n">
+        <v>6</v>
+      </c>
+      <c r="L120" t="n">
+        <v>9</v>
+      </c>
+      <c r="M120" t="n">
+        <v>2</v>
+      </c>
+      <c r="N120" t="n">
+        <v>3</v>
+      </c>
+      <c r="O120" t="n">
+        <v>1</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>2</v>
+      </c>
+      <c r="R120" t="n">
+        <v>2</v>
+      </c>
+      <c r="S120" t="n">
+        <v>2</v>
+      </c>
+      <c r="T120" t="n">
+        <v>10</v>
+      </c>
+      <c r="U120" t="n">
+        <v>4</v>
+      </c>
+      <c r="V120" t="n">
+        <v>12</v>
+      </c>
+      <c r="W120" t="n">
+        <v>12</v>
+      </c>
+      <c r="X120" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA120" t="inlineStr"/>
+      <c r="AB120" t="inlineStr"/>
+      <c r="AC120" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU120" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV120" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX120" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY120" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ120" t="n">
+        <v>41</v>
+      </c>
+      <c r="DA120" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB120" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC120" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD120" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DE120" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DF120" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DG120" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DH120" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DI120" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DJ120" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK120" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL120" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DM120" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DN120" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DO120" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP120" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ120" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV120" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW120" t="inlineStr"/>
+      <c r="DX120" t="inlineStr"/>
+      <c r="DY120" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="DZ120" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EA120" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="EB120" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EC120" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="ED120" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EE120" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EF120" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="EG120" t="inlineStr"/>
+      <c r="EH120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>13</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>46104.88194444445</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2</v>
+      </c>
+      <c r="H121" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" t="n">
+        <v>3</v>
+      </c>
+      <c r="J121" t="n">
+        <v>6</v>
+      </c>
+      <c r="K121" t="n">
+        <v>6</v>
+      </c>
+      <c r="L121" t="n">
+        <v>12</v>
+      </c>
+      <c r="M121" t="n">
+        <v>3</v>
+      </c>
+      <c r="N121" t="n">
+        <v>5</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>7</v>
+      </c>
+      <c r="R121" t="n">
+        <v>3</v>
+      </c>
+      <c r="S121" t="n">
+        <v>11</v>
+      </c>
+      <c r="T121" t="n">
+        <v>10</v>
+      </c>
+      <c r="U121" t="n">
+        <v>18</v>
+      </c>
+      <c r="V121" t="n">
+        <v>13</v>
+      </c>
+      <c r="W121" t="n">
+        <v>17</v>
+      </c>
+      <c r="X121" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>Estadio Nemesio Camacho El Campín</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AC121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>2133</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>78</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU121" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV121" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX121" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY121" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ121" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA121" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB121" t="n">
+        <v>27</v>
+      </c>
+      <c r="DC121" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD121" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE121" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DF121" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DG121" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DH121" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DI121" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DJ121" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK121" t="n">
+        <v>18</v>
+      </c>
+      <c r="DL121" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DM121" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DN121" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="DO121" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW121" t="inlineStr"/>
+      <c r="DX121" t="inlineStr"/>
+      <c r="DY121" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DZ121" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EA121" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="EB121" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EC121" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="ED121" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="EE121" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EF121" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EG121" t="inlineStr"/>
+      <c r="EH121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>13</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Jaguares de Córdoba</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Rionegro Águilas</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>46104.97222222222</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" t="n">
+        <v>2</v>
+      </c>
+      <c r="J122" t="n">
+        <v>5</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3</v>
+      </c>
+      <c r="L122" t="n">
+        <v>8</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1</v>
+      </c>
+      <c r="N122" t="n">
+        <v>2</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>2</v>
+      </c>
+      <c r="R122" t="n">
+        <v>1</v>
+      </c>
+      <c r="S122" t="n">
+        <v>13</v>
+      </c>
+      <c r="T122" t="n">
+        <v>8</v>
+      </c>
+      <c r="U122" t="n">
+        <v>15</v>
+      </c>
+      <c r="V122" t="n">
+        <v>9</v>
+      </c>
+      <c r="W122" t="n">
+        <v>6</v>
+      </c>
+      <c r="X122" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>Estadio de Fútbol Jaraguay de Montería</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>, Montería</t>
+        </is>
+      </c>
+      <c r="AC122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>49</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>15</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>2</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>7</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU122" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV122" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX122" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY122" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ122" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA122" t="n">
+        <v>65</v>
+      </c>
+      <c r="DB122" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC122" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD122" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DE122" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF122" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DG122" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DH122" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DI122" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DJ122" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK122" t="n">
+        <v>35</v>
+      </c>
+      <c r="DL122" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="DM122" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DN122" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DO122" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW122" t="inlineStr"/>
+      <c r="DX122" t="inlineStr"/>
+      <c r="DY122" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="DZ122" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EA122" t="inlineStr">
+        <is>
+          <t>4.58</t>
+        </is>
+      </c>
+      <c r="EB122" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EC122" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="ED122" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EE122" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EF122" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EG122" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EH122" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>13</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>46105.85416666666</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2</v>
+      </c>
+      <c r="I123" t="n">
+        <v>4</v>
+      </c>
+      <c r="J123" t="n">
+        <v>7</v>
+      </c>
+      <c r="K123" t="n">
+        <v>9</v>
+      </c>
+      <c r="L123" t="n">
+        <v>16</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>3</v>
+      </c>
+      <c r="O123" t="n">
+        <v>1</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>7</v>
+      </c>
+      <c r="R123" t="n">
+        <v>10</v>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="n">
+        <v>8</v>
+      </c>
+      <c r="U123" t="n">
+        <v>12</v>
+      </c>
+      <c r="V123" t="n">
+        <v>18</v>
+      </c>
+      <c r="W123" t="n">
+        <v>5</v>
+      </c>
+      <c r="X123" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>Estadio Hernán Ramírez Villegas</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>Villa Olímpica Pereira, Pereira</t>
+        </is>
+      </c>
+      <c r="AC123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>63</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>43</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>95</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU123" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV123" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX123" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY123" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ123" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA123" t="n">
+        <v>87</v>
+      </c>
+      <c r="DB123" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC123" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD123" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE123" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="DF123" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DG123" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DH123" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DI123" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DJ123" t="n">
+        <v>39</v>
+      </c>
+      <c r="DK123" t="n">
+        <v>14</v>
+      </c>
+      <c r="DL123" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DM123" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="DN123" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DO123" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW123" t="inlineStr"/>
+      <c r="DX123" t="inlineStr"/>
+      <c r="DY123" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="DZ123" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EA123" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="EB123" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EC123" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="ED123" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EE123" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EF123" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="EG123" t="inlineStr"/>
+      <c r="EH123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>13</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>46105.95833333334</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>2</v>
+      </c>
+      <c r="J124" t="n">
+        <v>6</v>
+      </c>
+      <c r="K124" t="n">
+        <v>8</v>
+      </c>
+      <c r="L124" t="n">
+        <v>14</v>
+      </c>
+      <c r="M124" t="n">
+        <v>2</v>
+      </c>
+      <c r="N124" t="n">
+        <v>2</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>2</v>
+      </c>
+      <c r="R124" t="n">
+        <v>5</v>
+      </c>
+      <c r="S124" t="n">
+        <v>8</v>
+      </c>
+      <c r="T124" t="n">
+        <v>8</v>
+      </c>
+      <c r="U124" t="n">
+        <v>10</v>
+      </c>
+      <c r="V124" t="n">
+        <v>13</v>
+      </c>
+      <c r="W124" t="n">
+        <v>18</v>
+      </c>
+      <c r="X124" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>Estadio Metropolitano Roberto Meléndez</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>Intersección de la Avenida Circunvalar con la Calle 45, Barranquilla</t>
+        </is>
+      </c>
+      <c r="AC124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>2131</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>52</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>17</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>66</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU124" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV124" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX124" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY124" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ124" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA124" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB124" t="n">
+        <v>48</v>
+      </c>
+      <c r="DC124" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD124" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DE124" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DF124" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DG124" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DH124" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DI124" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DJ124" t="n">
+        <v>44</v>
+      </c>
+      <c r="DK124" t="n">
+        <v>18</v>
+      </c>
+      <c r="DL124" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DM124" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DN124" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DO124" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW124" t="inlineStr"/>
+      <c r="DX124" t="inlineStr"/>
+      <c r="DY124" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="DZ124" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EA124" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="EB124" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EC124" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="ED124" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="EE124" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="EF124" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EG124" t="inlineStr"/>
+      <c r="EH124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>13</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>46106.04166666666</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2</v>
+      </c>
+      <c r="I125" t="n">
+        <v>3</v>
+      </c>
+      <c r="J125" t="n">
+        <v>5</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1</v>
+      </c>
+      <c r="L125" t="n">
+        <v>6</v>
+      </c>
+      <c r="M125" t="n">
+        <v>2</v>
+      </c>
+      <c r="N125" t="n">
+        <v>3</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>3</v>
+      </c>
+      <c r="R125" t="n">
+        <v>4</v>
+      </c>
+      <c r="S125" t="n">
+        <v>4</v>
+      </c>
+      <c r="T125" t="n">
+        <v>6</v>
+      </c>
+      <c r="U125" t="n">
+        <v>7</v>
+      </c>
+      <c r="V125" t="n">
+        <v>10</v>
+      </c>
+      <c r="W125" t="n">
+        <v>20</v>
+      </c>
+      <c r="X125" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>Estadio Metropolitano de Techo</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AC125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>2143</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>19</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>71</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU125" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV125" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX125" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY125" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ125" t="n">
+        <v>46</v>
+      </c>
+      <c r="DA125" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB125" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC125" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD125" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DE125" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DF125" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DG125" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH125" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DI125" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ125" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK125" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL125" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DM125" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DN125" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="DO125" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW125" t="inlineStr"/>
+      <c r="DX125" t="inlineStr"/>
+      <c r="DY125" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="DZ125" t="inlineStr">
+        <is>
           <t>1.47</t>
         </is>
       </c>
-      <c r="EA119" t="inlineStr">
-        <is>
-          <t>4.83</t>
-        </is>
-      </c>
-      <c r="EB119" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="EC119" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="ED119" t="inlineStr">
-        <is>
-          <t>2.72</t>
-        </is>
-      </c>
-      <c r="EE119" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="EF119" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
-      <c r="EG119" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="EH119" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
+      <c r="EA125" t="inlineStr">
+        <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="EB125" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EC125" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="ED125" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="EE125" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EF125" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EG125" t="inlineStr"/>
+      <c r="EH125" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH125" headerRowCount="1">
-  <autoFilter ref="A1:EH125"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH126" headerRowCount="1">
+  <autoFilter ref="A1:EH126"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH125"/>
+  <dimension ref="A1:EH126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1749,7 +1749,7 @@
         <v>0.5</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DE4" t="n">
         <v>1.62</v>
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -7402,7 +7402,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE15" t="n">
         <v>1.58</v>
@@ -8285,7 +8285,7 @@
         <v>0.67</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>2.13</v>
       </c>
       <c r="DO17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -10473,7 +10473,7 @@
         <v>1.08</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DF22" t="n">
         <v>2</v>
@@ -10503,7 +10503,7 @@
         <v>2.27</v>
       </c>
       <c r="DO22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -13546,7 +13546,7 @@
         <v>75</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DE29" t="n">
         <v>1.77</v>
@@ -13579,7 +13579,7 @@
         <v>3.03</v>
       </c>
       <c r="DO29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -16178,7 +16178,7 @@
         <v>67</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE35" t="n">
         <v>1.33</v>
@@ -17933,7 +17933,7 @@
         <v>2.25</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF39" t="n">
         <v>3</v>
@@ -17963,7 +17963,7 @@
         <v>3.9</v>
       </c>
       <c r="DO39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19673,7 +19673,7 @@
         <v>1.67</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DF43" t="n">
         <v>2</v>
@@ -22714,7 +22714,7 @@
         <v>60</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE50" t="n">
         <v>2.08</v>
@@ -22747,7 +22747,7 @@
         <v>1.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25806,7 +25806,7 @@
         <v>70</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DE57" t="n">
         <v>1.25</v>
@@ -25839,7 +25839,7 @@
         <v>2.74</v>
       </c>
       <c r="DO57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -26253,7 +26253,7 @@
         <v>1.54</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DF58" t="n">
         <v>0.83</v>
@@ -26283,7 +26283,7 @@
         <v>2</v>
       </c>
       <c r="DO58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29769,7 +29769,7 @@
         <v>1.69</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF66" t="n">
         <v>1.8</v>
@@ -29799,7 +29799,7 @@
         <v>3.08</v>
       </c>
       <c r="DO66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -30202,7 +30202,7 @@
         <v>71</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE67" t="n">
         <v>1.08</v>
@@ -33706,7 +33706,7 @@
         <v>83</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DE75" t="n">
         <v>0.85</v>
@@ -33739,7 +33739,7 @@
         <v>2.17</v>
       </c>
       <c r="DO75" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -35905,7 +35905,7 @@
         <v>0.92</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF80" t="n">
         <v>0.43</v>
@@ -35935,7 +35935,7 @@
         <v>2.69</v>
       </c>
       <c r="DO80" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39414,7 +39414,7 @@
         <v>60</v>
       </c>
       <c r="DD88" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE88" t="n">
         <v>1.62</v>
@@ -39447,7 +39447,7 @@
         <v>2.31</v>
       </c>
       <c r="DO88" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -41182,7 +41182,7 @@
         <v>73</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE92" t="n">
         <v>0.85</v>
@@ -41215,7 +41215,7 @@
         <v>1.85</v>
       </c>
       <c r="DO92" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -42081,7 +42081,7 @@
         <v>2.08</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF94" t="n">
         <v>2</v>
@@ -42111,7 +42111,7 @@
         <v>2.91</v>
       </c>
       <c r="DO94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -43833,7 +43833,7 @@
         <v>2.25</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DF98" t="n">
         <v>2.33</v>
@@ -46470,7 +46470,7 @@
         <v>61</v>
       </c>
       <c r="DD104" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DE104" t="n">
         <v>1.67</v>
@@ -46503,7 +46503,7 @@
         <v>2.83</v>
       </c>
       <c r="DO104" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -47786,7 +47786,7 @@
         <v>78</v>
       </c>
       <c r="DD107" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DE107" t="n">
         <v>0.62</v>
@@ -47819,7 +47819,7 @@
         <v>1.98</v>
       </c>
       <c r="DO107" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -51753,7 +51753,7 @@
         <v>1.33</v>
       </c>
       <c r="DE116" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF116" t="n">
         <v>1.5</v>
@@ -51783,7 +51783,7 @@
         <v>2.79</v>
       </c>
       <c r="DO116" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -54556,7 +54556,7 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O123" t="n">
         <v>1</v>
@@ -54608,7 +54608,7 @@
         <v>2</v>
       </c>
       <c r="AD123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE123" t="n">
         <v>2.8</v>
@@ -54692,7 +54692,7 @@
         <v>0</v>
       </c>
       <c r="BF123" t="n">
-        <v>-1</v>
+        <v>1500</v>
       </c>
       <c r="BG123" t="n">
         <v>-1</v>
@@ -54728,13 +54728,13 @@
         <v>1</v>
       </c>
       <c r="BR123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS123" t="n">
         <v>1</v>
       </c>
       <c r="BT123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU123" t="n">
         <v>1</v>
@@ -55019,7 +55019,7 @@
         <v>13</v>
       </c>
       <c r="W124" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X124" t="n">
         <v>8</v>
@@ -55128,7 +55128,7 @@
         <v>0</v>
       </c>
       <c r="BF124" t="n">
-        <v>-1</v>
+        <v>3566</v>
       </c>
       <c r="BG124" t="n">
         <v>2</v>
@@ -55419,10 +55419,10 @@
         <v>5</v>
       </c>
       <c r="K125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L125" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M125" t="n">
         <v>2</v>
@@ -55434,7 +55434,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q125" t="n">
         <v>3</v>
@@ -55443,13 +55443,13 @@
         <v>4</v>
       </c>
       <c r="S125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T125" t="n">
         <v>6</v>
       </c>
       <c r="U125" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V125" t="n">
         <v>10</v>
@@ -55458,7 +55458,7 @@
         <v>20</v>
       </c>
       <c r="X125" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y125" t="n">
         <v>55</v>
@@ -55480,7 +55480,7 @@
         <v>2</v>
       </c>
       <c r="AD125" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE125" t="n">
         <v>2.15</v>
@@ -55600,13 +55600,13 @@
         <v>1</v>
       </c>
       <c r="BR125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BS125" t="n">
         <v>3</v>
       </c>
       <c r="BT125" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU125" t="n">
         <v>1</v>
@@ -55624,13 +55624,13 @@
         <v>71</v>
       </c>
       <c r="BZ125" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="CA125" t="n">
         <v>1.05</v>
       </c>
       <c r="CB125" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="CC125" t="n">
         <v>0</v>
@@ -55814,6 +55814,442 @@
       </c>
       <c r="EG125" t="inlineStr"/>
       <c r="EH125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>13</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Llaneros</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>46107.04166666666</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>13</v>
+      </c>
+      <c r="K126" t="n">
+        <v>2</v>
+      </c>
+      <c r="L126" t="n">
+        <v>15</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>4</v>
+      </c>
+      <c r="R126" t="n">
+        <v>1</v>
+      </c>
+      <c r="S126" t="n">
+        <v>22</v>
+      </c>
+      <c r="T126" t="n">
+        <v>8</v>
+      </c>
+      <c r="U126" t="n">
+        <v>26</v>
+      </c>
+      <c r="V126" t="n">
+        <v>9</v>
+      </c>
+      <c r="W126" t="n">
+        <v>7</v>
+      </c>
+      <c r="X126" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>Estadio Olímpico Pascual Guerrero</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>Carrera 36 entre Calles 5 y 5B3, Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="AC126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>206</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>99</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>105</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>68</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU126" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV126" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX126" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY126" t="n">
+        <v>15</v>
+      </c>
+      <c r="CZ126" t="n">
+        <v>35</v>
+      </c>
+      <c r="DA126" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB126" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC126" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD126" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DE126" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DF126" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DG126" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH126" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DI126" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DJ126" t="n">
+        <v>65</v>
+      </c>
+      <c r="DK126" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL126" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DM126" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DN126" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="DO126" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW126" t="inlineStr"/>
+      <c r="DX126" t="inlineStr"/>
+      <c r="DY126" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="DZ126" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EA126" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="EB126" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EC126" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="ED126" t="inlineStr">
+        <is>
+          <t>7.60</t>
+        </is>
+      </c>
+      <c r="EE126" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="EF126" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EG126" t="inlineStr"/>
+      <c r="EH126" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH126" headerRowCount="1">
-  <autoFilter ref="A1:EH126"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH132" headerRowCount="1">
+  <autoFilter ref="A1:EH132"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH126"/>
+  <dimension ref="A1:EH132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1746,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DE2" t="n">
         <v>1.23</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2185,7 +2185,7 @@
         <v>1.08</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2629,7 +2629,7 @@
         <v>1.75</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
         <v>2.25</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DE6" t="n">
         <v>1.54</v>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4346,10 +4346,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4790,10 +4790,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4823,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DE11" t="n">
         <v>1.77</v>
@@ -6106,10 +6106,10 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
         <v>1.82</v>
       </c>
       <c r="DO12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6522,10 +6522,10 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6555,7 +6555,7 @@
         <v>1.86</v>
       </c>
       <c r="DO13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -6966,7 +6966,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DE14" t="n">
         <v>1.08</v>
@@ -6999,7 +6999,7 @@
         <v>1.99</v>
       </c>
       <c r="DO14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP14" t="b">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>1.23</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7435,7 +7435,7 @@
         <v>3.19</v>
       </c>
       <c r="DO15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -7854,7 +7854,7 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE16" t="n">
         <v>1.08</v>
@@ -8282,7 +8282,7 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DE17" t="n">
         <v>1.75</v>
@@ -8718,7 +8718,7 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE18" t="n">
         <v>2.08</v>
@@ -8751,7 +8751,7 @@
         <v>1.44</v>
       </c>
       <c r="DO18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9157,7 +9157,7 @@
         <v>1.54</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9593,7 +9593,7 @@
         <v>1.77</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -9623,7 +9623,7 @@
         <v>4.47</v>
       </c>
       <c r="DO20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10026,10 +10026,10 @@
         <v>100</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10059,7 +10059,7 @@
         <v>2.47</v>
       </c>
       <c r="DO21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10917,7 +10917,7 @@
         <v>1.08</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DF23" t="n">
         <v>0</v>
@@ -11350,10 +11350,10 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -11383,7 +11383,7 @@
         <v>1.88</v>
       </c>
       <c r="DO24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -11786,10 +11786,10 @@
         <v>25</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -11819,7 +11819,7 @@
         <v>2.57</v>
       </c>
       <c r="DO25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12666,10 +12666,10 @@
         <v>75</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DF27" t="n">
         <v>0.5</v>
@@ -12699,7 +12699,7 @@
         <v>2.21</v>
       </c>
       <c r="DO27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13102,10 +13102,10 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -13135,7 +13135,7 @@
         <v>2.03</v>
       </c>
       <c r="DO28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -13990,7 +13990,7 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DE30" t="n">
         <v>1.08</v>
@@ -14418,10 +14418,10 @@
         <v>67</v>
       </c>
       <c r="DD31" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DF31" t="n">
         <v>0.33</v>
@@ -14451,7 +14451,7 @@
         <v>2.8</v>
       </c>
       <c r="DO31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -14862,10 +14862,10 @@
         <v>50</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DE32" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF32" t="n">
         <v>1.67</v>
@@ -14895,7 +14895,7 @@
         <v>2.62</v>
       </c>
       <c r="DO32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15298,7 +15298,7 @@
         <v>50</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE33" t="n">
         <v>2.08</v>
@@ -15745,7 +15745,7 @@
         <v>1.77</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF34" t="n">
         <v>1.67</v>
@@ -16181,7 +16181,7 @@
         <v>1.23</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF35" t="n">
         <v>1.67</v>
@@ -16211,7 +16211,7 @@
         <v>2.16</v>
       </c>
       <c r="DO35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17050,10 +17050,10 @@
         <v>84</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DF37" t="n">
         <v>2</v>
@@ -17083,7 +17083,7 @@
         <v>2.43</v>
       </c>
       <c r="DO37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -17494,10 +17494,10 @@
         <v>67</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF38" t="n">
         <v>0.67</v>
@@ -17527,7 +17527,7 @@
         <v>2.42</v>
       </c>
       <c r="DO38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18369,7 +18369,7 @@
         <v>2.08</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DF40" t="n">
         <v>2.25</v>
@@ -18399,7 +18399,7 @@
         <v>2.56</v>
       </c>
       <c r="DO40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP40" t="b">
         <v>0</v>
@@ -18801,7 +18801,7 @@
         <v>1.08</v>
       </c>
       <c r="DE41" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF41" t="n">
         <v>0.5</v>
@@ -19234,10 +19234,10 @@
         <v>88</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DF42" t="n">
         <v>1.25</v>
@@ -19267,7 +19267,7 @@
         <v>2.02</v>
       </c>
       <c r="DO42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -19670,7 +19670,7 @@
         <v>63</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DE43" t="n">
         <v>1.23</v>
@@ -19703,7 +19703,7 @@
         <v>1.9</v>
       </c>
       <c r="DO43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20109,7 +20109,7 @@
         <v>1.08</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DF44" t="n">
         <v>1.5</v>
@@ -20139,7 +20139,7 @@
         <v>3.37</v>
       </c>
       <c r="DO44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -20522,10 +20522,10 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF45" t="n">
         <v>2</v>
@@ -20555,7 +20555,7 @@
         <v>2.5</v>
       </c>
       <c r="DO45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -20958,7 +20958,7 @@
         <v>50</v>
       </c>
       <c r="DD46" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DE46" t="n">
         <v>1.77</v>
@@ -20991,7 +20991,7 @@
         <v>2.87</v>
       </c>
       <c r="DO46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -21402,7 +21402,7 @@
         <v>63</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE47" t="n">
         <v>1.54</v>
@@ -21826,10 +21826,10 @@
         <v>59</v>
       </c>
       <c r="DD48" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DF48" t="n">
         <v>1.33</v>
@@ -21859,7 +21859,7 @@
         <v>1.75</v>
       </c>
       <c r="DO48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -22270,7 +22270,7 @@
         <v>80</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DE49" t="n">
         <v>1.08</v>
@@ -23158,10 +23158,10 @@
         <v>60</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DF51" t="n">
         <v>1.8</v>
@@ -23191,7 +23191,7 @@
         <v>2.38</v>
       </c>
       <c r="DO51" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP51" t="b">
         <v>0</v>
@@ -23605,7 +23605,7 @@
         <v>1.54</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF52" t="n">
         <v>0.4</v>
@@ -23635,7 +23635,7 @@
         <v>2.56</v>
       </c>
       <c r="DO52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -24046,10 +24046,10 @@
         <v>60</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -24079,7 +24079,7 @@
         <v>2.58</v>
       </c>
       <c r="DO53" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -24474,10 +24474,10 @@
         <v>68</v>
       </c>
       <c r="DD54" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF54" t="n">
         <v>0.2</v>
@@ -24507,7 +24507,7 @@
         <v>1.66</v>
       </c>
       <c r="DO54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -24929,7 +24929,7 @@
         <v>1.77</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF55" t="n">
         <v>1.4</v>
@@ -25809,7 +25809,7 @@
         <v>1.75</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DF57" t="n">
         <v>1.75</v>
@@ -26697,7 +26697,7 @@
         <v>1.08</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DF59" t="n">
         <v>0.83</v>
@@ -27149,7 +27149,7 @@
         <v>2.08</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF60" t="n">
         <v>2.17</v>
@@ -27590,7 +27590,7 @@
         <v>50</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DE61" t="n">
         <v>1.77</v>
@@ -27623,7 +27623,7 @@
         <v>2.63</v>
       </c>
       <c r="DO61" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -28026,7 +28026,7 @@
         <v>75</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE62" t="n">
         <v>2.25</v>
@@ -28465,7 +28465,7 @@
         <v>1.08</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF63" t="n">
         <v>1.17</v>
@@ -28495,7 +28495,7 @@
         <v>2.4</v>
       </c>
       <c r="DO63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -28898,10 +28898,10 @@
         <v>60</v>
       </c>
       <c r="DD64" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DF64" t="n">
         <v>0.4</v>
@@ -28931,7 +28931,7 @@
         <v>1.97</v>
       </c>
       <c r="DO64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -29334,10 +29334,10 @@
         <v>57</v>
       </c>
       <c r="DD65" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DF65" t="n">
         <v>1.4</v>
@@ -29367,7 +29367,7 @@
         <v>2.22</v>
       </c>
       <c r="DO65" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -29766,7 +29766,7 @@
         <v>90</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DE66" t="n">
         <v>1.75</v>
@@ -30646,7 +30646,7 @@
         <v>62</v>
       </c>
       <c r="DD68" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DE68" t="n">
         <v>2.08</v>
@@ -30679,7 +30679,7 @@
         <v>1.99</v>
       </c>
       <c r="DO68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -31526,10 +31526,10 @@
         <v>55</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DF70" t="n">
         <v>1.67</v>
@@ -31559,7 +31559,7 @@
         <v>2.63</v>
       </c>
       <c r="DO70" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP70" t="b">
         <v>0</v>
@@ -31965,7 +31965,7 @@
         <v>2.25</v>
       </c>
       <c r="DE71" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF71" t="n">
         <v>2.25</v>
@@ -32398,7 +32398,7 @@
         <v>64</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DE72" t="n">
         <v>1.54</v>
@@ -32842,10 +32842,10 @@
         <v>72</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -32875,7 +32875,7 @@
         <v>3.26</v>
       </c>
       <c r="DO73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -33270,10 +33270,10 @@
         <v>69</v>
       </c>
       <c r="DD74" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF74" t="n">
         <v>0.57</v>
@@ -33303,7 +33303,7 @@
         <v>2.19</v>
       </c>
       <c r="DO74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -33709,7 +33709,7 @@
         <v>1.75</v>
       </c>
       <c r="DE75" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF75" t="n">
         <v>1.67</v>
@@ -34142,10 +34142,10 @@
         <v>65</v>
       </c>
       <c r="DD76" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DF76" t="n">
         <v>0.43</v>
@@ -34175,7 +34175,7 @@
         <v>2.09</v>
       </c>
       <c r="DO76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -34586,7 +34586,7 @@
         <v>65</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DE77" t="n">
         <v>2.25</v>
@@ -35025,7 +35025,7 @@
         <v>1.54</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DF78" t="n">
         <v>1</v>
@@ -35055,7 +35055,7 @@
         <v>2.25</v>
       </c>
       <c r="DO78" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -35461,7 +35461,7 @@
         <v>1.77</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF79" t="n">
         <v>1.63</v>
@@ -35491,7 +35491,7 @@
         <v>2.48</v>
       </c>
       <c r="DO79" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -35902,7 +35902,7 @@
         <v>65</v>
       </c>
       <c r="DD80" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DE80" t="n">
         <v>1.75</v>
@@ -36346,10 +36346,10 @@
         <v>93</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF81" t="n">
         <v>1.43</v>
@@ -36379,7 +36379,7 @@
         <v>2.39</v>
       </c>
       <c r="DO81" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -36793,7 +36793,7 @@
         <v>1.08</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DF82" t="n">
         <v>0.88</v>
@@ -37237,7 +37237,7 @@
         <v>2.08</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DF83" t="n">
         <v>1.88</v>
@@ -37670,10 +37670,10 @@
         <v>60</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF84" t="n">
         <v>1.57</v>
@@ -37703,7 +37703,7 @@
         <v>2.54</v>
       </c>
       <c r="DO84" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP84" t="b">
         <v>0</v>
@@ -38106,7 +38106,7 @@
         <v>51</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE85" t="n">
         <v>1.08</v>
@@ -38542,7 +38542,7 @@
         <v>61</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DE86" t="n">
         <v>2.25</v>
@@ -38981,7 +38981,7 @@
         <v>1.08</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF87" t="n">
         <v>1.22</v>
@@ -39417,7 +39417,7 @@
         <v>1.23</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF88" t="n">
         <v>1.25</v>
@@ -39858,10 +39858,10 @@
         <v>75</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF89" t="n">
         <v>1.88</v>
@@ -39891,7 +39891,7 @@
         <v>2.77</v>
       </c>
       <c r="DO89" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -40302,7 +40302,7 @@
         <v>56</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE90" t="n">
         <v>1.77</v>
@@ -40746,7 +40746,7 @@
         <v>61</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE91" t="n">
         <v>2.25</v>
@@ -41185,7 +41185,7 @@
         <v>1.23</v>
       </c>
       <c r="DE92" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF92" t="n">
         <v>1.22</v>
@@ -41637,7 +41637,7 @@
         <v>1.54</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DF93" t="n">
         <v>1.22</v>
@@ -42514,10 +42514,10 @@
         <v>69</v>
       </c>
       <c r="DD95" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DE95" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DF95" t="n">
         <v>1.75</v>
@@ -42547,7 +42547,7 @@
         <v>2.19</v>
       </c>
       <c r="DO95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -42958,7 +42958,7 @@
         <v>88</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DE96" t="n">
         <v>2.25</v>
@@ -44274,10 +44274,10 @@
         <v>64</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DF99" t="n">
         <v>1.9</v>
@@ -44307,7 +44307,7 @@
         <v>2.56</v>
       </c>
       <c r="DO99" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP99" t="b">
         <v>0</v>
@@ -44718,10 +44718,10 @@
         <v>70</v>
       </c>
       <c r="DD100" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DE100" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DF100" t="n">
         <v>0.6</v>
@@ -44751,7 +44751,7 @@
         <v>2.22</v>
       </c>
       <c r="DO100" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -45154,7 +45154,7 @@
         <v>59</v>
       </c>
       <c r="DD101" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DE101" t="n">
         <v>1.54</v>
@@ -45187,7 +45187,7 @@
         <v>2.38</v>
       </c>
       <c r="DO101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -45590,10 +45590,10 @@
         <v>56</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DE102" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DF102" t="n">
         <v>1.11</v>
@@ -45623,7 +45623,7 @@
         <v>2.71</v>
       </c>
       <c r="DO102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -46026,10 +46026,10 @@
         <v>67</v>
       </c>
       <c r="DD103" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF103" t="n">
         <v>0.44</v>
@@ -46059,7 +46059,7 @@
         <v>2.12</v>
       </c>
       <c r="DO103" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -46473,7 +46473,7 @@
         <v>1.75</v>
       </c>
       <c r="DE104" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DF104" t="n">
         <v>1.78</v>
@@ -46914,7 +46914,7 @@
         <v>74</v>
       </c>
       <c r="DD105" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DE105" t="n">
         <v>1.08</v>
@@ -47350,7 +47350,7 @@
         <v>80</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DE106" t="n">
         <v>1.08</v>
@@ -47789,7 +47789,7 @@
         <v>1.23</v>
       </c>
       <c r="DE107" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DF107" t="n">
         <v>1.27</v>
@@ -48669,7 +48669,7 @@
         <v>2.08</v>
       </c>
       <c r="DE109" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF109" t="n">
         <v>1.91</v>
@@ -48699,7 +48699,7 @@
         <v>2.33</v>
       </c>
       <c r="DO109" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -49110,10 +49110,10 @@
         <v>63</v>
       </c>
       <c r="DD110" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DE110" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DF110" t="n">
         <v>1.82</v>
@@ -49143,7 +49143,7 @@
         <v>2.1</v>
       </c>
       <c r="DO110" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -49554,7 +49554,7 @@
         <v>67</v>
       </c>
       <c r="DD111" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DE111" t="n">
         <v>1.77</v>
@@ -49587,7 +49587,7 @@
         <v>2.93</v>
       </c>
       <c r="DO111" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -49990,10 +49990,10 @@
         <v>53</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DF112" t="n">
         <v>1.36</v>
@@ -50023,7 +50023,7 @@
         <v>2.73</v>
       </c>
       <c r="DO112" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -50426,10 +50426,10 @@
         <v>71</v>
       </c>
       <c r="DD113" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DE113" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DF113" t="n">
         <v>0.5</v>
@@ -50459,7 +50459,7 @@
         <v>2.1</v>
       </c>
       <c r="DO113" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -50870,7 +50870,7 @@
         <v>52</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DE114" t="n">
         <v>1.08</v>
@@ -50903,7 +50903,7 @@
         <v>2.67</v>
       </c>
       <c r="DO114" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -51317,7 +51317,7 @@
         <v>1.08</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DF115" t="n">
         <v>1</v>
@@ -51750,7 +51750,7 @@
         <v>70</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE116" t="n">
         <v>1.75</v>
@@ -52649,7 +52649,7 @@
         <v>2.25</v>
       </c>
       <c r="DE118" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF118" t="n">
         <v>2.18</v>
@@ -53090,10 +53090,10 @@
         <v>57</v>
       </c>
       <c r="DD119" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DE119" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DF119" t="n">
         <v>0.73</v>
@@ -53123,7 +53123,7 @@
         <v>2.45</v>
       </c>
       <c r="DO119" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -53526,10 +53526,10 @@
         <v>59</v>
       </c>
       <c r="DD120" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DF120" t="n">
         <v>0.64</v>
@@ -53559,7 +53559,7 @@
         <v>2.17</v>
       </c>
       <c r="DO120" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -53962,7 +53962,7 @@
         <v>69</v>
       </c>
       <c r="DD121" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DE121" t="n">
         <v>1.08</v>
@@ -54398,10 +54398,10 @@
         <v>64</v>
       </c>
       <c r="DD122" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DE122" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DF122" t="n">
         <v>0.83</v>
@@ -54431,7 +54431,7 @@
         <v>2.25</v>
       </c>
       <c r="DO122" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -54842,10 +54842,10 @@
         <v>78</v>
       </c>
       <c r="DD123" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DE123" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DF123" t="n">
         <v>0.45</v>
@@ -54875,7 +54875,7 @@
         <v>1.87</v>
       </c>
       <c r="DO123" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -55278,10 +55278,10 @@
         <v>82</v>
       </c>
       <c r="DD124" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DE124" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DF124" t="n">
         <v>1.58</v>
@@ -55311,7 +55311,7 @@
         <v>2.8</v>
       </c>
       <c r="DO124" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -56250,6 +56250,2602 @@
       </c>
       <c r="EG126" t="inlineStr"/>
       <c r="EH126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>14</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Rionegro Águilas</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Alianza Petrolera</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>46108.875</v>
+      </c>
+      <c r="G127" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" t="n">
+        <v>5</v>
+      </c>
+      <c r="K127" t="n">
+        <v>5</v>
+      </c>
+      <c r="L127" t="n">
+        <v>10</v>
+      </c>
+      <c r="M127" t="n">
+        <v>3</v>
+      </c>
+      <c r="N127" t="n">
+        <v>1</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>5</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1</v>
+      </c>
+      <c r="S127" t="n">
+        <v>7</v>
+      </c>
+      <c r="T127" t="n">
+        <v>8</v>
+      </c>
+      <c r="U127" t="n">
+        <v>12</v>
+      </c>
+      <c r="V127" t="n">
+        <v>9</v>
+      </c>
+      <c r="W127" t="n">
+        <v>12</v>
+      </c>
+      <c r="X127" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>Estadio Alberto Grisales</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>Route 45A, Rionegro, Antioquia</t>
+        </is>
+      </c>
+      <c r="AC127" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>2147</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>101</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>56</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU127" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV127" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX127" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY127" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ127" t="n">
+        <v>29</v>
+      </c>
+      <c r="DA127" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB127" t="n">
+        <v>21</v>
+      </c>
+      <c r="DC127" t="n">
+        <v>55</v>
+      </c>
+      <c r="DD127" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DE127" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DF127" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG127" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DH127" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI127" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DJ127" t="n">
+        <v>71</v>
+      </c>
+      <c r="DK127" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL127" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DM127" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DN127" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="DO127" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW127" t="inlineStr"/>
+      <c r="DX127" t="inlineStr"/>
+      <c r="DY127" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="DZ127" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EA127" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="EB127" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EC127" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="ED127" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="EE127" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="EF127" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EG127" t="inlineStr"/>
+      <c r="EH127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>14</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>46109.04861111111</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2</v>
+      </c>
+      <c r="I128" t="n">
+        <v>3</v>
+      </c>
+      <c r="J128" t="n">
+        <v>3</v>
+      </c>
+      <c r="K128" t="n">
+        <v>5</v>
+      </c>
+      <c r="L128" t="n">
+        <v>8</v>
+      </c>
+      <c r="M128" t="n">
+        <v>4</v>
+      </c>
+      <c r="N128" t="n">
+        <v>3</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>5</v>
+      </c>
+      <c r="R128" t="n">
+        <v>5</v>
+      </c>
+      <c r="S128" t="n">
+        <v>9</v>
+      </c>
+      <c r="T128" t="n">
+        <v>4</v>
+      </c>
+      <c r="U128" t="n">
+        <v>14</v>
+      </c>
+      <c r="V128" t="n">
+        <v>9</v>
+      </c>
+      <c r="W128" t="n">
+        <v>14</v>
+      </c>
+      <c r="X128" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>Estadio Alfonso López</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>Carrera 36 Nº 53-12, Cabecera del Llano, Bucaramanga</t>
+        </is>
+      </c>
+      <c r="AC128" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>2133</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>94</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU128" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV128" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX128" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY128" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ128" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA128" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB128" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC128" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD128" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DE128" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DF128" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DG128" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH128" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DI128" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DJ128" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK128" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL128" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DM128" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DN128" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="DO128" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW128" t="inlineStr"/>
+      <c r="DX128" t="inlineStr"/>
+      <c r="DY128" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="DZ128" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EA128" t="inlineStr">
+        <is>
+          <t>4.37</t>
+        </is>
+      </c>
+      <c r="EB128" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EC128" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="ED128" t="inlineStr">
+        <is>
+          <t>4.53</t>
+        </is>
+      </c>
+      <c r="EE128" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EF128" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EG128" t="inlineStr"/>
+      <c r="EH128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>14</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Boyacá Chicó</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>46109.875</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" t="n">
+        <v>2</v>
+      </c>
+      <c r="K129" t="n">
+        <v>3</v>
+      </c>
+      <c r="L129" t="n">
+        <v>5</v>
+      </c>
+      <c r="M129" t="n">
+        <v>4</v>
+      </c>
+      <c r="N129" t="n">
+        <v>4</v>
+      </c>
+      <c r="O129" t="n">
+        <v>2</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>2</v>
+      </c>
+      <c r="R129" t="n">
+        <v>4</v>
+      </c>
+      <c r="S129" t="n">
+        <v>6</v>
+      </c>
+      <c r="T129" t="n">
+        <v>14</v>
+      </c>
+      <c r="U129" t="n">
+        <v>8</v>
+      </c>
+      <c r="V129" t="n">
+        <v>18</v>
+      </c>
+      <c r="W129" t="n">
+        <v>10</v>
+      </c>
+      <c r="X129" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>64</v>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>Estadio General Santander</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>Avenida 0A 3-56, Barrio Lleras Restrepo, Cúcuta</t>
+        </is>
+      </c>
+      <c r="AC129" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>2153</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>16</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>51</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>54</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>8</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU129" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV129" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX129" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY129" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ129" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA129" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB129" t="n">
+        <v>44</v>
+      </c>
+      <c r="DC129" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD129" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DE129" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="DF129" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="DG129" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH129" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="DI129" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DJ129" t="n">
+        <v>41</v>
+      </c>
+      <c r="DK129" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL129" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DM129" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DN129" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DO129" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW129" t="inlineStr"/>
+      <c r="DX129" t="inlineStr"/>
+      <c r="DY129" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="DZ129" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EA129" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="EB129" t="inlineStr"/>
+      <c r="EC129" t="inlineStr"/>
+      <c r="ED129" t="inlineStr">
+        <is>
+          <t>5.33</t>
+        </is>
+      </c>
+      <c r="EE129" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="EF129" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EG129" t="inlineStr"/>
+      <c r="EH129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>14</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Jaguares de Córdoba</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>46109.96527777778</v>
+      </c>
+      <c r="G130" t="n">
+        <v>3</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" t="n">
+        <v>4</v>
+      </c>
+      <c r="J130" t="n">
+        <v>6</v>
+      </c>
+      <c r="K130" t="n">
+        <v>4</v>
+      </c>
+      <c r="L130" t="n">
+        <v>10</v>
+      </c>
+      <c r="M130" t="n">
+        <v>3</v>
+      </c>
+      <c r="N130" t="n">
+        <v>1</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>9</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6</v>
+      </c>
+      <c r="S130" t="n">
+        <v>16</v>
+      </c>
+      <c r="T130" t="n">
+        <v>11</v>
+      </c>
+      <c r="U130" t="n">
+        <v>25</v>
+      </c>
+      <c r="V130" t="n">
+        <v>17</v>
+      </c>
+      <c r="W130" t="n">
+        <v>7</v>
+      </c>
+      <c r="X130" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Murillo Toro</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
+        </is>
+      </c>
+      <c r="AC130" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>2140</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>18</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>105</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>65</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV130" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ130" t="n">
+        <v>36</v>
+      </c>
+      <c r="DA130" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB130" t="n">
+        <v>24</v>
+      </c>
+      <c r="DC130" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD130" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DE130" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DF130" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG130" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DH130" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DI130" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DJ130" t="n">
+        <v>65</v>
+      </c>
+      <c r="DK130" t="n">
+        <v>28</v>
+      </c>
+      <c r="DL130" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DM130" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="DN130" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DO130" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW130" t="inlineStr"/>
+      <c r="DX130" t="inlineStr"/>
+      <c r="DY130" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="DZ130" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EA130" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="EB130" t="inlineStr"/>
+      <c r="EC130" t="inlineStr"/>
+      <c r="ED130" t="inlineStr">
+        <is>
+          <t>10.51</t>
+        </is>
+      </c>
+      <c r="EE130" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="EF130" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EG130" t="inlineStr"/>
+      <c r="EH130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>14</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>46110.05555555555</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>1</v>
+      </c>
+      <c r="J131" t="n">
+        <v>5</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1</v>
+      </c>
+      <c r="L131" t="n">
+        <v>6</v>
+      </c>
+      <c r="M131" t="n">
+        <v>1</v>
+      </c>
+      <c r="N131" t="n">
+        <v>2</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>6</v>
+      </c>
+      <c r="R131" t="n">
+        <v>2</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="n">
+        <v>5</v>
+      </c>
+      <c r="U131" t="n">
+        <v>16</v>
+      </c>
+      <c r="V131" t="n">
+        <v>7</v>
+      </c>
+      <c r="W131" t="n">
+        <v>12</v>
+      </c>
+      <c r="X131" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>Estadio Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>BN 25, Palmira</t>
+        </is>
+      </c>
+      <c r="AC131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>2132</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>15</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>93</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU131" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV131" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX131" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY131" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ131" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA131" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB131" t="n">
+        <v>12</v>
+      </c>
+      <c r="DC131" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD131" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DE131" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="DF131" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DG131" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH131" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DI131" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DJ131" t="n">
+        <v>56</v>
+      </c>
+      <c r="DK131" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL131" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DM131" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DN131" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DO131" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW131" t="inlineStr"/>
+      <c r="DX131" t="inlineStr"/>
+      <c r="DY131" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="DZ131" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EA131" t="inlineStr">
+        <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="EB131" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EC131" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="ED131" t="inlineStr">
+        <is>
+          <t>11.48</t>
+        </is>
+      </c>
+      <c r="EE131" t="inlineStr">
+        <is>
+          <t>4.68</t>
+        </is>
+      </c>
+      <c r="EF131" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EG131" t="inlineStr"/>
+      <c r="EH131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>14</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>La Equidad</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>46110.88194444445</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>6</v>
+      </c>
+      <c r="K132" t="n">
+        <v>2</v>
+      </c>
+      <c r="L132" t="n">
+        <v>8</v>
+      </c>
+      <c r="M132" t="n">
+        <v>2</v>
+      </c>
+      <c r="N132" t="n">
+        <v>3</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>6</v>
+      </c>
+      <c r="R132" t="n">
+        <v>4</v>
+      </c>
+      <c r="S132" t="n">
+        <v>14</v>
+      </c>
+      <c r="T132" t="n">
+        <v>3</v>
+      </c>
+      <c r="U132" t="n">
+        <v>20</v>
+      </c>
+      <c r="V132" t="n">
+        <v>7</v>
+      </c>
+      <c r="W132" t="n">
+        <v>6</v>
+      </c>
+      <c r="X132" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>Estadio Metropolitano de Techo</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AC132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>2131</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>58</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>57</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU132" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV132" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX132" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY132" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ132" t="n">
+        <v>62</v>
+      </c>
+      <c r="DA132" t="n">
+        <v>89</v>
+      </c>
+      <c r="DB132" t="n">
+        <v>46</v>
+      </c>
+      <c r="DC132" t="n">
+        <v>81</v>
+      </c>
+      <c r="DD132" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE132" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DF132" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DG132" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DH132" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DI132" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DJ132" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK132" t="n">
+        <v>12</v>
+      </c>
+      <c r="DL132" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DM132" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DN132" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="DO132" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW132" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="DX132" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="DY132" t="inlineStr"/>
+      <c r="DZ132" t="inlineStr"/>
+      <c r="EA132" t="inlineStr"/>
+      <c r="EB132" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EC132" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="ED132" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EE132" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EF132" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EG132" t="inlineStr"/>
+      <c r="EH132" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH132" headerRowCount="1">
-  <autoFilter ref="A1:EH132"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH137" headerRowCount="1">
+  <autoFilter ref="A1:EH137"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -280,8 +280,8 @@
     <tableColumn id="134" name="pinnacle_ft_2"/>
     <tableColumn id="135" name="pinnacle_ft_x"/>
     <tableColumn id="136" name="pinnacle_ft_1"/>
-    <tableColumn id="137" name="pinnacle_corners_under_95"/>
-    <tableColumn id="138" name="pinnacle_corners_over_95"/>
+    <tableColumn id="137" name="pinnacle_corners_over_95"/>
+    <tableColumn id="138" name="pinnacle_corners_under_95"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH132"/>
+  <dimension ref="A1:EH137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -715,8 +715,8 @@
     <col width="18" customWidth="1" min="134" max="134"/>
     <col width="18" customWidth="1" min="135" max="135"/>
     <col width="18" customWidth="1" min="136" max="136"/>
-    <col width="32.4" customWidth="1" min="137" max="137"/>
-    <col width="31.2" customWidth="1" min="138" max="138"/>
+    <col width="31.2" customWidth="1" min="137" max="137"/>
+    <col width="32.4" customWidth="1" min="138" max="138"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="EG1" s="1" t="inlineStr">
         <is>
+          <t>pinnacle_corners_over_95</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
           <t>pinnacle_corners_under_95</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_corners_over_95</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
         <v>0.46</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -2182,7 +2182,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE3" t="n">
         <v>0.85</v>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="EG3" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
           <t>1.79</t>
-        </is>
-      </c>
-      <c r="EH3" t="inlineStr">
-        <is>
-          <t>1.94</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DE4" t="n">
         <v>1.5</v>
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3030,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DE5" t="n">
         <v>0.62</v>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="EG5" t="inlineStr">
         <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
           <t>1.83</t>
-        </is>
-      </c>
-      <c r="EH5" t="inlineStr">
-        <is>
-          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
         <v>1.46</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3910,10 +3910,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4793,7 +4793,7 @@
         <v>1.79</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4823,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5229,7 +5229,7 @@
         <v>1.38</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5665,7 +5665,7 @@
         <v>0.79</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6522,7 +6522,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DE13" t="n">
         <v>0.85</v>
@@ -6622,12 +6622,12 @@
       </c>
       <c r="EG13" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EH13" t="inlineStr">
+        <is>
           <t>1.92</t>
-        </is>
-      </c>
-      <c r="EH13" t="inlineStr">
-        <is>
-          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
         <v>0.46</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7402,7 +7402,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE15" t="n">
         <v>1.46</v>
@@ -7510,12 +7510,12 @@
       </c>
       <c r="EG15" t="inlineStr">
         <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EH15" t="inlineStr">
+        <is>
           <t>1.88</t>
-        </is>
-      </c>
-      <c r="EH15" t="inlineStr">
-        <is>
-          <t>1.84</t>
         </is>
       </c>
     </row>
@@ -7857,7 +7857,7 @@
         <v>1.36</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -7887,7 +7887,7 @@
         <v>2.53</v>
       </c>
       <c r="DO16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8285,7 +8285,7 @@
         <v>0.62</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>2.13</v>
       </c>
       <c r="DO17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -8718,10 +8718,10 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE18" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DF18" t="n">
         <v>1</v>
@@ -8751,7 +8751,7 @@
         <v>1.44</v>
       </c>
       <c r="DO18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9154,7 +9154,7 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE19" t="n">
         <v>1.79</v>
@@ -9187,7 +9187,7 @@
         <v>2.56</v>
       </c>
       <c r="DO19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9590,7 +9590,7 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="DE20" t="n">
         <v>1.38</v>
@@ -10470,10 +10470,10 @@
         <v>25</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF22" t="n">
         <v>2</v>
@@ -10503,7 +10503,7 @@
         <v>2.27</v>
       </c>
       <c r="DO22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -10914,10 +10914,10 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DF23" t="n">
         <v>0</v>
@@ -10947,7 +10947,7 @@
         <v>2.38</v>
       </c>
       <c r="DO23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11886,12 +11886,12 @@
       </c>
       <c r="EG25" t="inlineStr">
         <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EH25" t="inlineStr">
+        <is>
           <t>1.83</t>
-        </is>
-      </c>
-      <c r="EH25" t="inlineStr">
-        <is>
-          <t>1.91</t>
         </is>
       </c>
     </row>
@@ -12230,10 +12230,10 @@
         <v>75</v>
       </c>
       <c r="DD26" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -12263,7 +12263,7 @@
         <v>2.13</v>
       </c>
       <c r="DO26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -12666,7 +12666,7 @@
         <v>75</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE27" t="n">
         <v>1.36</v>
@@ -12699,7 +12699,7 @@
         <v>2.21</v>
       </c>
       <c r="DO27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13546,10 +13546,10 @@
         <v>75</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -13579,7 +13579,7 @@
         <v>3.03</v>
       </c>
       <c r="DO29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -13646,12 +13646,12 @@
       </c>
       <c r="EG29" t="inlineStr">
         <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EH29" t="inlineStr">
+        <is>
           <t>1.78</t>
-        </is>
-      </c>
-      <c r="EH29" t="inlineStr">
-        <is>
-          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -13993,7 +13993,7 @@
         <v>0.79</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DF30" t="n">
         <v>0.33</v>
@@ -14023,7 +14023,7 @@
         <v>2.24</v>
       </c>
       <c r="DO30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15301,7 +15301,7 @@
         <v>1.36</v>
       </c>
       <c r="DE33" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DF33" t="n">
         <v>1</v>
@@ -15331,7 +15331,7 @@
         <v>2.29</v>
       </c>
       <c r="DO33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -15742,7 +15742,7 @@
         <v>59</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="DE34" t="n">
         <v>0.79</v>
@@ -15775,7 +15775,7 @@
         <v>2.49</v>
       </c>
       <c r="DO34" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -16178,10 +16178,10 @@
         <v>67</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF35" t="n">
         <v>1.67</v>
@@ -16211,7 +16211,7 @@
         <v>2.16</v>
       </c>
       <c r="DO35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -16614,10 +16614,10 @@
         <v>84</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF36" t="n">
         <v>0</v>
@@ -16647,7 +16647,7 @@
         <v>2.84</v>
       </c>
       <c r="DO36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP36" t="b">
         <v>0</v>
@@ -17053,7 +17053,7 @@
         <v>1.5</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DF37" t="n">
         <v>2</v>
@@ -17083,7 +17083,7 @@
         <v>2.43</v>
       </c>
       <c r="DO37" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -17930,10 +17930,10 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DF39" t="n">
         <v>3</v>
@@ -17963,7 +17963,7 @@
         <v>3.9</v>
       </c>
       <c r="DO39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -18366,7 +18366,7 @@
         <v>88</v>
       </c>
       <c r="DD40" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DE40" t="n">
         <v>1.46</v>
@@ -18798,7 +18798,7 @@
         <v>63</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DE41" t="n">
         <v>1.5</v>
@@ -18831,7 +18831,7 @@
         <v>2.9</v>
       </c>
       <c r="DO41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -19234,7 +19234,7 @@
         <v>88</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE42" t="n">
         <v>0.79</v>
@@ -19267,7 +19267,7 @@
         <v>2.02</v>
       </c>
       <c r="DO42" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -19670,10 +19670,10 @@
         <v>63</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF43" t="n">
         <v>2</v>
@@ -19703,7 +19703,7 @@
         <v>1.9</v>
       </c>
       <c r="DO43" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20106,7 +20106,7 @@
         <v>50</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE44" t="n">
         <v>1.38</v>
@@ -20961,7 +20961,7 @@
         <v>0.85</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="DF46" t="n">
         <v>0.25</v>
@@ -21405,7 +21405,7 @@
         <v>1.36</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DF47" t="n">
         <v>1.5</v>
@@ -21435,7 +21435,7 @@
         <v>2.48</v>
       </c>
       <c r="DO47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP47" t="b">
         <v>0</v>
@@ -22273,7 +22273,7 @@
         <v>0.79</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF49" t="n">
         <v>0.4</v>
@@ -22303,7 +22303,7 @@
         <v>2.37</v>
       </c>
       <c r="DO49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -22714,10 +22714,10 @@
         <v>60</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE50" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DF50" t="n">
         <v>1.8</v>
@@ -22747,7 +22747,7 @@
         <v>1.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -23161,7 +23161,7 @@
         <v>1.46</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DF51" t="n">
         <v>1.8</v>
@@ -23602,10 +23602,10 @@
         <v>70</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF52" t="n">
         <v>0.4</v>
@@ -23635,7 +23635,7 @@
         <v>2.56</v>
       </c>
       <c r="DO52" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -23702,12 +23702,12 @@
       </c>
       <c r="EG52" t="inlineStr">
         <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EH52" t="inlineStr">
+        <is>
           <t>1.88</t>
-        </is>
-      </c>
-      <c r="EH52" t="inlineStr">
-        <is>
-          <t>1.85</t>
         </is>
       </c>
     </row>
@@ -24582,12 +24582,12 @@
       </c>
       <c r="EG54" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EH54" t="inlineStr">
+        <is>
           <t>1.79</t>
-        </is>
-      </c>
-      <c r="EH54" t="inlineStr">
-        <is>
-          <t>1.94</t>
         </is>
       </c>
     </row>
@@ -24926,7 +24926,7 @@
         <v>80</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="DE55" t="n">
         <v>1.79</v>
@@ -24959,7 +24959,7 @@
         <v>3.39</v>
       </c>
       <c r="DO55" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -25026,12 +25026,12 @@
       </c>
       <c r="EG55" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EH55" t="inlineStr">
+        <is>
           <t>1.95</t>
-        </is>
-      </c>
-      <c r="EH55" t="inlineStr">
-        <is>
-          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -25370,10 +25370,10 @@
         <v>70</v>
       </c>
       <c r="DD56" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DF56" t="n">
         <v>3</v>
@@ -25403,7 +25403,7 @@
         <v>4.13</v>
       </c>
       <c r="DO56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -25806,7 +25806,7 @@
         <v>70</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DE57" t="n">
         <v>1.38</v>
@@ -25839,7 +25839,7 @@
         <v>2.74</v>
       </c>
       <c r="DO57" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -26250,10 +26250,10 @@
         <v>59</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF58" t="n">
         <v>0.83</v>
@@ -26283,7 +26283,7 @@
         <v>2</v>
       </c>
       <c r="DO58" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -26350,12 +26350,12 @@
       </c>
       <c r="EG58" t="inlineStr">
         <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EH58" t="inlineStr">
+        <is>
           <t>1.76</t>
-        </is>
-      </c>
-      <c r="EH58" t="inlineStr">
-        <is>
-          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -26694,7 +26694,7 @@
         <v>64</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DE59" t="n">
         <v>0.46</v>
@@ -26727,7 +26727,7 @@
         <v>2.53</v>
       </c>
       <c r="DO59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -26802,12 +26802,12 @@
       </c>
       <c r="EG59" t="inlineStr">
         <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EH59" t="inlineStr">
+        <is>
           <t>1.76</t>
-        </is>
-      </c>
-      <c r="EH59" t="inlineStr">
-        <is>
-          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -27146,7 +27146,7 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DE60" t="n">
         <v>1.5</v>
@@ -27179,7 +27179,7 @@
         <v>2.31</v>
       </c>
       <c r="DO60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -27590,10 +27590,10 @@
         <v>50</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="DF61" t="n">
         <v>1.5</v>
@@ -27623,7 +27623,7 @@
         <v>2.63</v>
       </c>
       <c r="DO61" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -28029,7 +28029,7 @@
         <v>1.36</v>
       </c>
       <c r="DE62" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DF62" t="n">
         <v>1.17</v>
@@ -28059,7 +28059,7 @@
         <v>3.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -28462,7 +28462,7 @@
         <v>59</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE63" t="n">
         <v>0.62</v>
@@ -29769,7 +29769,7 @@
         <v>1.79</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DF66" t="n">
         <v>1.8</v>
@@ -29799,7 +29799,7 @@
         <v>3.08</v>
       </c>
       <c r="DO66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -30202,10 +30202,10 @@
         <v>71</v>
       </c>
       <c r="DD67" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DE67" t="n">
         <v>1.23</v>
-      </c>
-      <c r="DE67" t="n">
-        <v>1.08</v>
       </c>
       <c r="DF67" t="n">
         <v>1.29</v>
@@ -30235,7 +30235,7 @@
         <v>2.55</v>
       </c>
       <c r="DO67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -30649,7 +30649,7 @@
         <v>0.46</v>
       </c>
       <c r="DE68" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DF68" t="n">
         <v>0.5</v>
@@ -31090,10 +31090,10 @@
         <v>57</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DF69" t="n">
         <v>1.43</v>
@@ -31123,7 +31123,7 @@
         <v>3.02</v>
       </c>
       <c r="DO69" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -31962,7 +31962,7 @@
         <v>54</v>
       </c>
       <c r="DD71" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DE71" t="n">
         <v>0.85</v>
@@ -31995,7 +31995,7 @@
         <v>3.31</v>
       </c>
       <c r="DO71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -32401,7 +32401,7 @@
         <v>1.5</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DF72" t="n">
         <v>2</v>
@@ -32431,7 +32431,7 @@
         <v>2.49</v>
       </c>
       <c r="DO72" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -33273,7 +33273,7 @@
         <v>0.62</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF74" t="n">
         <v>0.57</v>
@@ -33706,7 +33706,7 @@
         <v>83</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DE75" t="n">
         <v>0.79</v>
@@ -33739,7 +33739,7 @@
         <v>2.17</v>
       </c>
       <c r="DO75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -34145,7 +34145,7 @@
         <v>0.79</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DF76" t="n">
         <v>0.43</v>
@@ -34175,7 +34175,7 @@
         <v>2.09</v>
       </c>
       <c r="DO76" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -34589,7 +34589,7 @@
         <v>1.38</v>
       </c>
       <c r="DE77" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DF77" t="n">
         <v>1.25</v>
@@ -34619,7 +34619,7 @@
         <v>3.5</v>
       </c>
       <c r="DO77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -35022,7 +35022,7 @@
         <v>61</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE78" t="n">
         <v>0.46</v>
@@ -35458,7 +35458,7 @@
         <v>63</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="DE79" t="n">
         <v>0.62</v>
@@ -35558,12 +35558,12 @@
       </c>
       <c r="EG79" t="inlineStr">
         <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
           <t>1.84</t>
-        </is>
-      </c>
-      <c r="EH79" t="inlineStr">
-        <is>
-          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -35905,7 +35905,7 @@
         <v>0.85</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DF80" t="n">
         <v>0.43</v>
@@ -35935,7 +35935,7 @@
         <v>2.69</v>
       </c>
       <c r="DO80" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -36790,7 +36790,7 @@
         <v>60</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DE82" t="n">
         <v>1.46</v>
@@ -36823,7 +36823,7 @@
         <v>2.82</v>
       </c>
       <c r="DO82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -37234,7 +37234,7 @@
         <v>82</v>
       </c>
       <c r="DD83" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DE83" t="n">
         <v>0.79</v>
@@ -37267,7 +37267,7 @@
         <v>2.12</v>
       </c>
       <c r="DO83" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -37670,7 +37670,7 @@
         <v>60</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE84" t="n">
         <v>1.5</v>
@@ -37703,7 +37703,7 @@
         <v>2.54</v>
       </c>
       <c r="DO84" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP84" t="b">
         <v>0</v>
@@ -38109,7 +38109,7 @@
         <v>1.36</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DF85" t="n">
         <v>1.38</v>
@@ -38139,7 +38139,7 @@
         <v>2.74</v>
       </c>
       <c r="DO85" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -38542,10 +38542,10 @@
         <v>61</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DE86" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DF86" t="n">
         <v>1.5</v>
@@ -38575,7 +38575,7 @@
         <v>3.17</v>
       </c>
       <c r="DO86" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -38978,7 +38978,7 @@
         <v>78</v>
       </c>
       <c r="DD87" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE87" t="n">
         <v>0.79</v>
@@ -39011,7 +39011,7 @@
         <v>2.24</v>
       </c>
       <c r="DO87" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -39414,7 +39414,7 @@
         <v>60</v>
       </c>
       <c r="DD88" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE88" t="n">
         <v>1.5</v>
@@ -39447,7 +39447,7 @@
         <v>2.31</v>
       </c>
       <c r="DO88" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -39514,12 +39514,12 @@
       </c>
       <c r="EG88" t="inlineStr">
         <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH88" t="inlineStr">
+        <is>
           <t>1.84</t>
-        </is>
-      </c>
-      <c r="EH88" t="inlineStr">
-        <is>
-          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -39958,12 +39958,12 @@
       </c>
       <c r="EG89" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH89" t="inlineStr">
+        <is>
           <t>1.76</t>
-        </is>
-      </c>
-      <c r="EH89" t="inlineStr">
-        <is>
-          <t>1.96</t>
         </is>
       </c>
     </row>
@@ -40305,7 +40305,7 @@
         <v>1.36</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="DF90" t="n">
         <v>1.33</v>
@@ -40335,7 +40335,7 @@
         <v>2.91</v>
       </c>
       <c r="DO90" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -40402,12 +40402,12 @@
       </c>
       <c r="EG90" t="inlineStr">
         <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EH90" t="inlineStr">
+        <is>
           <t>1.86</t>
-        </is>
-      </c>
-      <c r="EH90" t="inlineStr">
-        <is>
-          <t>1.87</t>
         </is>
       </c>
     </row>
@@ -40746,10 +40746,10 @@
         <v>61</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE91" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DF91" t="n">
         <v>1.5</v>
@@ -40779,7 +40779,7 @@
         <v>3.05</v>
       </c>
       <c r="DO91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -41182,7 +41182,7 @@
         <v>73</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE92" t="n">
         <v>0.79</v>
@@ -41215,7 +41215,7 @@
         <v>1.85</v>
       </c>
       <c r="DO92" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -41290,12 +41290,12 @@
       </c>
       <c r="EG92" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EH92" t="inlineStr">
+        <is>
           <t>1.96</t>
-        </is>
-      </c>
-      <c r="EH92" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -41634,7 +41634,7 @@
         <v>78</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE93" t="n">
         <v>0.79</v>
@@ -41667,7 +41667,7 @@
         <v>2.35</v>
       </c>
       <c r="DO93" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -41734,12 +41734,12 @@
       </c>
       <c r="EG93" t="inlineStr">
         <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EH93" t="inlineStr">
+        <is>
           <t>1.81</t>
-        </is>
-      </c>
-      <c r="EH93" t="inlineStr">
-        <is>
-          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -42078,10 +42078,10 @@
         <v>78</v>
       </c>
       <c r="DD94" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DF94" t="n">
         <v>2</v>
@@ -42111,7 +42111,7 @@
         <v>2.91</v>
       </c>
       <c r="DO94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -42961,7 +42961,7 @@
         <v>1.79</v>
       </c>
       <c r="DE96" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DF96" t="n">
         <v>1.78</v>
@@ -42991,7 +42991,7 @@
         <v>3.39</v>
       </c>
       <c r="DO96" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -43394,10 +43394,10 @@
         <v>70</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="DE97" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DF97" t="n">
         <v>1.9</v>
@@ -43427,7 +43427,7 @@
         <v>2.98</v>
       </c>
       <c r="DO97" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -43830,10 +43830,10 @@
         <v>74</v>
       </c>
       <c r="DD98" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF98" t="n">
         <v>2.33</v>
@@ -43863,7 +43863,7 @@
         <v>2.76</v>
       </c>
       <c r="DO98" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -43930,12 +43930,12 @@
       </c>
       <c r="EG98" t="inlineStr">
         <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EH98" t="inlineStr">
+        <is>
           <t>1.85</t>
-        </is>
-      </c>
-      <c r="EH98" t="inlineStr">
-        <is>
-          <t>1.87</t>
         </is>
       </c>
     </row>
@@ -44818,12 +44818,12 @@
       </c>
       <c r="EG100" t="inlineStr">
         <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EH100" t="inlineStr">
+        <is>
           <t>1.80</t>
-        </is>
-      </c>
-      <c r="EH100" t="inlineStr">
-        <is>
-          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -45157,7 +45157,7 @@
         <v>0.62</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DF101" t="n">
         <v>0.44</v>
@@ -46029,7 +46029,7 @@
         <v>0.46</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF103" t="n">
         <v>0.44</v>
@@ -46470,10 +46470,10 @@
         <v>61</v>
       </c>
       <c r="DD104" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DE104" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DF104" t="n">
         <v>1.78</v>
@@ -46503,7 +46503,7 @@
         <v>2.83</v>
       </c>
       <c r="DO104" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -46917,7 +46917,7 @@
         <v>0.79</v>
       </c>
       <c r="DE105" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF105" t="n">
         <v>1</v>
@@ -46947,7 +46947,7 @@
         <v>2.51</v>
       </c>
       <c r="DO105" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -47353,7 +47353,7 @@
         <v>1.79</v>
       </c>
       <c r="DE106" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DF106" t="n">
         <v>1.6</v>
@@ -47383,7 +47383,7 @@
         <v>2.91</v>
       </c>
       <c r="DO106" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -47786,7 +47786,7 @@
         <v>78</v>
       </c>
       <c r="DD107" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE107" t="n">
         <v>0.79</v>
@@ -47819,7 +47819,7 @@
         <v>1.98</v>
       </c>
       <c r="DO107" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -47886,12 +47886,12 @@
       </c>
       <c r="EG107" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH107" t="inlineStr">
+        <is>
           <t>1.76</t>
-        </is>
-      </c>
-      <c r="EH107" t="inlineStr">
-        <is>
-          <t>1.96</t>
         </is>
       </c>
     </row>
@@ -48230,10 +48230,10 @@
         <v>68</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DE108" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DF108" t="n">
         <v>1.27</v>
@@ -48263,7 +48263,7 @@
         <v>3.19</v>
       </c>
       <c r="DO108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -48666,7 +48666,7 @@
         <v>72</v>
       </c>
       <c r="DD109" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DE109" t="n">
         <v>0.62</v>
@@ -49557,7 +49557,7 @@
         <v>1.46</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="DF111" t="n">
         <v>1.8</v>
@@ -50870,10 +50870,10 @@
         <v>52</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DE114" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DF114" t="n">
         <v>1.6</v>
@@ -50903,7 +50903,7 @@
         <v>2.67</v>
       </c>
       <c r="DO114" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -51314,7 +51314,7 @@
         <v>85</v>
       </c>
       <c r="DD115" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DE115" t="n">
         <v>1.79</v>
@@ -51347,7 +51347,7 @@
         <v>3.04</v>
       </c>
       <c r="DO115" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -51750,10 +51750,10 @@
         <v>70</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE116" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DF116" t="n">
         <v>1.5</v>
@@ -51783,7 +51783,7 @@
         <v>2.79</v>
       </c>
       <c r="DO116" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -51858,12 +51858,12 @@
       </c>
       <c r="EG116" t="inlineStr">
         <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EH116" t="inlineStr">
+        <is>
           <t>1.83</t>
-        </is>
-      </c>
-      <c r="EH116" t="inlineStr">
-        <is>
-          <t>1.91</t>
         </is>
       </c>
     </row>
@@ -52202,10 +52202,10 @@
         <v>67</v>
       </c>
       <c r="DD117" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="DE117" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DF117" t="n">
         <v>1.92</v>
@@ -52235,7 +52235,7 @@
         <v>3.11</v>
       </c>
       <c r="DO117" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -52302,12 +52302,12 @@
       </c>
       <c r="EG117" t="inlineStr">
         <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH117" t="inlineStr">
+        <is>
           <t>1.84</t>
-        </is>
-      </c>
-      <c r="EH117" t="inlineStr">
-        <is>
-          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -52646,7 +52646,7 @@
         <v>70</v>
       </c>
       <c r="DD118" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DE118" t="n">
         <v>1.5</v>
@@ -52679,7 +52679,7 @@
         <v>2.92</v>
       </c>
       <c r="DO118" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -52746,12 +52746,12 @@
       </c>
       <c r="EG118" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH118" t="inlineStr">
+        <is>
           <t>1.76</t>
-        </is>
-      </c>
-      <c r="EH118" t="inlineStr">
-        <is>
-          <t>1.96</t>
         </is>
       </c>
     </row>
@@ -53190,12 +53190,12 @@
       </c>
       <c r="EG119" t="inlineStr">
         <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH119" t="inlineStr">
+        <is>
           <t>1.85</t>
-        </is>
-      </c>
-      <c r="EH119" t="inlineStr">
-        <is>
-          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -53529,7 +53529,7 @@
         <v>0.62</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DF120" t="n">
         <v>0.64</v>
@@ -53965,7 +53965,7 @@
         <v>1.38</v>
       </c>
       <c r="DE121" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="DF121" t="n">
         <v>1.09</v>
@@ -53995,7 +53995,7 @@
         <v>2.97</v>
       </c>
       <c r="DO121" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -54401,7 +54401,7 @@
         <v>0.79</v>
       </c>
       <c r="DE122" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF122" t="n">
         <v>0.83</v>
@@ -54431,7 +54431,7 @@
         <v>2.25</v>
       </c>
       <c r="DO122" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -54498,12 +54498,12 @@
       </c>
       <c r="EG122" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH122" t="inlineStr">
+        <is>
           <t>1.75</t>
-        </is>
-      </c>
-      <c r="EH122" t="inlineStr">
-        <is>
-          <t>1.96</t>
         </is>
       </c>
     </row>
@@ -55714,10 +55714,10 @@
         <v>71</v>
       </c>
       <c r="DD125" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE125" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DF125" t="n">
         <v>1.17</v>
@@ -55747,7 +55747,7 @@
         <v>2.73</v>
       </c>
       <c r="DO125" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -56150,10 +56150,10 @@
         <v>79</v>
       </c>
       <c r="DD126" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DE126" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF126" t="n">
         <v>1.82</v>
@@ -56183,7 +56183,7 @@
         <v>2.54</v>
       </c>
       <c r="DO126" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP126" t="b">
         <v>0</v>
@@ -56586,7 +56586,7 @@
         <v>55</v>
       </c>
       <c r="DD127" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE127" t="n">
         <v>0.85</v>
@@ -57163,10 +57163,10 @@
         <v>2</v>
       </c>
       <c r="K129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L129" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M129" t="n">
         <v>4</v>
@@ -57528,24 +57528,24 @@
       </c>
       <c r="EA129" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="EB129" t="inlineStr"/>
       <c r="EC129" t="inlineStr"/>
       <c r="ED129" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="EE129" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="EF129" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EG129" t="inlineStr"/>
@@ -57886,7 +57886,7 @@
         <v>64</v>
       </c>
       <c r="DD130" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DE130" t="n">
         <v>0.79</v>
@@ -57919,7 +57919,7 @@
         <v>2.27</v>
       </c>
       <c r="DO130" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -57946,34 +57946,34 @@
       <c r="DX130" t="inlineStr"/>
       <c r="DY130" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="DZ130" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="EA130" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EB130" t="inlineStr"/>
       <c r="EC130" t="inlineStr"/>
       <c r="ED130" t="inlineStr">
         <is>
-          <t>10.51</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="EE130" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="EF130" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EG130" t="inlineStr"/>
@@ -58374,17 +58374,17 @@
       <c r="DX131" t="inlineStr"/>
       <c r="DY131" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="DZ131" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EA131" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="EB131" t="inlineStr">
@@ -58399,17 +58399,17 @@
       </c>
       <c r="ED131" t="inlineStr">
         <is>
-          <t>11.48</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="EE131" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="EF131" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EG131" t="inlineStr"/>
@@ -58808,17 +58808,29 @@
       </c>
       <c r="DW132" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="DX132" t="inlineStr">
         <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="DY132" t="inlineStr"/>
-      <c r="DZ132" t="inlineStr"/>
-      <c r="EA132" t="inlineStr"/>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="DY132" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="DZ132" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EA132" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
       <c r="EB132" t="inlineStr">
         <is>
           <t>1.76</t>
@@ -58831,21 +58843,2193 @@
       </c>
       <c r="ED132" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="EE132" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="EF132" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EG132" t="inlineStr"/>
       <c r="EH132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>14</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>46110.97222222222</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2</v>
+      </c>
+      <c r="I133" t="n">
+        <v>3</v>
+      </c>
+      <c r="J133" t="n">
+        <v>7</v>
+      </c>
+      <c r="K133" t="n">
+        <v>2</v>
+      </c>
+      <c r="L133" t="n">
+        <v>9</v>
+      </c>
+      <c r="M133" t="n">
+        <v>3</v>
+      </c>
+      <c r="N133" t="n">
+        <v>6</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>1</v>
+      </c>
+      <c r="R133" t="n">
+        <v>7</v>
+      </c>
+      <c r="S133" t="n">
+        <v>14</v>
+      </c>
+      <c r="T133" t="n">
+        <v>4</v>
+      </c>
+      <c r="U133" t="n">
+        <v>15</v>
+      </c>
+      <c r="V133" t="n">
+        <v>11</v>
+      </c>
+      <c r="W133" t="n">
+        <v>10</v>
+      </c>
+      <c r="X133" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>Estadio Departamental Libertad</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>Carrera 8, San Juan de Pasto</t>
+        </is>
+      </c>
+      <c r="AC133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>2142</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>81</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU133" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV133" t="n">
+        <v>4</v>
+      </c>
+      <c r="CW133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX133" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY133" t="n">
+        <v>17</v>
+      </c>
+      <c r="CZ133" t="n">
+        <v>65</v>
+      </c>
+      <c r="DA133" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB133" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC133" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD133" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DE133" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DF133" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DG133" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DH133" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DI133" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DJ133" t="n">
+        <v>36</v>
+      </c>
+      <c r="DK133" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL133" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM133" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DN133" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DO133" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW133" t="inlineStr"/>
+      <c r="DX133" t="inlineStr"/>
+      <c r="DY133" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="DZ133" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EA133" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EB133" t="inlineStr"/>
+      <c r="EC133" t="inlineStr"/>
+      <c r="ED133" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EE133" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="EF133" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="EG133" t="inlineStr"/>
+      <c r="EH133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>14</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Llaneros</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>46111.625</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" t="n">
+        <v>2</v>
+      </c>
+      <c r="J134" t="n">
+        <v>8</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1</v>
+      </c>
+      <c r="L134" t="n">
+        <v>9</v>
+      </c>
+      <c r="M134" t="n">
+        <v>3</v>
+      </c>
+      <c r="N134" t="n">
+        <v>3</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>5</v>
+      </c>
+      <c r="R134" t="n">
+        <v>2</v>
+      </c>
+      <c r="S134" t="n">
+        <v>6</v>
+      </c>
+      <c r="T134" t="n">
+        <v>5</v>
+      </c>
+      <c r="U134" t="n">
+        <v>11</v>
+      </c>
+      <c r="V134" t="n">
+        <v>7</v>
+      </c>
+      <c r="W134" t="n">
+        <v>11</v>
+      </c>
+      <c r="X134" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Calle Lombana</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>, Villavicencio</t>
+        </is>
+      </c>
+      <c r="AC134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>12000</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>84</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>140</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU134" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV134" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX134" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY134" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ134" t="n">
+        <v>39</v>
+      </c>
+      <c r="DA134" t="n">
+        <v>89</v>
+      </c>
+      <c r="DB134" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC134" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD134" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DE134" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DF134" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DG134" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DH134" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DI134" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DJ134" t="n">
+        <v>62</v>
+      </c>
+      <c r="DK134" t="n">
+        <v>12</v>
+      </c>
+      <c r="DL134" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DM134" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DN134" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="DO134" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW134" t="inlineStr"/>
+      <c r="DX134" t="inlineStr"/>
+      <c r="DY134" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="DZ134" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EA134" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EB134" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EC134" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="ED134" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EE134" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="EF134" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EG134" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EH134" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>14</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>46111.96527777778</v>
+      </c>
+      <c r="G135" t="n">
+        <v>2</v>
+      </c>
+      <c r="H135" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" t="n">
+        <v>3</v>
+      </c>
+      <c r="J135" t="n">
+        <v>5</v>
+      </c>
+      <c r="K135" t="n">
+        <v>6</v>
+      </c>
+      <c r="L135" t="n">
+        <v>11</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1</v>
+      </c>
+      <c r="N135" t="n">
+        <v>3</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>4</v>
+      </c>
+      <c r="R135" t="n">
+        <v>2</v>
+      </c>
+      <c r="S135" t="n">
+        <v>14</v>
+      </c>
+      <c r="T135" t="n">
+        <v>9</v>
+      </c>
+      <c r="U135" t="n">
+        <v>18</v>
+      </c>
+      <c r="V135" t="n">
+        <v>11</v>
+      </c>
+      <c r="W135" t="n">
+        <v>10</v>
+      </c>
+      <c r="X135" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>Estadio Atanasio Girardot</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
+        </is>
+      </c>
+      <c r="AC135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>2137</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>60</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU135" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV135" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX135" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY135" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ135" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA135" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB135" t="n">
+        <v>46</v>
+      </c>
+      <c r="DC135" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD135" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DE135" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DF135" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DG135" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH135" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DI135" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ135" t="n">
+        <v>46</v>
+      </c>
+      <c r="DK135" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL135" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DM135" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DN135" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="DO135" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW135" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DX135" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="DY135" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="DZ135" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EA135" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="EB135" t="inlineStr"/>
+      <c r="EC135" t="inlineStr"/>
+      <c r="ED135" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EE135" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EF135" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EG135" t="inlineStr"/>
+      <c r="EH135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>14</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>46112.05555555555</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2</v>
+      </c>
+      <c r="H136" t="n">
+        <v>2</v>
+      </c>
+      <c r="I136" t="n">
+        <v>4</v>
+      </c>
+      <c r="J136" t="n">
+        <v>13</v>
+      </c>
+      <c r="K136" t="n">
+        <v>2</v>
+      </c>
+      <c r="L136" t="n">
+        <v>15</v>
+      </c>
+      <c r="M136" t="n">
+        <v>2</v>
+      </c>
+      <c r="N136" t="n">
+        <v>4</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>4</v>
+      </c>
+      <c r="R136" t="n">
+        <v>5</v>
+      </c>
+      <c r="S136" t="n">
+        <v>11</v>
+      </c>
+      <c r="T136" t="n">
+        <v>5</v>
+      </c>
+      <c r="U136" t="n">
+        <v>15</v>
+      </c>
+      <c r="V136" t="n">
+        <v>10</v>
+      </c>
+      <c r="W136" t="n">
+        <v>9</v>
+      </c>
+      <c r="X136" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>Estadio Nemesio Camacho El Campín</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AC136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU136" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV136" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX136" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY136" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ136" t="n">
+        <v>58</v>
+      </c>
+      <c r="DA136" t="n">
+        <v>81</v>
+      </c>
+      <c r="DB136" t="n">
+        <v>27</v>
+      </c>
+      <c r="DC136" t="n">
+        <v>66</v>
+      </c>
+      <c r="DD136" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE136" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DF136" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DG136" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DH136" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DI136" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DJ136" t="n">
+        <v>43</v>
+      </c>
+      <c r="DK136" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL136" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DM136" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DN136" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="DO136" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW136" t="inlineStr"/>
+      <c r="DX136" t="inlineStr"/>
+      <c r="DY136" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="DZ136" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EA136" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EB136" t="inlineStr"/>
+      <c r="EC136" t="inlineStr"/>
+      <c r="ED136" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="EE136" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="EF136" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EG136" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH136" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>15</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Rionegro Águilas</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>46113.04166666666</v>
+      </c>
+      <c r="G137" t="n">
+        <v>4</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" t="n">
+        <v>5</v>
+      </c>
+      <c r="J137" t="n">
+        <v>2</v>
+      </c>
+      <c r="K137" t="n">
+        <v>3</v>
+      </c>
+      <c r="L137" t="n">
+        <v>5</v>
+      </c>
+      <c r="M137" t="n">
+        <v>2</v>
+      </c>
+      <c r="N137" t="n">
+        <v>2</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>8</v>
+      </c>
+      <c r="R137" t="n">
+        <v>1</v>
+      </c>
+      <c r="S137" t="n">
+        <v>11</v>
+      </c>
+      <c r="T137" t="n">
+        <v>5</v>
+      </c>
+      <c r="U137" t="n">
+        <v>19</v>
+      </c>
+      <c r="V137" t="n">
+        <v>6</v>
+      </c>
+      <c r="W137" t="n">
+        <v>8</v>
+      </c>
+      <c r="X137" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Murillo Toro</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
+        </is>
+      </c>
+      <c r="AC137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>2140</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>86</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU137" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV137" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX137" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY137" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ137" t="n">
+        <v>31</v>
+      </c>
+      <c r="DA137" t="n">
+        <v>62</v>
+      </c>
+      <c r="DB137" t="n">
+        <v>16</v>
+      </c>
+      <c r="DC137" t="n">
+        <v>46</v>
+      </c>
+      <c r="DD137" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DE137" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DF137" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DG137" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DH137" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DI137" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DJ137" t="n">
+        <v>69</v>
+      </c>
+      <c r="DK137" t="n">
+        <v>39</v>
+      </c>
+      <c r="DL137" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DM137" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DN137" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DO137" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW137" t="inlineStr"/>
+      <c r="DX137" t="inlineStr"/>
+      <c r="DY137" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="DZ137" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EA137" t="inlineStr">
+        <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="EB137" t="inlineStr"/>
+      <c r="EC137" t="inlineStr"/>
+      <c r="ED137" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="EE137" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="EF137" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EG137" t="inlineStr"/>
+      <c r="EH137" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH137" headerRowCount="1">
-  <autoFilter ref="A1:EH137"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH144" headerRowCount="1">
+  <autoFilter ref="A1:EH144"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH137"/>
+  <dimension ref="A1:EH144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2185,7 +2185,7 @@
         <v>1.07</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2626,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="DE4" t="n">
         <v>1.5</v>
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3474,10 +3474,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -3910,10 +3910,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="DE8" t="n">
         <v>1.36</v>
@@ -5226,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE10" t="n">
         <v>1.36</v>
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5662,10 +5662,10 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6109,7 +6109,7 @@
         <v>1.5</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6525,7 +6525,7 @@
         <v>1.86</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6555,7 +6555,7 @@
         <v>1.86</v>
       </c>
       <c r="DO13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -6966,7 +6966,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DE14" t="n">
         <v>1.07</v>
@@ -6999,7 +6999,7 @@
         <v>1.99</v>
       </c>
       <c r="DO14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP14" t="b">
         <v>0</v>
@@ -7402,10 +7402,10 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7435,7 +7435,7 @@
         <v>3.19</v>
       </c>
       <c r="DO15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -7857,7 +7857,7 @@
         <v>1.36</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -7887,7 +7887,7 @@
         <v>2.53</v>
       </c>
       <c r="DO16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8282,10 +8282,10 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>2.13</v>
       </c>
       <c r="DO17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -8721,7 +8721,7 @@
         <v>1.36</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DF18" t="n">
         <v>1</v>
@@ -9154,7 +9154,7 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE19" t="n">
         <v>1.79</v>
@@ -9590,10 +9590,10 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -9623,7 +9623,7 @@
         <v>4.47</v>
       </c>
       <c r="DO20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10026,10 +10026,10 @@
         <v>100</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10059,7 +10059,7 @@
         <v>2.47</v>
       </c>
       <c r="DO21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10473,7 +10473,7 @@
         <v>1.07</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="DF22" t="n">
         <v>2</v>
@@ -10914,7 +10914,7 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE23" t="n">
         <v>1.86</v>
@@ -10947,7 +10947,7 @@
         <v>2.38</v>
       </c>
       <c r="DO23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11350,10 +11350,10 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -11383,7 +11383,7 @@
         <v>1.88</v>
       </c>
       <c r="DO24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -11786,10 +11786,10 @@
         <v>25</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -11819,7 +11819,7 @@
         <v>2.57</v>
       </c>
       <c r="DO25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12230,10 +12230,10 @@
         <v>75</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -12263,7 +12263,7 @@
         <v>2.13</v>
       </c>
       <c r="DO26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13102,7 +13102,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="DE28" t="n">
         <v>1.5</v>
@@ -13546,10 +13546,10 @@
         <v>75</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -13579,7 +13579,7 @@
         <v>3.03</v>
       </c>
       <c r="DO29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -13990,7 +13990,7 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DE30" t="n">
         <v>1.07</v>
@@ -14418,10 +14418,10 @@
         <v>67</v>
       </c>
       <c r="DD31" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DF31" t="n">
         <v>0.33</v>
@@ -14451,7 +14451,7 @@
         <v>2.8</v>
       </c>
       <c r="DO31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -14862,10 +14862,10 @@
         <v>50</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE32" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF32" t="n">
         <v>1.67</v>
@@ -14895,7 +14895,7 @@
         <v>2.62</v>
       </c>
       <c r="DO32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15301,7 +15301,7 @@
         <v>1.36</v>
       </c>
       <c r="DE33" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DF33" t="n">
         <v>1</v>
@@ -15742,10 +15742,10 @@
         <v>59</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="DF34" t="n">
         <v>1.67</v>
@@ -15775,7 +15775,7 @@
         <v>2.49</v>
       </c>
       <c r="DO34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -16178,7 +16178,7 @@
         <v>67</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="DE35" t="n">
         <v>1.36</v>
@@ -16614,10 +16614,10 @@
         <v>84</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF36" t="n">
         <v>0</v>
@@ -16647,7 +16647,7 @@
         <v>2.84</v>
       </c>
       <c r="DO36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP36" t="b">
         <v>0</v>
@@ -17494,7 +17494,7 @@
         <v>67</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DE38" t="n">
         <v>1.79</v>
@@ -17527,7 +17527,7 @@
         <v>2.42</v>
       </c>
       <c r="DO38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -17930,10 +17930,10 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="DF39" t="n">
         <v>3</v>
@@ -17963,7 +17963,7 @@
         <v>3.9</v>
       </c>
       <c r="DO39" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -18366,10 +18366,10 @@
         <v>88</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF40" t="n">
         <v>2.25</v>
@@ -18399,7 +18399,7 @@
         <v>2.56</v>
       </c>
       <c r="DO40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP40" t="b">
         <v>0</v>
@@ -18798,7 +18798,7 @@
         <v>63</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE41" t="n">
         <v>1.5</v>
@@ -18831,7 +18831,7 @@
         <v>2.9</v>
       </c>
       <c r="DO41" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -19237,7 +19237,7 @@
         <v>1.36</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DF42" t="n">
         <v>1.25</v>
@@ -19673,7 +19673,7 @@
         <v>1.86</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="DF43" t="n">
         <v>2</v>
@@ -20109,7 +20109,7 @@
         <v>1.07</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DF44" t="n">
         <v>1.5</v>
@@ -20139,7 +20139,7 @@
         <v>3.37</v>
       </c>
       <c r="DO44" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -20525,7 +20525,7 @@
         <v>1.79</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DF45" t="n">
         <v>2</v>
@@ -20555,7 +20555,7 @@
         <v>2.5</v>
       </c>
       <c r="DO45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -20958,10 +20958,10 @@
         <v>50</v>
       </c>
       <c r="DD46" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DF46" t="n">
         <v>0.25</v>
@@ -20991,7 +20991,7 @@
         <v>2.87</v>
       </c>
       <c r="DO46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -21405,7 +21405,7 @@
         <v>1.36</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DF47" t="n">
         <v>1.5</v>
@@ -21826,10 +21826,10 @@
         <v>59</v>
       </c>
       <c r="DD48" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DF48" t="n">
         <v>1.33</v>
@@ -21859,7 +21859,7 @@
         <v>1.75</v>
       </c>
       <c r="DO48" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -22270,10 +22270,10 @@
         <v>80</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF49" t="n">
         <v>0.4</v>
@@ -22303,7 +22303,7 @@
         <v>2.37</v>
       </c>
       <c r="DO49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -22714,10 +22714,10 @@
         <v>60</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DF50" t="n">
         <v>1.8</v>
@@ -22747,7 +22747,7 @@
         <v>1.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -23158,7 +23158,7 @@
         <v>60</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE51" t="n">
         <v>1.86</v>
@@ -23191,7 +23191,7 @@
         <v>2.38</v>
       </c>
       <c r="DO51" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP51" t="b">
         <v>0</v>
@@ -23602,7 +23602,7 @@
         <v>70</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE52" t="n">
         <v>1.36</v>
@@ -24474,10 +24474,10 @@
         <v>68</v>
       </c>
       <c r="DD54" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="DF54" t="n">
         <v>0.2</v>
@@ -24507,7 +24507,7 @@
         <v>1.66</v>
       </c>
       <c r="DO54" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -24926,7 +24926,7 @@
         <v>80</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DE55" t="n">
         <v>1.79</v>
@@ -25370,7 +25370,7 @@
         <v>70</v>
       </c>
       <c r="DD56" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="DE56" t="n">
         <v>1.07</v>
@@ -25403,7 +25403,7 @@
         <v>4.13</v>
       </c>
       <c r="DO56" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -25806,10 +25806,10 @@
         <v>70</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DF57" t="n">
         <v>1.75</v>
@@ -25839,7 +25839,7 @@
         <v>2.74</v>
       </c>
       <c r="DO57" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -26250,10 +26250,10 @@
         <v>59</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="DF58" t="n">
         <v>0.83</v>
@@ -26283,7 +26283,7 @@
         <v>2</v>
       </c>
       <c r="DO58" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -26694,10 +26694,10 @@
         <v>64</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DF59" t="n">
         <v>0.83</v>
@@ -26727,7 +26727,7 @@
         <v>2.53</v>
       </c>
       <c r="DO59" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -27146,7 +27146,7 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DE60" t="n">
         <v>1.5</v>
@@ -27593,7 +27593,7 @@
         <v>1.86</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DF61" t="n">
         <v>1.5</v>
@@ -28029,7 +28029,7 @@
         <v>1.36</v>
       </c>
       <c r="DE62" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="DF62" t="n">
         <v>1.17</v>
@@ -28059,7 +28059,7 @@
         <v>3.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -28465,7 +28465,7 @@
         <v>1.07</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DF63" t="n">
         <v>1.17</v>
@@ -28495,7 +28495,7 @@
         <v>2.4</v>
       </c>
       <c r="DO63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -28898,10 +28898,10 @@
         <v>60</v>
       </c>
       <c r="DD64" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DF64" t="n">
         <v>0.4</v>
@@ -28931,7 +28931,7 @@
         <v>1.97</v>
       </c>
       <c r="DO64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -29334,10 +29334,10 @@
         <v>57</v>
       </c>
       <c r="DD65" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DF65" t="n">
         <v>1.4</v>
@@ -29367,7 +29367,7 @@
         <v>2.22</v>
       </c>
       <c r="DO65" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -29769,7 +29769,7 @@
         <v>1.79</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="DF66" t="n">
         <v>1.8</v>
@@ -29799,7 +29799,7 @@
         <v>3.08</v>
       </c>
       <c r="DO66" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -30202,10 +30202,10 @@
         <v>71</v>
       </c>
       <c r="DD67" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE67" t="n">
         <v>1.21</v>
-      </c>
-      <c r="DE67" t="n">
-        <v>1.23</v>
       </c>
       <c r="DF67" t="n">
         <v>1.29</v>
@@ -30235,7 +30235,7 @@
         <v>2.55</v>
       </c>
       <c r="DO67" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -30646,10 +30646,10 @@
         <v>62</v>
       </c>
       <c r="DD68" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DF68" t="n">
         <v>0.5</v>
@@ -30679,7 +30679,7 @@
         <v>1.99</v>
       </c>
       <c r="DO68" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -31090,7 +31090,7 @@
         <v>57</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DE69" t="n">
         <v>1.07</v>
@@ -31526,7 +31526,7 @@
         <v>55</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE70" t="n">
         <v>1.36</v>
@@ -31559,7 +31559,7 @@
         <v>2.63</v>
       </c>
       <c r="DO70" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP70" t="b">
         <v>0</v>
@@ -31962,10 +31962,10 @@
         <v>54</v>
       </c>
       <c r="DD71" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="DE71" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF71" t="n">
         <v>2.25</v>
@@ -31995,7 +31995,7 @@
         <v>3.31</v>
       </c>
       <c r="DO71" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -32401,7 +32401,7 @@
         <v>1.5</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DF72" t="n">
         <v>2</v>
@@ -32842,7 +32842,7 @@
         <v>72</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE73" t="n">
         <v>1.79</v>
@@ -32875,7 +32875,7 @@
         <v>3.26</v>
       </c>
       <c r="DO73" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -33270,7 +33270,7 @@
         <v>69</v>
       </c>
       <c r="DD74" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DE74" t="n">
         <v>1.36</v>
@@ -33303,7 +33303,7 @@
         <v>2.19</v>
       </c>
       <c r="DO74" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -33706,10 +33706,10 @@
         <v>83</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="DE75" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="DF75" t="n">
         <v>1.67</v>
@@ -33739,7 +33739,7 @@
         <v>2.17</v>
       </c>
       <c r="DO75" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -34142,7 +34142,7 @@
         <v>65</v>
       </c>
       <c r="DD76" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DE76" t="n">
         <v>1.86</v>
@@ -34586,10 +34586,10 @@
         <v>65</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE77" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="DF77" t="n">
         <v>1.25</v>
@@ -34619,7 +34619,7 @@
         <v>3.5</v>
       </c>
       <c r="DO77" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -35022,10 +35022,10 @@
         <v>61</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DF78" t="n">
         <v>1</v>
@@ -35055,7 +35055,7 @@
         <v>2.25</v>
       </c>
       <c r="DO78" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -35458,10 +35458,10 @@
         <v>63</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DF79" t="n">
         <v>1.63</v>
@@ -35491,7 +35491,7 @@
         <v>2.48</v>
       </c>
       <c r="DO79" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -35902,10 +35902,10 @@
         <v>65</v>
       </c>
       <c r="DD80" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="DF80" t="n">
         <v>0.43</v>
@@ -35935,7 +35935,7 @@
         <v>2.69</v>
       </c>
       <c r="DO80" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -36346,7 +36346,7 @@
         <v>93</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="DE81" t="n">
         <v>1.79</v>
@@ -36790,10 +36790,10 @@
         <v>60</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF82" t="n">
         <v>0.88</v>
@@ -36823,7 +36823,7 @@
         <v>2.82</v>
       </c>
       <c r="DO82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -37234,10 +37234,10 @@
         <v>82</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DF83" t="n">
         <v>1.88</v>
@@ -37267,7 +37267,7 @@
         <v>2.12</v>
       </c>
       <c r="DO83" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -38545,7 +38545,7 @@
         <v>1.86</v>
       </c>
       <c r="DE86" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="DF86" t="n">
         <v>1.5</v>
@@ -38575,7 +38575,7 @@
         <v>3.17</v>
       </c>
       <c r="DO86" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -38981,7 +38981,7 @@
         <v>1.07</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="DF87" t="n">
         <v>1.22</v>
@@ -39414,7 +39414,7 @@
         <v>60</v>
       </c>
       <c r="DD88" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="DE88" t="n">
         <v>1.5</v>
@@ -39861,7 +39861,7 @@
         <v>1.79</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF89" t="n">
         <v>1.88</v>
@@ -39891,7 +39891,7 @@
         <v>2.77</v>
       </c>
       <c r="DO89" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -40305,7 +40305,7 @@
         <v>1.36</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DF90" t="n">
         <v>1.33</v>
@@ -40749,7 +40749,7 @@
         <v>1.36</v>
       </c>
       <c r="DE91" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="DF91" t="n">
         <v>1.5</v>
@@ -40779,7 +40779,7 @@
         <v>3.05</v>
       </c>
       <c r="DO91" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -41182,10 +41182,10 @@
         <v>73</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="DE92" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="DF92" t="n">
         <v>1.22</v>
@@ -41215,7 +41215,7 @@
         <v>1.85</v>
       </c>
       <c r="DO92" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -41634,10 +41634,10 @@
         <v>78</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DF93" t="n">
         <v>1.22</v>
@@ -41667,7 +41667,7 @@
         <v>2.35</v>
       </c>
       <c r="DO93" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -42078,10 +42078,10 @@
         <v>78</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="DF94" t="n">
         <v>2</v>
@@ -42111,7 +42111,7 @@
         <v>2.91</v>
       </c>
       <c r="DO94" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -42514,10 +42514,10 @@
         <v>69</v>
       </c>
       <c r="DD95" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE95" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DF95" t="n">
         <v>1.75</v>
@@ -42547,7 +42547,7 @@
         <v>2.19</v>
       </c>
       <c r="DO95" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -42961,7 +42961,7 @@
         <v>1.79</v>
       </c>
       <c r="DE96" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="DF96" t="n">
         <v>1.78</v>
@@ -42991,7 +42991,7 @@
         <v>3.39</v>
       </c>
       <c r="DO96" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -43394,10 +43394,10 @@
         <v>70</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DF97" t="n">
         <v>1.9</v>
@@ -43427,7 +43427,7 @@
         <v>2.98</v>
       </c>
       <c r="DO97" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -43830,10 +43830,10 @@
         <v>74</v>
       </c>
       <c r="DD98" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="DF98" t="n">
         <v>2.33</v>
@@ -43863,7 +43863,7 @@
         <v>2.76</v>
       </c>
       <c r="DO98" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -44277,7 +44277,7 @@
         <v>1.5</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF99" t="n">
         <v>1.9</v>
@@ -44307,7 +44307,7 @@
         <v>2.56</v>
       </c>
       <c r="DO99" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP99" t="b">
         <v>0</v>
@@ -44718,7 +44718,7 @@
         <v>70</v>
       </c>
       <c r="DD100" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DE100" t="n">
         <v>1.36</v>
@@ -45154,10 +45154,10 @@
         <v>59</v>
       </c>
       <c r="DD101" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DF101" t="n">
         <v>0.44</v>
@@ -45187,7 +45187,7 @@
         <v>2.38</v>
       </c>
       <c r="DO101" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -45590,10 +45590,10 @@
         <v>56</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE102" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF102" t="n">
         <v>1.11</v>
@@ -45623,7 +45623,7 @@
         <v>2.71</v>
       </c>
       <c r="DO102" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -46026,7 +46026,7 @@
         <v>67</v>
       </c>
       <c r="DD103" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DE103" t="n">
         <v>1.36</v>
@@ -46059,7 +46059,7 @@
         <v>2.12</v>
       </c>
       <c r="DO103" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -46470,7 +46470,7 @@
         <v>61</v>
       </c>
       <c r="DD104" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="DE104" t="n">
         <v>1.86</v>
@@ -46503,7 +46503,7 @@
         <v>2.83</v>
       </c>
       <c r="DO104" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -46914,10 +46914,10 @@
         <v>74</v>
       </c>
       <c r="DD105" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="DE105" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF105" t="n">
         <v>1</v>
@@ -46947,7 +46947,7 @@
         <v>2.51</v>
       </c>
       <c r="DO105" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -47786,10 +47786,10 @@
         <v>78</v>
       </c>
       <c r="DD107" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="DE107" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DF107" t="n">
         <v>1.27</v>
@@ -47819,7 +47819,7 @@
         <v>1.98</v>
       </c>
       <c r="DO107" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -48230,10 +48230,10 @@
         <v>68</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE108" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="DF108" t="n">
         <v>1.27</v>
@@ -48263,7 +48263,7 @@
         <v>3.19</v>
       </c>
       <c r="DO108" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -48666,10 +48666,10 @@
         <v>72</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DE109" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DF109" t="n">
         <v>1.91</v>
@@ -48699,7 +48699,7 @@
         <v>2.33</v>
       </c>
       <c r="DO109" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -49113,7 +49113,7 @@
         <v>1.5</v>
       </c>
       <c r="DE110" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DF110" t="n">
         <v>1.82</v>
@@ -49143,7 +49143,7 @@
         <v>2.1</v>
       </c>
       <c r="DO110" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -49554,10 +49554,10 @@
         <v>67</v>
       </c>
       <c r="DD111" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DF111" t="n">
         <v>1.8</v>
@@ -49587,7 +49587,7 @@
         <v>2.93</v>
       </c>
       <c r="DO111" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -49993,7 +49993,7 @@
         <v>1.36</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DF112" t="n">
         <v>1.36</v>
@@ -50023,7 +50023,7 @@
         <v>2.73</v>
       </c>
       <c r="DO112" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -50426,10 +50426,10 @@
         <v>71</v>
       </c>
       <c r="DD113" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DE113" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="DF113" t="n">
         <v>0.5</v>
@@ -50459,7 +50459,7 @@
         <v>2.1</v>
       </c>
       <c r="DO113" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -51314,7 +51314,7 @@
         <v>85</v>
       </c>
       <c r="DD115" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE115" t="n">
         <v>1.79</v>
@@ -51347,7 +51347,7 @@
         <v>3.04</v>
       </c>
       <c r="DO115" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -51753,7 +51753,7 @@
         <v>1.36</v>
       </c>
       <c r="DE116" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="DF116" t="n">
         <v>1.5</v>
@@ -51783,7 +51783,7 @@
         <v>2.79</v>
       </c>
       <c r="DO116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -52202,10 +52202,10 @@
         <v>67</v>
       </c>
       <c r="DD117" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DE117" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DF117" t="n">
         <v>1.92</v>
@@ -52235,7 +52235,7 @@
         <v>3.11</v>
       </c>
       <c r="DO117" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -52646,7 +52646,7 @@
         <v>70</v>
       </c>
       <c r="DD118" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="DE118" t="n">
         <v>1.5</v>
@@ -52679,7 +52679,7 @@
         <v>2.92</v>
       </c>
       <c r="DO118" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -53090,7 +53090,7 @@
         <v>57</v>
       </c>
       <c r="DD119" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DE119" t="n">
         <v>1.36</v>
@@ -53123,7 +53123,7 @@
         <v>2.45</v>
       </c>
       <c r="DO119" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -53526,7 +53526,7 @@
         <v>59</v>
       </c>
       <c r="DD120" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DE120" t="n">
         <v>1.86</v>
@@ -53559,7 +53559,7 @@
         <v>2.17</v>
       </c>
       <c r="DO120" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -53962,10 +53962,10 @@
         <v>69</v>
       </c>
       <c r="DD121" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DE121" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DF121" t="n">
         <v>1.09</v>
@@ -53995,7 +53995,7 @@
         <v>2.97</v>
       </c>
       <c r="DO121" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -54398,7 +54398,7 @@
         <v>64</v>
       </c>
       <c r="DD122" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="DE122" t="n">
         <v>1.36</v>
@@ -54842,10 +54842,10 @@
         <v>78</v>
       </c>
       <c r="DD123" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DE123" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DF123" t="n">
         <v>0.45</v>
@@ -54875,7 +54875,7 @@
         <v>1.87</v>
       </c>
       <c r="DO123" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -55281,7 +55281,7 @@
         <v>1.79</v>
       </c>
       <c r="DE124" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DF124" t="n">
         <v>1.58</v>
@@ -55311,7 +55311,7 @@
         <v>2.8</v>
       </c>
       <c r="DO124" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -55717,7 +55717,7 @@
         <v>1.07</v>
       </c>
       <c r="DE125" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DF125" t="n">
         <v>1.17</v>
@@ -56150,10 +56150,10 @@
         <v>79</v>
       </c>
       <c r="DD126" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="DE126" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="DF126" t="n">
         <v>1.82</v>
@@ -56183,7 +56183,7 @@
         <v>2.54</v>
       </c>
       <c r="DO126" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP126" t="b">
         <v>0</v>
@@ -56589,7 +56589,7 @@
         <v>1.36</v>
       </c>
       <c r="DE127" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DF127" t="n">
         <v>1.33</v>
@@ -56619,7 +56619,7 @@
         <v>2.36</v>
       </c>
       <c r="DO127" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -57022,10 +57022,10 @@
         <v>67</v>
       </c>
       <c r="DD128" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE128" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DF128" t="n">
         <v>1.58</v>
@@ -57055,7 +57055,7 @@
         <v>2.77</v>
       </c>
       <c r="DO128" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -57458,10 +57458,10 @@
         <v>80</v>
       </c>
       <c r="DD129" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DE129" t="n">
         <v>0.79</v>
-      </c>
-      <c r="DE129" t="n">
-        <v>0.62</v>
       </c>
       <c r="DF129" t="n">
         <v>0.62</v>
@@ -57491,7 +57491,7 @@
         <v>1.93</v>
       </c>
       <c r="DO129" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -57889,7 +57889,7 @@
         <v>1.86</v>
       </c>
       <c r="DE130" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="DF130" t="n">
         <v>1.67</v>
@@ -58317,7 +58317,7 @@
         <v>1.36</v>
       </c>
       <c r="DE131" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DF131" t="n">
         <v>1.23</v>
@@ -58347,7 +58347,7 @@
         <v>2.22</v>
       </c>
       <c r="DO131" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -59194,10 +59194,10 @@
         <v>80</v>
       </c>
       <c r="DD133" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DE133" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="DF133" t="n">
         <v>2.08</v>
@@ -59227,7 +59227,7 @@
         <v>3.05</v>
       </c>
       <c r="DO133" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -59622,10 +59622,10 @@
         <v>73</v>
       </c>
       <c r="DD134" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="DE134" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DF134" t="n">
         <v>1.23</v>
@@ -59655,7 +59655,7 @@
         <v>2.66</v>
       </c>
       <c r="DO134" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -59810,7 +59810,7 @@
         <v>10</v>
       </c>
       <c r="X135" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y135" t="n">
         <v>44</v>
@@ -59916,7 +59916,7 @@
         <v>0</v>
       </c>
       <c r="BF135" t="n">
-        <v>-1</v>
+        <v>12764</v>
       </c>
       <c r="BG135" t="n">
         <v>2</v>
@@ -60066,10 +60066,10 @@
         <v>75</v>
       </c>
       <c r="DD135" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="DF135" t="n">
         <v>1.08</v>
@@ -60099,7 +60099,7 @@
         <v>3.15</v>
       </c>
       <c r="DO135" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -60204,13 +60204,13 @@
         <v>4</v>
       </c>
       <c r="J136" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K136" t="n">
         <v>2</v>
       </c>
       <c r="L136" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M136" t="n">
         <v>2</v>
@@ -60231,13 +60231,13 @@
         <v>5</v>
       </c>
       <c r="S136" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T136" t="n">
         <v>5</v>
       </c>
       <c r="U136" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V136" t="n">
         <v>10</v>
@@ -60352,7 +60352,7 @@
         <v>0</v>
       </c>
       <c r="BF136" t="n">
-        <v>-1</v>
+        <v>29815</v>
       </c>
       <c r="BG136" t="n">
         <v>-1</v>
@@ -60412,13 +60412,13 @@
         <v>85</v>
       </c>
       <c r="BZ136" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="CA136" t="n">
         <v>1.18</v>
       </c>
       <c r="CB136" t="n">
-        <v>2.84</v>
+        <v>3.09</v>
       </c>
       <c r="CC136" t="n">
         <v>0</v>
@@ -60502,7 +60502,7 @@
         <v>66</v>
       </c>
       <c r="DD136" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE136" t="n">
         <v>1.07</v>
@@ -61030,6 +61030,3022 @@
       </c>
       <c r="EG137" t="inlineStr"/>
       <c r="EH137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>15</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Alianza Petrolera</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>46113.88194444445</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>7</v>
+      </c>
+      <c r="K138" t="n">
+        <v>5</v>
+      </c>
+      <c r="L138" t="n">
+        <v>12</v>
+      </c>
+      <c r="M138" t="n">
+        <v>3</v>
+      </c>
+      <c r="N138" t="n">
+        <v>3</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>2</v>
+      </c>
+      <c r="R138" t="n">
+        <v>5</v>
+      </c>
+      <c r="S138" t="n">
+        <v>8</v>
+      </c>
+      <c r="T138" t="n">
+        <v>8</v>
+      </c>
+      <c r="U138" t="n">
+        <v>10</v>
+      </c>
+      <c r="V138" t="n">
+        <v>13</v>
+      </c>
+      <c r="W138" t="n">
+        <v>14</v>
+      </c>
+      <c r="X138" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>Estadio Armando Maestre Pavajeau</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>, Valledupar</t>
+        </is>
+      </c>
+      <c r="AC138" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU138" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV138" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX138" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY138" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ138" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA138" t="n">
+        <v>74</v>
+      </c>
+      <c r="DB138" t="n">
+        <v>37</v>
+      </c>
+      <c r="DC138" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD138" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DE138" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DF138" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DG138" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DH138" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DI138" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DJ138" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK138" t="n">
+        <v>26</v>
+      </c>
+      <c r="DL138" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DM138" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DN138" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="DO138" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW138" t="inlineStr"/>
+      <c r="DX138" t="inlineStr"/>
+      <c r="DY138" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="DZ138" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EA138" t="inlineStr">
+        <is>
+          <t>5.42</t>
+        </is>
+      </c>
+      <c r="EB138" t="inlineStr"/>
+      <c r="EC138" t="inlineStr"/>
+      <c r="ED138" t="inlineStr">
+        <is>
+          <t>3.89</t>
+        </is>
+      </c>
+      <c r="EE138" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EF138" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EG138" t="inlineStr"/>
+      <c r="EH138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>15</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Llaneros</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>46113.97916666666</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" t="n">
+        <v>12</v>
+      </c>
+      <c r="K139" t="n">
+        <v>4</v>
+      </c>
+      <c r="L139" t="n">
+        <v>16</v>
+      </c>
+      <c r="M139" t="n">
+        <v>3</v>
+      </c>
+      <c r="N139" t="n">
+        <v>4</v>
+      </c>
+      <c r="O139" t="n">
+        <v>1</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>3</v>
+      </c>
+      <c r="R139" t="n">
+        <v>4</v>
+      </c>
+      <c r="S139" t="n">
+        <v>9</v>
+      </c>
+      <c r="T139" t="n">
+        <v>3</v>
+      </c>
+      <c r="U139" t="n">
+        <v>12</v>
+      </c>
+      <c r="V139" t="n">
+        <v>7</v>
+      </c>
+      <c r="W139" t="n">
+        <v>6</v>
+      </c>
+      <c r="X139" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>69</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>Estadio Nemesio Camacho El Campín</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AC139" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>2159</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>71</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>71</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU139" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV139" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX139" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY139" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ139" t="n">
+        <v>34</v>
+      </c>
+      <c r="DA139" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB139" t="n">
+        <v>22</v>
+      </c>
+      <c r="DC139" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD139" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DE139" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF139" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG139" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DH139" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DI139" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DJ139" t="n">
+        <v>67</v>
+      </c>
+      <c r="DK139" t="n">
+        <v>18</v>
+      </c>
+      <c r="DL139" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM139" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DN139" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DO139" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW139" t="inlineStr"/>
+      <c r="DX139" t="inlineStr"/>
+      <c r="DY139" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="DZ139" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EA139" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="EB139" t="inlineStr"/>
+      <c r="EC139" t="inlineStr"/>
+      <c r="ED139" t="inlineStr">
+        <is>
+          <t>7.81</t>
+        </is>
+      </c>
+      <c r="EE139" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="EF139" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EG139" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EH139" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>15</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>46114.0625</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>6</v>
+      </c>
+      <c r="K140" t="n">
+        <v>2</v>
+      </c>
+      <c r="L140" t="n">
+        <v>8</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1</v>
+      </c>
+      <c r="N140" t="n">
+        <v>1</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>5</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>19</v>
+      </c>
+      <c r="T140" t="n">
+        <v>4</v>
+      </c>
+      <c r="U140" t="n">
+        <v>24</v>
+      </c>
+      <c r="V140" t="n">
+        <v>4</v>
+      </c>
+      <c r="W140" t="n">
+        <v>10</v>
+      </c>
+      <c r="X140" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>Estadio Atanasio Girardot</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
+        </is>
+      </c>
+      <c r="AC140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>78</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>17</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>163</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>56</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU140" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV140" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX140" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY140" t="n">
+        <v>16</v>
+      </c>
+      <c r="CZ140" t="n">
+        <v>71</v>
+      </c>
+      <c r="DA140" t="n">
+        <v>89</v>
+      </c>
+      <c r="DB140" t="n">
+        <v>37</v>
+      </c>
+      <c r="DC140" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD140" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DE140" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DF140" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DG140" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DH140" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DI140" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DJ140" t="n">
+        <v>30</v>
+      </c>
+      <c r="DK140" t="n">
+        <v>11</v>
+      </c>
+      <c r="DL140" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DM140" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DN140" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="DO140" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW140" t="inlineStr"/>
+      <c r="DX140" t="inlineStr"/>
+      <c r="DY140" t="inlineStr"/>
+      <c r="DZ140" t="inlineStr"/>
+      <c r="EA140" t="inlineStr"/>
+      <c r="EB140" t="inlineStr"/>
+      <c r="EC140" t="inlineStr"/>
+      <c r="ED140" t="inlineStr">
+        <is>
+          <t>7.37</t>
+        </is>
+      </c>
+      <c r="EE140" t="inlineStr">
+        <is>
+          <t>4.59</t>
+        </is>
+      </c>
+      <c r="EF140" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EG140" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EH140" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>15</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Boyacá Chicó</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>46114.79166666666</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" t="n">
+        <v>8</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>8</v>
+      </c>
+      <c r="M141" t="n">
+        <v>3</v>
+      </c>
+      <c r="N141" t="n">
+        <v>5</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>6</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="n">
+        <v>17</v>
+      </c>
+      <c r="T141" t="n">
+        <v>4</v>
+      </c>
+      <c r="U141" t="n">
+        <v>23</v>
+      </c>
+      <c r="V141" t="n">
+        <v>4</v>
+      </c>
+      <c r="W141" t="n">
+        <v>15</v>
+      </c>
+      <c r="X141" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA141" t="inlineStr"/>
+      <c r="AB141" t="inlineStr"/>
+      <c r="AC141" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>2151</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>95</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>42</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU141" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV141" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX141" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY141" t="n">
+        <v>19</v>
+      </c>
+      <c r="CZ141" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA141" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB141" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC141" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD141" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DE141" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DF141" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="DG141" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="DH141" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="DI141" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="DJ141" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK141" t="n">
+        <v>31</v>
+      </c>
+      <c r="DL141" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DM141" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DN141" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DO141" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW141" t="inlineStr"/>
+      <c r="DX141" t="inlineStr"/>
+      <c r="DY141" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="DZ141" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EA141" t="inlineStr">
+        <is>
+          <t>5.36</t>
+        </is>
+      </c>
+      <c r="EB141" t="inlineStr"/>
+      <c r="EC141" t="inlineStr"/>
+      <c r="ED141" t="inlineStr">
+        <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="EE141" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EF141" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EG141" t="inlineStr"/>
+      <c r="EH141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>15</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>46114.88194444445</v>
+      </c>
+      <c r="G142" t="n">
+        <v>2</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>2</v>
+      </c>
+      <c r="J142" t="n">
+        <v>2</v>
+      </c>
+      <c r="K142" t="n">
+        <v>3</v>
+      </c>
+      <c r="L142" t="n">
+        <v>5</v>
+      </c>
+      <c r="M142" t="n">
+        <v>5</v>
+      </c>
+      <c r="N142" t="n">
+        <v>3</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>5</v>
+      </c>
+      <c r="R142" t="n">
+        <v>4</v>
+      </c>
+      <c r="S142" t="n">
+        <v>11</v>
+      </c>
+      <c r="T142" t="n">
+        <v>6</v>
+      </c>
+      <c r="U142" t="n">
+        <v>16</v>
+      </c>
+      <c r="V142" t="n">
+        <v>10</v>
+      </c>
+      <c r="W142" t="n">
+        <v>10</v>
+      </c>
+      <c r="X142" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>Estadio Olímpico Pascual Guerrero</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>Carrera 36 entre Calles 5 y 5B3, Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="AC142" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>2141</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>88</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU142" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV142" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX142" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY142" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ142" t="n">
+        <v>46</v>
+      </c>
+      <c r="DA142" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB142" t="n">
+        <v>46</v>
+      </c>
+      <c r="DC142" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD142" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DE142" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DF142" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DG142" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DH142" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DI142" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DJ142" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK142" t="n">
+        <v>31</v>
+      </c>
+      <c r="DL142" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DM142" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DN142" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DO142" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW142" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="DX142" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="DY142" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="DZ142" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EA142" t="inlineStr">
+        <is>
+          <t>4.37</t>
+        </is>
+      </c>
+      <c r="EB142" t="inlineStr"/>
+      <c r="EC142" t="inlineStr"/>
+      <c r="ED142" t="inlineStr">
+        <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="EE142" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EF142" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EG142" t="inlineStr"/>
+      <c r="EH142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>15</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Jaguares de Córdoba</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>46114.97222222222</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" t="n">
+        <v>2</v>
+      </c>
+      <c r="K143" t="n">
+        <v>5</v>
+      </c>
+      <c r="L143" t="n">
+        <v>7</v>
+      </c>
+      <c r="M143" t="n">
+        <v>2</v>
+      </c>
+      <c r="N143" t="n">
+        <v>2</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>4</v>
+      </c>
+      <c r="R143" t="n">
+        <v>7</v>
+      </c>
+      <c r="S143" t="n">
+        <v>9</v>
+      </c>
+      <c r="T143" t="n">
+        <v>6</v>
+      </c>
+      <c r="U143" t="n">
+        <v>13</v>
+      </c>
+      <c r="V143" t="n">
+        <v>13</v>
+      </c>
+      <c r="W143" t="n">
+        <v>12</v>
+      </c>
+      <c r="X143" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>Estadio de Fútbol Jaraguay de Montería</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>, Montería</t>
+        </is>
+      </c>
+      <c r="AC143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>2150</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>129</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>31</v>
+      </c>
+      <c r="CT143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU143" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV143" t="n">
+        <v>4</v>
+      </c>
+      <c r="CW143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX143" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY143" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ143" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA143" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB143" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC143" t="n">
+        <v>72</v>
+      </c>
+      <c r="DD143" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DE143" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF143" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DG143" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH143" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DI143" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ143" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK143" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL143" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DM143" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DN143" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="DO143" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW143" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="DX143" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="DY143" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="DZ143" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EA143" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EB143" t="inlineStr"/>
+      <c r="EC143" t="inlineStr"/>
+      <c r="ED143" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EE143" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="EF143" t="inlineStr">
+        <is>
+          <t>4.37</t>
+        </is>
+      </c>
+      <c r="EG143" t="inlineStr"/>
+      <c r="EH143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>15</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>46115.0625</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" t="n">
+        <v>2</v>
+      </c>
+      <c r="J144" t="n">
+        <v>3</v>
+      </c>
+      <c r="K144" t="n">
+        <v>5</v>
+      </c>
+      <c r="L144" t="n">
+        <v>8</v>
+      </c>
+      <c r="M144" t="n">
+        <v>3</v>
+      </c>
+      <c r="N144" t="n">
+        <v>3</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>1</v>
+      </c>
+      <c r="R144" t="n">
+        <v>4</v>
+      </c>
+      <c r="S144" t="n">
+        <v>12</v>
+      </c>
+      <c r="T144" t="n">
+        <v>12</v>
+      </c>
+      <c r="U144" t="n">
+        <v>13</v>
+      </c>
+      <c r="V144" t="n">
+        <v>16</v>
+      </c>
+      <c r="W144" t="n">
+        <v>8</v>
+      </c>
+      <c r="X144" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>Estadio Palogrande</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>Carrera 24 # 64 - 00, Manizales</t>
+        </is>
+      </c>
+      <c r="AC144" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>82</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ144" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM144" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN144" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ144" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT144" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV144" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW144" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX144" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY144" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ144" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CA144" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CB144" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="CC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR144" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS144" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU144" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV144" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX144" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY144" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ144" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA144" t="n">
+        <v>93</v>
+      </c>
+      <c r="DB144" t="n">
+        <v>48</v>
+      </c>
+      <c r="DC144" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD144" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE144" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DF144" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DG144" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DH144" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DI144" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DJ144" t="n">
+        <v>41</v>
+      </c>
+      <c r="DK144" t="n">
+        <v>8</v>
+      </c>
+      <c r="DL144" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM144" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DN144" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="DO144" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP144" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ144" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV144" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW144" t="inlineStr"/>
+      <c r="DX144" t="inlineStr"/>
+      <c r="DY144" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="DZ144" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EA144" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="EB144" t="inlineStr"/>
+      <c r="EC144" t="inlineStr"/>
+      <c r="ED144" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="EE144" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EF144" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EG144" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH144" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH144" headerRowCount="1">
-  <autoFilter ref="A1:EH144"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH147" headerRowCount="1">
+  <autoFilter ref="A1:EH147"/>
   <tableColumns count="138">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH144"/>
+  <dimension ref="A1:EH147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -2629,7 +2629,7 @@
         <v>1.71</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -4349,7 +4349,7 @@
         <v>0.93</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4790,10 +4790,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4823,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5226,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DE10" t="n">
         <v>1.36</v>
@@ -6106,7 +6106,7 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE12" t="n">
         <v>0.8</v>
@@ -6139,7 +6139,7 @@
         <v>1.82</v>
       </c>
       <c r="DO12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6522,7 +6522,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DE13" t="n">
         <v>0.86</v>
@@ -7854,7 +7854,7 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE16" t="n">
         <v>1.21</v>
@@ -9157,7 +9157,7 @@
         <v>1.4</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9187,7 +9187,7 @@
         <v>2.56</v>
       </c>
       <c r="DO19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9593,7 +9593,7 @@
         <v>1.67</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -9623,7 +9623,7 @@
         <v>4.47</v>
       </c>
       <c r="DO20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10503,7 +10503,7 @@
         <v>2.27</v>
       </c>
       <c r="DO22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -10917,7 +10917,7 @@
         <v>1.21</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DF23" t="n">
         <v>0</v>
@@ -11786,7 +11786,7 @@
         <v>25</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DE25" t="n">
         <v>0.43</v>
@@ -12669,7 +12669,7 @@
         <v>1.36</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DF27" t="n">
         <v>0.5</v>
@@ -13105,7 +13105,7 @@
         <v>0.93</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -13135,7 +13135,7 @@
         <v>2.03</v>
       </c>
       <c r="DO28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14023,7 +14023,7 @@
         <v>2.24</v>
       </c>
       <c r="DO30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14421,7 +14421,7 @@
         <v>0.79</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DF31" t="n">
         <v>0.33</v>
@@ -15298,7 +15298,7 @@
         <v>50</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE33" t="n">
         <v>1.87</v>
@@ -15331,7 +15331,7 @@
         <v>2.29</v>
       </c>
       <c r="DO33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17050,10 +17050,10 @@
         <v>84</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DF37" t="n">
         <v>2</v>
@@ -17083,7 +17083,7 @@
         <v>2.43</v>
       </c>
       <c r="DO37" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP37" t="b">
         <v>0</v>
@@ -17497,7 +17497,7 @@
         <v>0.43</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="DF38" t="n">
         <v>0.67</v>
@@ -18801,7 +18801,7 @@
         <v>1.21</v>
       </c>
       <c r="DE41" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF41" t="n">
         <v>0.5</v>
@@ -19670,7 +19670,7 @@
         <v>63</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DE43" t="n">
         <v>1.33</v>
@@ -19703,7 +19703,7 @@
         <v>1.9</v>
       </c>
       <c r="DO43" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20109,7 +20109,7 @@
         <v>1.07</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DF44" t="n">
         <v>1.5</v>
@@ -20139,7 +20139,7 @@
         <v>3.37</v>
       </c>
       <c r="DO44" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -20522,7 +20522,7 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="DE45" t="n">
         <v>0.79</v>
@@ -21402,7 +21402,7 @@
         <v>63</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE47" t="n">
         <v>1.4</v>
@@ -21435,7 +21435,7 @@
         <v>2.48</v>
       </c>
       <c r="DO47" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP47" t="b">
         <v>0</v>
@@ -23161,7 +23161,7 @@
         <v>1.36</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DF51" t="n">
         <v>1.8</v>
@@ -24046,10 +24046,10 @@
         <v>60</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -24079,7 +24079,7 @@
         <v>2.58</v>
       </c>
       <c r="DO53" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -24929,7 +24929,7 @@
         <v>1.67</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="DF55" t="n">
         <v>1.4</v>
@@ -24959,7 +24959,7 @@
         <v>3.39</v>
       </c>
       <c r="DO55" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -25809,7 +25809,7 @@
         <v>1.71</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DF57" t="n">
         <v>1.75</v>
@@ -27149,7 +27149,7 @@
         <v>1.87</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF60" t="n">
         <v>2.17</v>
@@ -27179,7 +27179,7 @@
         <v>2.31</v>
       </c>
       <c r="DO60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -27590,7 +27590,7 @@
         <v>50</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DE61" t="n">
         <v>1.67</v>
@@ -27623,7 +27623,7 @@
         <v>2.63</v>
       </c>
       <c r="DO61" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -28026,7 +28026,7 @@
         <v>75</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE62" t="n">
         <v>2.21</v>
@@ -29337,7 +29337,7 @@
         <v>0.93</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DF65" t="n">
         <v>1.4</v>
@@ -29367,7 +29367,7 @@
         <v>2.22</v>
       </c>
       <c r="DO65" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -29766,7 +29766,7 @@
         <v>90</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="DE66" t="n">
         <v>1.71</v>
@@ -31123,7 +31123,7 @@
         <v>3.02</v>
       </c>
       <c r="DO69" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -31529,7 +31529,7 @@
         <v>1.36</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DF70" t="n">
         <v>1.67</v>
@@ -32398,7 +32398,7 @@
         <v>64</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE72" t="n">
         <v>1.4</v>
@@ -32431,7 +32431,7 @@
         <v>2.49</v>
       </c>
       <c r="DO72" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -32842,10 +32842,10 @@
         <v>72</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -32875,7 +32875,7 @@
         <v>3.26</v>
       </c>
       <c r="DO73" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -34145,7 +34145,7 @@
         <v>0.8</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DF76" t="n">
         <v>0.43</v>
@@ -34175,7 +34175,7 @@
         <v>2.09</v>
       </c>
       <c r="DO76" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -34586,7 +34586,7 @@
         <v>65</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DE77" t="n">
         <v>2.21</v>
@@ -36349,7 +36349,7 @@
         <v>0.93</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="DF81" t="n">
         <v>1.43</v>
@@ -36379,7 +36379,7 @@
         <v>2.39</v>
       </c>
       <c r="DO81" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -37673,7 +37673,7 @@
         <v>1.36</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF84" t="n">
         <v>1.57</v>
@@ -38106,7 +38106,7 @@
         <v>51</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE85" t="n">
         <v>1.07</v>
@@ -38139,7 +38139,7 @@
         <v>2.74</v>
       </c>
       <c r="DO85" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -38542,7 +38542,7 @@
         <v>61</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DE86" t="n">
         <v>2.21</v>
@@ -39011,7 +39011,7 @@
         <v>2.24</v>
       </c>
       <c r="DO87" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -39417,7 +39417,7 @@
         <v>1.33</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF88" t="n">
         <v>1.25</v>
@@ -39447,7 +39447,7 @@
         <v>2.31</v>
       </c>
       <c r="DO88" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -39858,7 +39858,7 @@
         <v>75</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="DE89" t="n">
         <v>0.86</v>
@@ -40302,7 +40302,7 @@
         <v>56</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE90" t="n">
         <v>1.67</v>
@@ -40335,7 +40335,7 @@
         <v>2.91</v>
       </c>
       <c r="DO90" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42958,7 +42958,7 @@
         <v>88</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="DE96" t="n">
         <v>2.21</v>
@@ -44274,7 +44274,7 @@
         <v>64</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE99" t="n">
         <v>1.36</v>
@@ -44721,7 +44721,7 @@
         <v>0.8</v>
       </c>
       <c r="DE100" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DF100" t="n">
         <v>0.6</v>
@@ -44751,7 +44751,7 @@
         <v>2.22</v>
       </c>
       <c r="DO100" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -45590,7 +45590,7 @@
         <v>56</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DE102" t="n">
         <v>0.86</v>
@@ -46473,7 +46473,7 @@
         <v>1.71</v>
       </c>
       <c r="DE104" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DF104" t="n">
         <v>1.78</v>
@@ -47350,7 +47350,7 @@
         <v>80</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="DE106" t="n">
         <v>1.07</v>
@@ -47383,7 +47383,7 @@
         <v>2.91</v>
       </c>
       <c r="DO106" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -49110,7 +49110,7 @@
         <v>63</v>
       </c>
       <c r="DD110" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE110" t="n">
         <v>0.43</v>
@@ -49990,10 +49990,10 @@
         <v>53</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DF112" t="n">
         <v>1.36</v>
@@ -50023,7 +50023,7 @@
         <v>2.73</v>
       </c>
       <c r="DO112" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -50870,7 +50870,7 @@
         <v>52</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DE114" t="n">
         <v>1.07</v>
@@ -50903,7 +50903,7 @@
         <v>2.67</v>
       </c>
       <c r="DO114" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -51317,7 +51317,7 @@
         <v>1.21</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="DF115" t="n">
         <v>1</v>
@@ -52649,7 +52649,7 @@
         <v>2.21</v>
       </c>
       <c r="DE118" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DF118" t="n">
         <v>2.18</v>
@@ -53093,7 +53093,7 @@
         <v>0.86</v>
       </c>
       <c r="DE119" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DF119" t="n">
         <v>0.73</v>
@@ -53529,7 +53529,7 @@
         <v>0.79</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DF120" t="n">
         <v>0.64</v>
@@ -53962,7 +53962,7 @@
         <v>69</v>
       </c>
       <c r="DD121" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DE121" t="n">
         <v>1.21</v>
@@ -55278,7 +55278,7 @@
         <v>82</v>
       </c>
       <c r="DD124" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="DE124" t="n">
         <v>1.36</v>
@@ -55747,7 +55747,7 @@
         <v>2.73</v>
       </c>
       <c r="DO125" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -57025,7 +57025,7 @@
         <v>1.36</v>
       </c>
       <c r="DE128" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DF128" t="n">
         <v>1.58</v>
@@ -57886,7 +57886,7 @@
         <v>64</v>
       </c>
       <c r="DD130" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DE130" t="n">
         <v>0.93</v>
@@ -57919,7 +57919,7 @@
         <v>2.27</v>
       </c>
       <c r="DO130" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -58314,7 +58314,7 @@
         <v>65</v>
       </c>
       <c r="DD131" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE131" t="n">
         <v>0.43</v>
@@ -58750,10 +58750,10 @@
         <v>81</v>
       </c>
       <c r="DD132" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DE132" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="DF132" t="n">
         <v>1.62</v>
@@ -58783,7 +58783,7 @@
         <v>2.74</v>
       </c>
       <c r="DO132" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -60535,7 +60535,7 @@
         <v>2.84</v>
       </c>
       <c r="DO136" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -60938,7 +60938,7 @@
         <v>46</v>
       </c>
       <c r="DD137" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DE137" t="n">
         <v>1.36</v>
@@ -61523,22 +61523,22 @@
         <v>4</v>
       </c>
       <c r="S139" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T139" t="n">
         <v>3</v>
       </c>
       <c r="U139" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V139" t="n">
         <v>7</v>
       </c>
       <c r="W139" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="X139" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Y139" t="n">
         <v>69</v>
@@ -61704,13 +61704,13 @@
         <v>71</v>
       </c>
       <c r="BZ139" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="CA139" t="n">
         <v>0.89</v>
       </c>
       <c r="CB139" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="CC139" t="n">
         <v>0</v>
@@ -61794,7 +61794,7 @@
         <v>70</v>
       </c>
       <c r="DD139" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DE139" t="n">
         <v>1.33</v>
@@ -61827,7 +61827,7 @@
         <v>2.57</v>
       </c>
       <c r="DO139" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -61953,7 +61953,7 @@
         <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
@@ -61962,16 +61962,16 @@
         <v>19</v>
       </c>
       <c r="T140" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U140" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V140" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W140" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X140" t="n">
         <v>3</v>
@@ -62140,13 +62140,13 @@
         <v>56</v>
       </c>
       <c r="BZ140" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="CA140" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="CB140" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="CC140" t="n">
         <v>0</v>
@@ -62365,10 +62365,10 @@
         <v>8</v>
       </c>
       <c r="M141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N141" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -62386,13 +62386,13 @@
         <v>17</v>
       </c>
       <c r="T141" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U141" t="n">
         <v>23</v>
       </c>
       <c r="V141" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W141" t="n">
         <v>15</v>
@@ -62409,10 +62409,10 @@
       <c r="AA141" t="inlineStr"/>
       <c r="AB141" t="inlineStr"/>
       <c r="AC141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD141" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE141" t="n">
         <v>1.82</v>
@@ -62529,10 +62529,10 @@
         <v>1</v>
       </c>
       <c r="BQ141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BS141" t="n">
         <v>3</v>
@@ -62559,10 +62559,10 @@
         <v>2.18</v>
       </c>
       <c r="CA141" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="CB141" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="CC141" t="n">
         <v>0</v>
@@ -62779,10 +62779,10 @@
         <v>2</v>
       </c>
       <c r="K142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M142" t="n">
         <v>5</v>
@@ -62800,25 +62800,25 @@
         <v>5</v>
       </c>
       <c r="R142" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S142" t="n">
         <v>11</v>
       </c>
       <c r="T142" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U142" t="n">
         <v>16</v>
       </c>
       <c r="V142" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W142" t="n">
         <v>10</v>
       </c>
       <c r="X142" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y142" t="n">
         <v>55</v>
@@ -62987,10 +62987,10 @@
         <v>1.61</v>
       </c>
       <c r="CA142" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="CB142" t="n">
-        <v>2.82</v>
+        <v>3.01</v>
       </c>
       <c r="CC142" t="n">
         <v>1</v>
@@ -63672,13 +63672,13 @@
         <v>1</v>
       </c>
       <c r="R144" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S144" t="n">
         <v>12</v>
       </c>
       <c r="T144" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U144" t="n">
         <v>13</v>
@@ -63859,10 +63859,10 @@
         <v>1.14</v>
       </c>
       <c r="CA144" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="CB144" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="CC144" t="n">
         <v>0</v>
@@ -64046,6 +64046,1290 @@
           <t>1.85</t>
         </is>
       </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>15</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>La Equidad</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>46115.97222222222</v>
+      </c>
+      <c r="G145" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" t="n">
+        <v>2</v>
+      </c>
+      <c r="J145" t="n">
+        <v>2</v>
+      </c>
+      <c r="K145" t="n">
+        <v>3</v>
+      </c>
+      <c r="L145" t="n">
+        <v>5</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>3</v>
+      </c>
+      <c r="R145" t="n">
+        <v>7</v>
+      </c>
+      <c r="S145" t="n">
+        <v>7</v>
+      </c>
+      <c r="T145" t="n">
+        <v>10</v>
+      </c>
+      <c r="U145" t="n">
+        <v>10</v>
+      </c>
+      <c r="V145" t="n">
+        <v>17</v>
+      </c>
+      <c r="W145" t="n">
+        <v>8</v>
+      </c>
+      <c r="X145" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>Estadio Metropolitano de Techo</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>68</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM145" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV145" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW145" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX145" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY145" t="n">
+        <v>89</v>
+      </c>
+      <c r="BZ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA145" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CB145" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR145" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS145" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU145" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX145" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY145" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ145" t="n">
+        <v>54</v>
+      </c>
+      <c r="DA145" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB145" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC145" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD145" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DE145" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DF145" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DG145" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH145" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DI145" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ145" t="n">
+        <v>47</v>
+      </c>
+      <c r="DK145" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL145" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DM145" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DN145" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="DO145" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP145" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ145" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV145" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW145" t="inlineStr"/>
+      <c r="DX145" t="inlineStr"/>
+      <c r="DY145" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="DZ145" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EA145" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="EB145" t="inlineStr"/>
+      <c r="EC145" t="inlineStr"/>
+      <c r="ED145" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EE145" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EF145" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="EG145" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EH145" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>15</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>46116.0625</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="n">
+        <v>2</v>
+      </c>
+      <c r="I146" t="n">
+        <v>3</v>
+      </c>
+      <c r="J146" t="n">
+        <v>11</v>
+      </c>
+      <c r="K146" t="n">
+        <v>4</v>
+      </c>
+      <c r="L146" t="n">
+        <v>15</v>
+      </c>
+      <c r="M146" t="n">
+        <v>2</v>
+      </c>
+      <c r="N146" t="n">
+        <v>6</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>4</v>
+      </c>
+      <c r="R146" t="n">
+        <v>4</v>
+      </c>
+      <c r="S146" t="n">
+        <v>9</v>
+      </c>
+      <c r="T146" t="n">
+        <v>10</v>
+      </c>
+      <c r="U146" t="n">
+        <v>13</v>
+      </c>
+      <c r="V146" t="n">
+        <v>14</v>
+      </c>
+      <c r="W146" t="n">
+        <v>8</v>
+      </c>
+      <c r="X146" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA146" t="inlineStr"/>
+      <c r="AB146" t="inlineStr"/>
+      <c r="AC146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT146" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU146" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB146" t="n">
+        <v>2132</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI146" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK146" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL146" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM146" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN146" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP146" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR146" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS146" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT146" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV146" t="n">
+        <v>58</v>
+      </c>
+      <c r="BW146" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX146" t="n">
+        <v>113</v>
+      </c>
+      <c r="BY146" t="n">
+        <v>50</v>
+      </c>
+      <c r="BZ146" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CA146" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CB146" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CC146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR146" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS146" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU146" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV146" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX146" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY146" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ146" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA146" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB146" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC146" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD146" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE146" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DF146" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DG146" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DH146" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DI146" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DJ146" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK146" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL146" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DM146" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DN146" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DO146" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP146" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ146" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR146" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS146" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT146" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU146" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV146" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW146" t="inlineStr"/>
+      <c r="DX146" t="inlineStr"/>
+      <c r="DY146" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="DZ146" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EA146" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="EB146" t="inlineStr"/>
+      <c r="EC146" t="inlineStr"/>
+      <c r="ED146" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="EE146" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="EF146" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EG146" t="inlineStr"/>
+      <c r="EH146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>10</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>46117.02083333334</v>
+      </c>
+      <c r="G147" t="n">
+        <v>2</v>
+      </c>
+      <c r="H147" t="n">
+        <v>2</v>
+      </c>
+      <c r="I147" t="n">
+        <v>4</v>
+      </c>
+      <c r="J147" t="n">
+        <v>5</v>
+      </c>
+      <c r="K147" t="n">
+        <v>4</v>
+      </c>
+      <c r="L147" t="n">
+        <v>9</v>
+      </c>
+      <c r="M147" t="n">
+        <v>4</v>
+      </c>
+      <c r="N147" t="n">
+        <v>2</v>
+      </c>
+      <c r="O147" t="n">
+        <v>1</v>
+      </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>4</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6</v>
+      </c>
+      <c r="S147" t="n">
+        <v>11</v>
+      </c>
+      <c r="T147" t="n">
+        <v>12</v>
+      </c>
+      <c r="U147" t="n">
+        <v>15</v>
+      </c>
+      <c r="V147" t="n">
+        <v>18</v>
+      </c>
+      <c r="W147" t="n">
+        <v>8</v>
+      </c>
+      <c r="X147" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Murillo Toro</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
+        </is>
+      </c>
+      <c r="AC147" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ147" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR147" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT147" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV147" t="n">
+        <v>31</v>
+      </c>
+      <c r="BW147" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX147" t="n">
+        <v>88</v>
+      </c>
+      <c r="BY147" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ147" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CA147" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CB147" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="CC147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR147" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS147" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU147" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV147" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX147" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY147" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ147" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA147" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB147" t="n">
+        <v>22</v>
+      </c>
+      <c r="DC147" t="n">
+        <v>61</v>
+      </c>
+      <c r="DD147" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DE147" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DF147" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DG147" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DH147" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DI147" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DJ147" t="n">
+        <v>61</v>
+      </c>
+      <c r="DK147" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL147" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM147" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DN147" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="DO147" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP147" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ147" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR147" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS147" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT147" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU147" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV147" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW147" t="inlineStr"/>
+      <c r="DX147" t="inlineStr"/>
+      <c r="DY147" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="DZ147" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EA147" t="inlineStr">
+        <is>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="EB147" t="inlineStr"/>
+      <c r="EC147" t="inlineStr"/>
+      <c r="ED147" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="EE147" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="EF147" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EG147" t="inlineStr"/>
+      <c r="EH147" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,9 +141,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH147" headerRowCount="1">
-  <autoFilter ref="A1:EH147"/>
-  <tableColumns count="138">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EJ150" headerRowCount="1">
+  <autoFilter ref="A1:EJ150"/>
+  <tableColumns count="140">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
     <tableColumn id="3" name="game_week"/>
@@ -282,6 +282,8 @@
     <tableColumn id="136" name="pinnacle_ft_1"/>
     <tableColumn id="137" name="pinnacle_corners_over_95"/>
     <tableColumn id="138" name="pinnacle_corners_under_95"/>
+    <tableColumn id="139" name="pinnacle_1st_half_over15"/>
+    <tableColumn id="140" name="pinnacle_1st_half_under15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -576,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH147"/>
+  <dimension ref="A1:EJ150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -717,6 +719,8 @@
     <col width="18" customWidth="1" min="136" max="136"/>
     <col width="31.2" customWidth="1" min="137" max="137"/>
     <col width="32.4" customWidth="1" min="138" max="138"/>
+    <col width="31.2" customWidth="1" min="139" max="139"/>
+    <col width="32.4" customWidth="1" min="140" max="140"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1410,6 +1414,16 @@
           <t>pinnacle_corners_under_95</t>
         </is>
       </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_over15</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_under15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1746,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DE2" t="n">
         <v>1.33</v>
@@ -1779,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -1846,6 +1860,8 @@
       </c>
       <c r="EG2" t="inlineStr"/>
       <c r="EH2" t="inlineStr"/>
+      <c r="EI2" t="inlineStr"/>
+      <c r="EJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2185,7 +2201,7 @@
         <v>1.07</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2215,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2290,6 +2306,8 @@
           <t>1.79</t>
         </is>
       </c>
+      <c r="EI3" t="inlineStr"/>
+      <c r="EJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2626,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DE4" t="n">
         <v>1.47</v>
@@ -2659,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -2694,6 +2712,8 @@
       <c r="EF4" t="inlineStr"/>
       <c r="EG4" t="inlineStr"/>
       <c r="EH4" t="inlineStr"/>
+      <c r="EI4" t="inlineStr"/>
+      <c r="EJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3030,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="DE5" t="n">
         <v>0.79</v>
@@ -3138,6 +3158,8 @@
           <t>1.83</t>
         </is>
       </c>
+      <c r="EI5" t="inlineStr"/>
+      <c r="EJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3574,6 +3596,8 @@
       </c>
       <c r="EG6" t="inlineStr"/>
       <c r="EH6" t="inlineStr"/>
+      <c r="EI6" t="inlineStr"/>
+      <c r="EJ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4010,6 +4034,8 @@
       </c>
       <c r="EG7" t="inlineStr"/>
       <c r="EH7" t="inlineStr"/>
+      <c r="EI7" t="inlineStr"/>
+      <c r="EJ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4346,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DE8" t="n">
         <v>1.47</v>
@@ -4454,6 +4480,8 @@
       </c>
       <c r="EG8" t="inlineStr"/>
       <c r="EH8" t="inlineStr"/>
+      <c r="EI8" t="inlineStr"/>
+      <c r="EJ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4890,6 +4918,8 @@
       </c>
       <c r="EG9" t="inlineStr"/>
       <c r="EH9" t="inlineStr"/>
+      <c r="EI9" t="inlineStr"/>
+      <c r="EJ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5326,6 +5356,8 @@
       </c>
       <c r="EG10" t="inlineStr"/>
       <c r="EH10" t="inlineStr"/>
+      <c r="EI10" t="inlineStr"/>
+      <c r="EJ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5662,7 +5694,7 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DE11" t="n">
         <v>1.67</v>
@@ -5770,6 +5802,8 @@
       </c>
       <c r="EG11" t="inlineStr"/>
       <c r="EH11" t="inlineStr"/>
+      <c r="EI11" t="inlineStr"/>
+      <c r="EJ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6109,7 +6143,7 @@
         <v>1.47</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6186,6 +6220,8 @@
       </c>
       <c r="EG12" t="inlineStr"/>
       <c r="EH12" t="inlineStr"/>
+      <c r="EI12" t="inlineStr"/>
+      <c r="EJ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6525,7 +6561,7 @@
         <v>1.8</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6555,7 +6591,7 @@
         <v>1.86</v>
       </c>
       <c r="DO13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -6630,6 +6666,8 @@
           <t>1.92</t>
         </is>
       </c>
+      <c r="EI13" t="inlineStr"/>
+      <c r="EJ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6966,7 +7004,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DE14" t="n">
         <v>1.07</v>
@@ -6999,7 +7037,7 @@
         <v>1.99</v>
       </c>
       <c r="DO14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP14" t="b">
         <v>0</v>
@@ -7066,6 +7104,8 @@
       </c>
       <c r="EG14" t="inlineStr"/>
       <c r="EH14" t="inlineStr"/>
+      <c r="EI14" t="inlineStr"/>
+      <c r="EJ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7518,6 +7558,8 @@
           <t>1.88</t>
         </is>
       </c>
+      <c r="EI15" t="inlineStr"/>
+      <c r="EJ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7954,6 +7996,8 @@
       </c>
       <c r="EG16" t="inlineStr"/>
       <c r="EH16" t="inlineStr"/>
+      <c r="EI16" t="inlineStr"/>
+      <c r="EJ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8285,7 +8329,7 @@
         <v>0.79</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8382,6 +8426,8 @@
       </c>
       <c r="EG17" t="inlineStr"/>
       <c r="EH17" t="inlineStr"/>
+      <c r="EI17" t="inlineStr"/>
+      <c r="EJ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8818,6 +8864,8 @@
       </c>
       <c r="EG18" t="inlineStr"/>
       <c r="EH18" t="inlineStr"/>
+      <c r="EI18" t="inlineStr"/>
+      <c r="EJ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9254,6 +9302,8 @@
       </c>
       <c r="EG19" t="inlineStr"/>
       <c r="EH19" t="inlineStr"/>
+      <c r="EI19" t="inlineStr"/>
+      <c r="EJ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9690,6 +9740,8 @@
       </c>
       <c r="EG20" t="inlineStr"/>
       <c r="EH20" t="inlineStr"/>
+      <c r="EI20" t="inlineStr"/>
+      <c r="EJ20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10026,7 +10078,7 @@
         <v>100</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DE21" t="n">
         <v>1.36</v>
@@ -10134,6 +10186,8 @@
       </c>
       <c r="EG21" t="inlineStr"/>
       <c r="EH21" t="inlineStr"/>
+      <c r="EI21" t="inlineStr"/>
+      <c r="EJ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10578,6 +10632,8 @@
       </c>
       <c r="EG22" t="inlineStr"/>
       <c r="EH22" t="inlineStr"/>
+      <c r="EI22" t="inlineStr"/>
+      <c r="EJ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11014,6 +11070,8 @@
       </c>
       <c r="EG23" t="inlineStr"/>
       <c r="EH23" t="inlineStr"/>
+      <c r="EI23" t="inlineStr"/>
+      <c r="EJ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11350,7 +11408,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DE24" t="n">
         <v>0.79</v>
@@ -11450,6 +11508,8 @@
       </c>
       <c r="EG24" t="inlineStr"/>
       <c r="EH24" t="inlineStr"/>
+      <c r="EI24" t="inlineStr"/>
+      <c r="EJ24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11789,7 +11849,7 @@
         <v>1.27</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -11819,7 +11879,7 @@
         <v>2.57</v>
       </c>
       <c r="DO25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -11894,6 +11954,8 @@
           <t>1.83</t>
         </is>
       </c>
+      <c r="EI25" t="inlineStr"/>
+      <c r="EJ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12330,6 +12392,8 @@
       </c>
       <c r="EG26" t="inlineStr"/>
       <c r="EH26" t="inlineStr"/>
+      <c r="EI26" t="inlineStr"/>
+      <c r="EJ26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -12766,6 +12830,8 @@
       </c>
       <c r="EG27" t="inlineStr"/>
       <c r="EH27" t="inlineStr"/>
+      <c r="EI27" t="inlineStr"/>
+      <c r="EJ27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13102,7 +13168,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DE28" t="n">
         <v>1.47</v>
@@ -13210,6 +13276,8 @@
       </c>
       <c r="EG28" t="inlineStr"/>
       <c r="EH28" t="inlineStr"/>
+      <c r="EI28" t="inlineStr"/>
+      <c r="EJ28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -13546,7 +13614,7 @@
         <v>75</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DE29" t="n">
         <v>1.67</v>
@@ -13579,7 +13647,7 @@
         <v>3.03</v>
       </c>
       <c r="DO29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -13654,6 +13722,8 @@
           <t>1.78</t>
         </is>
       </c>
+      <c r="EI29" t="inlineStr"/>
+      <c r="EJ29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -13990,7 +14060,7 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DE30" t="n">
         <v>1.07</v>
@@ -14090,6 +14160,8 @@
       </c>
       <c r="EG30" t="inlineStr"/>
       <c r="EH30" t="inlineStr"/>
+      <c r="EI30" t="inlineStr"/>
+      <c r="EJ30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -14526,6 +14598,8 @@
       </c>
       <c r="EG31" t="inlineStr"/>
       <c r="EH31" t="inlineStr"/>
+      <c r="EI31" t="inlineStr"/>
+      <c r="EJ31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -14865,7 +14939,7 @@
         <v>1.36</v>
       </c>
       <c r="DE32" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF32" t="n">
         <v>1.67</v>
@@ -14962,6 +15036,8 @@
       </c>
       <c r="EG32" t="inlineStr"/>
       <c r="EH32" t="inlineStr"/>
+      <c r="EI32" t="inlineStr"/>
+      <c r="EJ32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15406,6 +15482,8 @@
       </c>
       <c r="EG33" t="inlineStr"/>
       <c r="EH33" t="inlineStr"/>
+      <c r="EI33" t="inlineStr"/>
+      <c r="EJ33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -15745,7 +15823,7 @@
         <v>1.67</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DF34" t="n">
         <v>1.67</v>
@@ -15842,6 +15920,8 @@
       </c>
       <c r="EG34" t="inlineStr"/>
       <c r="EH34" t="inlineStr"/>
+      <c r="EI34" t="inlineStr"/>
+      <c r="EJ34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16278,6 +16358,8 @@
       </c>
       <c r="EG35" t="inlineStr"/>
       <c r="EH35" t="inlineStr"/>
+      <c r="EI35" t="inlineStr"/>
+      <c r="EJ35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -16714,6 +16796,8 @@
       </c>
       <c r="EG36" t="inlineStr"/>
       <c r="EH36" t="inlineStr"/>
+      <c r="EI36" t="inlineStr"/>
+      <c r="EJ36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -17158,6 +17242,8 @@
       </c>
       <c r="EG37" t="inlineStr"/>
       <c r="EH37" t="inlineStr"/>
+      <c r="EI37" t="inlineStr"/>
+      <c r="EJ37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -17494,7 +17580,7 @@
         <v>67</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DE38" t="n">
         <v>1.67</v>
@@ -17527,7 +17613,7 @@
         <v>2.42</v>
       </c>
       <c r="DO38" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -17594,6 +17680,8 @@
       </c>
       <c r="EG38" t="inlineStr"/>
       <c r="EH38" t="inlineStr"/>
+      <c r="EI38" t="inlineStr"/>
+      <c r="EJ38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -17930,10 +18018,10 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DF39" t="n">
         <v>3</v>
@@ -17963,7 +18051,7 @@
         <v>3.9</v>
       </c>
       <c r="DO39" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -18030,6 +18118,8 @@
       </c>
       <c r="EG39" t="inlineStr"/>
       <c r="EH39" t="inlineStr"/>
+      <c r="EI39" t="inlineStr"/>
+      <c r="EJ39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -18462,6 +18552,8 @@
       </c>
       <c r="EG40" t="inlineStr"/>
       <c r="EH40" t="inlineStr"/>
+      <c r="EI40" t="inlineStr"/>
+      <c r="EJ40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -18898,6 +18990,8 @@
       </c>
       <c r="EG41" t="inlineStr"/>
       <c r="EH41" t="inlineStr"/>
+      <c r="EI41" t="inlineStr"/>
+      <c r="EJ41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -19237,7 +19331,7 @@
         <v>1.36</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF42" t="n">
         <v>1.25</v>
@@ -19334,6 +19428,8 @@
       </c>
       <c r="EG42" t="inlineStr"/>
       <c r="EH42" t="inlineStr"/>
+      <c r="EI42" t="inlineStr"/>
+      <c r="EJ42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -19770,6 +19866,8 @@
       </c>
       <c r="EG43" t="inlineStr"/>
       <c r="EH43" t="inlineStr"/>
+      <c r="EI43" t="inlineStr"/>
+      <c r="EJ43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -20186,6 +20284,8 @@
       </c>
       <c r="EG44" t="inlineStr"/>
       <c r="EH44" t="inlineStr"/>
+      <c r="EI44" t="inlineStr"/>
+      <c r="EJ44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -20622,6 +20722,8 @@
       </c>
       <c r="EG45" t="inlineStr"/>
       <c r="EH45" t="inlineStr"/>
+      <c r="EI45" t="inlineStr"/>
+      <c r="EJ45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -20958,7 +21060,7 @@
         <v>50</v>
       </c>
       <c r="DD46" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DE46" t="n">
         <v>1.67</v>
@@ -20991,7 +21093,7 @@
         <v>2.87</v>
       </c>
       <c r="DO46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -21066,6 +21168,8 @@
       </c>
       <c r="EG46" t="inlineStr"/>
       <c r="EH46" t="inlineStr"/>
+      <c r="EI46" t="inlineStr"/>
+      <c r="EJ46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -21490,6 +21594,8 @@
       </c>
       <c r="EG47" t="inlineStr"/>
       <c r="EH47" t="inlineStr"/>
+      <c r="EI47" t="inlineStr"/>
+      <c r="EJ47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -21826,10 +21932,10 @@
         <v>59</v>
       </c>
       <c r="DD48" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DF48" t="n">
         <v>1.33</v>
@@ -21859,7 +21965,7 @@
         <v>1.75</v>
       </c>
       <c r="DO48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -21934,6 +22040,8 @@
       </c>
       <c r="EG48" t="inlineStr"/>
       <c r="EH48" t="inlineStr"/>
+      <c r="EI48" t="inlineStr"/>
+      <c r="EJ48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -22270,7 +22378,7 @@
         <v>80</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DE49" t="n">
         <v>1.21</v>
@@ -22378,6 +22486,8 @@
       </c>
       <c r="EG49" t="inlineStr"/>
       <c r="EH49" t="inlineStr"/>
+      <c r="EI49" t="inlineStr"/>
+      <c r="EJ49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -22822,6 +22932,8 @@
       </c>
       <c r="EG50" t="inlineStr"/>
       <c r="EH50" t="inlineStr"/>
+      <c r="EI50" t="inlineStr"/>
+      <c r="EJ50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -23266,6 +23378,8 @@
       </c>
       <c r="EG51" t="inlineStr"/>
       <c r="EH51" t="inlineStr"/>
+      <c r="EI51" t="inlineStr"/>
+      <c r="EJ51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -23710,6 +23824,8 @@
           <t>1.88</t>
         </is>
       </c>
+      <c r="EI52" t="inlineStr"/>
+      <c r="EJ52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -24146,6 +24262,8 @@
       </c>
       <c r="EG53" t="inlineStr"/>
       <c r="EH53" t="inlineStr"/>
+      <c r="EI53" t="inlineStr"/>
+      <c r="EJ53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -24477,7 +24595,7 @@
         <v>0.79</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DF54" t="n">
         <v>0.2</v>
@@ -24590,6 +24708,8 @@
           <t>1.79</t>
         </is>
       </c>
+      <c r="EI54" t="inlineStr"/>
+      <c r="EJ54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -25034,6 +25154,8 @@
           <t>1.95</t>
         </is>
       </c>
+      <c r="EI55" t="inlineStr"/>
+      <c r="EJ55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -25370,7 +25492,7 @@
         <v>70</v>
       </c>
       <c r="DD56" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="DE56" t="n">
         <v>1.07</v>
@@ -25403,7 +25525,7 @@
         <v>4.13</v>
       </c>
       <c r="DO56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -25470,6 +25592,8 @@
       </c>
       <c r="EG56" t="inlineStr"/>
       <c r="EH56" t="inlineStr"/>
+      <c r="EI56" t="inlineStr"/>
+      <c r="EJ56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -25806,7 +25930,7 @@
         <v>70</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DE57" t="n">
         <v>1.27</v>
@@ -25839,7 +25963,7 @@
         <v>2.74</v>
       </c>
       <c r="DO57" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -25914,6 +26038,8 @@
       </c>
       <c r="EG57" t="inlineStr"/>
       <c r="EH57" t="inlineStr"/>
+      <c r="EI57" t="inlineStr"/>
+      <c r="EJ57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -26358,6 +26484,8 @@
           <t>1.76</t>
         </is>
       </c>
+      <c r="EI58" t="inlineStr"/>
+      <c r="EJ58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -26697,7 +26825,7 @@
         <v>1.21</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DF59" t="n">
         <v>0.83</v>
@@ -26810,6 +26938,8 @@
           <t>1.76</t>
         </is>
       </c>
+      <c r="EI59" t="inlineStr"/>
+      <c r="EJ59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -27254,6 +27384,8 @@
       </c>
       <c r="EG60" t="inlineStr"/>
       <c r="EH60" t="inlineStr"/>
+      <c r="EI60" t="inlineStr"/>
+      <c r="EJ60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -27690,6 +27822,8 @@
       </c>
       <c r="EG61" t="inlineStr"/>
       <c r="EH61" t="inlineStr"/>
+      <c r="EI61" t="inlineStr"/>
+      <c r="EJ61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -28029,7 +28163,7 @@
         <v>1.47</v>
       </c>
       <c r="DE62" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="DF62" t="n">
         <v>1.17</v>
@@ -28059,7 +28193,7 @@
         <v>3.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -28126,6 +28260,8 @@
       </c>
       <c r="EG62" t="inlineStr"/>
       <c r="EH62" t="inlineStr"/>
+      <c r="EI62" t="inlineStr"/>
+      <c r="EJ62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -28562,6 +28698,8 @@
       </c>
       <c r="EG63" t="inlineStr"/>
       <c r="EH63" t="inlineStr"/>
+      <c r="EI63" t="inlineStr"/>
+      <c r="EJ63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -28898,10 +29036,10 @@
         <v>60</v>
       </c>
       <c r="DD64" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF64" t="n">
         <v>0.4</v>
@@ -28931,7 +29069,7 @@
         <v>1.97</v>
       </c>
       <c r="DO64" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -28998,6 +29136,8 @@
       </c>
       <c r="EG64" t="inlineStr"/>
       <c r="EH64" t="inlineStr"/>
+      <c r="EI64" t="inlineStr"/>
+      <c r="EJ64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -29334,7 +29474,7 @@
         <v>57</v>
       </c>
       <c r="DD65" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DE65" t="n">
         <v>1.27</v>
@@ -29430,6 +29570,8 @@
       </c>
       <c r="EG65" t="inlineStr"/>
       <c r="EH65" t="inlineStr"/>
+      <c r="EI65" t="inlineStr"/>
+      <c r="EJ65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -29769,7 +29911,7 @@
         <v>1.67</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DF66" t="n">
         <v>1.8</v>
@@ -29799,7 +29941,7 @@
         <v>3.08</v>
       </c>
       <c r="DO66" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -29866,6 +30008,8 @@
       </c>
       <c r="EG66" t="inlineStr"/>
       <c r="EH66" t="inlineStr"/>
+      <c r="EI66" t="inlineStr"/>
+      <c r="EJ66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -30310,6 +30454,8 @@
       </c>
       <c r="EG67" t="inlineStr"/>
       <c r="EH67" t="inlineStr"/>
+      <c r="EI67" t="inlineStr"/>
+      <c r="EJ67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -30646,7 +30792,7 @@
         <v>62</v>
       </c>
       <c r="DD68" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DE68" t="n">
         <v>1.87</v>
@@ -30679,7 +30825,7 @@
         <v>1.99</v>
       </c>
       <c r="DO68" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -30754,6 +30900,8 @@
       </c>
       <c r="EG68" t="inlineStr"/>
       <c r="EH68" t="inlineStr"/>
+      <c r="EI68" t="inlineStr"/>
+      <c r="EJ68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -31190,6 +31338,8 @@
       </c>
       <c r="EG69" t="inlineStr"/>
       <c r="EH69" t="inlineStr"/>
+      <c r="EI69" t="inlineStr"/>
+      <c r="EJ69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -31626,6 +31776,8 @@
       </c>
       <c r="EG70" t="inlineStr"/>
       <c r="EH70" t="inlineStr"/>
+      <c r="EI70" t="inlineStr"/>
+      <c r="EJ70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -31962,10 +32114,10 @@
         <v>54</v>
       </c>
       <c r="DD71" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="DE71" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF71" t="n">
         <v>2.25</v>
@@ -31995,7 +32147,7 @@
         <v>3.31</v>
       </c>
       <c r="DO71" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -32062,6 +32214,8 @@
       </c>
       <c r="EG71" t="inlineStr"/>
       <c r="EH71" t="inlineStr"/>
+      <c r="EI71" t="inlineStr"/>
+      <c r="EJ71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -32506,6 +32660,8 @@
       </c>
       <c r="EG72" t="inlineStr"/>
       <c r="EH72" t="inlineStr"/>
+      <c r="EI72" t="inlineStr"/>
+      <c r="EJ72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -32942,6 +33098,8 @@
       </c>
       <c r="EG73" t="inlineStr"/>
       <c r="EH73" t="inlineStr"/>
+      <c r="EI73" t="inlineStr"/>
+      <c r="EJ73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -33370,6 +33528,8 @@
       </c>
       <c r="EG74" t="inlineStr"/>
       <c r="EH74" t="inlineStr"/>
+      <c r="EI74" t="inlineStr"/>
+      <c r="EJ74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -33706,10 +33866,10 @@
         <v>83</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DE75" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DF75" t="n">
         <v>1.67</v>
@@ -33739,7 +33899,7 @@
         <v>2.17</v>
       </c>
       <c r="DO75" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -33806,6 +33966,8 @@
       </c>
       <c r="EG75" t="inlineStr"/>
       <c r="EH75" t="inlineStr"/>
+      <c r="EI75" t="inlineStr"/>
+      <c r="EJ75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -34142,7 +34304,7 @@
         <v>65</v>
       </c>
       <c r="DD76" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DE76" t="n">
         <v>1.8</v>
@@ -34250,6 +34412,8 @@
       </c>
       <c r="EG76" t="inlineStr"/>
       <c r="EH76" t="inlineStr"/>
+      <c r="EI76" t="inlineStr"/>
+      <c r="EJ76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -34589,7 +34753,7 @@
         <v>1.27</v>
       </c>
       <c r="DE77" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="DF77" t="n">
         <v>1.25</v>
@@ -34619,7 +34783,7 @@
         <v>3.5</v>
       </c>
       <c r="DO77" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -34686,6 +34850,8 @@
       </c>
       <c r="EG77" t="inlineStr"/>
       <c r="EH77" t="inlineStr"/>
+      <c r="EI77" t="inlineStr"/>
+      <c r="EJ77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -35025,7 +35191,7 @@
         <v>1.4</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DF78" t="n">
         <v>1</v>
@@ -35055,7 +35221,7 @@
         <v>2.25</v>
       </c>
       <c r="DO78" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -35122,6 +35288,8 @@
       </c>
       <c r="EG78" t="inlineStr"/>
       <c r="EH78" t="inlineStr"/>
+      <c r="EI78" t="inlineStr"/>
+      <c r="EJ78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -35566,6 +35734,8 @@
           <t>1.84</t>
         </is>
       </c>
+      <c r="EI79" t="inlineStr"/>
+      <c r="EJ79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -35902,10 +36072,10 @@
         <v>65</v>
       </c>
       <c r="DD80" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DF80" t="n">
         <v>0.43</v>
@@ -35935,7 +36105,7 @@
         <v>2.69</v>
       </c>
       <c r="DO80" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -36010,6 +36180,8 @@
       </c>
       <c r="EG80" t="inlineStr"/>
       <c r="EH80" t="inlineStr"/>
+      <c r="EI80" t="inlineStr"/>
+      <c r="EJ80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -36346,7 +36518,7 @@
         <v>93</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DE81" t="n">
         <v>1.67</v>
@@ -36454,6 +36626,8 @@
       </c>
       <c r="EG81" t="inlineStr"/>
       <c r="EH81" t="inlineStr"/>
+      <c r="EI81" t="inlineStr"/>
+      <c r="EJ81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -36898,6 +37072,8 @@
       </c>
       <c r="EG82" t="inlineStr"/>
       <c r="EH82" t="inlineStr"/>
+      <c r="EI82" t="inlineStr"/>
+      <c r="EJ82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -37237,7 +37413,7 @@
         <v>1.87</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF83" t="n">
         <v>1.88</v>
@@ -37334,6 +37510,8 @@
       </c>
       <c r="EG83" t="inlineStr"/>
       <c r="EH83" t="inlineStr"/>
+      <c r="EI83" t="inlineStr"/>
+      <c r="EJ83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -37770,6 +37948,8 @@
       </c>
       <c r="EG84" t="inlineStr"/>
       <c r="EH84" t="inlineStr"/>
+      <c r="EI84" t="inlineStr"/>
+      <c r="EJ84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -38206,6 +38386,8 @@
       </c>
       <c r="EG85" t="inlineStr"/>
       <c r="EH85" t="inlineStr"/>
+      <c r="EI85" t="inlineStr"/>
+      <c r="EJ85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -38545,7 +38727,7 @@
         <v>1.8</v>
       </c>
       <c r="DE86" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="DF86" t="n">
         <v>1.5</v>
@@ -38575,7 +38757,7 @@
         <v>3.17</v>
       </c>
       <c r="DO86" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -38642,6 +38824,8 @@
       </c>
       <c r="EG86" t="inlineStr"/>
       <c r="EH86" t="inlineStr"/>
+      <c r="EI86" t="inlineStr"/>
+      <c r="EJ86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -38981,7 +39165,7 @@
         <v>1.07</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DF87" t="n">
         <v>1.22</v>
@@ -39078,6 +39262,8 @@
       </c>
       <c r="EG87" t="inlineStr"/>
       <c r="EH87" t="inlineStr"/>
+      <c r="EI87" t="inlineStr"/>
+      <c r="EJ87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -39522,6 +39708,8 @@
           <t>1.84</t>
         </is>
       </c>
+      <c r="EI88" t="inlineStr"/>
+      <c r="EJ88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -39861,7 +40049,7 @@
         <v>1.67</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF89" t="n">
         <v>1.88</v>
@@ -39891,7 +40079,7 @@
         <v>2.77</v>
       </c>
       <c r="DO89" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -39966,6 +40154,8 @@
           <t>1.76</t>
         </is>
       </c>
+      <c r="EI89" t="inlineStr"/>
+      <c r="EJ89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -40410,6 +40600,8 @@
           <t>1.86</t>
         </is>
       </c>
+      <c r="EI90" t="inlineStr"/>
+      <c r="EJ90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -40749,7 +40941,7 @@
         <v>1.36</v>
       </c>
       <c r="DE91" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="DF91" t="n">
         <v>1.5</v>
@@ -40846,6 +41038,8 @@
       </c>
       <c r="EG91" t="inlineStr"/>
       <c r="EH91" t="inlineStr"/>
+      <c r="EI91" t="inlineStr"/>
+      <c r="EJ91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -41185,7 +41379,7 @@
         <v>1.33</v>
       </c>
       <c r="DE92" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DF92" t="n">
         <v>1.22</v>
@@ -41298,6 +41492,8 @@
           <t>1.96</t>
         </is>
       </c>
+      <c r="EI92" t="inlineStr"/>
+      <c r="EJ92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -41637,7 +41833,7 @@
         <v>1.4</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF93" t="n">
         <v>1.22</v>
@@ -41742,6 +41938,8 @@
           <t>1.81</t>
         </is>
       </c>
+      <c r="EI93" t="inlineStr"/>
+      <c r="EJ93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -42081,7 +42279,7 @@
         <v>1.87</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DF94" t="n">
         <v>2</v>
@@ -42111,7 +42309,7 @@
         <v>2.91</v>
       </c>
       <c r="DO94" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -42178,6 +42376,8 @@
       </c>
       <c r="EG94" t="inlineStr"/>
       <c r="EH94" t="inlineStr"/>
+      <c r="EI94" t="inlineStr"/>
+      <c r="EJ94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -42517,7 +42717,7 @@
         <v>1.36</v>
       </c>
       <c r="DE95" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DF95" t="n">
         <v>1.75</v>
@@ -42622,6 +42822,8 @@
       </c>
       <c r="EG95" t="inlineStr"/>
       <c r="EH95" t="inlineStr"/>
+      <c r="EI95" t="inlineStr"/>
+      <c r="EJ95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -42961,7 +43163,7 @@
         <v>1.67</v>
       </c>
       <c r="DE96" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="DF96" t="n">
         <v>1.78</v>
@@ -42991,7 +43193,7 @@
         <v>3.39</v>
       </c>
       <c r="DO96" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -43058,6 +43260,8 @@
       </c>
       <c r="EG96" t="inlineStr"/>
       <c r="EH96" t="inlineStr"/>
+      <c r="EI96" t="inlineStr"/>
+      <c r="EJ96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -43494,6 +43698,8 @@
       </c>
       <c r="EG97" t="inlineStr"/>
       <c r="EH97" t="inlineStr"/>
+      <c r="EI97" t="inlineStr"/>
+      <c r="EJ97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -43830,7 +44036,7 @@
         <v>74</v>
       </c>
       <c r="DD98" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="DE98" t="n">
         <v>1.33</v>
@@ -43863,7 +44069,7 @@
         <v>2.76</v>
       </c>
       <c r="DO98" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -43938,6 +44144,8 @@
           <t>1.85</t>
         </is>
       </c>
+      <c r="EI98" t="inlineStr"/>
+      <c r="EJ98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -44382,6 +44590,8 @@
       </c>
       <c r="EG99" t="inlineStr"/>
       <c r="EH99" t="inlineStr"/>
+      <c r="EI99" t="inlineStr"/>
+      <c r="EJ99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -44718,7 +44928,7 @@
         <v>70</v>
       </c>
       <c r="DD100" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DE100" t="n">
         <v>1.47</v>
@@ -44826,6 +45036,8 @@
           <t>1.80</t>
         </is>
       </c>
+      <c r="EI100" t="inlineStr"/>
+      <c r="EJ100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -45254,6 +45466,8 @@
       </c>
       <c r="EG101" t="inlineStr"/>
       <c r="EH101" t="inlineStr"/>
+      <c r="EI101" t="inlineStr"/>
+      <c r="EJ101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -45593,7 +45807,7 @@
         <v>1.27</v>
       </c>
       <c r="DE102" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF102" t="n">
         <v>1.11</v>
@@ -45623,7 +45837,7 @@
         <v>2.71</v>
       </c>
       <c r="DO102" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -45690,6 +45904,8 @@
       </c>
       <c r="EG102" t="inlineStr"/>
       <c r="EH102" t="inlineStr"/>
+      <c r="EI102" t="inlineStr"/>
+      <c r="EJ102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -46026,7 +46242,7 @@
         <v>67</v>
       </c>
       <c r="DD103" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DE103" t="n">
         <v>1.36</v>
@@ -46134,6 +46350,8 @@
       </c>
       <c r="EG103" t="inlineStr"/>
       <c r="EH103" t="inlineStr"/>
+      <c r="EI103" t="inlineStr"/>
+      <c r="EJ103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -46470,7 +46688,7 @@
         <v>61</v>
       </c>
       <c r="DD104" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DE104" t="n">
         <v>1.8</v>
@@ -46503,7 +46721,7 @@
         <v>2.83</v>
       </c>
       <c r="DO104" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -46578,6 +46796,8 @@
       </c>
       <c r="EG104" t="inlineStr"/>
       <c r="EH104" t="inlineStr"/>
+      <c r="EI104" t="inlineStr"/>
+      <c r="EJ104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -46914,7 +47134,7 @@
         <v>74</v>
       </c>
       <c r="DD105" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DE105" t="n">
         <v>1.21</v>
@@ -47014,6 +47234,8 @@
       </c>
       <c r="EG105" t="inlineStr"/>
       <c r="EH105" t="inlineStr"/>
+      <c r="EI105" t="inlineStr"/>
+      <c r="EJ105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -47450,6 +47672,8 @@
       </c>
       <c r="EG106" t="inlineStr"/>
       <c r="EH106" t="inlineStr"/>
+      <c r="EI106" t="inlineStr"/>
+      <c r="EJ106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -47789,7 +48013,7 @@
         <v>1.33</v>
       </c>
       <c r="DE107" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF107" t="n">
         <v>1.27</v>
@@ -47894,6 +48118,8 @@
           <t>1.76</t>
         </is>
       </c>
+      <c r="EI107" t="inlineStr"/>
+      <c r="EJ107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -48233,7 +48459,7 @@
         <v>1.4</v>
       </c>
       <c r="DE108" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="DF108" t="n">
         <v>1.27</v>
@@ -48263,7 +48489,7 @@
         <v>3.19</v>
       </c>
       <c r="DO108" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -48330,6 +48556,8 @@
       </c>
       <c r="EG108" t="inlineStr"/>
       <c r="EH108" t="inlineStr"/>
+      <c r="EI108" t="inlineStr"/>
+      <c r="EJ108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -48774,6 +49002,8 @@
       </c>
       <c r="EG109" t="inlineStr"/>
       <c r="EH109" t="inlineStr"/>
+      <c r="EI109" t="inlineStr"/>
+      <c r="EJ109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -49113,7 +49343,7 @@
         <v>1.47</v>
       </c>
       <c r="DE110" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DF110" t="n">
         <v>1.82</v>
@@ -49143,7 +49373,7 @@
         <v>2.1</v>
       </c>
       <c r="DO110" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -49218,6 +49448,8 @@
       </c>
       <c r="EG110" t="inlineStr"/>
       <c r="EH110" t="inlineStr"/>
+      <c r="EI110" t="inlineStr"/>
+      <c r="EJ110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -49654,6 +49886,8 @@
       </c>
       <c r="EG111" t="inlineStr"/>
       <c r="EH111" t="inlineStr"/>
+      <c r="EI111" t="inlineStr"/>
+      <c r="EJ111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -50090,6 +50324,8 @@
       </c>
       <c r="EG112" t="inlineStr"/>
       <c r="EH112" t="inlineStr"/>
+      <c r="EI112" t="inlineStr"/>
+      <c r="EJ112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -50426,10 +50662,10 @@
         <v>71</v>
       </c>
       <c r="DD113" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DE113" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DF113" t="n">
         <v>0.5</v>
@@ -50459,7 +50695,7 @@
         <v>2.1</v>
       </c>
       <c r="DO113" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -50534,6 +50770,8 @@
       </c>
       <c r="EG113" t="inlineStr"/>
       <c r="EH113" t="inlineStr"/>
+      <c r="EI113" t="inlineStr"/>
+      <c r="EJ113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -50978,6 +51216,8 @@
       </c>
       <c r="EG114" t="inlineStr"/>
       <c r="EH114" t="inlineStr"/>
+      <c r="EI114" t="inlineStr"/>
+      <c r="EJ114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -51414,6 +51654,8 @@
       </c>
       <c r="EG115" t="inlineStr"/>
       <c r="EH115" t="inlineStr"/>
+      <c r="EI115" t="inlineStr"/>
+      <c r="EJ115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -51753,7 +51995,7 @@
         <v>1.36</v>
       </c>
       <c r="DE116" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DF116" t="n">
         <v>1.5</v>
@@ -51866,6 +52108,8 @@
           <t>1.83</t>
         </is>
       </c>
+      <c r="EI116" t="inlineStr"/>
+      <c r="EJ116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -52310,6 +52554,8 @@
           <t>1.84</t>
         </is>
       </c>
+      <c r="EI117" t="inlineStr"/>
+      <c r="EJ117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -52646,7 +52892,7 @@
         <v>70</v>
       </c>
       <c r="DD118" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="DE118" t="n">
         <v>1.47</v>
@@ -52679,7 +52925,7 @@
         <v>2.92</v>
       </c>
       <c r="DO118" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -52754,6 +53000,8 @@
           <t>1.76</t>
         </is>
       </c>
+      <c r="EI118" t="inlineStr"/>
+      <c r="EJ118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -53090,7 +53338,7 @@
         <v>57</v>
       </c>
       <c r="DD119" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DE119" t="n">
         <v>1.47</v>
@@ -53123,7 +53371,7 @@
         <v>2.45</v>
       </c>
       <c r="DO119" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -53198,6 +53446,8 @@
           <t>1.85</t>
         </is>
       </c>
+      <c r="EI119" t="inlineStr"/>
+      <c r="EJ119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -53626,6 +53876,8 @@
       </c>
       <c r="EG120" t="inlineStr"/>
       <c r="EH120" t="inlineStr"/>
+      <c r="EI120" t="inlineStr"/>
+      <c r="EJ120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -54062,6 +54314,8 @@
       </c>
       <c r="EG121" t="inlineStr"/>
       <c r="EH121" t="inlineStr"/>
+      <c r="EI121" t="inlineStr"/>
+      <c r="EJ121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -54398,7 +54652,7 @@
         <v>64</v>
       </c>
       <c r="DD122" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DE122" t="n">
         <v>1.36</v>
@@ -54506,6 +54760,8 @@
           <t>1.75</t>
         </is>
       </c>
+      <c r="EI122" t="inlineStr"/>
+      <c r="EJ122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -54842,10 +55098,10 @@
         <v>78</v>
       </c>
       <c r="DD123" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DE123" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF123" t="n">
         <v>0.45</v>
@@ -54875,7 +55131,7 @@
         <v>1.87</v>
       </c>
       <c r="DO123" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -54942,6 +55198,8 @@
       </c>
       <c r="EG123" t="inlineStr"/>
       <c r="EH123" t="inlineStr"/>
+      <c r="EI123" t="inlineStr"/>
+      <c r="EJ123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -55378,6 +55636,8 @@
       </c>
       <c r="EG124" t="inlineStr"/>
       <c r="EH124" t="inlineStr"/>
+      <c r="EI124" t="inlineStr"/>
+      <c r="EJ124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -55814,6 +56074,8 @@
       </c>
       <c r="EG125" t="inlineStr"/>
       <c r="EH125" t="inlineStr"/>
+      <c r="EI125" t="inlineStr"/>
+      <c r="EJ125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -56150,7 +56412,7 @@
         <v>79</v>
       </c>
       <c r="DD126" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DE126" t="n">
         <v>1.33</v>
@@ -56183,7 +56445,7 @@
         <v>2.54</v>
       </c>
       <c r="DO126" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP126" t="b">
         <v>0</v>
@@ -56250,6 +56512,8 @@
       </c>
       <c r="EG126" t="inlineStr"/>
       <c r="EH126" t="inlineStr"/>
+      <c r="EI126" t="inlineStr"/>
+      <c r="EJ126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -56589,7 +56853,7 @@
         <v>1.36</v>
       </c>
       <c r="DE127" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF127" t="n">
         <v>1.33</v>
@@ -56686,6 +56950,8 @@
       </c>
       <c r="EG127" t="inlineStr"/>
       <c r="EH127" t="inlineStr"/>
+      <c r="EI127" t="inlineStr"/>
+      <c r="EJ127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -57122,6 +57388,8 @@
       </c>
       <c r="EG128" t="inlineStr"/>
       <c r="EH128" t="inlineStr"/>
+      <c r="EI128" t="inlineStr"/>
+      <c r="EJ128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -57458,7 +57726,7 @@
         <v>80</v>
       </c>
       <c r="DD129" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DE129" t="n">
         <v>0.79</v>
@@ -57550,6 +57818,8 @@
       </c>
       <c r="EG129" t="inlineStr"/>
       <c r="EH129" t="inlineStr"/>
+      <c r="EI129" t="inlineStr"/>
+      <c r="EJ129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -57889,7 +58159,7 @@
         <v>1.8</v>
       </c>
       <c r="DE130" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DF130" t="n">
         <v>1.67</v>
@@ -57978,6 +58248,8 @@
       </c>
       <c r="EG130" t="inlineStr"/>
       <c r="EH130" t="inlineStr"/>
+      <c r="EI130" t="inlineStr"/>
+      <c r="EJ130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -58317,7 +58589,7 @@
         <v>1.47</v>
       </c>
       <c r="DE131" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DF131" t="n">
         <v>1.23</v>
@@ -58347,7 +58619,7 @@
         <v>2.22</v>
       </c>
       <c r="DO131" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -58414,6 +58686,8 @@
       </c>
       <c r="EG131" t="inlineStr"/>
       <c r="EH131" t="inlineStr"/>
+      <c r="EI131" t="inlineStr"/>
+      <c r="EJ131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -58858,6 +59132,8 @@
       </c>
       <c r="EG132" t="inlineStr"/>
       <c r="EH132" t="inlineStr"/>
+      <c r="EI132" t="inlineStr"/>
+      <c r="EJ132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -59197,7 +59473,7 @@
         <v>1.87</v>
       </c>
       <c r="DE133" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="DF133" t="n">
         <v>2.08</v>
@@ -59227,7 +59503,7 @@
         <v>3.05</v>
       </c>
       <c r="DO133" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -59286,6 +59562,8 @@
       </c>
       <c r="EG133" t="inlineStr"/>
       <c r="EH133" t="inlineStr"/>
+      <c r="EI133" t="inlineStr"/>
+      <c r="EJ133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -59730,6 +60008,8 @@
           <t>1.87</t>
         </is>
       </c>
+      <c r="EI134" t="inlineStr"/>
+      <c r="EJ134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -60069,7 +60349,7 @@
         <v>1.21</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DF135" t="n">
         <v>1.08</v>
@@ -60166,6 +60446,8 @@
       </c>
       <c r="EG135" t="inlineStr"/>
       <c r="EH135" t="inlineStr"/>
+      <c r="EI135" t="inlineStr"/>
+      <c r="EJ135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -60602,6 +60884,8 @@
           <t>1.75</t>
         </is>
       </c>
+      <c r="EI136" t="inlineStr"/>
+      <c r="EJ136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -61030,6 +61314,8 @@
       </c>
       <c r="EG137" t="inlineStr"/>
       <c r="EH137" t="inlineStr"/>
+      <c r="EI137" t="inlineStr"/>
+      <c r="EJ137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -61366,7 +61652,7 @@
         <v>71</v>
       </c>
       <c r="DD138" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DE138" t="n">
         <v>1.87</v>
@@ -61399,7 +61685,7 @@
         <v>2.48</v>
       </c>
       <c r="DO138" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP138" t="b">
         <v>0</v>
@@ -61458,6 +61744,8 @@
       </c>
       <c r="EG138" t="inlineStr"/>
       <c r="EH138" t="inlineStr"/>
+      <c r="EI138" t="inlineStr"/>
+      <c r="EJ138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -61894,6 +62182,8 @@
           <t>1.80</t>
         </is>
       </c>
+      <c r="EI139" t="inlineStr"/>
+      <c r="EJ139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -62230,10 +62520,10 @@
         <v>86</v>
       </c>
       <c r="DD140" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="DE140" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF140" t="n">
         <v>2.31</v>
@@ -62263,7 +62553,7 @@
         <v>2.69</v>
       </c>
       <c r="DO140" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP140" t="b">
         <v>0</v>
@@ -62318,6 +62608,8 @@
           <t>1.91</t>
         </is>
       </c>
+      <c r="EI140" t="inlineStr"/>
+      <c r="EJ140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -62496,7 +62788,7 @@
         <v>0</v>
       </c>
       <c r="BF141" t="n">
-        <v>-1</v>
+        <v>200</v>
       </c>
       <c r="BG141" t="n">
         <v>2</v>
@@ -62649,7 +62941,7 @@
         <v>0.79</v>
       </c>
       <c r="DE141" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DF141" t="n">
         <v>0.62</v>
@@ -62738,6 +63030,8 @@
       </c>
       <c r="EG141" t="inlineStr"/>
       <c r="EH141" t="inlineStr"/>
+      <c r="EI141" t="inlineStr"/>
+      <c r="EJ141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -62924,7 +63218,7 @@
         <v>0</v>
       </c>
       <c r="BF142" t="n">
-        <v>-1</v>
+        <v>9000</v>
       </c>
       <c r="BG142" t="n">
         <v>2</v>
@@ -63074,7 +63368,7 @@
         <v>73</v>
       </c>
       <c r="DD142" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DE142" t="n">
         <v>1.36</v>
@@ -63174,6 +63468,8 @@
       </c>
       <c r="EG142" t="inlineStr"/>
       <c r="EH142" t="inlineStr"/>
+      <c r="EI142" t="inlineStr"/>
+      <c r="EJ142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -63360,7 +63656,7 @@
         <v>0</v>
       </c>
       <c r="BF143" t="n">
-        <v>-1</v>
+        <v>5000</v>
       </c>
       <c r="BG143" t="n">
         <v>2</v>
@@ -63510,7 +63806,7 @@
         <v>72</v>
       </c>
       <c r="DD143" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DE143" t="n">
         <v>1.4</v>
@@ -63610,6 +63906,8 @@
       </c>
       <c r="EG143" t="inlineStr"/>
       <c r="EH143" t="inlineStr"/>
+      <c r="EI143" t="inlineStr"/>
+      <c r="EJ143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -63796,7 +64094,7 @@
         <v>0</v>
       </c>
       <c r="BF144" t="n">
-        <v>-1</v>
+        <v>16000</v>
       </c>
       <c r="BG144" t="n">
         <v>2</v>
@@ -64046,6 +64344,8 @@
           <t>1.85</t>
         </is>
       </c>
+      <c r="EI144" t="inlineStr"/>
+      <c r="EJ144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -64232,7 +64532,7 @@
         <v>0</v>
       </c>
       <c r="BF145" t="n">
-        <v>-1</v>
+        <v>500</v>
       </c>
       <c r="BG145" t="n">
         <v>2</v>
@@ -64482,6 +64782,8 @@
           <t>1.78</t>
         </is>
       </c>
+      <c r="EI145" t="inlineStr"/>
+      <c r="EJ145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -64660,7 +64962,7 @@
         <v>0</v>
       </c>
       <c r="BF146" t="n">
-        <v>-1</v>
+        <v>9000</v>
       </c>
       <c r="BG146" t="n">
         <v>2</v>
@@ -64902,6 +65204,8 @@
       </c>
       <c r="EG146" t="inlineStr"/>
       <c r="EH146" t="inlineStr"/>
+      <c r="EI146" t="inlineStr"/>
+      <c r="EJ146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -64943,10 +65247,10 @@
         <v>5</v>
       </c>
       <c r="K147" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L147" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M147" t="n">
         <v>4</v>
@@ -65088,31 +65392,31 @@
         <v>0</v>
       </c>
       <c r="BF147" t="n">
-        <v>-1</v>
+        <v>8000</v>
       </c>
       <c r="BG147" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH147" t="n">
         <v>1</v>
       </c>
       <c r="BI147" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BJ147" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK147" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BL147" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM147" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BN147" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BO147" t="n">
         <v>1</v>
@@ -65187,10 +65491,10 @@
         <v>0</v>
       </c>
       <c r="CM147" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CN147" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO147" t="n">
         <v>0</v>
@@ -65330,6 +65634,1330 @@
       </c>
       <c r="EG147" t="inlineStr"/>
       <c r="EH147" t="inlineStr"/>
+      <c r="EI147" t="inlineStr"/>
+      <c r="EJ147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>16</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>46117.875</v>
+      </c>
+      <c r="G148" t="n">
+        <v>2</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>2</v>
+      </c>
+      <c r="J148" t="n">
+        <v>5</v>
+      </c>
+      <c r="K148" t="n">
+        <v>4</v>
+      </c>
+      <c r="L148" t="n">
+        <v>9</v>
+      </c>
+      <c r="M148" t="n">
+        <v>3</v>
+      </c>
+      <c r="N148" t="n">
+        <v>5</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>5</v>
+      </c>
+      <c r="R148" t="n">
+        <v>4</v>
+      </c>
+      <c r="S148" t="n">
+        <v>1</v>
+      </c>
+      <c r="T148" t="n">
+        <v>14</v>
+      </c>
+      <c r="U148" t="n">
+        <v>6</v>
+      </c>
+      <c r="V148" t="n">
+        <v>18</v>
+      </c>
+      <c r="W148" t="n">
+        <v>11</v>
+      </c>
+      <c r="X148" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>64</v>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>Estadio General Santander</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>Avenida 0A 3-56, Barrio Lleras Restrepo, Cúcuta</t>
+        </is>
+      </c>
+      <c r="AC148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>2153</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ148" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK148" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM148" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN148" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ148" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR148" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS148" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT148" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV148" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW148" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX148" t="n">
+        <v>53</v>
+      </c>
+      <c r="BY148" t="n">
+        <v>100</v>
+      </c>
+      <c r="BZ148" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CA148" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CB148" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="CC148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR148" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS148" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU148" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV148" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX148" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY148" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ148" t="n">
+        <v>52</v>
+      </c>
+      <c r="DA148" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB148" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC148" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD148" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DE148" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DF148" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DG148" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DH148" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DI148" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DJ148" t="n">
+        <v>49</v>
+      </c>
+      <c r="DK148" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL148" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="DM148" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DN148" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DO148" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP148" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ148" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR148" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS148" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT148" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU148" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV148" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW148" t="inlineStr"/>
+      <c r="DX148" t="inlineStr"/>
+      <c r="DY148" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="DZ148" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EA148" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="EB148" t="inlineStr"/>
+      <c r="EC148" t="inlineStr"/>
+      <c r="ED148" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EE148" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EF148" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="EG148" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH148" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EI148" t="inlineStr"/>
+      <c r="EJ148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>6</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Alianza Petrolera</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>46118.85416666666</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2</v>
+      </c>
+      <c r="H149" t="n">
+        <v>3</v>
+      </c>
+      <c r="I149" t="n">
+        <v>5</v>
+      </c>
+      <c r="J149" t="n">
+        <v>5</v>
+      </c>
+      <c r="K149" t="n">
+        <v>5</v>
+      </c>
+      <c r="L149" t="n">
+        <v>10</v>
+      </c>
+      <c r="M149" t="n">
+        <v>2</v>
+      </c>
+      <c r="N149" t="n">
+        <v>3</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>6</v>
+      </c>
+      <c r="R149" t="n">
+        <v>5</v>
+      </c>
+      <c r="S149" t="n">
+        <v>9</v>
+      </c>
+      <c r="T149" t="n">
+        <v>6</v>
+      </c>
+      <c r="U149" t="n">
+        <v>15</v>
+      </c>
+      <c r="V149" t="n">
+        <v>11</v>
+      </c>
+      <c r="W149" t="n">
+        <v>10</v>
+      </c>
+      <c r="X149" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>Estadio Hernán Ramírez Villegas</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>Villa Olímpica Pereira, Pereira</t>
+        </is>
+      </c>
+      <c r="AC149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>2146</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI149" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ149" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM149" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN149" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR149" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT149" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV149" t="n">
+        <v>31</v>
+      </c>
+      <c r="BW149" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX149" t="n">
+        <v>82</v>
+      </c>
+      <c r="BY149" t="n">
+        <v>63</v>
+      </c>
+      <c r="BZ149" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CA149" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CB149" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CC149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN149" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR149" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS149" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU149" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV149" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX149" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY149" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ149" t="n">
+        <v>36</v>
+      </c>
+      <c r="DA149" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB149" t="n">
+        <v>18</v>
+      </c>
+      <c r="DC149" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD149" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DE149" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF149" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DG149" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DH149" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DI149" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DJ149" t="n">
+        <v>65</v>
+      </c>
+      <c r="DK149" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL149" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DM149" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DN149" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="DO149" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU149" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW149" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="DX149" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="DY149" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="DZ149" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EA149" t="inlineStr">
+        <is>
+          <t>5.11</t>
+        </is>
+      </c>
+      <c r="EB149" t="inlineStr"/>
+      <c r="EC149" t="inlineStr"/>
+      <c r="ED149" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EE149" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="EF149" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="EG149" t="inlineStr"/>
+      <c r="EH149" t="inlineStr"/>
+      <c r="EI149" t="inlineStr"/>
+      <c r="EJ149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>2</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Jaguares de Córdoba</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>46119.04861111111</v>
+      </c>
+      <c r="G150" t="n">
+        <v>2</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" t="n">
+        <v>3</v>
+      </c>
+      <c r="J150" t="n">
+        <v>4</v>
+      </c>
+      <c r="K150" t="n">
+        <v>2</v>
+      </c>
+      <c r="L150" t="n">
+        <v>6</v>
+      </c>
+      <c r="M150" t="n">
+        <v>2</v>
+      </c>
+      <c r="N150" t="n">
+        <v>2</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>6</v>
+      </c>
+      <c r="R150" t="n">
+        <v>1</v>
+      </c>
+      <c r="S150" t="n">
+        <v>14</v>
+      </c>
+      <c r="T150" t="n">
+        <v>9</v>
+      </c>
+      <c r="U150" t="n">
+        <v>20</v>
+      </c>
+      <c r="V150" t="n">
+        <v>10</v>
+      </c>
+      <c r="W150" t="n">
+        <v>6</v>
+      </c>
+      <c r="X150" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>Estadio Atanasio Girardot</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
+        </is>
+      </c>
+      <c r="AC150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB150" t="n">
+        <v>2142</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM150" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN150" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV150" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW150" t="n">
+        <v>16</v>
+      </c>
+      <c r="BX150" t="n">
+        <v>106</v>
+      </c>
+      <c r="BY150" t="n">
+        <v>64</v>
+      </c>
+      <c r="BZ150" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CA150" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="CB150" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM150" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR150" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS150" t="n">
+        <v>9</v>
+      </c>
+      <c r="CT150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU150" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV150" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX150" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY150" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ150" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA150" t="n">
+        <v>76</v>
+      </c>
+      <c r="DB150" t="n">
+        <v>21</v>
+      </c>
+      <c r="DC150" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD150" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DE150" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DF150" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DG150" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DH150" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DI150" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DJ150" t="n">
+        <v>41</v>
+      </c>
+      <c r="DK150" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL150" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DM150" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DN150" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="DO150" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP150" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ150" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR150" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS150" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT150" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU150" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV150" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW150" t="inlineStr"/>
+      <c r="DX150" t="inlineStr"/>
+      <c r="DY150" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="DZ150" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="EA150" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EB150" t="inlineStr"/>
+      <c r="EC150" t="inlineStr"/>
+      <c r="ED150" t="inlineStr">
+        <is>
+          <t>10.82</t>
+        </is>
+      </c>
+      <c r="EE150" t="inlineStr">
+        <is>
+          <t>5.92</t>
+        </is>
+      </c>
+      <c r="EF150" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EG150" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EH150" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EI150" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EJ150" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EJ150" headerRowCount="1">
-  <autoFilter ref="A1:EJ150"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EJ151" headerRowCount="1">
+  <autoFilter ref="A1:EJ151"/>
   <tableColumns count="140">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -578,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EJ150"/>
+  <dimension ref="A1:EJ151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DE6" t="n">
         <v>1.4</v>
@@ -3529,7 +3529,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -5259,7 +5259,7 @@
         <v>1.27</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5289,7 +5289,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -7445,7 +7445,7 @@
         <v>1.33</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7475,7 +7475,7 @@
         <v>3.19</v>
       </c>
       <c r="DO15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8764,7 +8764,7 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE18" t="n">
         <v>1.87</v>
@@ -8797,7 +8797,7 @@
         <v>1.44</v>
       </c>
       <c r="DO18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -10081,7 +10081,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10111,7 +10111,7 @@
         <v>2.47</v>
       </c>
       <c r="DO21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -12730,7 +12730,7 @@
         <v>75</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE27" t="n">
         <v>1.47</v>
@@ -12763,7 +12763,7 @@
         <v>2.21</v>
       </c>
       <c r="DO27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14936,7 +14936,7 @@
         <v>50</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DE32" t="n">
         <v>1</v>
@@ -14969,7 +14969,7 @@
         <v>2.62</v>
       </c>
       <c r="DO32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16261,7 +16261,7 @@
         <v>1.33</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DF35" t="n">
         <v>1.67</v>
@@ -16291,7 +16291,7 @@
         <v>2.16</v>
       </c>
       <c r="DO35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18459,7 +18459,7 @@
         <v>1.87</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DF40" t="n">
         <v>2.25</v>
@@ -18489,7 +18489,7 @@
         <v>2.56</v>
       </c>
       <c r="DO40" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP40" t="b">
         <v>0</v>
@@ -19328,7 +19328,7 @@
         <v>88</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE42" t="n">
         <v>0.9399999999999999</v>
@@ -19361,7 +19361,7 @@
         <v>2.02</v>
       </c>
       <c r="DO42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -23270,7 +23270,7 @@
         <v>60</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DE51" t="n">
         <v>1.8</v>
@@ -23303,7 +23303,7 @@
         <v>2.38</v>
       </c>
       <c r="DO51" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP51" t="b">
         <v>0</v>
@@ -23719,7 +23719,7 @@
         <v>1.4</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DF52" t="n">
         <v>0.4</v>
@@ -23749,7 +23749,7 @@
         <v>2.56</v>
       </c>
       <c r="DO52" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -31676,7 +31676,7 @@
         <v>55</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DE70" t="n">
         <v>1.47</v>
@@ -31709,7 +31709,7 @@
         <v>2.63</v>
       </c>
       <c r="DO70" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP70" t="b">
         <v>0</v>
@@ -33431,7 +33431,7 @@
         <v>0.79</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DF74" t="n">
         <v>0.57</v>
@@ -36967,7 +36967,7 @@
         <v>1.21</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DF82" t="n">
         <v>0.88</v>
@@ -37848,7 +37848,7 @@
         <v>60</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE84" t="n">
         <v>1.47</v>
@@ -37881,7 +37881,7 @@
         <v>2.54</v>
       </c>
       <c r="DO84" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP84" t="b">
         <v>0</v>
@@ -40938,7 +40938,7 @@
         <v>61</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE91" t="n">
         <v>2.27</v>
@@ -40971,7 +40971,7 @@
         <v>3.05</v>
       </c>
       <c r="DO91" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -42714,7 +42714,7 @@
         <v>69</v>
       </c>
       <c r="DD95" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DE95" t="n">
         <v>0.4</v>
@@ -42747,7 +42747,7 @@
         <v>2.19</v>
       </c>
       <c r="DO95" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -44485,7 +44485,7 @@
         <v>1.47</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DF99" t="n">
         <v>1.9</v>
@@ -44515,7 +44515,7 @@
         <v>2.56</v>
       </c>
       <c r="DO99" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP99" t="b">
         <v>0</v>
@@ -46245,7 +46245,7 @@
         <v>0.4</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DF103" t="n">
         <v>0.44</v>
@@ -46275,7 +46275,7 @@
         <v>2.12</v>
       </c>
       <c r="DO103" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -49786,7 +49786,7 @@
         <v>67</v>
       </c>
       <c r="DD111" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DE111" t="n">
         <v>1.67</v>
@@ -49819,7 +49819,7 @@
         <v>2.93</v>
       </c>
       <c r="DO111" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -51992,7 +51992,7 @@
         <v>70</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE116" t="n">
         <v>1.6</v>
@@ -52025,7 +52025,7 @@
         <v>2.79</v>
       </c>
       <c r="DO116" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -54655,7 +54655,7 @@
         <v>0.88</v>
       </c>
       <c r="DE122" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DF122" t="n">
         <v>0.83</v>
@@ -54685,7 +54685,7 @@
         <v>2.25</v>
       </c>
       <c r="DO122" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -55539,7 +55539,7 @@
         <v>1.67</v>
       </c>
       <c r="DE124" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DF124" t="n">
         <v>1.58</v>
@@ -55569,7 +55569,7 @@
         <v>2.8</v>
       </c>
       <c r="DO124" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -56850,7 +56850,7 @@
         <v>55</v>
       </c>
       <c r="DD127" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DE127" t="n">
         <v>1</v>
@@ -56883,7 +56883,7 @@
         <v>2.36</v>
       </c>
       <c r="DO127" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -57288,7 +57288,7 @@
         <v>67</v>
       </c>
       <c r="DD128" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DE128" t="n">
         <v>1.27</v>
@@ -57321,7 +57321,7 @@
         <v>2.77</v>
       </c>
       <c r="DO128" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -61225,7 +61225,7 @@
         <v>1.8</v>
       </c>
       <c r="DE137" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DF137" t="n">
         <v>1.77</v>
@@ -61255,7 +61255,7 @@
         <v>2.63</v>
       </c>
       <c r="DO137" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP137" t="b">
         <v>1</v>
@@ -63371,7 +63371,7 @@
         <v>1.6</v>
       </c>
       <c r="DE142" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DF142" t="n">
         <v>1.62</v>
@@ -63401,7 +63401,7 @@
         <v>2.92</v>
       </c>
       <c r="DO142" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -65822,7 +65822,7 @@
         <v>0</v>
       </c>
       <c r="BF148" t="n">
-        <v>-1</v>
+        <v>3000</v>
       </c>
       <c r="BG148" t="n">
         <v>2</v>
@@ -66260,7 +66260,7 @@
         <v>0</v>
       </c>
       <c r="BF149" t="n">
-        <v>-1</v>
+        <v>200</v>
       </c>
       <c r="BG149" t="n">
         <v>2</v>
@@ -66562,7 +66562,7 @@
         <v>2</v>
       </c>
       <c r="N150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -66614,7 +66614,7 @@
         <v>2</v>
       </c>
       <c r="AD150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE150" t="n">
         <v>1.2</v>
@@ -66698,7 +66698,7 @@
         <v>0</v>
       </c>
       <c r="BF150" t="n">
-        <v>-1</v>
+        <v>18508</v>
       </c>
       <c r="BG150" t="n">
         <v>2</v>
@@ -66734,13 +66734,13 @@
         <v>1</v>
       </c>
       <c r="BR150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS150" t="n">
         <v>2</v>
       </c>
       <c r="BT150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU150" t="n">
         <v>1</v>
@@ -66958,6 +66958,452 @@
           <t>1.77</t>
         </is>
       </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>7</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Rionegro Águilas</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>46119.875</v>
+      </c>
+      <c r="G151" t="n">
+        <v>2</v>
+      </c>
+      <c r="H151" t="n">
+        <v>1</v>
+      </c>
+      <c r="I151" t="n">
+        <v>3</v>
+      </c>
+      <c r="J151" t="n">
+        <v>1</v>
+      </c>
+      <c r="K151" t="n">
+        <v>6</v>
+      </c>
+      <c r="L151" t="n">
+        <v>7</v>
+      </c>
+      <c r="M151" t="n">
+        <v>3</v>
+      </c>
+      <c r="N151" t="n">
+        <v>2</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>3</v>
+      </c>
+      <c r="R151" t="n">
+        <v>3</v>
+      </c>
+      <c r="S151" t="n">
+        <v>2</v>
+      </c>
+      <c r="T151" t="n">
+        <v>13</v>
+      </c>
+      <c r="U151" t="n">
+        <v>5</v>
+      </c>
+      <c r="V151" t="n">
+        <v>16</v>
+      </c>
+      <c r="W151" t="n">
+        <v>8</v>
+      </c>
+      <c r="X151" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>Estadio Alberto Grisales</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>Route 45A, Rionegro, Antioquia</t>
+        </is>
+      </c>
+      <c r="AC151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>2147</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF151" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BG151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ151" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM151" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT151" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV151" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW151" t="n">
+        <v>63</v>
+      </c>
+      <c r="BX151" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY151" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ151" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="CA151" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CB151" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR151" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS151" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU151" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV151" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX151" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY151" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ151" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA151" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB151" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC151" t="n">
+        <v>57</v>
+      </c>
+      <c r="DD151" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DE151" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DF151" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DG151" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DH151" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DI151" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DJ151" t="n">
+        <v>61</v>
+      </c>
+      <c r="DK151" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL151" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DM151" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DN151" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="DO151" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP151" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ151" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR151" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV151" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW151" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="DX151" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="DY151" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="DZ151" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EA151" t="inlineStr">
+        <is>
+          <t>5.09</t>
+        </is>
+      </c>
+      <c r="EB151" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EC151" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="ED151" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="EE151" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EF151" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="EG151" t="inlineStr"/>
+      <c r="EH151" t="inlineStr"/>
+      <c r="EI151" t="inlineStr"/>
+      <c r="EJ151" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EJ151" headerRowCount="1">
-  <autoFilter ref="A1:EJ151"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EJ155" headerRowCount="1">
+  <autoFilter ref="A1:EJ155"/>
   <tableColumns count="140">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -578,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EJ151"/>
+  <dimension ref="A1:EJ155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1760,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DE2" t="n">
         <v>1.33</v>
@@ -3050,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DE5" t="n">
         <v>0.79</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4818,10 +4818,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4851,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5259,7 +5259,7 @@
         <v>1.27</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -5727,7 +5727,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6558,7 +6558,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DE13" t="n">
         <v>1</v>
@@ -7004,7 +7004,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DE14" t="n">
         <v>1.07</v>
@@ -7899,7 +7899,7 @@
         <v>1.47</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -7929,7 +7929,7 @@
         <v>2.53</v>
       </c>
       <c r="DO16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8764,10 +8764,10 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DF18" t="n">
         <v>1</v>
@@ -8797,7 +8797,7 @@
         <v>1.44</v>
       </c>
       <c r="DO18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9205,7 +9205,7 @@
         <v>1.4</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9640,7 +9640,7 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DE20" t="n">
         <v>1.27</v>
@@ -10970,10 +10970,10 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DF23" t="n">
         <v>0</v>
@@ -11003,7 +11003,7 @@
         <v>2.38</v>
       </c>
       <c r="DO23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11849,7 +11849,7 @@
         <v>1.27</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -12292,7 +12292,7 @@
         <v>75</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DE26" t="n">
         <v>1.4</v>
@@ -12730,7 +12730,7 @@
         <v>75</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="DE27" t="n">
         <v>1.47</v>
@@ -13617,7 +13617,7 @@
         <v>1.6</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -15377,7 +15377,7 @@
         <v>1.47</v>
       </c>
       <c r="DE33" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DF33" t="n">
         <v>1</v>
@@ -15820,7 +15820,7 @@
         <v>59</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DE34" t="n">
         <v>0.88</v>
@@ -15853,7 +15853,7 @@
         <v>2.49</v>
       </c>
       <c r="DO34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -16261,7 +16261,7 @@
         <v>1.33</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="DF35" t="n">
         <v>1.67</v>
@@ -16699,7 +16699,7 @@
         <v>1.4</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF36" t="n">
         <v>0</v>
@@ -16729,7 +16729,7 @@
         <v>2.84</v>
       </c>
       <c r="DO36" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP36" t="b">
         <v>0</v>
@@ -17137,7 +17137,7 @@
         <v>1.47</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DF37" t="n">
         <v>2</v>
@@ -17580,10 +17580,10 @@
         <v>67</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DF38" t="n">
         <v>0.67</v>
@@ -17613,7 +17613,7 @@
         <v>2.42</v>
       </c>
       <c r="DO38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18018,7 +18018,7 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DE39" t="n">
         <v>1.6</v>
@@ -18456,7 +18456,7 @@
         <v>88</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DE40" t="n">
         <v>1.27</v>
@@ -18890,7 +18890,7 @@
         <v>63</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE41" t="n">
         <v>1.47</v>
@@ -18923,7 +18923,7 @@
         <v>2.9</v>
       </c>
       <c r="DO41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -19328,7 +19328,7 @@
         <v>88</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="DE42" t="n">
         <v>0.9399999999999999</v>
@@ -19361,7 +19361,7 @@
         <v>2.02</v>
       </c>
       <c r="DO42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -19766,7 +19766,7 @@
         <v>63</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DE43" t="n">
         <v>1.33</v>
@@ -20622,7 +20622,7 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DE45" t="n">
         <v>0.79</v>
@@ -21063,7 +21063,7 @@
         <v>1</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DF46" t="n">
         <v>0.25</v>
@@ -21935,7 +21935,7 @@
         <v>0.88</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DF48" t="n">
         <v>1.33</v>
@@ -21965,7 +21965,7 @@
         <v>1.75</v>
       </c>
       <c r="DO48" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -22381,7 +22381,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF49" t="n">
         <v>0.4</v>
@@ -22411,7 +22411,7 @@
         <v>2.37</v>
       </c>
       <c r="DO49" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -22827,7 +22827,7 @@
         <v>1.33</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DF50" t="n">
         <v>1.8</v>
@@ -23273,7 +23273,7 @@
         <v>1.27</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DF51" t="n">
         <v>1.8</v>
@@ -23719,7 +23719,7 @@
         <v>1.4</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="DF52" t="n">
         <v>0.4</v>
@@ -25046,10 +25046,10 @@
         <v>80</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DF55" t="n">
         <v>1.4</v>
@@ -25079,7 +25079,7 @@
         <v>3.39</v>
       </c>
       <c r="DO55" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -25492,7 +25492,7 @@
         <v>70</v>
       </c>
       <c r="DD56" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DE56" t="n">
         <v>1.07</v>
@@ -26822,10 +26822,10 @@
         <v>64</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DF59" t="n">
         <v>0.83</v>
@@ -26855,7 +26855,7 @@
         <v>2.53</v>
       </c>
       <c r="DO59" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -27276,7 +27276,7 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DE60" t="n">
         <v>1.47</v>
@@ -27722,10 +27722,10 @@
         <v>50</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DF61" t="n">
         <v>1.5</v>
@@ -27755,7 +27755,7 @@
         <v>2.63</v>
       </c>
       <c r="DO61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -28163,7 +28163,7 @@
         <v>1.47</v>
       </c>
       <c r="DE62" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DF62" t="n">
         <v>1.17</v>
@@ -29908,7 +29908,7 @@
         <v>90</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DE66" t="n">
         <v>1.6</v>
@@ -30349,7 +30349,7 @@
         <v>1.33</v>
       </c>
       <c r="DE67" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF67" t="n">
         <v>1.29</v>
@@ -30379,7 +30379,7 @@
         <v>2.55</v>
       </c>
       <c r="DO67" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -30792,10 +30792,10 @@
         <v>62</v>
       </c>
       <c r="DD68" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DF68" t="n">
         <v>0.5</v>
@@ -30825,7 +30825,7 @@
         <v>1.99</v>
       </c>
       <c r="DO68" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -31238,7 +31238,7 @@
         <v>57</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DE69" t="n">
         <v>1.07</v>
@@ -32114,7 +32114,7 @@
         <v>54</v>
       </c>
       <c r="DD71" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DE71" t="n">
         <v>1</v>
@@ -33001,7 +33001,7 @@
         <v>1.27</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -33431,7 +33431,7 @@
         <v>0.79</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="DF74" t="n">
         <v>0.57</v>
@@ -34307,7 +34307,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DF76" t="n">
         <v>0.43</v>
@@ -34337,7 +34337,7 @@
         <v>2.09</v>
       </c>
       <c r="DO76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -34753,7 +34753,7 @@
         <v>1.27</v>
       </c>
       <c r="DE77" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DF77" t="n">
         <v>1.25</v>
@@ -35191,7 +35191,7 @@
         <v>1.4</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DF78" t="n">
         <v>1</v>
@@ -35626,7 +35626,7 @@
         <v>63</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DE79" t="n">
         <v>0.79</v>
@@ -36521,7 +36521,7 @@
         <v>0.88</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DF81" t="n">
         <v>1.43</v>
@@ -36551,7 +36551,7 @@
         <v>2.39</v>
       </c>
       <c r="DO81" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -36964,7 +36964,7 @@
         <v>60</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE82" t="n">
         <v>1.27</v>
@@ -36997,7 +36997,7 @@
         <v>2.82</v>
       </c>
       <c r="DO82" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -37410,7 +37410,7 @@
         <v>82</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DE83" t="n">
         <v>0.9399999999999999</v>
@@ -37443,7 +37443,7 @@
         <v>2.12</v>
       </c>
       <c r="DO83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -37848,7 +37848,7 @@
         <v>60</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="DE84" t="n">
         <v>1.47</v>
@@ -38724,10 +38724,10 @@
         <v>61</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DE86" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DF86" t="n">
         <v>1.5</v>
@@ -38757,7 +38757,7 @@
         <v>3.17</v>
       </c>
       <c r="DO86" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -40046,7 +40046,7 @@
         <v>75</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DE89" t="n">
         <v>1</v>
@@ -40495,7 +40495,7 @@
         <v>1.47</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DF90" t="n">
         <v>1.33</v>
@@ -40938,10 +40938,10 @@
         <v>61</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="DE91" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DF91" t="n">
         <v>1.5</v>
@@ -40971,7 +40971,7 @@
         <v>3.05</v>
       </c>
       <c r="DO91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -42276,7 +42276,7 @@
         <v>78</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DE94" t="n">
         <v>1.6</v>
@@ -42717,7 +42717,7 @@
         <v>1.27</v>
       </c>
       <c r="DE95" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DF95" t="n">
         <v>1.75</v>
@@ -43160,10 +43160,10 @@
         <v>88</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DE96" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DF96" t="n">
         <v>1.78</v>
@@ -43193,7 +43193,7 @@
         <v>3.39</v>
       </c>
       <c r="DO96" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -43598,10 +43598,10 @@
         <v>70</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DF97" t="n">
         <v>1.9</v>
@@ -43631,7 +43631,7 @@
         <v>2.98</v>
       </c>
       <c r="DO97" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -44036,7 +44036,7 @@
         <v>74</v>
       </c>
       <c r="DD98" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DE98" t="n">
         <v>1.33</v>
@@ -46242,10 +46242,10 @@
         <v>67</v>
       </c>
       <c r="DD103" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="DF103" t="n">
         <v>0.44</v>
@@ -46275,7 +46275,7 @@
         <v>2.12</v>
       </c>
       <c r="DO103" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -46691,7 +46691,7 @@
         <v>1.6</v>
       </c>
       <c r="DE104" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DF104" t="n">
         <v>1.78</v>
@@ -47137,7 +47137,7 @@
         <v>0.88</v>
       </c>
       <c r="DE105" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF105" t="n">
         <v>1</v>
@@ -47167,7 +47167,7 @@
         <v>2.51</v>
       </c>
       <c r="DO105" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -47572,7 +47572,7 @@
         <v>80</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DE106" t="n">
         <v>1.07</v>
@@ -48459,7 +48459,7 @@
         <v>1.4</v>
       </c>
       <c r="DE108" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DF108" t="n">
         <v>1.27</v>
@@ -48894,7 +48894,7 @@
         <v>72</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DE109" t="n">
         <v>0.79</v>
@@ -49343,7 +49343,7 @@
         <v>1.47</v>
       </c>
       <c r="DE110" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DF110" t="n">
         <v>1.82</v>
@@ -49789,7 +49789,7 @@
         <v>1.27</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DF111" t="n">
         <v>1.8</v>
@@ -51108,7 +51108,7 @@
         <v>52</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DE114" t="n">
         <v>1.07</v>
@@ -51554,10 +51554,10 @@
         <v>85</v>
       </c>
       <c r="DD115" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DF115" t="n">
         <v>1</v>
@@ -51587,7 +51587,7 @@
         <v>3.04</v>
       </c>
       <c r="DO115" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -51992,7 +51992,7 @@
         <v>70</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="DE116" t="n">
         <v>1.6</v>
@@ -52446,7 +52446,7 @@
         <v>67</v>
       </c>
       <c r="DD117" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DE117" t="n">
         <v>1.4</v>
@@ -52892,7 +52892,7 @@
         <v>70</v>
       </c>
       <c r="DD118" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DE118" t="n">
         <v>1.47</v>
@@ -53779,7 +53779,7 @@
         <v>0.79</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DF120" t="n">
         <v>0.64</v>
@@ -54217,7 +54217,7 @@
         <v>1.27</v>
       </c>
       <c r="DE121" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF121" t="n">
         <v>1.09</v>
@@ -54247,7 +54247,7 @@
         <v>2.97</v>
       </c>
       <c r="DO121" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -54655,7 +54655,7 @@
         <v>0.88</v>
       </c>
       <c r="DE122" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="DF122" t="n">
         <v>0.83</v>
@@ -54685,7 +54685,7 @@
         <v>2.25</v>
       </c>
       <c r="DO122" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -55098,7 +55098,7 @@
         <v>78</v>
       </c>
       <c r="DD123" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DE123" t="n">
         <v>0.9399999999999999</v>
@@ -55131,7 +55131,7 @@
         <v>1.87</v>
       </c>
       <c r="DO123" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -55536,7 +55536,7 @@
         <v>82</v>
       </c>
       <c r="DD124" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DE124" t="n">
         <v>1.27</v>
@@ -55977,7 +55977,7 @@
         <v>1.07</v>
       </c>
       <c r="DE125" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DF125" t="n">
         <v>1.17</v>
@@ -56850,7 +56850,7 @@
         <v>55</v>
       </c>
       <c r="DD127" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="DE127" t="n">
         <v>1</v>
@@ -58156,7 +58156,7 @@
         <v>64</v>
       </c>
       <c r="DD130" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DE130" t="n">
         <v>0.88</v>
@@ -58189,7 +58189,7 @@
         <v>2.27</v>
       </c>
       <c r="DO130" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -58589,7 +58589,7 @@
         <v>1.47</v>
       </c>
       <c r="DE131" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DF131" t="n">
         <v>1.23</v>
@@ -59027,7 +59027,7 @@
         <v>1.47</v>
       </c>
       <c r="DE132" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DF132" t="n">
         <v>1.62</v>
@@ -59470,10 +59470,10 @@
         <v>80</v>
       </c>
       <c r="DD133" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DE133" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DF133" t="n">
         <v>2.08</v>
@@ -59503,7 +59503,7 @@
         <v>3.05</v>
       </c>
       <c r="DO133" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -59903,7 +59903,7 @@
         <v>1.33</v>
       </c>
       <c r="DE134" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DF134" t="n">
         <v>1.23</v>
@@ -60346,7 +60346,7 @@
         <v>75</v>
       </c>
       <c r="DD135" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DE135" t="n">
         <v>1.6</v>
@@ -60379,7 +60379,7 @@
         <v>3.15</v>
       </c>
       <c r="DO135" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -61222,10 +61222,10 @@
         <v>46</v>
       </c>
       <c r="DD137" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DE137" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="DF137" t="n">
         <v>1.77</v>
@@ -61255,7 +61255,7 @@
         <v>2.63</v>
       </c>
       <c r="DO137" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP137" t="b">
         <v>1</v>
@@ -61655,7 +61655,7 @@
         <v>1</v>
       </c>
       <c r="DE138" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DF138" t="n">
         <v>0.85</v>
@@ -62520,7 +62520,7 @@
         <v>86</v>
       </c>
       <c r="DD140" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DE140" t="n">
         <v>0.9399999999999999</v>
@@ -62553,7 +62553,7 @@
         <v>2.69</v>
       </c>
       <c r="DO140" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP140" t="b">
         <v>0</v>
@@ -62941,7 +62941,7 @@
         <v>0.79</v>
       </c>
       <c r="DE141" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DF141" t="n">
         <v>0.62</v>
@@ -64244,10 +64244,10 @@
         <v>78</v>
       </c>
       <c r="DD144" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DE144" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF144" t="n">
         <v>1.71</v>
@@ -64277,7 +64277,7 @@
         <v>3.06</v>
       </c>
       <c r="DO144" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -65112,7 +65112,7 @@
         <v>75</v>
       </c>
       <c r="DD146" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DE146" t="n">
         <v>1.47</v>
@@ -65542,7 +65542,7 @@
         <v>61</v>
       </c>
       <c r="DD147" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DE147" t="n">
         <v>1.27</v>
@@ -66410,7 +66410,7 @@
         <v>64</v>
       </c>
       <c r="DD149" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DE149" t="n">
         <v>1</v>
@@ -66848,7 +66848,7 @@
         <v>76</v>
       </c>
       <c r="DD150" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DE150" t="n">
         <v>0.88</v>
@@ -66881,7 +66881,7 @@
         <v>2.74</v>
       </c>
       <c r="DO150" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -67026,25 +67026,25 @@
         <v>2</v>
       </c>
       <c r="T151" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U151" t="n">
         <v>5</v>
       </c>
       <c r="V151" t="n">
+        <v>17</v>
+      </c>
+      <c r="W151" t="n">
+        <v>9</v>
+      </c>
+      <c r="X151" t="n">
         <v>16</v>
       </c>
-      <c r="W151" t="n">
-        <v>8</v>
-      </c>
-      <c r="X151" t="n">
-        <v>15</v>
-      </c>
       <c r="Y151" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Z151" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
@@ -67207,10 +67207,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="CA151" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="CB151" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="CC151" t="n">
         <v>0</v>
@@ -67261,22 +67261,22 @@
         <v>16</v>
       </c>
       <c r="CS151" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="CT151" t="n">
         <v>1</v>
       </c>
       <c r="CU151" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CV151" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CW151" t="n">
         <v>1</v>
       </c>
       <c r="CX151" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CY151" t="n">
         <v>4</v>
@@ -67294,7 +67294,7 @@
         <v>57</v>
       </c>
       <c r="DD151" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="DE151" t="n">
         <v>1.27</v>
@@ -67404,6 +67404,1750 @@
       <c r="EH151" t="inlineStr"/>
       <c r="EI151" t="inlineStr"/>
       <c r="EJ151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>16</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>46122.85416666666</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>5</v>
+      </c>
+      <c r="K152" t="n">
+        <v>7</v>
+      </c>
+      <c r="L152" t="n">
+        <v>12</v>
+      </c>
+      <c r="M152" t="n">
+        <v>3</v>
+      </c>
+      <c r="N152" t="n">
+        <v>1</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>4</v>
+      </c>
+      <c r="R152" t="n">
+        <v>5</v>
+      </c>
+      <c r="S152" t="n">
+        <v>13</v>
+      </c>
+      <c r="T152" t="n">
+        <v>7</v>
+      </c>
+      <c r="U152" t="n">
+        <v>17</v>
+      </c>
+      <c r="V152" t="n">
+        <v>12</v>
+      </c>
+      <c r="W152" t="n">
+        <v>8</v>
+      </c>
+      <c r="X152" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>64</v>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>Estadio Hernán Ramírez Villegas</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>Villa Olímpica Pereira, Pereira</t>
+        </is>
+      </c>
+      <c r="AC152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ152" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR152" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT152" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV152" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW152" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX152" t="n">
+        <v>40</v>
+      </c>
+      <c r="BY152" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ152" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CA152" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB152" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="CC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR152" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS152" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU152" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV152" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX152" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY152" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ152" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA152" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB152" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC152" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD152" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DE152" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DF152" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DG152" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DH152" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DI152" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DJ152" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK152" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL152" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DM152" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DN152" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DO152" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW152" t="inlineStr"/>
+      <c r="DX152" t="inlineStr"/>
+      <c r="DY152" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="DZ152" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EA152" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EB152" t="inlineStr"/>
+      <c r="EC152" t="inlineStr"/>
+      <c r="ED152" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EE152" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="EF152" t="inlineStr">
+        <is>
+          <t>5.42</t>
+        </is>
+      </c>
+      <c r="EG152" t="inlineStr"/>
+      <c r="EH152" t="inlineStr"/>
+      <c r="EI152" t="inlineStr"/>
+      <c r="EJ152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>16</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>46123.04513888889</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1</v>
+      </c>
+      <c r="K153" t="n">
+        <v>4</v>
+      </c>
+      <c r="L153" t="n">
+        <v>5</v>
+      </c>
+      <c r="M153" t="n">
+        <v>1</v>
+      </c>
+      <c r="N153" t="n">
+        <v>2</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>1</v>
+      </c>
+      <c r="R153" t="n">
+        <v>2</v>
+      </c>
+      <c r="S153" t="n">
+        <v>1</v>
+      </c>
+      <c r="T153" t="n">
+        <v>7</v>
+      </c>
+      <c r="U153" t="n">
+        <v>2</v>
+      </c>
+      <c r="V153" t="n">
+        <v>9</v>
+      </c>
+      <c r="W153" t="n">
+        <v>10</v>
+      </c>
+      <c r="X153" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>Estadio Departamental Libertad</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>Carrera 8, San Juan de Pasto</t>
+        </is>
+      </c>
+      <c r="AC153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>2143</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD153" t="n">
+        <v>53</v>
+      </c>
+      <c r="BE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ153" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM153" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS153" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV153" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW153" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX153" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY153" t="n">
+        <v>63</v>
+      </c>
+      <c r="BZ153" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CA153" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CB153" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR153" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS153" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU153" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV153" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX153" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY153" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ153" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA153" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB153" t="n">
+        <v>37</v>
+      </c>
+      <c r="DC153" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD153" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DE153" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DF153" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DG153" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DH153" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DI153" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DJ153" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK153" t="n">
+        <v>27</v>
+      </c>
+      <c r="DL153" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM153" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DN153" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DO153" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP153" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW153" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="DX153" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="DY153" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="DZ153" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EA153" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="EB153" t="inlineStr"/>
+      <c r="EC153" t="inlineStr"/>
+      <c r="ED153" t="inlineStr">
+        <is>
+          <t>5.48</t>
+        </is>
+      </c>
+      <c r="EE153" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="EF153" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EG153" t="inlineStr"/>
+      <c r="EH153" t="inlineStr"/>
+      <c r="EI153" t="inlineStr"/>
+      <c r="EJ153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>16</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Rionegro Águilas</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>46123.875</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>3</v>
+      </c>
+      <c r="I154" t="n">
+        <v>3</v>
+      </c>
+      <c r="J154" t="n">
+        <v>8</v>
+      </c>
+      <c r="K154" t="n">
+        <v>2</v>
+      </c>
+      <c r="L154" t="n">
+        <v>10</v>
+      </c>
+      <c r="M154" t="n">
+        <v>1</v>
+      </c>
+      <c r="N154" t="n">
+        <v>4</v>
+      </c>
+      <c r="O154" t="n">
+        <v>1</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>3</v>
+      </c>
+      <c r="R154" t="n">
+        <v>4</v>
+      </c>
+      <c r="S154" t="n">
+        <v>11</v>
+      </c>
+      <c r="T154" t="n">
+        <v>6</v>
+      </c>
+      <c r="U154" t="n">
+        <v>14</v>
+      </c>
+      <c r="V154" t="n">
+        <v>10</v>
+      </c>
+      <c r="W154" t="n">
+        <v>7</v>
+      </c>
+      <c r="X154" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>Estadio Alberto Grisales</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>Route 45A, Rionegro, Antioquia</t>
+        </is>
+      </c>
+      <c r="AC154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>2131</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI154" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK154" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM154" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN154" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT154" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV154" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW154" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX154" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY154" t="n">
+        <v>73</v>
+      </c>
+      <c r="BZ154" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CA154" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CB154" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR154" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS154" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU154" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV154" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX154" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY154" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ154" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA154" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB154" t="n">
+        <v>27</v>
+      </c>
+      <c r="DC154" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD154" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DE154" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DF154" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DG154" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DH154" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DI154" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DJ154" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK154" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL154" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DM154" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DN154" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DO154" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW154" t="inlineStr"/>
+      <c r="DX154" t="inlineStr"/>
+      <c r="DY154" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="DZ154" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EA154" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="EB154" t="inlineStr"/>
+      <c r="EC154" t="inlineStr"/>
+      <c r="ED154" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="EE154" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="EF154" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EG154" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EH154" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EI154" t="inlineStr"/>
+      <c r="EJ154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>16</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>46124.05555555555</v>
+      </c>
+      <c r="G155" t="n">
+        <v>2</v>
+      </c>
+      <c r="H155" t="n">
+        <v>3</v>
+      </c>
+      <c r="I155" t="n">
+        <v>5</v>
+      </c>
+      <c r="J155" t="n">
+        <v>3</v>
+      </c>
+      <c r="K155" t="n">
+        <v>4</v>
+      </c>
+      <c r="L155" t="n">
+        <v>7</v>
+      </c>
+      <c r="M155" t="n">
+        <v>1</v>
+      </c>
+      <c r="N155" t="n">
+        <v>2</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>7</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6</v>
+      </c>
+      <c r="S155" t="n">
+        <v>3</v>
+      </c>
+      <c r="T155" t="n">
+        <v>10</v>
+      </c>
+      <c r="U155" t="n">
+        <v>10</v>
+      </c>
+      <c r="V155" t="n">
+        <v>16</v>
+      </c>
+      <c r="W155" t="n">
+        <v>4</v>
+      </c>
+      <c r="X155" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>Estadio Atanasio Girardot</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
+        </is>
+      </c>
+      <c r="AC155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>2142</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT155" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV155" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW155" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX155" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY155" t="n">
+        <v>94</v>
+      </c>
+      <c r="BZ155" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CA155" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CB155" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL155" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR155" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS155" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU155" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV155" t="n">
+        <v>4</v>
+      </c>
+      <c r="CW155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX155" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY155" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ155" t="n">
+        <v>69</v>
+      </c>
+      <c r="DA155" t="n">
+        <v>83</v>
+      </c>
+      <c r="DB155" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC155" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD155" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DE155" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DF155" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DG155" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DH155" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DI155" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DJ155" t="n">
+        <v>32</v>
+      </c>
+      <c r="DK155" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL155" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DM155" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DN155" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="DO155" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW155" t="inlineStr"/>
+      <c r="DX155" t="inlineStr"/>
+      <c r="DY155" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="DZ155" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EA155" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="EB155" t="inlineStr"/>
+      <c r="EC155" t="inlineStr"/>
+      <c r="ED155" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EE155" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EF155" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="EG155" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EH155" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EI155" t="inlineStr"/>
+      <c r="EJ155" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EJ201" headerRowCount="1">
-  <autoFilter ref="A1:EJ201"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EJ203" headerRowCount="1">
+  <autoFilter ref="A1:EJ203"/>
   <tableColumns count="140">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EJ201"/>
+  <dimension ref="A1:EJ203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DE5" t="n">
         <v>0.89</v>
@@ -4806,10 +4806,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5244,7 +5244,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DE10" t="n">
         <v>1.37</v>
@@ -6546,7 +6546,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DE13" t="n">
         <v>0.89</v>
@@ -9193,7 +9193,7 @@
         <v>1.37</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9631,7 +9631,7 @@
         <v>1.62</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -10961,7 +10961,7 @@
         <v>1.37</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DF23" t="n">
         <v>0</v>
@@ -11834,7 +11834,7 @@
         <v>25</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DE25" t="n">
         <v>0.53</v>
@@ -14481,7 +14481,7 @@
         <v>0.89</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DF31" t="n">
         <v>0.33</v>
@@ -17125,7 +17125,7 @@
         <v>1.33</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DF37" t="n">
         <v>2</v>
@@ -17571,7 +17571,7 @@
         <v>0.53</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DF38" t="n">
         <v>0.67</v>
@@ -18006,7 +18006,7 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DE39" t="n">
         <v>1.62</v>
@@ -19754,7 +19754,7 @@
         <v>63</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DE43" t="n">
         <v>1.16</v>
@@ -20195,7 +20195,7 @@
         <v>1.16</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DF44" t="n">
         <v>1.5</v>
@@ -20610,7 +20610,7 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DE45" t="n">
         <v>0.89</v>
@@ -23261,7 +23261,7 @@
         <v>1.21</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DF51" t="n">
         <v>1.8</v>
@@ -25037,7 +25037,7 @@
         <v>1.62</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DF55" t="n">
         <v>1.4</v>
@@ -25480,7 +25480,7 @@
         <v>70</v>
       </c>
       <c r="DD56" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DE56" t="n">
         <v>1.16</v>
@@ -25921,7 +25921,7 @@
         <v>1.62</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DF57" t="n">
         <v>1.75</v>
@@ -27710,7 +27710,7 @@
         <v>50</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DE61" t="n">
         <v>1.62</v>
@@ -28151,7 +28151,7 @@
         <v>1.42</v>
       </c>
       <c r="DE62" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DF62" t="n">
         <v>1.17</v>
@@ -29465,7 +29465,7 @@
         <v>0.95</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DF65" t="n">
         <v>1.4</v>
@@ -29896,7 +29896,7 @@
         <v>90</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DE66" t="n">
         <v>1.62</v>
@@ -32102,7 +32102,7 @@
         <v>54</v>
       </c>
       <c r="DD71" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DE71" t="n">
         <v>0.89</v>
@@ -32986,10 +32986,10 @@
         <v>72</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -33019,7 +33019,7 @@
         <v>3.26</v>
       </c>
       <c r="DO73" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -34295,7 +34295,7 @@
         <v>0.84</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DF76" t="n">
         <v>0.43</v>
@@ -34738,10 +34738,10 @@
         <v>65</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DE77" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DF77" t="n">
         <v>1.25</v>
@@ -34771,7 +34771,7 @@
         <v>3.5</v>
       </c>
       <c r="DO77" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -36509,7 +36509,7 @@
         <v>0.95</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DF81" t="n">
         <v>1.43</v>
@@ -38712,10 +38712,10 @@
         <v>61</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DE86" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DF86" t="n">
         <v>1.5</v>
@@ -38745,7 +38745,7 @@
         <v>3.17</v>
       </c>
       <c r="DO86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -40034,7 +40034,7 @@
         <v>75</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DE89" t="n">
         <v>0.89</v>
@@ -40929,7 +40929,7 @@
         <v>1.37</v>
       </c>
       <c r="DE91" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DF91" t="n">
         <v>1.5</v>
@@ -43148,10 +43148,10 @@
         <v>88</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DE96" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DF96" t="n">
         <v>1.78</v>
@@ -43181,7 +43181,7 @@
         <v>3.39</v>
       </c>
       <c r="DO96" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -44024,7 +44024,7 @@
         <v>74</v>
       </c>
       <c r="DD98" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DE98" t="n">
         <v>1.16</v>
@@ -45792,7 +45792,7 @@
         <v>56</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DE102" t="n">
         <v>0.89</v>
@@ -46679,7 +46679,7 @@
         <v>1.62</v>
       </c>
       <c r="DE104" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DF104" t="n">
         <v>1.78</v>
@@ -47560,7 +47560,7 @@
         <v>80</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DE106" t="n">
         <v>1.16</v>
@@ -48447,7 +48447,7 @@
         <v>1.37</v>
       </c>
       <c r="DE108" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DF108" t="n">
         <v>1.27</v>
@@ -50215,7 +50215,7 @@
         <v>1.42</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DF112" t="n">
         <v>1.36</v>
@@ -51096,7 +51096,7 @@
         <v>52</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DE114" t="n">
         <v>1.16</v>
@@ -51545,7 +51545,7 @@
         <v>1.37</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DF115" t="n">
         <v>1</v>
@@ -52880,7 +52880,7 @@
         <v>70</v>
       </c>
       <c r="DD118" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DE118" t="n">
         <v>1.33</v>
@@ -53767,7 +53767,7 @@
         <v>0.89</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DF120" t="n">
         <v>0.64</v>
@@ -54202,7 +54202,7 @@
         <v>69</v>
       </c>
       <c r="DD121" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DE121" t="n">
         <v>1.37</v>
@@ -55524,7 +55524,7 @@
         <v>82</v>
       </c>
       <c r="DD124" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DE124" t="n">
         <v>1.21</v>
@@ -57279,7 +57279,7 @@
         <v>1.21</v>
       </c>
       <c r="DE128" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DF128" t="n">
         <v>1.58</v>
@@ -58144,7 +58144,7 @@
         <v>64</v>
       </c>
       <c r="DD130" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DE130" t="n">
         <v>0.95</v>
@@ -59015,7 +59015,7 @@
         <v>1.33</v>
       </c>
       <c r="DE132" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DF132" t="n">
         <v>1.62</v>
@@ -59461,7 +59461,7 @@
         <v>1.62</v>
       </c>
       <c r="DE133" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DF133" t="n">
         <v>2.08</v>
@@ -61210,7 +61210,7 @@
         <v>46</v>
       </c>
       <c r="DD137" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DE137" t="n">
         <v>1.37</v>
@@ -62070,7 +62070,7 @@
         <v>70</v>
       </c>
       <c r="DD139" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DE139" t="n">
         <v>1.16</v>
@@ -62508,7 +62508,7 @@
         <v>86</v>
       </c>
       <c r="DD140" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DE140" t="n">
         <v>0.84</v>
@@ -65100,7 +65100,7 @@
         <v>75</v>
       </c>
       <c r="DD146" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DE146" t="n">
         <v>1.42</v>
@@ -65530,10 +65530,10 @@
         <v>61</v>
       </c>
       <c r="DD147" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DE147" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DF147" t="n">
         <v>1.86</v>
@@ -65563,7 +65563,7 @@
         <v>2.85</v>
       </c>
       <c r="DO147" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -66836,7 +66836,7 @@
         <v>76</v>
       </c>
       <c r="DD150" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DE150" t="n">
         <v>0.95</v>
@@ -68161,7 +68161,7 @@
         <v>1.62</v>
       </c>
       <c r="DE153" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DF153" t="n">
         <v>1.87</v>
@@ -68599,7 +68599,7 @@
         <v>1.37</v>
       </c>
       <c r="DE154" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DF154" t="n">
         <v>1.47</v>
@@ -69037,7 +69037,7 @@
         <v>1.37</v>
       </c>
       <c r="DE155" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DF155" t="n">
         <v>1.21</v>
@@ -69475,7 +69475,7 @@
         <v>1.37</v>
       </c>
       <c r="DE156" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DF156" t="n">
         <v>1.4</v>
@@ -72084,7 +72084,7 @@
         <v>66</v>
       </c>
       <c r="DD162" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DE162" t="n">
         <v>0.53</v>
@@ -72944,7 +72944,7 @@
         <v>72</v>
       </c>
       <c r="DD164" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DE164" t="n">
         <v>0.84</v>
@@ -73820,7 +73820,7 @@
         <v>79</v>
       </c>
       <c r="DD166" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DE166" t="n">
         <v>1.16</v>
@@ -75126,7 +75126,7 @@
         <v>78</v>
       </c>
       <c r="DD169" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DE169" t="n">
         <v>1.21</v>
@@ -76443,7 +76443,7 @@
         <v>1.62</v>
       </c>
       <c r="DE172" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DF172" t="n">
         <v>2</v>
@@ -76889,7 +76889,7 @@
         <v>1.37</v>
       </c>
       <c r="DE173" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DF173" t="n">
         <v>1.29</v>
@@ -77327,7 +77327,7 @@
         <v>0.84</v>
       </c>
       <c r="DE174" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DF174" t="n">
         <v>0.88</v>
@@ -78195,7 +78195,7 @@
         <v>0.53</v>
       </c>
       <c r="DE176" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DF176" t="n">
         <v>0.41</v>
@@ -80799,7 +80799,7 @@
         <v>1.62</v>
       </c>
       <c r="DE182" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DF182" t="n">
         <v>1.67</v>
@@ -82631,176 +82631,176 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Deportes Tolima</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Deportivo Cali</t>
+          <t>La Equidad</t>
         </is>
       </c>
       <c r="F187" s="1" t="n">
         <v>46145.85416666666</v>
       </c>
       <c r="G187" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H187" t="n">
         <v>1</v>
       </c>
       <c r="I187" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J187" t="n">
+        <v>4</v>
+      </c>
+      <c r="K187" t="n">
+        <v>1</v>
+      </c>
+      <c r="L187" t="n">
         <v>5</v>
       </c>
-      <c r="K187" t="n">
-        <v>3</v>
-      </c>
-      <c r="L187" t="n">
-        <v>8</v>
-      </c>
       <c r="M187" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N187" t="n">
         <v>3</v>
       </c>
       <c r="O187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P187" t="n">
         <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R187" t="n">
         <v>4</v>
       </c>
       <c r="S187" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T187" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U187" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V187" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W187" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X187" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y187" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Z187" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>Estadio Manuel Murillo Toro</t>
+          <t>Estadio Nemesio Camacho El Campín</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
+          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
         </is>
       </c>
       <c r="AC187" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AD187" t="n">
         <v>3</v>
       </c>
       <c r="AE187" t="n">
-        <v>2.65</v>
+        <v>1.84</v>
       </c>
       <c r="AF187" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="AG187" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="AH187" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AI187" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AJ187" t="n">
         <v>4.15</v>
       </c>
       <c r="AK187" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AL187" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AM187" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AN187" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="AO187" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AR187" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AS187" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="AT187" t="n">
         <v>1.28</v>
       </c>
       <c r="AU187" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW187" t="n">
         <v>0</v>
       </c>
       <c r="AX187" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY187" t="n">
         <v>1</v>
       </c>
       <c r="AZ187" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BA187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB187" t="n">
-        <v>-1</v>
+        <v>2133</v>
       </c>
       <c r="BC187" t="n">
         <v>1</v>
       </c>
       <c r="BD187" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="BE187" t="n">
         <v>0</v>
       </c>
       <c r="BF187" t="n">
-        <v>8000</v>
+        <v>16955</v>
       </c>
       <c r="BG187" t="n">
         <v>2</v>
@@ -82809,181 +82809,181 @@
         <v>1</v>
       </c>
       <c r="BI187" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ187" t="n">
         <v>1</v>
       </c>
       <c r="BK187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM187" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BN187" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ187" t="n">
         <v>4</v>
       </c>
       <c r="BR187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT187" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU187" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV187" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW187" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX187" t="n">
+        <v>101</v>
+      </c>
+      <c r="BY187" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ187" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CA187" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CB187" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CC187" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE187" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI187" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ187" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM187" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ187" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR187" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS187" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT187" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU187" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV187" t="n">
         <v>6</v>
       </c>
-      <c r="BU187" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV187" t="n">
-        <v>19</v>
-      </c>
-      <c r="BW187" t="n">
-        <v>58</v>
-      </c>
-      <c r="BX187" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY187" t="n">
-        <v>142</v>
-      </c>
-      <c r="BZ187" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="CA187" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CB187" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="CC187" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD187" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE187" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF187" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG187" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH187" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI187" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ187" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK187" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL187" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM187" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN187" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO187" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP187" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ187" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR187" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS187" t="n">
+      <c r="CW187" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX187" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY187" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ187" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA187" t="n">
+        <v>81</v>
+      </c>
+      <c r="DB187" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC187" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD187" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DE187" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF187" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DG187" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DH187" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DI187" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DJ187" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK187" t="n">
         <v>20</v>
       </c>
-      <c r="CT187" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU187" t="n">
-        <v>10</v>
-      </c>
-      <c r="CV187" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW187" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX187" t="n">
-        <v>12</v>
-      </c>
-      <c r="CY187" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ187" t="n">
-        <v>31</v>
-      </c>
-      <c r="DA187" t="n">
-        <v>64</v>
-      </c>
-      <c r="DB187" t="n">
-        <v>20</v>
-      </c>
-      <c r="DC187" t="n">
-        <v>59</v>
-      </c>
-      <c r="DD187" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="DE187" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="DF187" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DG187" t="n">
+      <c r="DL187" t="n">
         <v>1.44</v>
       </c>
-      <c r="DH187" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DI187" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DJ187" t="n">
-        <v>70</v>
-      </c>
-      <c r="DK187" t="n">
-        <v>36</v>
-      </c>
-      <c r="DL187" t="n">
-        <v>1.41</v>
-      </c>
       <c r="DM187" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="DN187" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="DO187" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="DP187" t="b">
         <v>1</v>
@@ -82992,10 +82992,10 @@
         <v>1</v>
       </c>
       <c r="DR187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT187" t="b">
         <v>0</v>
@@ -83010,46 +83010,38 @@
       <c r="DX187" t="inlineStr"/>
       <c r="DY187" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="DZ187" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EA187" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="EB187" t="inlineStr"/>
       <c r="EC187" t="inlineStr"/>
       <c r="ED187" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="EE187" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EF187" t="inlineStr">
         <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="EG187" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EH187" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EG187" t="inlineStr"/>
+      <c r="EH187" t="inlineStr"/>
       <c r="EI187" t="inlineStr"/>
       <c r="EJ187" t="inlineStr"/>
     </row>
@@ -83069,12 +83061,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Independiente Medellín</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Rionegro Águilas</t>
+          <t>Deportivo Cali</t>
         </is>
       </c>
       <c r="F188" s="1" t="n">
@@ -83084,25 +83076,25 @@
         <v>1</v>
       </c>
       <c r="H188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J188" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L188" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M188" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O188" t="n">
         <v>1</v>
@@ -83111,161 +83103,161 @@
         <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R188" t="n">
         <v>4</v>
       </c>
       <c r="S188" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T188" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U188" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="V188" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="W188" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X188" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Murillo Toro</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
+        </is>
+      </c>
+      <c r="AC188" t="n">
         <v>7</v>
       </c>
-      <c r="Y188" t="n">
-        <v>70</v>
-      </c>
-      <c r="Z188" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA188" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
-      <c r="AC188" t="n">
+      <c r="AD188" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI188" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AK188" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL188" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM188" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN188" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AO188" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AP188" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ188" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR188" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS188" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AT188" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB188" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD188" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE188" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF188" t="n">
+        <v>8000</v>
+      </c>
+      <c r="BG188" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI188" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK188" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL188" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM188" t="n">
         <v>4</v>
       </c>
-      <c r="AD188" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE188" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF188" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AG188" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AH188" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI188" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AJ188" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AK188" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL188" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AM188" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AN188" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO188" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AP188" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AQ188" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR188" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AS188" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AT188" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AU188" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW188" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX188" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY188" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ188" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA188" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB188" t="n">
-        <v>2147</v>
-      </c>
-      <c r="BC188" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD188" t="n">
-        <v>62</v>
-      </c>
-      <c r="BE188" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF188" t="n">
-        <v>20000</v>
-      </c>
-      <c r="BG188" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH188" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI188" t="n">
-        <v>6</v>
-      </c>
-      <c r="BJ188" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK188" t="n">
+      <c r="BN188" t="n">
         <v>4</v>
       </c>
-      <c r="BL188" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM188" t="n">
-        <v>7</v>
-      </c>
-      <c r="BN188" t="n">
-        <v>5</v>
-      </c>
       <c r="BO188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP188" t="n">
         <v>1</v>
@@ -83274,151 +83266,151 @@
         <v>4</v>
       </c>
       <c r="BR188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT188" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BU188" t="n">
         <v>1</v>
       </c>
       <c r="BV188" t="n">
+        <v>19</v>
+      </c>
+      <c r="BW188" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX188" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY188" t="n">
+        <v>142</v>
+      </c>
+      <c r="BZ188" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CA188" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CB188" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CC188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM188" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR188" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS188" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU188" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV188" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX188" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY188" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ188" t="n">
+        <v>31</v>
+      </c>
+      <c r="DA188" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB188" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC188" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD188" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DE188" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DF188" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG188" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DH188" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DI188" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DJ188" t="n">
         <v>70</v>
       </c>
-      <c r="BW188" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX188" t="n">
-        <v>120</v>
-      </c>
-      <c r="BY188" t="n">
-        <v>44</v>
-      </c>
-      <c r="BZ188" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="CA188" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="CB188" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="CC188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI188" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ188" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM188" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP188" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ188" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR188" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS188" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT188" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU188" t="n">
-        <v>7</v>
-      </c>
-      <c r="CV188" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW188" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX188" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY188" t="n">
-        <v>18</v>
-      </c>
-      <c r="CZ188" t="n">
-        <v>50</v>
-      </c>
-      <c r="DA188" t="n">
-        <v>73</v>
-      </c>
-      <c r="DB188" t="n">
-        <v>28</v>
-      </c>
-      <c r="DC188" t="n">
-        <v>64</v>
-      </c>
-      <c r="DD188" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="DE188" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="DF188" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DG188" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="DH188" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DI188" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="DJ188" t="n">
-        <v>50</v>
-      </c>
       <c r="DK188" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="DL188" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="DM188" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="DN188" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="DO188" t="n">
         <v>19</v>
@@ -83430,7 +83422,7 @@
         <v>1</v>
       </c>
       <c r="DR188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS188" t="b">
         <v>0</v>
@@ -83448,44 +83440,44 @@
       <c r="DX188" t="inlineStr"/>
       <c r="DY188" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="DZ188" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EA188" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="EB188" t="inlineStr"/>
       <c r="EC188" t="inlineStr"/>
       <c r="ED188" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EE188" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="EF188" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="EG188" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EH188" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EI188" t="inlineStr"/>
@@ -83507,43 +83499,43 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Independiente Medellín</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>La Equidad</t>
+          <t>Rionegro Águilas</t>
         </is>
       </c>
       <c r="F189" s="1" t="n">
         <v>46145.85416666666</v>
       </c>
       <c r="G189" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I189" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J189" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L189" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M189" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P189" t="n">
         <v>0</v>
@@ -83555,158 +83547,158 @@
         <v>4</v>
       </c>
       <c r="S189" t="n">
+        <v>14</v>
+      </c>
+      <c r="T189" t="n">
+        <v>6</v>
+      </c>
+      <c r="U189" t="n">
+        <v>21</v>
+      </c>
+      <c r="V189" t="n">
+        <v>10</v>
+      </c>
+      <c r="W189" t="n">
+        <v>10</v>
+      </c>
+      <c r="X189" t="n">
         <v>7</v>
       </c>
-      <c r="T189" t="n">
-        <v>14</v>
-      </c>
-      <c r="U189" t="n">
-        <v>14</v>
-      </c>
-      <c r="V189" t="n">
-        <v>18</v>
-      </c>
-      <c r="W189" t="n">
-        <v>6</v>
-      </c>
-      <c r="X189" t="n">
-        <v>8</v>
-      </c>
       <c r="Y189" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="Z189" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
+          <t>Estadio Atanasio Girardot</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
+          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
         </is>
       </c>
       <c r="AC189" t="n">
         <v>4</v>
       </c>
       <c r="AD189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE189" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG189" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AH189" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI189" t="n">
         <v>1.84</v>
       </c>
-      <c r="AF189" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG189" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AH189" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI189" t="n">
-        <v>2.29</v>
-      </c>
       <c r="AJ189" t="n">
-        <v>4.15</v>
+        <v>2.92</v>
       </c>
       <c r="AK189" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL189" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AM189" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AN189" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="AO189" t="n">
-        <v>2.06</v>
+        <v>2.31</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AR189" t="n">
-        <v>2.95</v>
+        <v>2.66</v>
       </c>
       <c r="AS189" t="n">
-        <v>2.41</v>
+        <v>2.9</v>
       </c>
       <c r="AT189" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AU189" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA189" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB189" t="n">
+        <v>2147</v>
+      </c>
+      <c r="BC189" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD189" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE189" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF189" t="n">
+        <v>20000</v>
+      </c>
+      <c r="BG189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH189" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI189" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ189" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK189" t="n">
         <v>4</v>
       </c>
-      <c r="AV189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX189" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY189" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ189" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA189" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB189" t="n">
-        <v>2133</v>
-      </c>
-      <c r="BC189" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD189" t="n">
-        <v>70</v>
-      </c>
-      <c r="BE189" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF189" t="n">
-        <v>16955</v>
-      </c>
-      <c r="BG189" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH189" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI189" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ189" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK189" t="n">
-        <v>3</v>
-      </c>
       <c r="BL189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM189" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BN189" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BO189" t="n">
         <v>0</v>
       </c>
       <c r="BP189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ189" t="n">
         <v>4</v>
@@ -83715,7 +83707,7 @@
         <v>1</v>
       </c>
       <c r="BS189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT189" t="n">
         <v>5</v>
@@ -83724,34 +83716,34 @@
         <v>1</v>
       </c>
       <c r="BV189" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BW189" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="BX189" t="n">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="BY189" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="BZ189" t="n">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="CA189" t="n">
-        <v>1.62</v>
+        <v>0.98</v>
       </c>
       <c r="CB189" t="n">
         <v>3.29</v>
       </c>
       <c r="CC189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD189" t="n">
         <v>0</v>
       </c>
       <c r="CE189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF189" t="n">
         <v>0</v>
@@ -83775,7 +83767,7 @@
         <v>0</v>
       </c>
       <c r="CM189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN189" t="n">
         <v>0</v>
@@ -83790,10 +83782,10 @@
         <v>1</v>
       </c>
       <c r="CR189" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CS189" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="CT189" t="n">
         <v>1</v>
@@ -83802,64 +83794,64 @@
         <v>7</v>
       </c>
       <c r="CV189" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="CW189" t="n">
         <v>1</v>
       </c>
       <c r="CX189" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CY189" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="CZ189" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="DA189" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="DB189" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="DC189" t="n">
         <v>64</v>
       </c>
       <c r="DD189" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="DE189" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="DF189" t="n">
         <v>1.44</v>
       </c>
       <c r="DG189" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="DH189" t="n">
         <v>1.44</v>
       </c>
       <c r="DI189" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="DJ189" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="DK189" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="DL189" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="DM189" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="DN189" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="DO189" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="DP189" t="b">
         <v>1</v>
@@ -83871,7 +83863,7 @@
         <v>1</v>
       </c>
       <c r="DS189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT189" t="b">
         <v>0</v>
@@ -83886,38 +83878,46 @@
       <c r="DX189" t="inlineStr"/>
       <c r="DY189" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="DZ189" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="EA189" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EB189" t="inlineStr"/>
       <c r="EC189" t="inlineStr"/>
       <c r="ED189" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="EE189" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="EF189" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="EG189" t="inlineStr"/>
-      <c r="EH189" t="inlineStr"/>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EG189" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH189" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
       <c r="EI189" t="inlineStr"/>
       <c r="EJ189" t="inlineStr"/>
     </row>
@@ -83937,40 +83937,40 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>América de Cali</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F190" s="1" t="n">
         <v>46145.94791666666</v>
       </c>
       <c r="G190" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H190" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I190" t="n">
+        <v>1</v>
+      </c>
+      <c r="J190" t="n">
         <v>7</v>
       </c>
-      <c r="J190" t="n">
-        <v>5</v>
-      </c>
       <c r="K190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L190" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -83979,141 +83979,149 @@
         <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R190" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S190" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T190" t="n">
         <v>5</v>
       </c>
       <c r="U190" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="V190" t="n">
+        <v>5</v>
+      </c>
+      <c r="W190" t="n">
+        <v>12</v>
+      </c>
+      <c r="X190" t="n">
         <v>10</v>
       </c>
-      <c r="W190" t="n">
-        <v>15</v>
-      </c>
-      <c r="X190" t="n">
-        <v>11</v>
-      </c>
       <c r="Y190" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Z190" t="n">
-        <v>54</v>
-      </c>
-      <c r="AA190" t="inlineStr"/>
-      <c r="AB190" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>Estadio Olímpico Pascual Guerrero</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>Carrera 36 entre Calles 5 y 5B3, Santiago de Cali</t>
+        </is>
+      </c>
       <c r="AC190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE190" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AF190" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AG190" t="n">
-        <v>4.69</v>
+        <v>6.4</v>
       </c>
       <c r="AH190" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AI190" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AJ190" t="n">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="AK190" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AL190" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AM190" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AN190" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AO190" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AR190" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AS190" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AT190" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AU190" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AV190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ190" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA190" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB190" t="n">
+        <v>2141</v>
+      </c>
+      <c r="BC190" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD190" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE190" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF190" t="n">
+        <v>6000</v>
+      </c>
+      <c r="BG190" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH190" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI190" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ190" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK190" t="n">
         <v>4</v>
-      </c>
-      <c r="AY190" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ190" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA190" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB190" t="n">
-        <v>2131</v>
-      </c>
-      <c r="BC190" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD190" t="n">
-        <v>53</v>
-      </c>
-      <c r="BE190" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF190" t="n">
-        <v>9000</v>
-      </c>
-      <c r="BG190" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH190" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI190" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ190" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK190" t="n">
-        <v>3</v>
       </c>
       <c r="BL190" t="n">
         <v>0</v>
@@ -84122,7 +84130,7 @@
         <v>4</v>
       </c>
       <c r="BN190" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO190" t="n">
         <v>0</v>
@@ -84131,10 +84139,10 @@
         <v>0</v>
       </c>
       <c r="BQ190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS190" t="n">
         <v>0</v>
@@ -84146,200 +84154,208 @@
         <v>1</v>
       </c>
       <c r="BV190" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="BW190" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="BX190" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY190" t="n">
+        <v>74</v>
+      </c>
+      <c r="BZ190" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CA190" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="CB190" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CC190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI190" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ190" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN190" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ190" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR190" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS190" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT190" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU190" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV190" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW190" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX190" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY190" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ190" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA190" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB190" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC190" t="n">
         <v>75</v>
       </c>
-      <c r="BY190" t="n">
-        <v>63</v>
-      </c>
-      <c r="BZ190" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CA190" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="CB190" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="CC190" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD190" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE190" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF190" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG190" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH190" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI190" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ190" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK190" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL190" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM190" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN190" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO190" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP190" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ190" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR190" t="n">
-        <v>14</v>
-      </c>
-      <c r="CS190" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT190" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU190" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV190" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW190" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX190" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY190" t="n">
-        <v>2</v>
-      </c>
-      <c r="CZ190" t="n">
+      <c r="DD190" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DE190" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="DF190" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG190" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DH190" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DI190" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DJ190" t="n">
         <v>56</v>
       </c>
-      <c r="DA190" t="n">
-        <v>83</v>
-      </c>
-      <c r="DB190" t="n">
-        <v>45</v>
-      </c>
-      <c r="DC190" t="n">
-        <v>83</v>
-      </c>
-      <c r="DD190" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="DE190" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="DF190" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="DG190" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="DH190" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="DI190" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="DJ190" t="n">
-        <v>44</v>
-      </c>
       <c r="DK190" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="DL190" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="DM190" t="n">
-        <v>1.34</v>
+        <v>0.97</v>
       </c>
       <c r="DN190" t="n">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
       <c r="DO190" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="DP190" t="b">
         <v>1</v>
       </c>
       <c r="DQ190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW190" t="inlineStr"/>
       <c r="DX190" t="inlineStr"/>
       <c r="DY190" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="DZ190" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="EA190" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EB190" t="inlineStr"/>
       <c r="EC190" t="inlineStr"/>
       <c r="ED190" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="EE190" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="EF190" t="inlineStr">
         <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EG190" t="inlineStr"/>
-      <c r="EH190" t="inlineStr"/>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EG190" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH190" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
       <c r="EI190" t="inlineStr"/>
       <c r="EJ190" t="inlineStr"/>
     </row>
@@ -84359,40 +84375,40 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>América de Cali</t>
+          <t>Junior</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="F191" s="1" t="n">
         <v>46145.94791666666</v>
       </c>
       <c r="G191" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J191" t="n">
+        <v>5</v>
+      </c>
+      <c r="K191" t="n">
+        <v>2</v>
+      </c>
+      <c r="L191" t="n">
         <v>7</v>
       </c>
-      <c r="K191" t="n">
-        <v>1</v>
-      </c>
-      <c r="L191" t="n">
-        <v>8</v>
-      </c>
       <c r="M191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -84401,134 +84417,126 @@
         <v>0</v>
       </c>
       <c r="Q191" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R191" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S191" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T191" t="n">
         <v>5</v>
       </c>
       <c r="U191" t="n">
+        <v>9</v>
+      </c>
+      <c r="V191" t="n">
+        <v>10</v>
+      </c>
+      <c r="W191" t="n">
         <v>15</v>
       </c>
-      <c r="V191" t="n">
-        <v>5</v>
-      </c>
-      <c r="W191" t="n">
-        <v>12</v>
-      </c>
       <c r="X191" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y191" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Z191" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA191" t="inlineStr">
-        <is>
-          <t>Estadio Olímpico Pascual Guerrero</t>
-        </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>Carrera 36 entre Calles 5 y 5B3, Santiago de Cali</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="AA191" t="inlineStr"/>
+      <c r="AB191" t="inlineStr"/>
       <c r="AC191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE191" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="AH191" t="n">
         <v>1.36</v>
       </c>
-      <c r="AF191" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AG191" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AH191" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AI191" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AJ191" t="n">
-        <v>2.77</v>
+        <v>3.8</v>
       </c>
       <c r="AK191" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AL191" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AM191" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AN191" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AO191" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AR191" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AS191" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AT191" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AU191" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AV191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX191" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AY191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ191" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BA191" t="n">
         <v>1</v>
       </c>
       <c r="BB191" t="n">
-        <v>2141</v>
+        <v>2131</v>
       </c>
       <c r="BC191" t="n">
         <v>1</v>
       </c>
       <c r="BD191" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="BE191" t="n">
         <v>0</v>
       </c>
       <c r="BF191" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="BG191" t="n">
         <v>2</v>
@@ -84537,13 +84545,13 @@
         <v>1</v>
       </c>
       <c r="BI191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK191" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL191" t="n">
         <v>0</v>
@@ -84552,7 +84560,7 @@
         <v>4</v>
       </c>
       <c r="BN191" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO191" t="n">
         <v>0</v>
@@ -84561,10 +84569,10 @@
         <v>0</v>
       </c>
       <c r="BQ191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS191" t="n">
         <v>0</v>
@@ -84576,25 +84584,25 @@
         <v>1</v>
       </c>
       <c r="BV191" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BW191" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="BX191" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="BY191" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="BZ191" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="CA191" t="n">
-        <v>0.49</v>
+        <v>1.21</v>
       </c>
       <c r="CB191" t="n">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="CC191" t="n">
         <v>0</v>
@@ -84630,7 +84638,7 @@
         <v>0</v>
       </c>
       <c r="CN191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO191" t="n">
         <v>0</v>
@@ -84642,142 +84650,134 @@
         <v>1</v>
       </c>
       <c r="CR191" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CS191" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="CT191" t="n">
         <v>1</v>
       </c>
       <c r="CU191" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CV191" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CW191" t="n">
         <v>1</v>
       </c>
       <c r="CX191" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CY191" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="CZ191" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA191" t="n">
+        <v>83</v>
+      </c>
+      <c r="DB191" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC191" t="n">
+        <v>83</v>
+      </c>
+      <c r="DD191" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DE191" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DF191" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DG191" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DH191" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DI191" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DJ191" t="n">
         <v>44</v>
       </c>
-      <c r="DA191" t="n">
-        <v>67</v>
-      </c>
-      <c r="DB191" t="n">
-        <v>25</v>
-      </c>
-      <c r="DC191" t="n">
-        <v>75</v>
-      </c>
-      <c r="DD191" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="DE191" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="DF191" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DG191" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="DH191" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DI191" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="DJ191" t="n">
-        <v>56</v>
-      </c>
       <c r="DK191" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="DL191" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="DM191" t="n">
-        <v>0.97</v>
+        <v>1.34</v>
       </c>
       <c r="DN191" t="n">
-        <v>2.46</v>
+        <v>2.67</v>
       </c>
       <c r="DO191" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="DP191" t="b">
         <v>1</v>
       </c>
       <c r="DQ191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW191" t="inlineStr"/>
       <c r="DX191" t="inlineStr"/>
       <c r="DY191" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="DZ191" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="EA191" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="EB191" t="inlineStr"/>
       <c r="EC191" t="inlineStr"/>
       <c r="ED191" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="EE191" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EF191" t="inlineStr">
         <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EG191" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EH191" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EG191" t="inlineStr"/>
+      <c r="EH191" t="inlineStr"/>
       <c r="EI191" t="inlineStr"/>
       <c r="EJ191" t="inlineStr"/>
     </row>
@@ -85119,7 +85119,7 @@
         <v>1.33</v>
       </c>
       <c r="DE192" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DF192" t="n">
         <v>1.47</v>
@@ -85542,7 +85542,7 @@
         <v>71</v>
       </c>
       <c r="DD193" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DE193" t="n">
         <v>1.62</v>
@@ -85975,7 +85975,7 @@
         <v>1.62</v>
       </c>
       <c r="DE194" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DF194" t="n">
         <v>1.74</v>
@@ -86405,7 +86405,7 @@
         <v>1.62</v>
       </c>
       <c r="DE195" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DF195" t="n">
         <v>1.74</v>
@@ -86840,7 +86840,7 @@
         <v>70</v>
       </c>
       <c r="DD196" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DE196" t="n">
         <v>1.33</v>
@@ -87270,7 +87270,7 @@
         <v>70</v>
       </c>
       <c r="DD197" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DE197" t="n">
         <v>1.62</v>
@@ -87703,7 +87703,7 @@
         <v>1.62</v>
       </c>
       <c r="DE198" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DF198" t="n">
         <v>1.7</v>
@@ -88130,7 +88130,7 @@
         <v>83</v>
       </c>
       <c r="DD199" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DE199" t="n">
         <v>1.62</v>
@@ -88568,10 +88568,10 @@
         <v>74</v>
       </c>
       <c r="DD200" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DE200" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DF200" t="n">
         <v>1.76</v>
@@ -88601,7 +88601,7 @@
         <v>3.12</v>
       </c>
       <c r="DO200" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP200" t="b">
         <v>1</v>
@@ -89006,10 +89006,10 @@
         <v>79</v>
       </c>
       <c r="DD201" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DE201" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DF201" t="n">
         <v>1.57</v>
@@ -89039,7 +89039,7 @@
         <v>2.75</v>
       </c>
       <c r="DO201" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP201" t="b">
         <v>1</v>
@@ -89089,6 +89089,882 @@
       <c r="EI201" t="inlineStr"/>
       <c r="EJ201" t="inlineStr"/>
     </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>0</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="F202" s="1" t="n">
+        <v>46165.95833333334</v>
+      </c>
+      <c r="G202" t="n">
+        <v>3</v>
+      </c>
+      <c r="H202" t="n">
+        <v>1</v>
+      </c>
+      <c r="I202" t="n">
+        <v>4</v>
+      </c>
+      <c r="J202" t="n">
+        <v>7</v>
+      </c>
+      <c r="K202" t="n">
+        <v>4</v>
+      </c>
+      <c r="L202" t="n">
+        <v>11</v>
+      </c>
+      <c r="M202" t="n">
+        <v>2</v>
+      </c>
+      <c r="N202" t="n">
+        <v>1</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>7</v>
+      </c>
+      <c r="R202" t="n">
+        <v>3</v>
+      </c>
+      <c r="S202" t="n">
+        <v>16</v>
+      </c>
+      <c r="T202" t="n">
+        <v>11</v>
+      </c>
+      <c r="U202" t="n">
+        <v>23</v>
+      </c>
+      <c r="V202" t="n">
+        <v>14</v>
+      </c>
+      <c r="W202" t="n">
+        <v>15</v>
+      </c>
+      <c r="X202" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>Estadio Atanasio Girardot</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
+        </is>
+      </c>
+      <c r="AC202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ202" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR202" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS202" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT202" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU202" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX202" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB202" t="n">
+        <v>2142</v>
+      </c>
+      <c r="BC202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF202" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG202" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI202" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ202" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK202" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL202" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM202" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN202" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO202" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS202" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV202" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW202" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX202" t="n">
+        <v>71</v>
+      </c>
+      <c r="BY202" t="n">
+        <v>68</v>
+      </c>
+      <c r="BZ202" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CA202" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CB202" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CC202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI202" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ202" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO202" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ202" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR202" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS202" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT202" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU202" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV202" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW202" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX202" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY202" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ202" t="n">
+        <v>46</v>
+      </c>
+      <c r="DA202" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB202" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC202" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD202" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="DE202" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DF202" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DG202" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DH202" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DI202" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DJ202" t="n">
+        <v>55</v>
+      </c>
+      <c r="DK202" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL202" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DM202" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DN202" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="DO202" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP202" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ202" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR202" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS202" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT202" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU202" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV202" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW202" t="inlineStr"/>
+      <c r="DX202" t="inlineStr"/>
+      <c r="DY202" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="DZ202" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EA202" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EB202" t="inlineStr"/>
+      <c r="EC202" t="inlineStr"/>
+      <c r="ED202" t="inlineStr">
+        <is>
+          <t>4.74</t>
+        </is>
+      </c>
+      <c r="EE202" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="EF202" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EG202" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EH202" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EI202" t="inlineStr"/>
+      <c r="EJ202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F203" s="1" t="n">
+        <v>46166.0625</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>7</v>
+      </c>
+      <c r="K203" t="n">
+        <v>3</v>
+      </c>
+      <c r="L203" t="n">
+        <v>10</v>
+      </c>
+      <c r="M203" t="n">
+        <v>2</v>
+      </c>
+      <c r="N203" t="n">
+        <v>3</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>6</v>
+      </c>
+      <c r="R203" t="n">
+        <v>2</v>
+      </c>
+      <c r="S203" t="n">
+        <v>18</v>
+      </c>
+      <c r="T203" t="n">
+        <v>2</v>
+      </c>
+      <c r="U203" t="n">
+        <v>24</v>
+      </c>
+      <c r="V203" t="n">
+        <v>4</v>
+      </c>
+      <c r="W203" t="n">
+        <v>14</v>
+      </c>
+      <c r="X203" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>Estadio Metropolitano Roberto Meléndez</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>Intersección de la Avenida Circunvalar con la Calle 45, Barranquilla</t>
+        </is>
+      </c>
+      <c r="AC203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ203" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR203" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS203" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT203" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA203" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB203" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC203" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD203" t="n">
+        <v>66</v>
+      </c>
+      <c r="BE203" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF203" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG203" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH203" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI203" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ203" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK203" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL203" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM203" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN203" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO203" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP203" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ203" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR203" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS203" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT203" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU203" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV203" t="n">
+        <v>69</v>
+      </c>
+      <c r="BW203" t="n">
+        <v>15</v>
+      </c>
+      <c r="BX203" t="n">
+        <v>129</v>
+      </c>
+      <c r="BY203" t="n">
+        <v>68</v>
+      </c>
+      <c r="BZ203" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CA203" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="CB203" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="CC203" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD203" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE203" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF203" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG203" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH203" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI203" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ203" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK203" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL203" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM203" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN203" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO203" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP203" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ203" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR203" t="n">
+        <v>30</v>
+      </c>
+      <c r="CS203" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT203" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU203" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV203" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW203" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX203" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY203" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ203" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA203" t="n">
+        <v>89</v>
+      </c>
+      <c r="DB203" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC203" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD203" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DE203" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DF203" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DG203" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DH203" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DI203" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DJ203" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK203" t="n">
+        <v>12</v>
+      </c>
+      <c r="DL203" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DM203" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DN203" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="DO203" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP203" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ203" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR203" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS203" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT203" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU203" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV203" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW203" t="inlineStr"/>
+      <c r="DX203" t="inlineStr"/>
+      <c r="DY203" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="DZ203" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EA203" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="EB203" t="inlineStr"/>
+      <c r="EC203" t="inlineStr"/>
+      <c r="ED203" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="EE203" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EF203" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EG203" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH203" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EI203" t="inlineStr"/>
+      <c r="EJ203" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -89274,7 +89274,7 @@
         <v>0</v>
       </c>
       <c r="BF202" t="n">
-        <v>-1</v>
+        <v>43103</v>
       </c>
       <c r="BG202" t="n">
         <v>2</v>
@@ -89712,7 +89712,7 @@
         <v>0</v>
       </c>
       <c r="BF203" t="n">
-        <v>-1</v>
+        <v>11000</v>
       </c>
       <c r="BG203" t="n">
         <v>2</v>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -595,8 +595,8 @@
     <col width="16.8" customWidth="1" min="24" max="24"/>
     <col width="22.8" customWidth="1" min="25" max="25"/>
     <col width="22.8" customWidth="1" min="26" max="26"/>
-    <col width="48" customWidth="1" min="27" max="27"/>
-    <col width="50" customWidth="1" min="28" max="28"/>
+    <col width="16.8" customWidth="1" min="27" max="27"/>
+    <col width="21.6" customWidth="1" min="28" max="28"/>
     <col width="21.6" customWidth="1" min="29" max="29"/>
     <col width="21.6" customWidth="1" min="30" max="30"/>
     <col width="18" customWidth="1" min="31" max="31"/>
@@ -1500,16 +1500,8 @@
       <c r="Z2" t="n">
         <v>39</v>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Estadio Hernán Ramírez Villegas</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Villa Olímpica Pereira, Pereira</t>
-        </is>
-      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
         <v>4</v>
       </c>
@@ -1938,16 +1930,8 @@
       <c r="Z3" t="n">
         <v>41</v>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
         <v>1</v>
       </c>
@@ -2384,16 +2368,8 @@
       <c r="Z4" t="n">
         <v>43</v>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Estadio Olímpico Pascual Guerrero</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Carrera 36 entre Calles 5 y 5B3, Santiago de Cali</t>
-        </is>
-      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
         <v>5</v>
       </c>
@@ -2790,16 +2766,8 @@
       <c r="Z5" t="n">
         <v>40</v>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
         <v>3</v>
       </c>
@@ -3236,16 +3204,8 @@
       <c r="Z6" t="n">
         <v>42</v>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Estadio Alfonso López</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Carrera 36 Nº 53-12, Cabecera del Llano, Bucaramanga</t>
-        </is>
-      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
         <v>3</v>
       </c>
@@ -3674,16 +3634,8 @@
       <c r="Z7" t="n">
         <v>57</v>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Estadio Departamental Libertad</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Carrera 8, San Juan de Pasto</t>
-        </is>
-      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
         <v>3</v>
       </c>
@@ -4112,16 +4064,8 @@
       <c r="Z8" t="n">
         <v>55</v>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Estadio de Fútbol Jaraguay de Montería</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>, Montería</t>
-        </is>
-      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
         <v>3</v>
       </c>
@@ -4558,16 +4502,8 @@
       <c r="Z9" t="n">
         <v>33</v>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano Roberto Meléndez</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Intersección de la Avenida Circunvalar con la Calle 45, Barranquilla</t>
-        </is>
-      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
         <v>3</v>
       </c>
@@ -4996,16 +4932,8 @@
       <c r="Z10" t="n">
         <v>37</v>
       </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
         <v>2</v>
       </c>
@@ -5434,16 +5362,8 @@
       <c r="Z11" t="n">
         <v>64</v>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Estadio General Santander</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Avenida 0A 3-56, Barrio Lleras Restrepo, Cúcuta</t>
-        </is>
-      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
         <v>5</v>
       </c>
@@ -5880,16 +5800,8 @@
       <c r="Z12" t="n">
         <v>38</v>
       </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
         <v>5</v>
       </c>
@@ -6298,16 +6210,8 @@
       <c r="Z13" t="n">
         <v>39</v>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Murillo Toro</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
-        </is>
-      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
         <v>2</v>
       </c>
@@ -6744,16 +6648,8 @@
       <c r="Z14" t="n">
         <v>62</v>
       </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Estadio Hernán Ramírez Villegas</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Villa Olímpica Pereira, Pereira</t>
-        </is>
-      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
         <v>1</v>
       </c>
@@ -7182,16 +7078,8 @@
       <c r="Z15" t="n">
         <v>56</v>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Calle Lombana</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>, Villavicencio</t>
-        </is>
-      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
         <v>4</v>
       </c>
@@ -7636,16 +7524,8 @@
       <c r="Z16" t="n">
         <v>20</v>
       </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Estadio Deportivo Cali</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>BN 25, Palmira</t>
-        </is>
-      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
         <v>5</v>
       </c>
@@ -8504,16 +8384,8 @@
       <c r="Z18" t="n">
         <v>54</v>
       </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Estadio Alberto Grisales</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Route 45A, Rionegro, Antioquia</t>
-        </is>
-      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
         <v>3</v>
       </c>
@@ -8942,16 +8814,8 @@
       <c r="Z19" t="n">
         <v>43</v>
       </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
         <v>3</v>
       </c>
@@ -9380,16 +9244,8 @@
       <c r="Z20" t="n">
         <v>41</v>
       </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>Estadio Palogrande</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>Carrera 24 # 64 - 00, Manizales</t>
-        </is>
-      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
         <v>2</v>
       </c>
@@ -9818,16 +9674,8 @@
       <c r="Z21" t="n">
         <v>52</v>
       </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>Estadio General Santander</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>Avenida 0A 3-56, Barrio Lleras Restrepo, Cúcuta</t>
-        </is>
-      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
         <v>3</v>
       </c>
@@ -10264,16 +10112,8 @@
       <c r="Z22" t="n">
         <v>46</v>
       </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
         <v>4</v>
       </c>
@@ -10710,16 +10550,8 @@
       <c r="Z23" t="n">
         <v>32</v>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
         <v>2</v>
       </c>
@@ -11148,16 +10980,8 @@
       <c r="Z24" t="n">
         <v>35</v>
       </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Estadio Armando Maestre Pavajeau</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>, Valledupar</t>
-        </is>
-      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
         <v>4</v>
       </c>
@@ -11586,16 +11410,8 @@
       <c r="Z25" t="n">
         <v>38</v>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
         <v>6</v>
       </c>
@@ -12032,16 +11848,8 @@
       <c r="Z26" t="n">
         <v>31</v>
       </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Estadio Departamental Libertad</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>Carrera 8, San Juan de Pasto</t>
-        </is>
-      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
         <v>3</v>
       </c>
@@ -12470,16 +12278,8 @@
       <c r="Z27" t="n">
         <v>48</v>
       </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>Estadio Alberto Grisales</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>Route 45A, Rionegro, Antioquia</t>
-        </is>
-      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
         <v>2</v>
       </c>
@@ -12908,16 +12708,8 @@
       <c r="Z28" t="n">
         <v>35</v>
       </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>Estadio de Fútbol Jaraguay de Montería</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>, Montería</t>
-        </is>
-      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
         <v>2</v>
       </c>
@@ -13354,16 +13146,8 @@
       <c r="Z29" t="n">
         <v>40</v>
       </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Estadio Olímpico Pascual Guerrero</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>Carrera 36 entre Calles 5 y 5B3, Santiago de Cali</t>
-        </is>
-      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
         <v>4</v>
       </c>
@@ -13800,16 +13584,8 @@
       <c r="Z30" t="n">
         <v>60</v>
       </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>Estadio General Santander</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>Avenida 0A 3-56, Barrio Lleras Restrepo, Cúcuta</t>
-        </is>
-      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
         <v>4</v>
       </c>
@@ -14676,16 +14452,8 @@
       <c r="Z32" t="n">
         <v>48</v>
       </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>Estadio Alfonso López</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>Carrera 36 Nº 53-12, Cabecera del Llano, Bucaramanga</t>
-        </is>
-      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
         <v>3</v>
       </c>
@@ -15114,16 +14882,8 @@
       <c r="Z33" t="n">
         <v>52</v>
       </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Estadio Deportivo Cali</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>BN 25, Palmira</t>
-        </is>
-      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
         <v>5</v>
       </c>
@@ -15560,16 +15320,8 @@
       <c r="Z34" t="n">
         <v>34</v>
       </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Estadio Palogrande</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>Carrera 24 # 64 - 00, Manizales</t>
-        </is>
-      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
         <v>5</v>
       </c>
@@ -15998,16 +15750,8 @@
       <c r="Z35" t="n">
         <v>62</v>
       </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Calle Lombana</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>, Villavicencio</t>
-        </is>
-      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
         <v>2</v>
       </c>
@@ -16436,16 +16180,8 @@
       <c r="Z36" t="n">
         <v>49</v>
       </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
         <v>7</v>
       </c>
@@ -16874,16 +16610,8 @@
       <c r="Z37" t="n">
         <v>46</v>
       </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
         <v>3</v>
       </c>
@@ -17320,16 +17048,8 @@
       <c r="Z38" t="n">
         <v>63</v>
       </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>Estadio Hernán Ramírez Villegas</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>Villa Olímpica Pereira, Pereira</t>
-        </is>
-      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
         <v>5</v>
       </c>
@@ -17758,16 +17478,8 @@
       <c r="Z39" t="n">
         <v>53</v>
       </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
         <v>3</v>
       </c>
@@ -18196,16 +17908,8 @@
       <c r="Z40" t="n">
         <v>56</v>
       </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>Estadio Departamental Libertad</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>Carrera 8, San Juan de Pasto</t>
-        </is>
-      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
         <v>4</v>
       </c>
@@ -18630,16 +18334,8 @@
       <c r="Z41" t="n">
         <v>36</v>
       </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
         <v>1</v>
       </c>
@@ -19068,16 +18764,8 @@
       <c r="Z42" t="n">
         <v>57</v>
       </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>Estadio Alberto Grisales</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>Route 45A, Rionegro, Antioquia</t>
-        </is>
-      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
         <v>2</v>
       </c>
@@ -19506,16 +19194,8 @@
       <c r="Z43" t="n">
         <v>36</v>
       </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Murillo Toro</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
-        </is>
-      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
         <v>0</v>
       </c>
@@ -19944,16 +19624,8 @@
       <c r="Z44" t="n">
         <v>41</v>
       </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
         <v>5</v>
       </c>
@@ -20362,16 +20034,8 @@
       <c r="Z45" t="n">
         <v>39</v>
       </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano Roberto Meléndez</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>Intersección de la Avenida Circunvalar con la Calle 45, Barranquilla</t>
-        </is>
-      </c>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
         <v>1</v>
       </c>
@@ -20800,16 +20464,8 @@
       <c r="Z46" t="n">
         <v>42</v>
       </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>Estadio Armando Maestre Pavajeau</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>, Valledupar</t>
-        </is>
-      </c>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
         <v>5</v>
       </c>
@@ -21246,16 +20902,8 @@
       <c r="Z47" t="n">
         <v>40</v>
       </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Estadio Deportivo Cali</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>BN 25, Palmira</t>
-        </is>
-      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
         <v>1</v>
       </c>
@@ -21672,16 +21320,8 @@
       <c r="Z48" t="n">
         <v>51</v>
       </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>Estadio de Fútbol Jaraguay de Montería</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>, Montería</t>
-        </is>
-      </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
         <v>3</v>
       </c>
@@ -22118,16 +21758,8 @@
       <c r="Z49" t="n">
         <v>54</v>
       </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>Estadio General Santander</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>Avenida 0A 3-56, Barrio Lleras Restrepo, Cúcuta</t>
-        </is>
-      </c>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
         <v>3</v>
       </c>
@@ -22564,16 +22196,8 @@
       <c r="Z50" t="n">
         <v>50</v>
       </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Calle Lombana</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>, Villavicencio</t>
-        </is>
-      </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
         <v>4</v>
       </c>
@@ -23010,16 +22634,8 @@
       <c r="Z51" t="n">
         <v>56</v>
       </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>Estadio Alfonso López</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>Carrera 36 Nº 53-12, Cabecera del Llano, Bucaramanga</t>
-        </is>
-      </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
         <v>4</v>
       </c>
@@ -23456,16 +23072,8 @@
       <c r="Z52" t="n">
         <v>42</v>
       </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
         <v>5</v>
       </c>
@@ -23902,16 +23510,8 @@
       <c r="Z53" t="n">
         <v>56</v>
       </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
         <v>5</v>
       </c>
@@ -24786,16 +24386,8 @@
       <c r="Z55" t="n">
         <v>52</v>
       </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>Estadio Palogrande</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>Carrera 24 # 64 - 00, Manizales</t>
-        </is>
-      </c>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
         <v>2</v>
       </c>
@@ -25232,16 +24824,8 @@
       <c r="Z56" t="n">
         <v>45</v>
       </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
         <v>2</v>
       </c>
@@ -25670,16 +25254,8 @@
       <c r="Z57" t="n">
         <v>39</v>
       </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>Estadio Olímpico Pascual Guerrero</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>Carrera 36 entre Calles 5 y 5B3, Santiago de Cali</t>
-        </is>
-      </c>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
         <v>5</v>
       </c>
@@ -26116,16 +25692,8 @@
       <c r="Z58" t="n">
         <v>63</v>
       </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
         <v>4</v>
       </c>
@@ -26562,16 +26130,8 @@
       <c r="Z59" t="n">
         <v>33</v>
       </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
         <v>3</v>
       </c>
@@ -27016,16 +26576,8 @@
       <c r="Z60" t="n">
         <v>39</v>
       </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>Estadio Departamental Libertad</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>Carrera 8, San Juan de Pasto</t>
-        </is>
-      </c>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
         <v>0</v>
       </c>
@@ -27462,16 +27014,8 @@
       <c r="Z61" t="n">
         <v>41</v>
       </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Murillo Toro</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
-        </is>
-      </c>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
         <v>2</v>
       </c>
@@ -27900,16 +27444,8 @@
       <c r="Z62" t="n">
         <v>59</v>
       </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>Estadio Deportivo Cali</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>BN 25, Palmira</t>
-        </is>
-      </c>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
         <v>4</v>
       </c>
@@ -28338,16 +27874,8 @@
       <c r="Z63" t="n">
         <v>37</v>
       </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
         <v>2</v>
       </c>
@@ -28776,16 +28304,8 @@
       <c r="Z64" t="n">
         <v>46</v>
       </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>Estadio Armando Maestre Pavajeau</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>, Valledupar</t>
-        </is>
-      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
         <v>3</v>
       </c>
@@ -29214,16 +28734,8 @@
       <c r="Z65" t="n">
         <v>60</v>
       </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>Estadio de Fútbol Jaraguay de Montería</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>, Montería</t>
-        </is>
-      </c>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
         <v>5</v>
       </c>
@@ -29648,16 +29160,8 @@
       <c r="Z66" t="n">
         <v>48</v>
       </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano Roberto Meléndez</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>Intersección de la Avenida Circunvalar con la Calle 45, Barranquilla</t>
-        </is>
-      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
@@ -30086,16 +29590,8 @@
       <c r="Z67" t="n">
         <v>37</v>
       </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Calle Lombana</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>, Villavicencio</t>
-        </is>
-      </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
         <v>1</v>
       </c>
@@ -30532,16 +30028,8 @@
       <c r="Z68" t="n">
         <v>58</v>
       </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>Estadio Hernán Ramírez Villegas</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>Villa Olímpica Pereira, Pereira</t>
-        </is>
-      </c>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
         <v>3</v>
       </c>
@@ -30978,16 +30466,8 @@
       <c r="Z69" t="n">
         <v>41</v>
       </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>Estadio Palogrande</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>Carrera 24 # 64 - 00, Manizales</t>
-        </is>
-      </c>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
         <v>5</v>
       </c>
@@ -31416,16 +30896,8 @@
       <c r="Z70" t="n">
         <v>39</v>
       </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>Estadio Alfonso López</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>Carrera 36 Nº 53-12, Cabecera del Llano, Bucaramanga</t>
-        </is>
-      </c>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
@@ -31854,16 +31326,8 @@
       <c r="Z71" t="n">
         <v>48</v>
       </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
         <v>4</v>
       </c>
@@ -32292,16 +31756,8 @@
       <c r="Z72" t="n">
         <v>49</v>
       </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
         <v>4</v>
       </c>
@@ -32738,16 +32194,8 @@
       <c r="Z73" t="n">
         <v>57</v>
       </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
         <v>4</v>
       </c>
@@ -33606,16 +33054,8 @@
       <c r="Z75" t="n">
         <v>36</v>
       </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>Estadio Olímpico Pascual Guerrero</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>Carrera 36 entre Calles 5 y 5B3, Santiago de Cali</t>
-        </is>
-      </c>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
         <v>3</v>
       </c>
@@ -34044,16 +33484,8 @@
       <c r="Z76" t="n">
         <v>62</v>
       </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>Estadio General Santander</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>Avenida 0A 3-56, Barrio Lleras Restrepo, Cúcuta</t>
-        </is>
-      </c>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
@@ -34490,16 +33922,8 @@
       <c r="Z77" t="n">
         <v>60</v>
       </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
         <v>3</v>
       </c>
@@ -34928,16 +34352,8 @@
       <c r="Z78" t="n">
         <v>45</v>
       </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
         <v>1</v>
       </c>
@@ -35366,16 +34782,8 @@
       <c r="Z79" t="n">
         <v>38</v>
       </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>Estadio Palogrande</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>Carrera 24 # 64 - 00, Manizales</t>
-        </is>
-      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
         <v>2</v>
       </c>
@@ -35812,16 +35220,8 @@
       <c r="Z80" t="n">
         <v>58</v>
       </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>Estadio Armando Maestre Pavajeau</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>, Valledupar</t>
-        </is>
-      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
         <v>5</v>
       </c>
@@ -36258,16 +35658,8 @@
       <c r="Z81" t="n">
         <v>43</v>
       </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>Estadio de Fútbol Jaraguay de Montería</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>, Montería</t>
-        </is>
-      </c>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
         <v>4</v>
       </c>
@@ -36704,16 +36096,8 @@
       <c r="Z82" t="n">
         <v>42</v>
       </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
@@ -37150,16 +36534,8 @@
       <c r="Z83" t="n">
         <v>47</v>
       </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>Estadio Departamental Libertad</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>Carrera 8, San Juan de Pasto</t>
-        </is>
-      </c>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
         <v>0</v>
       </c>
@@ -37588,16 +36964,8 @@
       <c r="Z84" t="n">
         <v>48</v>
       </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>Estadio Alberto Grisales</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>Route 45A, Rionegro, Antioquia</t>
-        </is>
-      </c>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
         <v>4</v>
       </c>
@@ -38026,16 +37394,8 @@
       <c r="Z85" t="n">
         <v>57</v>
       </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>Estadio Deportivo Cali</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>BN 25, Palmira</t>
-        </is>
-      </c>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
         <v>1</v>
       </c>
@@ -38464,16 +37824,8 @@
       <c r="Z86" t="n">
         <v>37</v>
       </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Murillo Toro</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
-        </is>
-      </c>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
         <v>4</v>
       </c>
@@ -38902,16 +38254,8 @@
       <c r="Z87" t="n">
         <v>39</v>
       </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
         <v>3</v>
       </c>
@@ -39340,16 +38684,8 @@
       <c r="Z88" t="n">
         <v>40</v>
       </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Calle Lombana</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>, Villavicencio</t>
-        </is>
-      </c>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
         <v>4</v>
       </c>
@@ -39786,16 +39122,8 @@
       <c r="Z89" t="n">
         <v>34</v>
       </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano Roberto Meléndez</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>Intersección de la Avenida Circunvalar con la Calle 45, Barranquilla</t>
-        </is>
-      </c>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
         <v>3</v>
       </c>
@@ -40232,16 +39560,8 @@
       <c r="Z90" t="n">
         <v>38</v>
       </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>Estadio Deportivo Cali</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>BN 25, Palmira</t>
-        </is>
-      </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
         <v>6</v>
       </c>
@@ -40678,16 +39998,8 @@
       <c r="Z91" t="n">
         <v>65</v>
       </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>Estadio Alberto Grisales</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>Route 45A, Rionegro, Antioquia</t>
-        </is>
-      </c>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="n">
         <v>3</v>
       </c>
@@ -41116,16 +40428,8 @@
       <c r="Z92" t="n">
         <v>51</v>
       </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Calle Lombana</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>, Villavicencio</t>
-        </is>
-      </c>
+      <c r="AA92" t="inlineStr"/>
+      <c r="AB92" t="inlineStr"/>
       <c r="AC92" t="n">
         <v>2</v>
       </c>
@@ -41570,16 +40874,8 @@
       <c r="Z93" t="n">
         <v>55</v>
       </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="n">
         <v>2</v>
       </c>
@@ -42016,16 +41312,8 @@
       <c r="Z94" t="n">
         <v>68</v>
       </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>Estadio Departamental Libertad</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>Carrera 8, San Juan de Pasto</t>
-        </is>
-      </c>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
@@ -42454,16 +41742,8 @@
       <c r="Z95" t="n">
         <v>46</v>
       </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>Estadio Alfonso López</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>Carrera 36 Nº 53-12, Cabecera del Llano, Bucaramanga</t>
-        </is>
-      </c>
+      <c r="AA95" t="inlineStr"/>
+      <c r="AB95" t="inlineStr"/>
       <c r="AC95" t="n">
         <v>1</v>
       </c>
@@ -42900,16 +42180,8 @@
       <c r="Z96" t="n">
         <v>67</v>
       </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano Roberto Meléndez</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>Intersección de la Avenida Circunvalar con la Calle 45, Barranquilla</t>
-        </is>
-      </c>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="n">
         <v>2</v>
       </c>
@@ -43338,16 +42610,8 @@
       <c r="Z97" t="n">
         <v>44</v>
       </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>Estadio Palogrande</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>Carrera 24 # 64 - 00, Manizales</t>
-        </is>
-      </c>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="n">
         <v>1</v>
       </c>
@@ -43776,16 +43040,8 @@
       <c r="Z98" t="n">
         <v>44</v>
       </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="n">
         <v>1</v>
       </c>
@@ -44222,16 +43478,8 @@
       <c r="Z99" t="n">
         <v>49</v>
       </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="n">
         <v>2</v>
       </c>
@@ -44668,16 +43916,8 @@
       <c r="Z100" t="n">
         <v>34</v>
       </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>Estadio General Santander</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>Avenida 0A 3-56, Barrio Lleras Restrepo, Cúcuta</t>
-        </is>
-      </c>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="n">
         <v>3</v>
       </c>
@@ -45544,16 +44784,8 @@
       <c r="Z102" t="n">
         <v>45</v>
       </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA102" t="inlineStr"/>
+      <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="n">
         <v>2</v>
       </c>
@@ -45982,16 +45214,8 @@
       <c r="Z103" t="n">
         <v>44</v>
       </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>Estadio Hernán Ramírez Villegas</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>Villa Olímpica Pereira, Pereira</t>
-        </is>
-      </c>
+      <c r="AA103" t="inlineStr"/>
+      <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="n">
         <v>2</v>
       </c>
@@ -46428,16 +45652,8 @@
       <c r="Z104" t="n">
         <v>45</v>
       </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>Estadio Olímpico Pascual Guerrero</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>Carrera 36 entre Calles 5 y 5B3, Santiago de Cali</t>
-        </is>
-      </c>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="n">
         <v>3</v>
       </c>
@@ -46874,16 +46090,8 @@
       <c r="Z105" t="n">
         <v>70</v>
       </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>Estadio de Fútbol Jaraguay de Montería</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>, Montería</t>
-        </is>
-      </c>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr"/>
       <c r="AC105" t="n">
         <v>4</v>
       </c>
@@ -47312,16 +46520,8 @@
       <c r="Z106" t="n">
         <v>46</v>
       </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano Roberto Meléndez</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>Intersección de la Avenida Circunvalar con la Calle 45, Barranquilla</t>
-        </is>
-      </c>
+      <c r="AA106" t="inlineStr"/>
+      <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="n">
         <v>3</v>
       </c>
@@ -47750,16 +46950,8 @@
       <c r="Z107" t="n">
         <v>46</v>
       </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Calle Lombana</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>, Villavicencio</t>
-        </is>
-      </c>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="n">
         <v>3</v>
       </c>
@@ -48196,16 +47388,8 @@
       <c r="Z108" t="n">
         <v>51</v>
       </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="n">
         <v>2</v>
       </c>
@@ -48634,16 +47818,8 @@
       <c r="Z109" t="n">
         <v>32</v>
       </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>Estadio Departamental Libertad</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>Carrera 8, San Juan de Pasto</t>
-        </is>
-      </c>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr"/>
       <c r="AC109" t="n">
         <v>2</v>
       </c>
@@ -49080,16 +48256,8 @@
       <c r="Z110" t="n">
         <v>28</v>
       </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr"/>
       <c r="AC110" t="n">
         <v>1</v>
       </c>
@@ -49526,16 +48694,8 @@
       <c r="Z111" t="n">
         <v>37</v>
       </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>Estadio Alfonso López</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>Carrera 36 Nº 53-12, Cabecera del Llano, Bucaramanga</t>
-        </is>
-      </c>
+      <c r="AA111" t="inlineStr"/>
+      <c r="AB111" t="inlineStr"/>
       <c r="AC111" t="n">
         <v>1</v>
       </c>
@@ -49964,16 +49124,8 @@
       <c r="Z112" t="n">
         <v>52</v>
       </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>Estadio Deportivo Cali</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>BN 25, Palmira</t>
-        </is>
-      </c>
+      <c r="AA112" t="inlineStr"/>
+      <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="n">
         <v>4</v>
       </c>
@@ -50402,16 +49554,8 @@
       <c r="Z113" t="n">
         <v>64</v>
       </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>Estadio Armando Maestre Pavajeau</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>, Valledupar</t>
-        </is>
-      </c>
+      <c r="AA113" t="inlineStr"/>
+      <c r="AB113" t="inlineStr"/>
       <c r="AC113" t="n">
         <v>3</v>
       </c>
@@ -50848,16 +49992,8 @@
       <c r="Z114" t="n">
         <v>32</v>
       </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Murillo Toro</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
-        </is>
-      </c>
+      <c r="AA114" t="inlineStr"/>
+      <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="n">
         <v>2</v>
       </c>
@@ -51294,16 +50430,8 @@
       <c r="Z115" t="n">
         <v>59</v>
       </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="n">
         <v>3</v>
       </c>
@@ -51732,16 +50860,8 @@
       <c r="Z116" t="n">
         <v>41</v>
       </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>Estadio Alberto Grisales</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>Route 45A, Rionegro, Antioquia</t>
-        </is>
-      </c>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr"/>
       <c r="AC116" t="n">
         <v>3</v>
       </c>
@@ -52186,16 +51306,8 @@
       <c r="Z117" t="n">
         <v>32</v>
       </c>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t>Estadio Palogrande</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>Carrera 24 # 64 - 00, Manizales</t>
-        </is>
-      </c>
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr"/>
       <c r="AC117" t="n">
         <v>2</v>
       </c>
@@ -52632,16 +51744,8 @@
       <c r="Z118" t="n">
         <v>29</v>
       </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA118" t="inlineStr"/>
+      <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="n">
         <v>3</v>
       </c>
@@ -53078,16 +52182,8 @@
       <c r="Z119" t="n">
         <v>60</v>
       </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>Estadio Armando Maestre Pavajeau</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>, Valledupar</t>
-        </is>
-      </c>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="n">
         <v>2</v>
       </c>
@@ -53954,16 +53050,8 @@
       <c r="Z121" t="n">
         <v>51</v>
       </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA121" t="inlineStr"/>
+      <c r="AB121" t="inlineStr"/>
       <c r="AC121" t="n">
         <v>3</v>
       </c>
@@ -54392,16 +53480,8 @@
       <c r="Z122" t="n">
         <v>53</v>
       </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>Estadio de Fútbol Jaraguay de Montería</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>, Montería</t>
-        </is>
-      </c>
+      <c r="AA122" t="inlineStr"/>
+      <c r="AB122" t="inlineStr"/>
       <c r="AC122" t="n">
         <v>1</v>
       </c>
@@ -54838,16 +53918,8 @@
       <c r="Z123" t="n">
         <v>60</v>
       </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>Estadio Hernán Ramírez Villegas</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>Villa Olímpica Pereira, Pereira</t>
-        </is>
-      </c>
+      <c r="AA123" t="inlineStr"/>
+      <c r="AB123" t="inlineStr"/>
       <c r="AC123" t="n">
         <v>2</v>
       </c>
@@ -55276,16 +54348,8 @@
       <c r="Z124" t="n">
         <v>41</v>
       </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano Roberto Meléndez</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>Intersección de la Avenida Circunvalar con la Calle 45, Barranquilla</t>
-        </is>
-      </c>
+      <c r="AA124" t="inlineStr"/>
+      <c r="AB124" t="inlineStr"/>
       <c r="AC124" t="n">
         <v>2</v>
       </c>
@@ -55714,16 +54778,8 @@
       <c r="Z125" t="n">
         <v>45</v>
       </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA125" t="inlineStr"/>
+      <c r="AB125" t="inlineStr"/>
       <c r="AC125" t="n">
         <v>2</v>
       </c>
@@ -56152,16 +55208,8 @@
       <c r="Z126" t="n">
         <v>35</v>
       </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>Estadio Olímpico Pascual Guerrero</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>Carrera 36 entre Calles 5 y 5B3, Santiago de Cali</t>
-        </is>
-      </c>
+      <c r="AA126" t="inlineStr"/>
+      <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="n">
         <v>2</v>
       </c>
@@ -56590,16 +55638,8 @@
       <c r="Z127" t="n">
         <v>45</v>
       </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>Estadio Alberto Grisales</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>Route 45A, Rionegro, Antioquia</t>
-        </is>
-      </c>
+      <c r="AA127" t="inlineStr"/>
+      <c r="AB127" t="inlineStr"/>
       <c r="AC127" t="n">
         <v>3</v>
       </c>
@@ -57028,16 +56068,8 @@
       <c r="Z128" t="n">
         <v>42</v>
       </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>Estadio Alfonso López</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>Carrera 36 Nº 53-12, Cabecera del Llano, Bucaramanga</t>
-        </is>
-      </c>
+      <c r="AA128" t="inlineStr"/>
+      <c r="AB128" t="inlineStr"/>
       <c r="AC128" t="n">
         <v>4</v>
       </c>
@@ -57466,16 +56498,8 @@
       <c r="Z129" t="n">
         <v>64</v>
       </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>Estadio General Santander</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>Avenida 0A 3-56, Barrio Lleras Restrepo, Cúcuta</t>
-        </is>
-      </c>
+      <c r="AA129" t="inlineStr"/>
+      <c r="AB129" t="inlineStr"/>
       <c r="AC129" t="n">
         <v>6</v>
       </c>
@@ -57896,16 +56920,8 @@
       <c r="Z130" t="n">
         <v>35</v>
       </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Murillo Toro</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
-        </is>
-      </c>
+      <c r="AA130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr"/>
       <c r="AC130" t="n">
         <v>3</v>
       </c>
@@ -58326,16 +57342,8 @@
       <c r="Z131" t="n">
         <v>50</v>
       </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>Estadio Deportivo Cali</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>BN 25, Palmira</t>
-        </is>
-      </c>
+      <c r="AA131" t="inlineStr"/>
+      <c r="AB131" t="inlineStr"/>
       <c r="AC131" t="n">
         <v>1</v>
       </c>
@@ -58764,16 +57772,8 @@
       <c r="Z132" t="n">
         <v>49</v>
       </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA132" t="inlineStr"/>
+      <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="n">
         <v>2</v>
       </c>
@@ -59210,16 +58210,8 @@
       <c r="Z133" t="n">
         <v>47</v>
       </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>Estadio Departamental Libertad</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>Carrera 8, San Juan de Pasto</t>
-        </is>
-      </c>
+      <c r="AA133" t="inlineStr"/>
+      <c r="AB133" t="inlineStr"/>
       <c r="AC133" t="n">
         <v>3</v>
       </c>
@@ -59640,16 +58632,8 @@
       <c r="Z134" t="n">
         <v>48</v>
       </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Calle Lombana</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>, Villavicencio</t>
-        </is>
-      </c>
+      <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="n">
         <v>3</v>
       </c>
@@ -60086,16 +59070,8 @@
       <c r="Z135" t="n">
         <v>56</v>
       </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA135" t="inlineStr"/>
+      <c r="AB135" t="inlineStr"/>
       <c r="AC135" t="n">
         <v>1</v>
       </c>
@@ -60524,16 +59500,8 @@
       <c r="Z136" t="n">
         <v>51</v>
       </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA136" t="inlineStr"/>
+      <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="n">
         <v>2</v>
       </c>
@@ -60962,16 +59930,8 @@
       <c r="Z137" t="n">
         <v>32</v>
       </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Murillo Toro</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
-        </is>
-      </c>
+      <c r="AA137" t="inlineStr"/>
+      <c r="AB137" t="inlineStr"/>
       <c r="AC137" t="n">
         <v>2</v>
       </c>
@@ -61392,16 +60352,8 @@
       <c r="Z138" t="n">
         <v>53</v>
       </c>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>Estadio Armando Maestre Pavajeau</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>, Valledupar</t>
-        </is>
-      </c>
+      <c r="AA138" t="inlineStr"/>
+      <c r="AB138" t="inlineStr"/>
       <c r="AC138" t="n">
         <v>4</v>
       </c>
@@ -61822,16 +60774,8 @@
       <c r="Z139" t="n">
         <v>31</v>
       </c>
-      <c r="AA139" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA139" t="inlineStr"/>
+      <c r="AB139" t="inlineStr"/>
       <c r="AC139" t="n">
         <v>4</v>
       </c>
@@ -62260,16 +61204,8 @@
       <c r="Z140" t="n">
         <v>34</v>
       </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA140" t="inlineStr"/>
+      <c r="AB140" t="inlineStr"/>
       <c r="AC140" t="n">
         <v>1</v>
       </c>
@@ -63108,16 +62044,8 @@
       <c r="Z142" t="n">
         <v>45</v>
       </c>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>Estadio Olímpico Pascual Guerrero</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>Carrera 36 entre Calles 5 y 5B3, Santiago de Cali</t>
-        </is>
-      </c>
+      <c r="AA142" t="inlineStr"/>
+      <c r="AB142" t="inlineStr"/>
       <c r="AC142" t="n">
         <v>5</v>
       </c>
@@ -63546,16 +62474,8 @@
       <c r="Z143" t="n">
         <v>57</v>
       </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>Estadio de Fútbol Jaraguay de Montería</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>, Montería</t>
-        </is>
-      </c>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
       <c r="AC143" t="n">
         <v>2</v>
       </c>
@@ -63984,16 +62904,8 @@
       <c r="Z144" t="n">
         <v>46</v>
       </c>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>Estadio Palogrande</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>Carrera 24 # 64 - 00, Manizales</t>
-        </is>
-      </c>
+      <c r="AA144" t="inlineStr"/>
+      <c r="AB144" t="inlineStr"/>
       <c r="AC144" t="n">
         <v>3</v>
       </c>
@@ -64422,16 +63334,8 @@
       <c r="Z145" t="n">
         <v>49</v>
       </c>
-      <c r="AA145" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA145" t="inlineStr"/>
+      <c r="AB145" t="inlineStr"/>
       <c r="AC145" t="n">
         <v>0</v>
       </c>
@@ -65282,16 +64186,8 @@
       <c r="Z147" t="n">
         <v>36</v>
       </c>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Murillo Toro</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
-        </is>
-      </c>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="n">
         <v>5</v>
       </c>
@@ -65712,16 +64608,8 @@
       <c r="Z148" t="n">
         <v>64</v>
       </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>Estadio General Santander</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>Avenida 0A 3-56, Barrio Lleras Restrepo, Cúcuta</t>
-        </is>
-      </c>
+      <c r="AA148" t="inlineStr"/>
+      <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="n">
         <v>3</v>
       </c>
@@ -66150,16 +65038,8 @@
       <c r="Z149" t="n">
         <v>41</v>
       </c>
-      <c r="AA149" t="inlineStr">
-        <is>
-          <t>Estadio Hernán Ramírez Villegas</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>Villa Olímpica Pereira, Pereira</t>
-        </is>
-      </c>
+      <c r="AA149" t="inlineStr"/>
+      <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="n">
         <v>2</v>
       </c>
@@ -66588,16 +65468,8 @@
       <c r="Z150" t="n">
         <v>49</v>
       </c>
-      <c r="AA150" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA150" t="inlineStr"/>
+      <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="n">
         <v>2</v>
       </c>
@@ -67034,16 +65906,8 @@
       <c r="Z151" t="n">
         <v>58</v>
       </c>
-      <c r="AA151" t="inlineStr">
-        <is>
-          <t>Estadio Alberto Grisales</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>Route 45A, Rionegro, Antioquia</t>
-        </is>
-      </c>
+      <c r="AA151" t="inlineStr"/>
+      <c r="AB151" t="inlineStr"/>
       <c r="AC151" t="n">
         <v>3</v>
       </c>
@@ -67480,16 +66344,8 @@
       <c r="Z152" t="n">
         <v>64</v>
       </c>
-      <c r="AA152" t="inlineStr">
-        <is>
-          <t>Estadio Hernán Ramírez Villegas</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>Villa Olímpica Pereira, Pereira</t>
-        </is>
-      </c>
+      <c r="AA152" t="inlineStr"/>
+      <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="n">
         <v>3</v>
       </c>
@@ -67910,16 +66766,8 @@
       <c r="Z153" t="n">
         <v>47</v>
       </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>Estadio Departamental Libertad</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>Carrera 8, San Juan de Pasto</t>
-        </is>
-      </c>
+      <c r="AA153" t="inlineStr"/>
+      <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="n">
         <v>1</v>
       </c>
@@ -68348,16 +67196,8 @@
       <c r="Z154" t="n">
         <v>43</v>
       </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>Estadio Alberto Grisales</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>Route 45A, Rionegro, Antioquia</t>
-        </is>
-      </c>
+      <c r="AA154" t="inlineStr"/>
+      <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="n">
         <v>2</v>
       </c>
@@ -68786,16 +67626,8 @@
       <c r="Z155" t="n">
         <v>58</v>
       </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA155" t="inlineStr"/>
+      <c r="AB155" t="inlineStr"/>
       <c r="AC155" t="n">
         <v>1</v>
       </c>
@@ -69224,16 +68056,8 @@
       <c r="Z156" t="n">
         <v>47</v>
       </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA156" t="inlineStr"/>
+      <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="n">
         <v>7</v>
       </c>
@@ -69662,16 +68486,8 @@
       <c r="Z157" t="n">
         <v>31</v>
       </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>Estadio Deportivo Cali</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>BN 25, Palmira</t>
-        </is>
-      </c>
+      <c r="AA157" t="inlineStr"/>
+      <c r="AB157" t="inlineStr"/>
       <c r="AC157" t="n">
         <v>2</v>
       </c>
@@ -70092,16 +68908,8 @@
       <c r="Z158" t="n">
         <v>51</v>
       </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>Estadio Alfonso López</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>Carrera 36 Nº 53-12, Cabecera del Llano, Bucaramanga</t>
-        </is>
-      </c>
+      <c r="AA158" t="inlineStr"/>
+      <c r="AB158" t="inlineStr"/>
       <c r="AC158" t="n">
         <v>3</v>
       </c>
@@ -70530,16 +69338,8 @@
       <c r="Z159" t="n">
         <v>39</v>
       </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA159" t="inlineStr"/>
+      <c r="AB159" t="inlineStr"/>
       <c r="AC159" t="n">
         <v>0</v>
       </c>
@@ -71398,16 +70198,8 @@
       <c r="Z161" t="n">
         <v>52</v>
       </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>Estadio de Fútbol Jaraguay de Montería</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>, Montería</t>
-        </is>
-      </c>
+      <c r="AA161" t="inlineStr"/>
+      <c r="AB161" t="inlineStr"/>
       <c r="AC161" t="n">
         <v>3</v>
       </c>
@@ -71836,16 +70628,8 @@
       <c r="Z162" t="n">
         <v>35</v>
       </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Murillo Toro</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
-        </is>
-      </c>
+      <c r="AA162" t="inlineStr"/>
+      <c r="AB162" t="inlineStr"/>
       <c r="AC162" t="n">
         <v>0</v>
       </c>
@@ -72266,16 +71050,8 @@
       <c r="Z163" t="n">
         <v>35</v>
       </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA163" t="inlineStr"/>
+      <c r="AB163" t="inlineStr"/>
       <c r="AC163" t="n">
         <v>3</v>
       </c>
@@ -72696,16 +71472,8 @@
       <c r="Z164" t="n">
         <v>62</v>
       </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA164" t="inlineStr"/>
+      <c r="AB164" t="inlineStr"/>
       <c r="AC164" t="n">
         <v>2</v>
       </c>
@@ -73134,16 +71902,8 @@
       <c r="Z165" t="n">
         <v>42</v>
       </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>Estadio Armando Maestre Pavajeau</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>, Valledupar</t>
-        </is>
-      </c>
+      <c r="AA165" t="inlineStr"/>
+      <c r="AB165" t="inlineStr"/>
       <c r="AC165" t="n">
         <v>4</v>
       </c>
@@ -73572,16 +72332,8 @@
       <c r="Z166" t="n">
         <v>42</v>
       </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano Roberto Meléndez</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>Intersección de la Avenida Circunvalar con la Calle 45, Barranquilla</t>
-        </is>
-      </c>
+      <c r="AA166" t="inlineStr"/>
+      <c r="AB166" t="inlineStr"/>
       <c r="AC166" t="n">
         <v>3</v>
       </c>
@@ -74010,16 +72762,8 @@
       <c r="Z167" t="n">
         <v>45</v>
       </c>
-      <c r="AA167" t="inlineStr">
-        <is>
-          <t>Estadio Olímpico Pascual Guerrero</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>Carrera 36 entre Calles 5 y 5B3, Santiago de Cali</t>
-        </is>
-      </c>
+      <c r="AA167" t="inlineStr"/>
+      <c r="AB167" t="inlineStr"/>
       <c r="AC167" t="n">
         <v>3</v>
       </c>
@@ -74448,16 +73192,8 @@
       <c r="Z168" t="n">
         <v>37</v>
       </c>
-      <c r="AA168" t="inlineStr">
-        <is>
-          <t>Estadio Palogrande</t>
-        </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>Carrera 24 # 64 - 00, Manizales</t>
-        </is>
-      </c>
+      <c r="AA168" t="inlineStr"/>
+      <c r="AB168" t="inlineStr"/>
       <c r="AC168" t="n">
         <v>3</v>
       </c>
@@ -74878,16 +73614,8 @@
       <c r="Z169" t="n">
         <v>46</v>
       </c>
-      <c r="AA169" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA169" t="inlineStr"/>
+      <c r="AB169" t="inlineStr"/>
       <c r="AC169" t="n">
         <v>2</v>
       </c>
@@ -75316,16 +74044,8 @@
       <c r="Z170" t="n">
         <v>31</v>
       </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA170" t="inlineStr"/>
+      <c r="AB170" t="inlineStr"/>
       <c r="AC170" t="n">
         <v>3</v>
       </c>
@@ -75754,16 +74474,8 @@
       <c r="Z171" t="n">
         <v>38</v>
       </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA171" t="inlineStr"/>
+      <c r="AB171" t="inlineStr"/>
       <c r="AC171" t="n">
         <v>2</v>
       </c>
@@ -76192,16 +74904,8 @@
       <c r="Z172" t="n">
         <v>49</v>
       </c>
-      <c r="AA172" t="inlineStr">
-        <is>
-          <t>Estadio Departamental Libertad</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>Carrera 8, San Juan de Pasto</t>
-        </is>
-      </c>
+      <c r="AA172" t="inlineStr"/>
+      <c r="AB172" t="inlineStr"/>
       <c r="AC172" t="n">
         <v>3</v>
       </c>
@@ -76638,16 +75342,8 @@
       <c r="Z173" t="n">
         <v>59</v>
       </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA173" t="inlineStr"/>
+      <c r="AB173" t="inlineStr"/>
       <c r="AC173" t="n">
         <v>4</v>
       </c>
@@ -77076,16 +75772,8 @@
       <c r="Z174" t="n">
         <v>58</v>
       </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>Estadio General Santander</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>Avenida 0A 3-56, Barrio Lleras Restrepo, Cúcuta</t>
-        </is>
-      </c>
+      <c r="AA174" t="inlineStr"/>
+      <c r="AB174" t="inlineStr"/>
       <c r="AC174" t="n">
         <v>1</v>
       </c>
@@ -77506,16 +76194,8 @@
       <c r="Z175" t="n">
         <v>51</v>
       </c>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>Estadio Alfonso López</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>Carrera 36 Nº 53-12, Cabecera del Llano, Bucaramanga</t>
-        </is>
-      </c>
+      <c r="AA175" t="inlineStr"/>
+      <c r="AB175" t="inlineStr"/>
       <c r="AC175" t="n">
         <v>2</v>
       </c>
@@ -77944,16 +76624,8 @@
       <c r="Z176" t="n">
         <v>54</v>
       </c>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>Estadio Hernán Ramírez Villegas</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>Villa Olímpica Pereira, Pereira</t>
-        </is>
-      </c>
+      <c r="AA176" t="inlineStr"/>
+      <c r="AB176" t="inlineStr"/>
       <c r="AC176" t="n">
         <v>3</v>
       </c>
@@ -78382,16 +77054,8 @@
       <c r="Z177" t="n">
         <v>49</v>
       </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>Estadio Deportivo Cali</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>BN 25, Palmira</t>
-        </is>
-      </c>
+      <c r="AA177" t="inlineStr"/>
+      <c r="AB177" t="inlineStr"/>
       <c r="AC177" t="n">
         <v>1</v>
       </c>
@@ -78812,16 +77476,8 @@
       <c r="Z178" t="n">
         <v>47</v>
       </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA178" t="inlineStr"/>
+      <c r="AB178" t="inlineStr"/>
       <c r="AC178" t="n">
         <v>1</v>
       </c>
@@ -79242,16 +77898,8 @@
       <c r="Z179" t="n">
         <v>50</v>
       </c>
-      <c r="AA179" t="inlineStr">
-        <is>
-          <t>Estadio Alberto Grisales</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>Route 45A, Rionegro, Antioquia</t>
-        </is>
-      </c>
+      <c r="AA179" t="inlineStr"/>
+      <c r="AB179" t="inlineStr"/>
       <c r="AC179" t="n">
         <v>4</v>
       </c>
@@ -79680,16 +78328,8 @@
       <c r="Z180" t="n">
         <v>42</v>
       </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Calle Lombana</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>, Villavicencio</t>
-        </is>
-      </c>
+      <c r="AA180" t="inlineStr"/>
+      <c r="AB180" t="inlineStr"/>
       <c r="AC180" t="n">
         <v>1</v>
       </c>
@@ -80110,16 +78750,8 @@
       <c r="Z181" t="n">
         <v>63</v>
       </c>
-      <c r="AA181" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA181" t="inlineStr"/>
+      <c r="AB181" t="inlineStr"/>
       <c r="AC181" t="n">
         <v>3</v>
       </c>
@@ -80548,16 +79180,8 @@
       <c r="Z182" t="n">
         <v>55</v>
       </c>
-      <c r="AA182" t="inlineStr">
-        <is>
-          <t>Estadio Palogrande</t>
-        </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>Carrera 24 # 64 - 00, Manizales</t>
-        </is>
-      </c>
+      <c r="AA182" t="inlineStr"/>
+      <c r="AB182" t="inlineStr"/>
       <c r="AC182" t="n">
         <v>3</v>
       </c>
@@ -81404,16 +80028,8 @@
       <c r="Z184" t="n">
         <v>48</v>
       </c>
-      <c r="AA184" t="inlineStr">
-        <is>
-          <t>Estadio de Fútbol Jaraguay de Montería</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>, Montería</t>
-        </is>
-      </c>
+      <c r="AA184" t="inlineStr"/>
+      <c r="AB184" t="inlineStr"/>
       <c r="AC184" t="n">
         <v>5</v>
       </c>
@@ -81834,16 +80450,8 @@
       <c r="Z185" t="n">
         <v>40</v>
       </c>
-      <c r="AA185" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA185" t="inlineStr"/>
+      <c r="AB185" t="inlineStr"/>
       <c r="AC185" t="n">
         <v>1</v>
       </c>
@@ -82264,16 +80872,8 @@
       <c r="Z186" t="n">
         <v>56</v>
       </c>
-      <c r="AA186" t="inlineStr">
-        <is>
-          <t>Estadio Armando Maestre Pavajeau</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>, Valledupar</t>
-        </is>
-      </c>
+      <c r="AA186" t="inlineStr"/>
+      <c r="AB186" t="inlineStr"/>
       <c r="AC186" t="n">
         <v>6</v>
       </c>
@@ -82702,16 +81302,8 @@
       <c r="Z187" t="n">
         <v>47</v>
       </c>
-      <c r="AA187" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA187" t="inlineStr"/>
+      <c r="AB187" t="inlineStr"/>
       <c r="AC187" t="n">
         <v>4</v>
       </c>
@@ -83132,16 +81724,8 @@
       <c r="Z188" t="n">
         <v>55</v>
       </c>
-      <c r="AA188" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Murillo Toro</t>
-        </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
-        </is>
-      </c>
+      <c r="AA188" t="inlineStr"/>
+      <c r="AB188" t="inlineStr"/>
       <c r="AC188" t="n">
         <v>7</v>
       </c>
@@ -83570,16 +82154,8 @@
       <c r="Z189" t="n">
         <v>30</v>
       </c>
-      <c r="AA189" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA189" t="inlineStr"/>
+      <c r="AB189" t="inlineStr"/>
       <c r="AC189" t="n">
         <v>4</v>
       </c>
@@ -84008,16 +82584,8 @@
       <c r="Z190" t="n">
         <v>57</v>
       </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>Estadio Olímpico Pascual Guerrero</t>
-        </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>Carrera 36 entre Calles 5 y 5B3, Santiago de Cali</t>
-        </is>
-      </c>
+      <c r="AA190" t="inlineStr"/>
+      <c r="AB190" t="inlineStr"/>
       <c r="AC190" t="n">
         <v>3</v>
       </c>
@@ -84868,16 +83436,8 @@
       <c r="Z192" t="n">
         <v>58</v>
       </c>
-      <c r="AA192" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano de Techo</t>
-        </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>Tv 71D, Kennedy, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA192" t="inlineStr"/>
+      <c r="AB192" t="inlineStr"/>
       <c r="AC192" t="n">
         <v>4</v>
       </c>
@@ -85294,16 +83854,8 @@
       <c r="Z193" t="n">
         <v>37</v>
       </c>
-      <c r="AA193" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Murillo Toro</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
-        </is>
-      </c>
+      <c r="AA193" t="inlineStr"/>
+      <c r="AB193" t="inlineStr"/>
       <c r="AC193" t="n">
         <v>0</v>
       </c>
@@ -85724,16 +84276,8 @@
       <c r="Z194" t="n">
         <v>34</v>
       </c>
-      <c r="AA194" t="inlineStr">
-        <is>
-          <t>Estadio Olímpico Pascual Guerrero</t>
-        </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>Carrera 36 entre Calles 5 y 5B3, Santiago de Cali</t>
-        </is>
-      </c>
+      <c r="AA194" t="inlineStr"/>
+      <c r="AB194" t="inlineStr"/>
       <c r="AC194" t="n">
         <v>1</v>
       </c>
@@ -86154,16 +84698,8 @@
       <c r="Z195" t="n">
         <v>43</v>
       </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>Estadio Palogrande</t>
-        </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>Carrera 24 # 64 - 00, Manizales</t>
-        </is>
-      </c>
+      <c r="AA195" t="inlineStr"/>
+      <c r="AB195" t="inlineStr"/>
       <c r="AC195" t="n">
         <v>1</v>
       </c>
@@ -86592,16 +85128,8 @@
       <c r="Z196" t="n">
         <v>40</v>
       </c>
-      <c r="AA196" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA196" t="inlineStr"/>
+      <c r="AB196" t="inlineStr"/>
       <c r="AC196" t="n">
         <v>0</v>
       </c>
@@ -87022,16 +85550,8 @@
       <c r="Z197" t="n">
         <v>54</v>
       </c>
-      <c r="AA197" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA197" t="inlineStr"/>
+      <c r="AB197" t="inlineStr"/>
       <c r="AC197" t="n">
         <v>3</v>
       </c>
@@ -87452,16 +85972,8 @@
       <c r="Z198" t="n">
         <v>51</v>
       </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>Estadio Departamental Libertad</t>
-        </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>Carrera 8, San Juan de Pasto</t>
-        </is>
-      </c>
+      <c r="AA198" t="inlineStr"/>
+      <c r="AB198" t="inlineStr"/>
       <c r="AC198" t="n">
         <v>2</v>
       </c>
@@ -87882,16 +86394,8 @@
       <c r="Z199" t="n">
         <v>48</v>
       </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano Roberto Meléndez</t>
-        </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>Intersección de la Avenida Circunvalar con la Calle 45, Barranquilla</t>
-        </is>
-      </c>
+      <c r="AA199" t="inlineStr"/>
+      <c r="AB199" t="inlineStr"/>
       <c r="AC199" t="n">
         <v>8</v>
       </c>
@@ -88320,16 +86824,8 @@
       <c r="Z200" t="n">
         <v>52</v>
       </c>
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>Estadio Manuel Murillo Toro</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>Carrera 4A Bis Nº 34 - 60 con Calle 36, Ibagué</t>
-        </is>
-      </c>
+      <c r="AA200" t="inlineStr"/>
+      <c r="AB200" t="inlineStr"/>
       <c r="AC200" t="n">
         <v>4</v>
       </c>
@@ -88758,16 +87254,8 @@
       <c r="Z201" t="n">
         <v>47</v>
       </c>
-      <c r="AA201" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Camacho El Campín</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>Avenida N.Q.S Calle 57, Bogotá, D.C.</t>
-        </is>
-      </c>
+      <c r="AA201" t="inlineStr"/>
+      <c r="AB201" t="inlineStr"/>
       <c r="AC201" t="n">
         <v>2</v>
       </c>
@@ -89176,16 +87664,8 @@
       <c r="Z202" t="n">
         <v>58</v>
       </c>
-      <c r="AA202" t="inlineStr">
-        <is>
-          <t>Estadio Atanasio Girardot</t>
-        </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>Entre carreras 70 y 73 y las Calles 48 y 50, Medellín</t>
-        </is>
-      </c>
+      <c r="AA202" t="inlineStr"/>
+      <c r="AB202" t="inlineStr"/>
       <c r="AC202" t="n">
         <v>2</v>
       </c>
@@ -89614,16 +88094,8 @@
       <c r="Z203" t="n">
         <v>32</v>
       </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>Estadio Metropolitano Roberto Meléndez</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>Intersección de la Avenida Circunvalar con la Calle 45, Barranquilla</t>
-        </is>
-      </c>
+      <c r="AA203" t="inlineStr"/>
+      <c r="AB203" t="inlineStr"/>
       <c r="AC203" t="n">
         <v>2</v>
       </c>

--- a/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
+++ b/data/matches/leagues/Colombia_Primera_Liga_2026.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EJ203" headerRowCount="1">
-  <autoFilter ref="A1:EJ203"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EJ204" headerRowCount="1">
+  <autoFilter ref="A1:EJ204"/>
   <tableColumns count="140">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EJ203"/>
+  <dimension ref="A1:EJ204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DE5" t="n">
         <v>0.89</v>
@@ -4742,7 +4742,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DE9" t="n">
         <v>1.61</v>
@@ -9057,7 +9057,7 @@
         <v>1.37</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -17291,7 +17291,7 @@
         <v>0.53</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DF38" t="n">
         <v>0.67</v>
@@ -17718,7 +17718,7 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DE39" t="n">
         <v>1.62</v>
@@ -20274,7 +20274,7 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DE45" t="n">
         <v>0.89</v>
@@ -24629,7 +24629,7 @@
         <v>1.62</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DF55" t="n">
         <v>1.4</v>
@@ -25064,7 +25064,7 @@
         <v>70</v>
       </c>
       <c r="DD56" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DE56" t="n">
         <v>1.16</v>
@@ -27687,7 +27687,7 @@
         <v>1.42</v>
       </c>
       <c r="DE62" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DF62" t="n">
         <v>1.17</v>
@@ -29400,7 +29400,7 @@
         <v>90</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DE66" t="n">
         <v>1.62</v>
@@ -31566,7 +31566,7 @@
         <v>54</v>
       </c>
       <c r="DD71" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DE71" t="n">
         <v>0.89</v>
@@ -32437,7 +32437,7 @@
         <v>1.52</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -34165,7 +34165,7 @@
         <v>1.52</v>
       </c>
       <c r="DE77" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DF77" t="n">
         <v>1.25</v>
@@ -35901,7 +35901,7 @@
         <v>0.95</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DF81" t="n">
         <v>1.43</v>
@@ -38067,7 +38067,7 @@
         <v>1.61</v>
       </c>
       <c r="DE86" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DF86" t="n">
         <v>1.5</v>
@@ -39362,7 +39362,7 @@
         <v>75</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DE89" t="n">
         <v>0.89</v>
@@ -40241,7 +40241,7 @@
         <v>1.37</v>
       </c>
       <c r="DE91" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DF91" t="n">
         <v>1.5</v>
@@ -42420,10 +42420,10 @@
         <v>88</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DE96" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DF96" t="n">
         <v>1.78</v>
@@ -42453,7 +42453,7 @@
         <v>3.39</v>
       </c>
       <c r="DO96" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -43280,7 +43280,7 @@
         <v>74</v>
       </c>
       <c r="DD98" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DE98" t="n">
         <v>1.16</v>
@@ -46760,7 +46760,7 @@
         <v>80</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DE106" t="n">
         <v>1.16</v>
@@ -47631,7 +47631,7 @@
         <v>1.37</v>
       </c>
       <c r="DE108" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DF108" t="n">
         <v>1.27</v>
@@ -50673,7 +50673,7 @@
         <v>1.37</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DF115" t="n">
         <v>1</v>
@@ -51984,7 +51984,7 @@
         <v>70</v>
       </c>
       <c r="DD118" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DE118" t="n">
         <v>1.33</v>
@@ -54588,7 +54588,7 @@
         <v>82</v>
       </c>
       <c r="DD124" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DE124" t="n">
         <v>1.21</v>
@@ -58015,7 +58015,7 @@
         <v>1.33</v>
       </c>
       <c r="DE132" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DF132" t="n">
         <v>1.62</v>
@@ -58453,7 +58453,7 @@
         <v>1.62</v>
       </c>
       <c r="DE133" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DF133" t="n">
         <v>2.08</v>
@@ -61444,7 +61444,7 @@
         <v>86</v>
       </c>
       <c r="DD140" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DE140" t="n">
         <v>0.84</v>
@@ -64004,7 +64004,7 @@
         <v>75</v>
       </c>
       <c r="DD146" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DE146" t="n">
         <v>1.42</v>
@@ -65708,7 +65708,7 @@
         <v>76</v>
       </c>
       <c r="DD150" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DE150" t="n">
         <v>0.95</v>
@@ -67439,7 +67439,7 @@
         <v>1.37</v>
       </c>
       <c r="DE154" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DF154" t="n">
         <v>1.47</v>
@@ -67869,7 +67869,7 @@
         <v>1.37</v>
       </c>
       <c r="DE155" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DF155" t="n">
         <v>1.21</v>
@@ -69705,162 +69705,162 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Boyacá Chicó</t>
+          <t>Jaguares de Córdoba</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Deportivo Cali</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="F160" s="1" t="n">
         <v>46129.875</v>
       </c>
       <c r="G160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H160" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J160" t="n">
+        <v>4</v>
+      </c>
+      <c r="K160" t="n">
+        <v>2</v>
+      </c>
+      <c r="L160" t="n">
+        <v>6</v>
+      </c>
+      <c r="M160" t="n">
+        <v>3</v>
+      </c>
+      <c r="N160" t="n">
+        <v>6</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>9</v>
+      </c>
+      <c r="R160" t="n">
         <v>5</v>
       </c>
-      <c r="K160" t="n">
-        <v>5</v>
-      </c>
-      <c r="L160" t="n">
+      <c r="S160" t="n">
         <v>10</v>
-      </c>
-      <c r="M160" t="n">
-        <v>2</v>
-      </c>
-      <c r="N160" t="n">
-        <v>4</v>
-      </c>
-      <c r="O160" t="n">
-        <v>0</v>
-      </c>
-      <c r="P160" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>4</v>
-      </c>
-      <c r="R160" t="n">
-        <v>2</v>
-      </c>
-      <c r="S160" t="n">
-        <v>5</v>
       </c>
       <c r="T160" t="n">
         <v>6</v>
       </c>
       <c r="U160" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="V160" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W160" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X160" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Y160" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z160" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA160" t="inlineStr"/>
       <c r="AB160" t="inlineStr"/>
       <c r="AC160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD160" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE160" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="AF160" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AG160" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AH160" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI160" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="AJ160" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="AK160" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AL160" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AM160" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AN160" t="n">
-        <v>2.1</v>
+        <v>2.93</v>
       </c>
       <c r="AO160" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AR160" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AS160" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AT160" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AU160" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX160" t="n">
         <v>1</v>
       </c>
       <c r="AY160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA160" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB160" t="n">
-        <v>2151</v>
+        <v>2143</v>
       </c>
       <c r="BC160" t="n">
         <v>1</v>
       </c>
       <c r="BD160" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BE160" t="n">
         <v>0</v>
@@ -69875,178 +69875,178 @@
         <v>1</v>
       </c>
       <c r="BI160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM160" t="n">
         <v>4</v>
       </c>
-      <c r="BK160" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL160" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM160" t="n">
+      <c r="BN160" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ160" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR160" t="n">
         <v>6</v>
       </c>
-      <c r="BN160" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO160" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP160" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ160" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR160" t="n">
-        <v>3</v>
-      </c>
       <c r="BS160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT160" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BU160" t="n">
         <v>1</v>
       </c>
       <c r="BV160" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="BW160" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="BX160" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="BY160" t="n">
+        <v>91</v>
+      </c>
+      <c r="BZ160" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CA160" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CB160" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="CC160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR160" t="n">
+        <v>10</v>
+      </c>
+      <c r="CS160" t="n">
+        <v>9</v>
+      </c>
+      <c r="CT160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU160" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV160" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX160" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY160" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ160" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA160" t="n">
         <v>72</v>
       </c>
-      <c r="BZ160" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="CA160" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="CB160" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CC160" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD160" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE160" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF160" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG160" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH160" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI160" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ160" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK160" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL160" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM160" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN160" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO160" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP160" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ160" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR160" t="n">
-        <v>11</v>
-      </c>
-      <c r="CS160" t="n">
-        <v>23</v>
-      </c>
-      <c r="CT160" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU160" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV160" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW160" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX160" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY160" t="n">
-        <v>4</v>
-      </c>
-      <c r="CZ160" t="n">
-        <v>39</v>
-      </c>
-      <c r="DA160" t="n">
-        <v>65</v>
-      </c>
       <c r="DB160" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="DC160" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="DD160" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="DE160" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="DF160" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="DG160" t="n">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="DH160" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="DI160" t="n">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="DJ160" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="DK160" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="DL160" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="DM160" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="DN160" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="DO160" t="n">
         <v>19</v>
@@ -70055,55 +70055,63 @@
         <v>1</v>
       </c>
       <c r="DQ160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU160" t="b">
         <v>0</v>
       </c>
       <c r="DV160" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW160" t="inlineStr"/>
-      <c r="DX160" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="DW160" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="DX160" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
       <c r="DY160" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="DZ160" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EA160" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="EB160" t="inlineStr"/>
       <c r="EC160" t="inlineStr"/>
       <c r="ED160" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="EE160" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="EF160" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="EG160" t="inlineStr"/>
@@ -70127,41 +70135,41 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Jaguares de Córdoba</t>
+          <t>Boyacá Chicó</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Deportivo Cali</t>
         </is>
       </c>
       <c r="F161" s="1" t="n">
         <v>46129.875</v>
       </c>
       <c r="G161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H161" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" t="n">
         <v>5</v>
       </c>
-      <c r="J161" t="n">
+      <c r="K161" t="n">
+        <v>5</v>
+      </c>
+      <c r="L161" t="n">
+        <v>10</v>
+      </c>
+      <c r="M161" t="n">
+        <v>2</v>
+      </c>
+      <c r="N161" t="n">
         <v>4</v>
       </c>
-      <c r="K161" t="n">
-        <v>2</v>
-      </c>
-      <c r="L161" t="n">
-        <v>6</v>
-      </c>
-      <c r="M161" t="n">
-        <v>3</v>
-      </c>
-      <c r="N161" t="n">
-        <v>6</v>
-      </c>
       <c r="O161" t="n">
         <v>0</v>
       </c>
@@ -70169,120 +70177,120 @@
         <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="R161" t="n">
+        <v>2</v>
+      </c>
+      <c r="S161" t="n">
         <v>5</v>
-      </c>
-      <c r="S161" t="n">
-        <v>10</v>
       </c>
       <c r="T161" t="n">
         <v>6</v>
       </c>
       <c r="U161" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="V161" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W161" t="n">
+        <v>13</v>
+      </c>
+      <c r="X161" t="n">
         <v>14</v>
       </c>
-      <c r="X161" t="n">
-        <v>12</v>
-      </c>
       <c r="Y161" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z161" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA161" t="inlineStr"/>
       <c r="AB161" t="inlineStr"/>
       <c r="AC161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD161" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE161" t="n">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="AF161" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AG161" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AH161" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI161" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="AJ161" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="AK161" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AL161" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AM161" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AN161" t="n">
-        <v>2.93</v>
+        <v>2.1</v>
       </c>
       <c r="AO161" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AR161" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AS161" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AT161" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AU161" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX161" t="n">
         <v>1</v>
       </c>
       <c r="AY161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA161" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB161" t="n">
-        <v>2143</v>
+        <v>2151</v>
       </c>
       <c r="BC161" t="n">
         <v>1</v>
       </c>
       <c r="BD161" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BE161" t="n">
         <v>0</v>
@@ -70297,64 +70305,64 @@
         <v>1</v>
       </c>
       <c r="BI161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ161" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BK161" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL161" t="n">
         <v>1</v>
       </c>
       <c r="BM161" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN161" t="n">
         <v>4</v>
       </c>
-      <c r="BN161" t="n">
-        <v>2</v>
-      </c>
       <c r="BO161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR161" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BS161" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT161" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BU161" t="n">
         <v>1</v>
       </c>
       <c r="BV161" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="BW161" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="BX161" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="BY161" t="n">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="BZ161" t="n">
-        <v>2.12</v>
+        <v>1.07</v>
       </c>
       <c r="CA161" t="n">
-        <v>1.32</v>
+        <v>0.99</v>
       </c>
       <c r="CB161" t="n">
-        <v>3.44</v>
+        <v>2.06</v>
       </c>
       <c r="CC161" t="n">
         <v>0</v>
@@ -70393,82 +70401,82 @@
         <v>0</v>
       </c>
       <c r="CO161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ161" t="n">
         <v>1</v>
       </c>
       <c r="CR161" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CS161" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="CT161" t="n">
         <v>1</v>
       </c>
       <c r="CU161" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CV161" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CW161" t="n">
         <v>1</v>
       </c>
       <c r="CX161" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CY161" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="CZ161" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="DA161" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="DB161" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="DC161" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="DD161" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="DE161" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="DF161" t="n">
-        <v>0.88</v>
+        <v>0.73</v>
       </c>
       <c r="DG161" t="n">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="DH161" t="n">
-        <v>0.88</v>
+        <v>0.73</v>
       </c>
       <c r="DI161" t="n">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="DJ161" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="DK161" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="DL161" t="n">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="DM161" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="DN161" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="DO161" t="n">
         <v>19</v>
@@ -70477,63 +70485,55 @@
         <v>1</v>
       </c>
       <c r="DQ161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU161" t="b">
         <v>0</v>
       </c>
       <c r="DV161" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW161" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="DX161" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DW161" t="inlineStr"/>
+      <c r="DX161" t="inlineStr"/>
       <c r="DY161" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="DZ161" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EA161" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="EB161" t="inlineStr"/>
       <c r="EC161" t="inlineStr"/>
       <c r="ED161" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EE161" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EF161" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EG161" t="inlineStr"/>
@@ -72572,7 +72572,7 @@
         <v>79</v>
       </c>
       <c r="DD166" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DE166" t="n">
         <v>1.16</v>
@@ -73854,7 +73854,7 @@
         <v>78</v>
       </c>
       <c r="DD169" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DE169" t="n">
         <v>1.21</v>
@@ -76015,7 +76015,7 @@
         <v>0.84</v>
       </c>
       <c r="DE174" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DF174" t="n">
         <v>0.88</v>
@@ -76867,7 +76867,7 @@
         <v>0.53</v>
       </c>
       <c r="DE176" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DF176" t="n">
         <v>0.41</v>
@@ -79423,7 +79423,7 @@
         <v>1.62</v>
       </c>
       <c r="DE182" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DF182" t="n">
         <v>1.67</v>
@@ -80379,141 +80379,141 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>Independiente Medellín</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Rionegro Águilas</t>
         </is>
       </c>
       <c r="F185" s="1" t="n">
         <v>46145.85416666666</v>
       </c>
       <c r="G185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I185" t="n">
         <v>3</v>
       </c>
       <c r="J185" t="n">
+        <v>10</v>
+      </c>
+      <c r="K185" t="n">
+        <v>2</v>
+      </c>
+      <c r="L185" t="n">
+        <v>12</v>
+      </c>
+      <c r="M185" t="n">
+        <v>3</v>
+      </c>
+      <c r="N185" t="n">
+        <v>2</v>
+      </c>
+      <c r="O185" t="n">
+        <v>1</v>
+      </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>7</v>
+      </c>
+      <c r="R185" t="n">
+        <v>4</v>
+      </c>
+      <c r="S185" t="n">
+        <v>14</v>
+      </c>
+      <c r="T185" t="n">
         <v>6</v>
       </c>
-      <c r="K185" t="n">
-        <v>3</v>
-      </c>
-      <c r="L185" t="n">
-        <v>9</v>
-      </c>
-      <c r="M185" t="n">
-        <v>1</v>
-      </c>
-      <c r="N185" t="n">
-        <v>2</v>
-      </c>
-      <c r="O185" t="n">
-        <v>0</v>
-      </c>
-      <c r="P185" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q185" t="n">
-        <v>3</v>
-      </c>
-      <c r="R185" t="n">
-        <v>3</v>
-      </c>
-      <c r="S185" t="n">
+      <c r="U185" t="n">
+        <v>21</v>
+      </c>
+      <c r="V185" t="n">
+        <v>10</v>
+      </c>
+      <c r="W185" t="n">
+        <v>10</v>
+      </c>
+      <c r="X185" t="n">
         <v>7</v>
       </c>
-      <c r="T185" t="n">
-        <v>14</v>
-      </c>
-      <c r="U185" t="n">
-        <v>10</v>
-      </c>
-      <c r="V185" t="n">
-        <v>17</v>
-      </c>
-      <c r="W185" t="n">
-        <v>8</v>
-      </c>
-      <c r="X185" t="n">
-        <v>13</v>
-      </c>
       <c r="Y185" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Z185" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AA185" t="inlineStr"/>
       <c r="AB185" t="inlineStr"/>
       <c r="AC185" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD185" t="n">
         <v>2</v>
       </c>
       <c r="AE185" t="n">
-        <v>2.87</v>
+        <v>1.37</v>
       </c>
       <c r="AF185" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG185" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AK185" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL185" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AM185" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN185" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO185" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AP185" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ185" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR185" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AS185" t="n">
         <v>2.9</v>
       </c>
-      <c r="AG185" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AH185" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI185" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ185" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AK185" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AL185" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AM185" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AN185" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AO185" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AP185" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AQ185" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR185" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AS185" t="n">
-        <v>2.41</v>
-      </c>
       <c r="AT185" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AU185" t="n">
         <v>3</v>
       </c>
       <c r="AV185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX185" t="n">
         <v>1</v>
@@ -80528,19 +80528,19 @@
         <v>1</v>
       </c>
       <c r="BB185" t="n">
-        <v>2152</v>
+        <v>2147</v>
       </c>
       <c r="BC185" t="n">
         <v>1</v>
       </c>
       <c r="BD185" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="BE185" t="n">
         <v>0</v>
       </c>
       <c r="BF185" t="n">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="BG185" t="n">
         <v>2</v>
@@ -80549,175 +80549,175 @@
         <v>1</v>
       </c>
       <c r="BI185" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BJ185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK185" t="n">
         <v>4</v>
       </c>
       <c r="BL185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BM185" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BN185" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ185" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT185" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV185" t="n">
+        <v>70</v>
+      </c>
+      <c r="BW185" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX185" t="n">
+        <v>120</v>
+      </c>
+      <c r="BY185" t="n">
+        <v>44</v>
+      </c>
+      <c r="BZ185" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CA185" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="CB185" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CC185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM185" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR185" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS185" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU185" t="n">
         <v>7</v>
       </c>
-      <c r="BO185" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP185" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ185" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR185" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS185" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT185" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU185" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV185" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW185" t="n">
-        <v>34</v>
-      </c>
-      <c r="BX185" t="n">
-        <v>91</v>
-      </c>
-      <c r="BY185" t="n">
-        <v>58</v>
-      </c>
-      <c r="BZ185" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="CA185" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CB185" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="CC185" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD185" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE185" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF185" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG185" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH185" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI185" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ185" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK185" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL185" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM185" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN185" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO185" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP185" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ185" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR185" t="n">
-        <v>23</v>
-      </c>
-      <c r="CS185" t="n">
-        <v>13</v>
-      </c>
-      <c r="CT185" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU185" t="n">
-        <v>13</v>
-      </c>
       <c r="CV185" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CW185" t="n">
         <v>1</v>
       </c>
       <c r="CX185" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="CY185" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="CZ185" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="DA185" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="DB185" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="DC185" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="DD185" t="n">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="DE185" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="DF185" t="n">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="DG185" t="n">
         <v>1.28</v>
       </c>
       <c r="DH185" t="n">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="DI185" t="n">
         <v>1.28</v>
       </c>
       <c r="DJ185" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="DK185" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="DL185" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="DM185" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="DN185" t="n">
         <v>2.67</v>
@@ -80750,38 +80750,46 @@
       <c r="DX185" t="inlineStr"/>
       <c r="DY185" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="DZ185" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="EA185" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EB185" t="inlineStr"/>
       <c r="EC185" t="inlineStr"/>
       <c r="ED185" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="EE185" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="EF185" t="inlineStr">
         <is>
-          <t>2.65</t>
-        </is>
-      </c>
-      <c r="EG185" t="inlineStr"/>
-      <c r="EH185" t="inlineStr"/>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EG185" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH185" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
       <c r="EI185" t="inlineStr"/>
       <c r="EJ185" t="inlineStr"/>
     </row>
@@ -80801,43 +80809,43 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Alianza Petrolera</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Deportivo Cali</t>
         </is>
       </c>
       <c r="F186" s="1" t="n">
         <v>46145.85416666666</v>
       </c>
       <c r="G186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I186" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J186" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K186" t="n">
+        <v>3</v>
+      </c>
+      <c r="L186" t="n">
         <v>8</v>
       </c>
-      <c r="L186" t="n">
-        <v>11</v>
-      </c>
       <c r="M186" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N186" t="n">
         <v>3</v>
       </c>
       <c r="O186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P186" t="n">
         <v>0</v>
@@ -80846,90 +80854,90 @@
         <v>4</v>
       </c>
       <c r="R186" t="n">
+        <v>4</v>
+      </c>
+      <c r="S186" t="n">
         <v>9</v>
       </c>
-      <c r="S186" t="n">
-        <v>3</v>
-      </c>
       <c r="T186" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U186" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="V186" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W186" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="X186" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y186" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z186" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AA186" t="inlineStr"/>
       <c r="AB186" t="inlineStr"/>
       <c r="AC186" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD186" t="n">
         <v>3</v>
       </c>
       <c r="AE186" t="n">
-        <v>3.95</v>
+        <v>2.65</v>
       </c>
       <c r="AF186" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG186" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH186" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI186" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AJ186" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AK186" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL186" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM186" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN186" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AO186" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AP186" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ186" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR186" t="n">
         <v>3.1</v>
       </c>
-      <c r="AG186" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AH186" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI186" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AJ186" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AK186" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AL186" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AM186" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AN186" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AO186" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AP186" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AQ186" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR186" t="n">
-        <v>3.16</v>
-      </c>
       <c r="AS186" t="n">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="AT186" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AU186" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV186" t="n">
         <v>1</v>
@@ -80938,13 +80946,13 @@
         <v>0</v>
       </c>
       <c r="AX186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA186" t="n">
         <v>1</v>
@@ -80956,13 +80964,13 @@
         <v>1</v>
       </c>
       <c r="BD186" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BE186" t="n">
         <v>0</v>
       </c>
       <c r="BF186" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="BG186" t="n">
         <v>2</v>
@@ -80974,19 +80982,19 @@
         <v>3</v>
       </c>
       <c r="BJ186" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BK186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BM186" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BN186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO186" t="n">
         <v>2</v>
@@ -81010,37 +81018,37 @@
         <v>1</v>
       </c>
       <c r="BV186" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="BW186" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="BX186" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="BY186" t="n">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="BZ186" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="CA186" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="CB186" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="CC186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG186" t="n">
         <v>0</v>
@@ -81061,10 +81069,10 @@
         <v>0</v>
       </c>
       <c r="CM186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CO186" t="n">
         <v>0</v>
@@ -81076,73 +81084,73 @@
         <v>1</v>
       </c>
       <c r="CR186" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="CS186" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="CT186" t="n">
         <v>1</v>
       </c>
       <c r="CU186" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV186" t="n">
         <v>8</v>
       </c>
-      <c r="CV186" t="n">
-        <v>16</v>
-      </c>
       <c r="CW186" t="n">
         <v>1</v>
       </c>
       <c r="CX186" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CY186" t="n">
         <v>8</v>
       </c>
       <c r="CZ186" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="DA186" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB186" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC186" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD186" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DE186" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DF186" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG186" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DH186" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DI186" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DJ186" t="n">
         <v>70</v>
       </c>
-      <c r="DB186" t="n">
-        <v>31</v>
-      </c>
-      <c r="DC186" t="n">
-        <v>61</v>
-      </c>
-      <c r="DD186" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="DE186" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="DF186" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="DG186" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="DH186" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="DI186" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="DJ186" t="n">
-        <v>56</v>
-      </c>
       <c r="DK186" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="DL186" t="n">
-        <v>1.13</v>
+        <v>1.41</v>
       </c>
       <c r="DM186" t="n">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="DN186" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="DO186" t="n">
         <v>19</v>
@@ -81154,10 +81162,10 @@
         <v>1</v>
       </c>
       <c r="DR186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT186" t="b">
         <v>0</v>
@@ -81172,44 +81180,44 @@
       <c r="DX186" t="inlineStr"/>
       <c r="DY186" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="DZ186" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EA186" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="EB186" t="inlineStr"/>
       <c r="EC186" t="inlineStr"/>
       <c r="ED186" t="inlineStr">
         <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EE186" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EF186" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EG186" t="inlineStr">
+        <is>
           <t>1.97</t>
         </is>
       </c>
-      <c r="EE186" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
-      </c>
-      <c r="EF186" t="inlineStr">
-        <is>
-          <t>3.76</t>
-        </is>
-      </c>
-      <c r="EG186" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
       <c r="EH186" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EI186" t="inlineStr"/>
@@ -81653,43 +81661,43 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Deportes Tolima</t>
+          <t>Alianza Petrolera</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Deportivo Cali</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F188" s="1" t="n">
         <v>46145.85416666666</v>
       </c>
       <c r="G188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I188" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J188" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K188" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L188" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M188" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N188" t="n">
         <v>3</v>
       </c>
       <c r="O188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P188" t="n">
         <v>0</v>
@@ -81698,90 +81706,90 @@
         <v>4</v>
       </c>
       <c r="R188" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S188" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T188" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="U188" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="V188" t="n">
+        <v>15</v>
+      </c>
+      <c r="W188" t="n">
         <v>16</v>
       </c>
-      <c r="W188" t="n">
-        <v>9</v>
-      </c>
       <c r="X188" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y188" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Z188" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA188" t="inlineStr"/>
       <c r="AB188" t="inlineStr"/>
       <c r="AC188" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD188" t="n">
         <v>3</v>
       </c>
       <c r="AE188" t="n">
-        <v>2.65</v>
+        <v>3.95</v>
       </c>
       <c r="AF188" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AG188" t="n">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="AH188" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AI188" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="AJ188" t="n">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AK188" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AL188" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AM188" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AN188" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="AO188" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR188" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="AS188" t="n">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="AT188" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AU188" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV188" t="n">
         <v>1</v>
@@ -81790,13 +81798,13 @@
         <v>0</v>
       </c>
       <c r="AX188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA188" t="n">
         <v>1</v>
@@ -81808,13 +81816,13 @@
         <v>1</v>
       </c>
       <c r="BD188" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BE188" t="n">
         <v>0</v>
       </c>
       <c r="BF188" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="BG188" t="n">
         <v>2</v>
@@ -81826,19 +81834,19 @@
         <v>3</v>
       </c>
       <c r="BJ188" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM188" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BN188" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO188" t="n">
         <v>2</v>
@@ -81862,37 +81870,37 @@
         <v>1</v>
       </c>
       <c r="BV188" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="BW188" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="BX188" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BY188" t="n">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="BZ188" t="n">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="CA188" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="CB188" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="CC188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG188" t="n">
         <v>0</v>
@@ -81913,10 +81921,10 @@
         <v>0</v>
       </c>
       <c r="CM188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO188" t="n">
         <v>0</v>
@@ -81928,73 +81936,73 @@
         <v>1</v>
       </c>
       <c r="CR188" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="CS188" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="CT188" t="n">
         <v>1</v>
       </c>
       <c r="CU188" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CV188" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="CW188" t="n">
         <v>1</v>
       </c>
       <c r="CX188" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="CY188" t="n">
         <v>8</v>
       </c>
       <c r="CZ188" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA188" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB188" t="n">
         <v>31</v>
       </c>
-      <c r="DA188" t="n">
-        <v>64</v>
-      </c>
-      <c r="DB188" t="n">
-        <v>20</v>
-      </c>
       <c r="DC188" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="DD188" t="n">
-        <v>1.61</v>
+        <v>0.89</v>
       </c>
       <c r="DE188" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="DF188" t="n">
-        <v>1.67</v>
+        <v>0.89</v>
       </c>
       <c r="DG188" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="DH188" t="n">
-        <v>1.67</v>
+        <v>0.89</v>
       </c>
       <c r="DI188" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="DJ188" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="DK188" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="DL188" t="n">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="DM188" t="n">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="DN188" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="DO188" t="n">
         <v>19</v>
@@ -82006,10 +82014,10 @@
         <v>1</v>
       </c>
       <c r="DR188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT188" t="b">
         <v>0</v>
@@ -82024,44 +82032,44 @@
       <c r="DX188" t="inlineStr"/>
       <c r="DY188" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="DZ188" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EA188" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="EB188" t="inlineStr"/>
       <c r="EC188" t="inlineStr"/>
       <c r="ED188" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EE188" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EF188" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="EG188" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EH188" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EI188" t="inlineStr"/>
@@ -82083,141 +82091,141 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Independiente Medellín</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Rionegro Águilas</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="F189" s="1" t="n">
         <v>46145.85416666666</v>
       </c>
       <c r="G189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I189" t="n">
         <v>3</v>
       </c>
       <c r="J189" t="n">
+        <v>6</v>
+      </c>
+      <c r="K189" t="n">
+        <v>3</v>
+      </c>
+      <c r="L189" t="n">
+        <v>9</v>
+      </c>
+      <c r="M189" t="n">
+        <v>1</v>
+      </c>
+      <c r="N189" t="n">
+        <v>2</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>3</v>
+      </c>
+      <c r="R189" t="n">
+        <v>3</v>
+      </c>
+      <c r="S189" t="n">
+        <v>7</v>
+      </c>
+      <c r="T189" t="n">
+        <v>14</v>
+      </c>
+      <c r="U189" t="n">
         <v>10</v>
       </c>
-      <c r="K189" t="n">
-        <v>2</v>
-      </c>
-      <c r="L189" t="n">
-        <v>12</v>
-      </c>
-      <c r="M189" t="n">
-        <v>3</v>
-      </c>
-      <c r="N189" t="n">
-        <v>2</v>
-      </c>
-      <c r="O189" t="n">
-        <v>1</v>
-      </c>
-      <c r="P189" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q189" t="n">
-        <v>7</v>
-      </c>
-      <c r="R189" t="n">
-        <v>4</v>
-      </c>
-      <c r="S189" t="n">
-        <v>14</v>
-      </c>
-      <c r="T189" t="n">
-        <v>6</v>
-      </c>
-      <c r="U189" t="n">
-        <v>21</v>
-      </c>
       <c r="V189" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="W189" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X189" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Y189" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="Z189" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AA189" t="inlineStr"/>
       <c r="AB189" t="inlineStr"/>
       <c r="AC189" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD189" t="n">
         <v>2</v>
       </c>
       <c r="AE189" t="n">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="AF189" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="AG189" t="n">
-        <v>6.5</v>
+        <v>2.28</v>
       </c>
       <c r="AH189" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AI189" t="n">
-        <v>1.84</v>
+        <v>2.38</v>
       </c>
       <c r="AJ189" t="n">
-        <v>2.92</v>
+        <v>4.5</v>
       </c>
       <c r="AK189" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AL189" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="AM189" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AN189" t="n">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="AO189" t="n">
-        <v>2.31</v>
+        <v>2.03</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AR189" t="n">
-        <v>2.66</v>
+        <v>3.35</v>
       </c>
       <c r="AS189" t="n">
-        <v>2.9</v>
+        <v>2.41</v>
       </c>
       <c r="AT189" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AU189" t="n">
         <v>3</v>
       </c>
       <c r="AV189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX189" t="n">
         <v>1</v>
@@ -82232,19 +82240,19 @@
         <v>1</v>
       </c>
       <c r="BB189" t="n">
-        <v>2147</v>
+        <v>2152</v>
       </c>
       <c r="BC189" t="n">
         <v>1</v>
       </c>
       <c r="BD189" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="BE189" t="n">
         <v>0</v>
       </c>
       <c r="BF189" t="n">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="BG189" t="n">
         <v>2</v>
@@ -82253,23 +82261,23 @@
         <v>1</v>
       </c>
       <c r="BI189" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BJ189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK189" t="n">
         <v>4</v>
       </c>
       <c r="BL189" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BM189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN189" t="n">
         <v>7</v>
       </c>
-      <c r="BN189" t="n">
-        <v>5</v>
-      </c>
       <c r="BO189" t="n">
         <v>0</v>
       </c>
@@ -82277,7 +82285,7 @@
         <v>1</v>
       </c>
       <c r="BQ189" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BR189" t="n">
         <v>1</v>
@@ -82286,142 +82294,142 @@
         <v>1</v>
       </c>
       <c r="BT189" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU189" t="n">
         <v>1</v>
       </c>
       <c r="BV189" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="BW189" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX189" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY189" t="n">
+        <v>58</v>
+      </c>
+      <c r="BZ189" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CA189" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CB189" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CC189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR189" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS189" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU189" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV189" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX189" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY189" t="n">
         <v>9</v>
       </c>
-      <c r="BX189" t="n">
-        <v>120</v>
-      </c>
-      <c r="BY189" t="n">
-        <v>44</v>
-      </c>
-      <c r="BZ189" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="CA189" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="CB189" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="CC189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI189" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ189" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM189" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP189" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ189" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR189" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS189" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT189" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU189" t="n">
-        <v>7</v>
-      </c>
-      <c r="CV189" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW189" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX189" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY189" t="n">
-        <v>18</v>
-      </c>
       <c r="CZ189" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="DA189" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="DB189" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="DC189" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="DD189" t="n">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="DE189" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="DF189" t="n">
-        <v>1.44</v>
+        <v>1.06</v>
       </c>
       <c r="DG189" t="n">
         <v>1.28</v>
       </c>
       <c r="DH189" t="n">
-        <v>1.44</v>
+        <v>1.06</v>
       </c>
       <c r="DI189" t="n">
         <v>1.28</v>
       </c>
       <c r="DJ189" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="DK189" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="DL189" t="n">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="DM189" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="DN189" t="n">
         <v>2.67</v>
@@ -82454,46 +82462,38 @@
       <c r="DX189" t="inlineStr"/>
       <c r="DY189" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="DZ189" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EA189" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="EB189" t="inlineStr"/>
       <c r="EC189" t="inlineStr"/>
       <c r="ED189" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EE189" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="EF189" t="inlineStr">
         <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EG189" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EH189" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EG189" t="inlineStr"/>
+      <c r="EH189" t="inlineStr"/>
       <c r="EI189" t="inlineStr"/>
       <c r="EJ189" t="inlineStr"/>
     </row>
@@ -83254,7 +83254,7 @@
         <v>83</v>
       </c>
       <c r="DD191" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DE191" t="n">
         <v>1.62</v>
@@ -83679,7 +83679,7 @@
         <v>1.33</v>
       </c>
       <c r="DE192" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DF192" t="n">
         <v>1.47</v>
@@ -84941,7 +84941,7 @@
         <v>1.62</v>
       </c>
       <c r="DE195" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DF195" t="n">
         <v>1.74</v>
@@ -85368,7 +85368,7 @@
         <v>70</v>
       </c>
       <c r="DD196" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DE196" t="n">
         <v>1.33</v>
@@ -86634,7 +86634,7 @@
         <v>83</v>
       </c>
       <c r="DD199" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DE199" t="n">
         <v>1.62</v>
@@ -87067,7 +87067,7 @@
         <v>1.61</v>
       </c>
       <c r="DE200" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DF200" t="n">
         <v>1.76</v>
@@ -87497,7 +87497,7 @@
         <v>1.52</v>
       </c>
       <c r="DE201" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DF201" t="n">
         <v>1.57</v>
@@ -87904,7 +87904,7 @@
         <v>71</v>
       </c>
       <c r="DD202" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="DE202" t="n">
         <v>1.61</v>
@@ -88334,7 +88334,7 @@
         <v>80</v>
       </c>
       <c r="DD203" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DE203" t="n">
         <v>1.52</v>
@@ -88436,6 +88436,436 @@
       </c>
       <c r="EI203" t="inlineStr"/>
       <c r="EJ203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Colombia_Primera_Liga_2026</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="F204" s="1" t="n">
+        <v>46176.02083333334</v>
+      </c>
+      <c r="G204" t="n">
+        <v>3</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" t="n">
+        <v>3</v>
+      </c>
+      <c r="J204" t="n">
+        <v>6</v>
+      </c>
+      <c r="K204" t="n">
+        <v>3</v>
+      </c>
+      <c r="L204" t="n">
+        <v>9</v>
+      </c>
+      <c r="M204" t="n">
+        <v>3</v>
+      </c>
+      <c r="N204" t="n">
+        <v>5</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="P204" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>8</v>
+      </c>
+      <c r="R204" t="n">
+        <v>3</v>
+      </c>
+      <c r="S204" t="n">
+        <v>13</v>
+      </c>
+      <c r="T204" t="n">
+        <v>6</v>
+      </c>
+      <c r="U204" t="n">
+        <v>21</v>
+      </c>
+      <c r="V204" t="n">
+        <v>9</v>
+      </c>
+      <c r="W204" t="n">
+        <v>13</v>
+      </c>
+      <c r="X204" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA204" t="inlineStr"/>
+      <c r="AB204" t="inlineStr"/>
+      <c r="AC204" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AK204" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AP204" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AQ204" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR204" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS204" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT204" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU204" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA204" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB204" t="n">
+        <v>2131</v>
+      </c>
+      <c r="BC204" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE204" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF204" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG204" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH204" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI204" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ204" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK204" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL204" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM204" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN204" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO204" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP204" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ204" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR204" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS204" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT204" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU204" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV204" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW204" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX204" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY204" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ204" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CA204" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB204" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="CC204" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD204" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE204" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF204" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG204" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH204" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI204" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ204" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK204" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL204" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM204" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN204" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO204" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP204" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ204" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR204" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS204" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT204" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU204" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV204" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW204" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX204" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY204" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ204" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA204" t="n">
+        <v>81</v>
+      </c>
+      <c r="DB204" t="n">
+        <v>37</v>
+      </c>
+      <c r="DC204" t="n">
+        <v>81</v>
+      </c>
+      <c r="DD204" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DE204" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DF204" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DG204" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="DH204" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DI204" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="DJ204" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK204" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL204" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DM204" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DN204" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="DO204" t="n">
+        <v>24</v>
+      </c>
+      <c r="DP204" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ204" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR204" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS204" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT204" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU204" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV204" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW204" t="inlineStr"/>
+      <c r="DX204" t="inlineStr"/>
+      <c r="DY204" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="DZ204" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EA204" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EB204" t="inlineStr"/>
+      <c r="EC204" t="inlineStr"/>
+      <c r="ED204" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EE204" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="EF204" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EG204" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EH204" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EI204" t="inlineStr"/>
+      <c r="EJ204" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
